--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9685,1004 +9685,1319 @@
       <c r="L177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>2b9e23144e980ec3a792a018223edf9b62a0954e91ea02f4032abe2648217111</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer of Cloud Application and AI</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5778305379?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H178" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="I178" s="3" t="inlineStr">
         <is>
           <t>We help the world run better At SAP, we keep it simple: you bring your best to us, and we'll bring out the best in you. We're builders touching over 20 industries and 80% of global commerce, and we need your unique talents to help shape what's next. The work is challenging - but it matters. You'll f</t>
         </is>
       </c>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>e0c2921994dd30c422b9c977d3cb09eb2e2ab99db8ac19c0b859e1a65edc4d3d</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Software Development Engineer II, Internet Edge Services - Outbound Traffic Controller</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5745854733?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H179" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I179" s="3" t="inlineStr">
         <is>
           <t>We're seeking a talented Software Development Engineer to join our dynamic team. In this role, you'll be responsible for building, enhancing, and operating Amazon's internet outbound traffic controller - a critical system that ensures optimal customer experience during high-traffic events such as Th</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L179" s="2" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>142029ac784dbf4656b9395fe20f3787b53cdefc81ed8d4f3fe9ab103ce5a890</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Solink</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>Software Engineer, COOP</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424764961</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>f2536816f277724fd725ece9b3ecb649535926b871e988ac8a503842435e7958</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Software Development - C++</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430164131</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L181" s="2" t="inlineStr"/>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>1f69ca984d030b09ddee2f7c47f288de0f897f9a04a7dd83217ca4a68ba07f13</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426427101</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>aafb3b7e871cfe70662b2eee7bbb7ad536f7d3f8c566fb89f2857a353edf9b90</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>MDA Space</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>Engineering Student - Software Fall 2026 (12-16 months)</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>Brampton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426619842</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L183" s="2" t="inlineStr"/>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>d2eedb73a4c92d2c5173b00fc23198b78b30ea383ae93a1042140611f6a714c0</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411512214</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>634ffd3b2e2a7c46afc32ce175442087596a7b05a97c1260ff0ab163766b8193</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Kabam</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (Gameplay) Co-op</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=ffd8d754a9851242</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H185" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I185" s="3" t="inlineStr">
         <is>
           <t>At Kabam, we’re constantly raising the bar of excellence in free\-to\-play gaming. We hire for passion and diversity so that we can triumph in our collective skill. Our teams are made up of a fusion of personalities and interests bound together by a collaborative nature, fun\-loving culture, and a d</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>055a39255d5e9e5397fc39aadf57787d0cc5ca42f0550beed701e8f4b2369e5c</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>Synopsys Inc</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Fall 2026 Internship - Lumerical Photonics Software Development Intern - C++</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431304826</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>37ddf053ad4fe11c7d27a65ffa43442a8ca85dd86e6dac1b02bebb6ea3977013</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Analog Devices</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Embedded Software Co-Op</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427394558</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr"/>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>e4478062e66186c96d13aa7f84017e45b252c1757fe058778547ccf7c01caf90</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Harris Computer</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>(Remote) Co-Op Student Developer</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427120659</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>429ef05725364422ba1f69de3e25b48621572fde4b82061d1d4b0d86a0596b20</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Test and Automated Test Co-op</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430573910</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="inlineStr"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>ad53c5727c4a45dbb4c5ebaa91e8ee899d9ba021ab731c7836424906cb8def8f</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr"/>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr"/>
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434085436</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>9afec8edc5a113083075872d94e6f9afb4470c0674c1d3872550ca0620bbf8b8</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>Rockwell Automation</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Co-op, Robotics Integration and Development</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429740016</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L191" s="2" t="inlineStr"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>fd257e541aa7d909e9bab3782d21dea4952b53c7707f144d5f2b7f05cf4fbcd2</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr"/>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr"/>
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>FluidAI Medical</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>Data and AI Engineering Associate (Co-op 8+ Months Preferred)</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4432955443</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>00b6c9cfa706a71230f2442f1b900788466746739ad34c5b91b873e701d8ee86</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>SS&amp;C Technologies</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Intern - Technical</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4378635211</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>a1796a1a88627035df7b49ac41a3082cdbfad1d151c10382618eb8e3d890030c</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>System Test Developer Coop</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428099488</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>2f8a46c5d9ff43f66970634487fe5523afa674bd5d8a50695206010a745f0691</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr"/>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr"/>
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>ATB Financial</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>Data Analyst, Internal Assurance (16-month term)</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434037844</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="inlineStr"/>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>a82dc137ba8ae2c5e8137d9716ebda1372508da2e6d79340442ea197707ba066</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>WorkSafeBC</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>Co-op Student, Data Analytics (Internal Audit Team)</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431167792</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>8e398d4ff96191a43c3f7eee21492b03d7af5f770e4311fe405e33bee3238292</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>ERCO Worldwide</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>Business Intelligence Analyst Co-Op</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
         <is>
           <t>Gatineau, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4420989074</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="inlineStr"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>60e3ab179c2787bf0795ad66faf36c57f38818830dd16c1f62639a78cfb404ab</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Fujitsu</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Intern Researcher</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7e64c2b48e95e65e</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description
+Intern Researcher
+Job Location: Toronto, Ontario
+Location Flexibility: Primary Location Only
+Req Id: 8977
+Posting Start Date: 6/15/26
+At Fujitsu, we are driven by our purpose to make the world more sustainable by building trust in society through innovation.
+We have been a pioneer </t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>c96e57afe613866187d27feed8fc404d49daa42716b55bfcbecae903fa840bdb</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr"/>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Kabam</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (Gameplay) Co-op</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434061120</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>f8eaf05df865d5275bdc4a20abbcd7df03ee4e1c4ea0c48258a92648c64c4c6b</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Intern - RTOS development</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=4a56dd982fff08f2</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>- **Intern RTOS Development**
+Location: Kanata, ON
+**ABOUT WIND RIVER**
+Within the Wind River Cloud team, we work with large\-scale projects including Kubernetes, Docker, OpenStack and fast\-paced Open\-Source technologies that are in high demand from our customers.
+Wind River Cloud has adopte</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>bdfae98ff731b5241c69f2ca93131bbc8ecef86f938ffcb168a576dcb7ccb301</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Software Test Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406430191</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>9d00002ba28fb56b72bb14e634e3caae24c911bc98aa616b7821705ca4f8a8ee</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>2026 Fall Student Opportunities Technology &amp; Operations - Software Developer, 8 Months</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433071105</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>f3b5f4054fa4ae55fb5c63fd422ff2d13f83987979fb37fbd02d7a04699c7822</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Coveo</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern (Professional Services team), Fall 2026</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Québec, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427001347</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10685,47 +10685,47 @@
       <c r="L197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>60e3ab179c2787bf0795ad66faf36c57f38818830dd16c1f62639a78cfb404ab</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>Intern Researcher</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7e64c2b48e95e65e</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H198" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="I198" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description
 Intern Researcher
@@ -10737,102 +10737,102 @@
 We have been a pioneer </t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>c96e57afe613866187d27feed8fc404d49daa42716b55bfcbecae903fa840bdb</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr"/>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr"/>
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Kabam</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (Gameplay) Co-op</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434061120</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>f8eaf05df865d5275bdc4a20abbcd7df03ee4e1c4ea0c48258a92648c64c4c6b</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>Intern - RTOS development</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G200" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=4a56dd982fff08f2</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H200" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I200" s="3" t="inlineStr">
         <is>
           <t>- **Intern RTOS Development**
 Location: Kanata, ON
@@ -10841,163 +10841,409 @@
 Wind River Cloud has adopte</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>bdfae98ff731b5241c69f2ca93131bbc8ecef86f938ffcb168a576dcb7ccb301</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>Software Test Co-op/Intern</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406430191</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="inlineStr"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="A202" s="3" t="inlineStr">
         <is>
           <t>9d00002ba28fb56b72bb14e634e3caae24c911bc98aa616b7821705ca4f8a8ee</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>RBC</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Student Opportunities Technology &amp; Operations - Software Developer, 8 Months</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433071105</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>f3b5f4054fa4ae55fb5c63fd422ff2d13f83987979fb37fbd02d7a04699c7822</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>Coveo</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern (Professional Services team), Fall 2026</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>Québec, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427001347</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="inlineStr"/>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>6284632573188b520c76cd7aa45fba122be70cc07b2de8cd99a2828c64c87cc6</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411296638</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>aab8740c055197287a2522a1f29e29cd23c5cc31a46f3657d4f096348fc6efd2</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Teck Resources Limited</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Mining Solutions Co-op</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430293008</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>e62246605f497611d3f50958a321cc91edff78c618eef1024726a72ee6ec740f</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>J.D. Irving, Limited</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Software Developer Student/Intern – Fall 2026</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Saint John, New Brunswick, Canada</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4419895507</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>e20b1ccd202880615cb463eb1e641d9188586d19771c57dfdcf166c06eff81ee</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4432508447</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>b0953fd726bc810175e6cb94d8ffc2bf5fff4be6f5277e834f1d6548132fdda3</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Harris Computer</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>(Remote) Co-Op Student Developer</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427132494</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11000,250 +11000,500 @@
       <c r="L203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>6284632573188b520c76cd7aa45fba122be70cc07b2de8cd99a2828c64c87cc6</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Magnet Forensics</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Fall 2026)</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411296638</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>aab8740c055197287a2522a1f29e29cd23c5cc31a46f3657d4f096348fc6efd2</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Teck Resources Limited</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>Mining Solutions Co-op</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr"/>
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430293008</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L205" s="2" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t>e62246605f497611d3f50958a321cc91edff78c618eef1024726a72ee6ec740f</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>J.D. Irving, Limited</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>Microsoft Software Developer Student/Intern – Fall 2026</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>Saint John, New Brunswick, Canada</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4419895507</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>e20b1ccd202880615cb463eb1e641d9188586d19771c57dfdcf166c06eff81ee</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>AI Automation Engineer Co-op</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4432508447</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L207" s="2" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr"/>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
         <is>
           <t>b0953fd726bc810175e6cb94d8ffc2bf5fff4be6f5277e834f1d6548132fdda3</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>Harris Computer</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>(Remote) Co-Op Student Developer</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427132494</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>a5b2baca53a69a2efab96d79863c1b404b8ca059eda34558b7923874778fe7ad</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Engineer in Test Co-op (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429117288</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>9fe5829647683f4a5a7338ae896c6bd085db23be32d7dcc1e7715f5a5f9e9b95</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Clio</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Business Operations Co-op</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431878961</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>62dd93c9c0ff458c755dca953cf2eb52eca404648caa12b803c52d675de4f636</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>FPS Food Process Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>IT Co-op (8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429680552</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>86be4ee8da2a6885c43b81e61bdcb98bb711231f0859a5037b7caef906050263</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>FPS Food Process Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>IT Co-op Student (8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429337381</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>bc106ede985b0102d50d901daefc602e53ae05b1fc11e70ce1fdd930ed04678c</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Intellect Design Arena Ltd</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427227636</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11246,254 +11246,504 @@
       <c r="L208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="A209" s="3" t="inlineStr">
         <is>
           <t>a5b2baca53a69a2efab96d79863c1b404b8ca059eda34558b7923874778fe7ad</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>Magnet Forensics</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>Software Developer Engineer in Test Co-op (Fall 2026)</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429117288</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L209" s="2" t="inlineStr"/>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t>9fe5829647683f4a5a7338ae896c6bd085db23be32d7dcc1e7715f5a5f9e9b95</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>Clio</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>Business Operations Co-op</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431878961</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr"/>
+      <c r="J210" s="3" t="inlineStr"/>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="A211" s="3" t="inlineStr">
         <is>
           <t>62dd93c9c0ff458c755dca953cf2eb52eca404648caa12b803c52d675de4f636</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>FPS Food Process Solutions Corporation</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>IT Co-op (8 or 12 months)</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429680552</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L211" s="2" t="inlineStr"/>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr"/>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+      <c r="A212" s="3" t="inlineStr">
         <is>
           <t>86be4ee8da2a6885c43b81e61bdcb98bb711231f0859a5037b7caef906050263</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B212" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>FPS Food Process Solutions Corporation</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>IT Co-op Student (8 or 12 months)</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G212" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429337381</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr"/>
+      <c r="J212" s="3" t="inlineStr"/>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="A213" s="3" t="inlineStr">
         <is>
           <t>bc106ede985b0102d50d901daefc602e53ae05b1fc11e70ce1fdd930ed04678c</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B213" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>Intellect Design Arena Ltd</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>Intern</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427227636</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr"/>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>43c5568b13e42424228788c449b326ca40a70d5f38fc1e9b2ba2e4efc4ba0220</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>House of Commons of Canada Chambre des communes du Canada</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Étudiant∙e∙s coop – Divers postes</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4350716201</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>1678cc7662caba09b83824d5104ac6da806f2973ae7fc90d3a0b50d2edc663e4</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>House of Commons of Canada Chambre des communes du Canada</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Students - Various Positions</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4350836087</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>d9beb99aab9bb9fafe0bd386f574a2df99ac41724228d47594a5d1fde47600e6</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Data Science Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4399797344</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>47f2e761883358844d4caf61c9065df1c75e9f188016b3dd79710df22a53b496</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>IP R&amp;D Lab Technologist Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406420926</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>9a2d5740515385f8e24947f75e3349c1d190f60c6b25a3effa15885bd58d9a88</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Brunel Law School</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Graduate Intern (Data Analyst) - 16900</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Uxbridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4426616918</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8658,205 +8658,205 @@
       <c r="L156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>1d8c44ab0dc4127952ad8042a5ba3c8805e8d1315249debf03466cf1fe6a353b</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds, Inc.</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds Full-Stack Developer (2026 Summer and Fall Internship)</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5780128564?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description ResponsiveAds is the leader in advanced HTML5 premium ad creatives that are dynamic to any screen, user and context. The existing ad tech is stuck inside a box that can't adapt quickly enough. ResponsiveAds takes the "responsive" paradigm from web CMS, ad serving, and</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>a7f81d06f10bedb0985cded6baaf97da0094ddeec21334665c8dc44e71ef0ff8</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>Support Software Developer Co-op/Intern</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4403793996</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>c5c557e2a92284c59f0a7506ab846fcdbedcf428a5b60d1fef8f7840fb31d645</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en développement logiciel - COOP Software developer</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>Remote, CA</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=ad01fa4945f38ff8</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H159" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>c0bd9bbc425e25b9d89151fbaafe6f688c7c77eca3503db5d6981fb422a6405c</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>LUCID Vision Labs</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>FPGA Co-Op / Internship</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=c2a063ef647c71ff</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>**Job Title:** FPGA Co\-Op / Internship
 **Reports To:** Engineer Manager, FPGA – Burnaby BC
@@ -8864,1015 +8864,1997 @@
 We are seeking a highly motivated and talented FPGA Engineer Co\-op/Intern to join our team. In this role, you will be responsible for designing, implementing, and testing digital circu</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>c821d0cfca5b64c7422b2831c461d33ec94314aebb5c9c903c9a2fffba196c1a</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Thurber Engineering Ltd.</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>Geotechnical Engineering Intern (2026062691)</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=2f8ff64662851dbc</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H161" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>### **Overview**
 Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Ottawa, Ontario**.
 Thurber provides geotechnical, environmental and construction materials engineering and testing services for a variety of industries across Canad</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr"/>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>34e800dc8044d0e7cf823ab02c338f3300c65338ec9ec510a62a679e6a68b69e</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Rockwell Automation</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>Co-op, Robotics Research – Data Engineering</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G162" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429718924</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
         <is>
           <t>4f4353d257c82a4034c2695fa1c762d4505c6c2ffc705710c386480c06816b25</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Themis Intelligence</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>Research Engineer - Post-training (Co-op / Intern)</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427289786</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr"/>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="inlineStr"/>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>2d7724c73bd4f7d772b1999a084ec9ecd088f497ad737fe1a8a6c9eaea7fd47c</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>People Inc.</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>Infrastructure Engineering Intern</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr"/>
+      <c r="G164" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4385529980</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr"/>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>ad53c5727c4a45dbb4c5ebaa91e8ee899d9ba021ab731c7836424906cb8def8f</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G165" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434085436</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr"/>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr"/>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>9d00002ba28fb56b72bb14e634e3caae24c911bc98aa616b7821705ca4f8a8ee</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>RBC</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Student Opportunities Technology &amp; Operations - Software Developer, 8 Months</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433071105</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>a29ccfc597992c2f54121ec69dd76d3bf25678c75ff3c5bb3708254536a8776d</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Sun Life</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>Student, Associate Software Engineer (Fall 2026)</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>North York, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4432472344</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>00b6c9cfa706a71230f2442f1b900788466746739ad34c5b91b873e701d8ee86</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>SS&amp;C Technologies</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>Intern - Technical</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G168" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4378635211</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>2238eb5361b0eacac2b00496e2f8e95387f9a09d2cbdbf9fa7255e221ba54c3d</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Info-Tech Research Group</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>Co-op Software Developer - Fall 2026 (September - December) - Canada, Ontario (REMOTE)</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G169" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4419920308</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr"/>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>ede87a4dbc9b1ceebfdd93c704c7dec087237294578d56ac1676cee3caa0cb2e</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Demonware</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Co-Ops - Software Development - Demonware (Vancouver)</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G170" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4416724234</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="inlineStr"/>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>37c1538b374f922891f67166f36095e986b7d47044aa9165520e7cd586c1f85c</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Activision</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Co-Ops - Software Development - Demonware (Vancouver)</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417796601</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr"/>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>aafb3b7e871cfe70662b2eee7bbb7ad536f7d3f8c566fb89f2857a353edf9b90</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>MDA Space</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>Engineering Student - Software Fall 2026 (12-16 months)</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>Brampton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426619842</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>d97a4f466240e6e58fb77dbf30b7d8df369a61b91c59818a8708e2a77aaa30c2</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Sanctuary AI</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>Firmware Engineering Intern (September 2026 - April 2027)</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423602045</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr"/>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>1fe63fed60547910f0db79c893c799e98442b574572cdde4583b5a50c25538bc</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Helcim</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (Internal Tools &amp; Systems)</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4418686539</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>142029ac784dbf4656b9395fe20f3787b53cdefc81ed8d4f3fe9ab103ce5a890</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Solink</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>Software Engineer, COOP</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424764961</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>c96e57afe613866187d27feed8fc404d49daa42716b55bfcbecae903fa840bdb</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Kabam</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (Gameplay) Co-op</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434061120</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>326ab709e9af41f617781f8a7ea59764ca6d6a38491cfaeee6fbd5d1e6dddefd</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Behaviour Interactive</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>Technical Animator – Internship Fall 2026</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433523646</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L177" s="2" t="inlineStr"/>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr"/>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>a81e39cfb1d4309420541997d532d8b1aab36d0592b67ea7d937c9781f5a6452</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Behaviour Interactive</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>Technical Animator - Internship Fall 2026 | Animateur·trice technique - Stage Automne 2026</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433528457</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>aa4b5cef4abce80e65925faa2ed284e02b1228cd5545bd72898744e9894e5493</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>The Princess Margaret Cancer Foundation</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Junior Report Developer, Analytics &amp; Insights (Internship)</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430985292</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L179" s="2" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>5d4cba9fd714acd38e7dadbf891633cc9bf138d50f85f791bae8cc58e173362a</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Definity</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>Data Specialist - Claim Operations Management - Fall 2026 Co-op/Intern</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430173023</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>82f3d6a83d8816ae55350a1919e598741cfec6f0a2455ccf7ebac25607bfa92d</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Business Web Solutions</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Web Developer Intern - Remote</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>King and Spadina, City of Toronto</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5772635270?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>This is a remote position. Job Overview We are looking for aspiring Web Developer Interns who want to gain practical experience in website development and design. This remote internship, lasting between 1 and 6 months, allows interns to work on real-world assignments while learning modern developmen</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>b328ece79f0f6ce8b686985e3ec62916ed41e05ca97dfb329e1acfae1e9a53e0</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Ricoh</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Developer Gen AI</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, ON, CA</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=5dde0767165d721f</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>GenAI Developer Intern  
+Job Profile
+We are seeking a curious and innovative GenAI Developer intern to join our team. In this role, you will work on cutting\-edge generative AI solutions, including large language models (LLMs), prompt engineering, and AI\-powered applications. You’ll collaborat</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>133d8b4c55fefb3c660169569cda557024e6500e758d46367feacbc998083162</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Kinaxis</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Co-op/Intern Cloud Developer, Platform Engineering</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=5d04c28d49ec7a1b</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>About Kinaxis:
+**About Kinaxis**
+Are you looking to join an innovative, market\-leading company where you can truly elevate your career? At Kinaxis we are serious about culture, we are serious about technology, we are serious about customers, and we are serious about not taking ourselves too serio</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>60e3ab179c2787bf0795ad66faf36c57f38818830dd16c1f62639a78cfb404ab</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Fujitsu</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Intern Researcher</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7e64c2b48e95e65e</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description
+Intern Researcher
+Job Location: Toronto, Ontario
+Location Flexibility: Primary Location Only
+Req Id: 8977
+Posting Start Date: 6/15/26
+At Fujitsu, we are driven by our purpose to make the world more sustainable by building trust in society through innovation.
+We have been a pioneer </t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>7aee0e44d02667b5461f6e85fe0c303dda29bb47e3c04b026abf85466b2a4497</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Geotechnical Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=9b051a12b62906ad</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Learning begins in the classroom but there’s no better place to gain real\-world experience than with Stantec. Interns are an integral part of our teams, working to solve some of the world's most complex challenges.
+As an intern, you’ll work alongside our experienced practitioners and with our cli</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>dca0cf8bbb4a75d18e02af47c95f684fa9666c4b5587097739fda6013c3ea7bc</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>AIM Defence</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Computer Vision Engineering Intern – Full-Time, Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4423305269</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>4ee449834608ea9f0af96b93115f0962a6f3a9330d3946a5cb1b66b63a990c50</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Intern - RTOS development</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434257753</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>1db70ada37509ebb9920c8c5a5556bcc5b4ac4747a370aa58b9c8facb0f8ec0c</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Ricoh Colombia</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Developer Gen AI</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434905139</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>1877250cb8894ffb14c79fe588a9ea9a8dd1c172f41ca4765497abfdc9f4dfb1</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>White Widget</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Back, Manitoba, Canada</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433613983</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>eec667a61dfae420add313e65c602214d3ff034f818eb9e59d4602668c940e7f</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer – Intern</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424262762</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>fd257e541aa7d909e9bab3782d21dea4952b53c7707f144d5f2b7f05cf4fbcd2</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>FluidAI Medical</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Data and AI Engineering Associate (Co-op 8+ Months Preferred)</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4432955443</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>7845f469f21e8b0144dc479776ad3b7ef681013a7895feceb83b6d596ef5e36c</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Grand River Hospital</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Student, Finance (AI Solutions Developer)</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433532382</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>a5c44fcf62b676f65ec981ce46012dca0ec83cbd3855944838d7cca62947d3f4</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Definity</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Test Automation Developer - Fall 2026 Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429119142</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>fe91e6f86f81d020eb02e44f35fee4b4a2f8c46b79d13d511233fe7f48c9883a</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Service Router Automation Eng. Student</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406722240</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>3e0d1e9cfe2637bbd70ea5d0410ea952c68efab832b0598de6dd0ba75d4e1995</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>NW Automation Practice Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406438041</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2bf69fd7a035a2eea9093fe1492050287382b483a70e07d463e3f6075a5aa91e</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>EllisDon</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Student Positions (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4425249444</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>dc174fd928fdd6f7151248fc4cdf3b834687da037b8f5594910bd79389a34365</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Canam</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Intern – Field Services Coordinator</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424217775</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>8c30b4d2138a10a0e757e1dfb0ac6b24ad44f92891d31f8744b2cb28e7b2bb91</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>General Dynamics Mission Systems–Canada</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Fall 2026 - Engineering and Project Management Specialist - 4-Months</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421860292</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>9a2d5740515385f8e24947f75e3349c1d190f60c6b25a3effa15885bd58d9a88</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Brunel Law School</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Graduate Intern (Data Analyst) - 16900</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Uxbridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4426616918</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9875,213 +9875,213 @@
       <c r="L180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>82f3d6a83d8816ae55350a1919e598741cfec6f0a2455ccf7ebac25607bfa92d</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Business Web Solutions</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Web Developer Intern - Remote</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>King and Spadina, City of Toronto</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5772635270?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H181" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I181" s="3" t="inlineStr">
         <is>
           <t>This is a remote position. Job Overview We are looking for aspiring Web Developer Interns who want to gain practical experience in website development and design. This remote internship, lasting between 1 and 6 months, allows interns to work on real-world assignments while learning modern developmen</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L181" s="2" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>b328ece79f0f6ce8b686985e3ec62916ed41e05ca97dfb329e1acfae1e9a53e0</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Ricoh</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>Intern, Developer Gen AI</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>Mississauga, ON, CA</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=5dde0767165d721f</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H182" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I182" s="3" t="inlineStr">
         <is>
           <t>GenAI Developer Intern  
 Job Profile
 We are seeking a curious and innovative GenAI Developer intern to join our team. In this role, you will work on cutting\-edge generative AI solutions, including large language models (LLMs), prompt engineering, and AI\-powered applications. You’ll collaborat</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr"/>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>133d8b4c55fefb3c660169569cda557024e6500e758d46367feacbc998083162</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Cloud Developer, Platform Engineering</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=5d04c28d49ec7a1b</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H183" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I183" s="3" t="inlineStr">
         <is>
           <t>About Kinaxis:
 **About Kinaxis**
 Are you looking to join an innovative, market\-leading company where you can truly elevate your career? At Kinaxis we are serious about culture, we are serious about technology, we are serious about customers, and we are serious about not taking ourselves too serio</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L183" s="2" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>60e3ab179c2787bf0795ad66faf36c57f38818830dd16c1f62639a78cfb404ab</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>Intern Researcher</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7e64c2b48e95e65e</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H184" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description
 Intern Researcher
@@ -10093,768 +10093,1214 @@
 We have been a pioneer </t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>7aee0e44d02667b5461f6e85fe0c303dda29bb47e3c04b026abf85466b2a4497</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Stantec</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Geotechnical Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=9b051a12b62906ad</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H185" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I185" s="3" t="inlineStr">
         <is>
           <t>Learning begins in the classroom but there’s no better place to gain real\-world experience than with Stantec. Interns are an integral part of our teams, working to solve some of the world's most complex challenges.
 As an intern, you’ll work alongside our experienced practitioners and with our cli</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>dca0cf8bbb4a75d18e02af47c95f684fa9666c4b5587097739fda6013c3ea7bc</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>AIM Defence</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Computer Vision Engineering Intern – Full-Time, Vancouver, BC, Canada</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423305269</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>4ee449834608ea9f0af96b93115f0962a6f3a9330d3946a5cb1b66b63a990c50</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Intern - RTOS development</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434257753</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr"/>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>1db70ada37509ebb9920c8c5a5556bcc5b4ac4747a370aa58b9c8facb0f8ec0c</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Ricoh Colombia</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>Intern, Developer Gen AI</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434905139</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>1877250cb8894ffb14c79fe588a9ea9a8dd1c172f41ca4765497abfdc9f4dfb1</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>White Widget</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>Back, Manitoba, Canada</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433613983</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="inlineStr"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>eec667a61dfae420add313e65c602214d3ff034f818eb9e59d4602668c940e7f</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>Embedded Software Engineer – Intern</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424262762</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>fd257e541aa7d909e9bab3782d21dea4952b53c7707f144d5f2b7f05cf4fbcd2</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>FluidAI Medical</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Data and AI Engineering Associate (Co-op 8+ Months Preferred)</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4432955443</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L191" s="2" t="inlineStr"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>7845f469f21e8b0144dc479776ad3b7ef681013a7895feceb83b6d596ef5e36c</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Grand River Hospital</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>Student, Finance (AI Solutions Developer)</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433532382</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>a5c44fcf62b676f65ec981ce46012dca0ec83cbd3855944838d7cca62947d3f4</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Definity</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Test Automation Developer - Fall 2026 Co-op/Intern</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429119142</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>fe91e6f86f81d020eb02e44f35fee4b4a2f8c46b79d13d511233fe7f48c9883a</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>Service Router Automation Eng. Student</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406722240</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>3e0d1e9cfe2637bbd70ea5d0410ea952c68efab832b0598de6dd0ba75d4e1995</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>NW Automation Practice Co-op/Intern</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406438041</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="inlineStr"/>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>2bf69fd7a035a2eea9093fe1492050287382b483a70e07d463e3f6075a5aa91e</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>EllisDon</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>Student Positions (Fall 2026)</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4425249444</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>dc174fd928fdd6f7151248fc4cdf3b834687da037b8f5594910bd79389a34365</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>Canam</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>Intern – Field Services Coordinator</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424217775</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="inlineStr"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>8c30b4d2138a10a0e757e1dfb0ac6b24ad44f92891d31f8744b2cb28e7b2bb91</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>General Dynamics Mission Systems–Canada</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>Co-op Fall 2026 - Engineering and Project Management Specialist - 4-Months</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421860292</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>9a2d5740515385f8e24947f75e3349c1d190f60c6b25a3effa15885bd58d9a88</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Brunel Law School</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Graduate Intern (Data Analyst) - 16900</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>Uxbridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426616918</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>aab8740c055197287a2522a1f29e29cd23c5cc31a46f3657d4f096348fc6efd2</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Teck Resources Limited</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Mining Solutions Co-op</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430293008</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>e4bf46849301576084fde0beb50d714c36d0d0d021e031b4084fb8620ad148ab</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Arlo Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417991193</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>62dd93c9c0ff458c755dca953cf2eb52eca404648caa12b803c52d675de4f636</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>FPS Food Process Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>IT Co-op (8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429680552</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>86be4ee8da2a6885c43b81e61bdcb98bb711231f0859a5037b7caef906050263</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>FPS Food Process Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>IT Co-op Student (8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429337381</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>736b24c06552eb6c858406d2ced902cae896403786fab844b542041dcefac1e8</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Signalling Design Intern (Fall 2026, 8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414340867</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>d5875c779a83b8208c7715852c547abc22c177f96474c2e29bb0f4027890c5b4</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Apera AI</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Roboticist – (Co-Op)</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4419210083</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>8ed4446894ce2a62aefca12bced3b528803a1341493dfb949d65f449df17f694</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer Intern (4 months - September 2026)</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431450488</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>9afec8edc5a113083075872d94e6f9afb4470c0674c1d3872550ca0620bbf8b8</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Robotics Integration and Development</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429740016</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>1f244d3dc11274b377685ff7d6542477e70c012e94a52c6714057494b51e4fa7</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Solink</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, COOP</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424782454</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10857,450 +10857,1502 @@
       <c r="L199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>aab8740c055197287a2522a1f29e29cd23c5cc31a46f3657d4f096348fc6efd2</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Teck Resources Limited</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>Mining Solutions Co-op</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430293008</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>e4bf46849301576084fde0beb50d714c36d0d0d021e031b4084fb8620ad148ab</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>Test Engineer Co-op</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417991193</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="inlineStr"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="A202" s="3" t="inlineStr">
         <is>
           <t>62dd93c9c0ff458c755dca953cf2eb52eca404648caa12b803c52d675de4f636</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>FPS Food Process Solutions Corporation</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>IT Co-op (8 or 12 months)</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429680552</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>86be4ee8da2a6885c43b81e61bdcb98bb711231f0859a5037b7caef906050263</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>FPS Food Process Solutions Corporation</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>IT Co-op Student (8 or 12 months)</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429337381</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="inlineStr"/>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>736b24c06552eb6c858406d2ced902cae896403786fab844b542041dcefac1e8</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Signalling Design Intern (Fall 2026, 8 or 12 months)</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414340867</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>d5875c779a83b8208c7715852c547abc22c177f96474c2e29bb0f4027890c5b4</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Apera AI</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>Roboticist – (Co-Op)</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4419210083</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L205" s="2" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t>8ed4446894ce2a62aefca12bced3b528803a1341493dfb949d65f449df17f694</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>Embedded Software Engineer Intern (4 months - September 2026)</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431450488</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>9afec8edc5a113083075872d94e6f9afb4470c0674c1d3872550ca0620bbf8b8</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>Rockwell Automation</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>Co-op, Robotics Integration and Development</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429740016</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L207" s="2" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr"/>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
         <is>
           <t>1f244d3dc11274b377685ff7d6542477e70c012e94a52c6714057494b51e4fa7</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>Solink</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>Software Engineer, COOP</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424782454</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>9b0200c300b31ec95ae36f559eb0fd57a4546df03706884b29bf5f44105995be</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782238697?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Position Title: SAP Concur iXp Intern – Software Developer Location: Vancouver, BC Start Date: September 8, 2026 Contract Duration: 8 months Hours: 40 hours per week; Full‑time internship Responsibilities Build web apps and cloud services in a microservice architecture Understand, debug, and make me</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>8acdb7ad1af54b468bb38b1672d1e058b8bfb8b94732fe5ce77ed578e22fc0ed</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer, Cloud Platform Services, Applications &amp; Products [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782560365?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>We help the world run better At SAP, we keep it simple: you bring your best to us, and we'll bring out the best in you. We're builders touching over 20 industries and 80% of global commerce, and we need your unique talents to help shape what's next. The work is challenging - but it matters. You'll f</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>693ab6ba392ebe62ea517e9a1985ab51b156571c8d1c8a0277c6fcb2fe49c3e2</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>IT Network Software/AI Development - Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ottawa region</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782242954?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT Network Software/AI Development - Co-op/Intern Number of Positions: 4 Duration: 4 months to 12 months Term: September to December 2026 Location: In office at 600 March Rd. Ottawa, Canada. How You Will Contribute And What You Will Learn Support the design, development, and maintenance of internal </t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>06f038c1a3f36f2f7dda53c8e50148069bbec29ee28f94a5638913d4fd1731aa</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>jobs.hanzilla.co - Jobboard</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>IT Network Software/AI Development - Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ottawa region</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782242963?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>IT Network Software/AI Development - Co-op/InternSoftware EngineeringInternship IT Network Software/AI Development - Co-op/Internat Nokia LocationKanata, Ontario DetailsCo-op · 4mo · Fall 2026 PostedJun 12, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the Rol</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>44b96cd14910a470e55228df0540a4149cffa7e5c7a55eddd1d1c6597e0e597d</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>jobs.hanzilla.co - Jobboard</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782240695?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)at rivianvw.tech LocationVancouver, British Columbia DetailsCo-op · 8mo · Fall 2026–Spring 2027 PostedJun 09, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the RoleDevelop Android connectivity</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ef7adceea4ff06e2e0110862e05b54c45536e287f94115d795ac6e84fd03651a</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Recognized</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern- Android Connectivity- Vancouver, BC (Fall/Spring Co-Op)</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782231083?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>a2dd40f2973fbbf39189478657ab5df1220313893d7c2c2cbd173d8c6635085e</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Vosyn Inc</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>AI Integration &amp; Data Engineer (Vibecoding) - Master-Level Internship</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782235740?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>About Us At Vosyn, we embrace the exciting, game-changing world of Artificial Intelligence, driving innovation and pioneering impactful projects across various industries. We are a trailblazing Language Synthesis AI firm reshaping global communication by dissolving language barriers and empowering u</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>90ddeac6d86ff32584308b144d4fd37db17cfa14343aad5c656632dee257b5db</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Short Term 2026 Software Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4412180457</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>adbc40cf64d6efcc0c3aa7b2a2a5dfd7abeb6497b2a2db92bda30779a779562a</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Fall 2026: Software Developer Co-op (8 months)</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434706769</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>7afa59f9cd5ac306c33c648d9e3f3f8e1f8edf6258ae3390888b533f2a9b7d49</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Canada Life</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer (Student Position)</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Regina, Saskatchewan, Canada</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434152970</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>f04b06531bc76e84ce96e6b72dcf326c3039759dd4d429f9ccba23dc57c6c185</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Student</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Etobicoke, ON, CA</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=0ffe3ace782c40f3</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>**Job descriptions may display in multiple languages****based on your language selection.**
+**What we offer:**
+------------------
+At Magna, you can expect an engaging and dynamic environment where you can help to develop industry\-leading automotive technologies. We invest in our employees, provi</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2f4b3e0a0dc5c866a67d8af1fa0ff4661513c2b16228c6e8fde3439f141f83a6</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Zafarro Restoration Inc.</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering Intern (Co-op / Internship)</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Greater Toronto Area, ON, CA</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=75881add41fb048d</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zafarro Restoration Inc. is a Canadian restoration contractor specializing in building envelope restoration, concrete repair, waterproofing, masonry restoration, balcony rehabilitation, and underground parking garage restoration. We work on residential and commercial high\-rise buildings throughout </t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>8b4f77198576b05b80d327b424b3ede120a80cb8ba55dde72ae94a529f957c3a</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Student</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Etobicoke, ON, CA</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=18a31d037350f459</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>**Job descriptions may display in multiple languages** **based on your language selection.**
+**What we offer:**
+------------------
+At Magna, you can expect an engaging and dynamic environment where you can help to develop industry\-leading automotive technologies. We invest in our employees, provi</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>532439e9a807a17bec91748c9794df11c5ac1135b8216d75813a26fd1f0a21ef</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Short Term 2026 Firmware Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4412186374</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>160d3bdada33b595ae75460098000bc20d8959b6969e71f64ca546fff941bb79</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer, Cloud Platform Services, Applications &amp; Products [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434175218</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>55346cd368b70de0e3a373f3ac270b9c6234ac718d12849f5c71e5cf70e873d2</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Ribbon Communications</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Canada (Co-op)</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1cd35ee14cdba273</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ribbon Communications is looking for a hands\-on UI Engineer to assist in the design and development of features in our next\-generation application user interface. The ideal candidate will have experience in or interest and aptitude toward contemporary user interface design.
+The position will be </t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>c5a9982d1d7cb6991e8fa03c6d56c3e960cab025574c315500ef6505c33a8219</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Ricoh USA, Inc.</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Developer Gen AI</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434903258</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>5c184e29ea823d714a2442a465f65c8750538574cb1e42ef50153bc4d3bf7b65</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Coveo</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Backend Development Intern, Fall 2026</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427012174</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>0d0033c5b45f0207f20cb99553596a741bdfe93ee2e0acaebc1665769b2e5020</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>NEXTIN LABS (formerly ForAll A Tech)</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Laravel Web Developer
+Full-Time Internship</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Regional Municipality of York, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433227399</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>a11e91d2944502e6ad7092c9938fc073083f2eb46e1c7a2e084c738f5b03637b</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Kinaxis</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Co-op/Intern Cloud Developer, Platform Engineering</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434732602</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L228"/>
+  <dimension ref="A1:L233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11303,575 +11303,575 @@
       <c r="L208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="A209" s="3" t="inlineStr">
         <is>
           <t>9b0200c300b31ec95ae36f559eb0fd57a4546df03706884b29bf5f44105995be</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782238697?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H209" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I209" s="3" t="inlineStr">
         <is>
           <t>Position Title: SAP Concur iXp Intern – Software Developer Location: Vancouver, BC Start Date: September 8, 2026 Contract Duration: 8 months Hours: 40 hours per week; Full‑time internship Responsibilities Build web apps and cloud services in a microservice architecture Understand, debug, and make me</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L209" s="2" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t>8acdb7ad1af54b468bb38b1672d1e058b8bfb8b94732fe5ce77ed578e22fc0ed</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer, Cloud Platform Services, Applications &amp; Products [Vancouver]</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782560365?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H210" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I210" s="3" t="inlineStr">
         <is>
           <t>We help the world run better At SAP, we keep it simple: you bring your best to us, and we'll bring out the best in you. We're builders touching over 20 industries and 80% of global commerce, and we need your unique talents to help shape what's next. The work is challenging - but it matters. You'll f</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="J210" s="3" t="inlineStr"/>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="A211" s="3" t="inlineStr">
         <is>
           <t>693ab6ba392ebe62ea517e9a1985ab51b156571c8d1c8a0277c6fcb2fe49c3e2</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>IT Network Software/AI Development - Co-op/Intern</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ottawa region</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782242954?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H211" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I211" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">IT Network Software/AI Development - Co-op/Intern Number of Positions: 4 Duration: 4 months to 12 months Term: September to December 2026 Location: In office at 600 March Rd. Ottawa, Canada. How You Will Contribute And What You Will Learn Support the design, development, and maintenance of internal </t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L211" s="2" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr"/>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+      <c r="A212" s="3" t="inlineStr">
         <is>
           <t>06f038c1a3f36f2f7dda53c8e50148069bbec29ee28f94a5638913d4fd1731aa</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B212" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>jobs.hanzilla.co - Jobboard</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>IT Network Software/AI Development - Co-op/Intern</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ottawa region</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G212" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782242963?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H212" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I212" s="3" t="inlineStr">
         <is>
           <t>IT Network Software/AI Development - Co-op/InternSoftware EngineeringInternship IT Network Software/AI Development - Co-op/Internat Nokia LocationKanata, Ontario DetailsCo-op · 4mo · Fall 2026 PostedJun 12, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the Rol</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="J212" s="3" t="inlineStr"/>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="A213" s="3" t="inlineStr">
         <is>
           <t>44b96cd14910a470e55228df0540a4149cffa7e5c7a55eddd1d1c6597e0e597d</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B213" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>jobs.hanzilla.co - Jobboard</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782240695?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H213" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I213" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)at rivianvw.tech LocationVancouver, British Columbia DetailsCo-op · 8mo · Fall 2026–Spring 2027 PostedJun 09, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the RoleDevelop Android connectivity</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr"/>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+      <c r="A214" s="3" t="inlineStr">
         <is>
           <t>ef7adceea4ff06e2e0110862e05b54c45536e287f94115d795ac6e84fd03651a</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B214" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C214" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>Recognized</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern- Android Connectivity- Vancouver, BC (Fall/Spring Co-Op)</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G214" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782231083?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H214" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I214" s="3" t="inlineStr">
         <is>
           <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr"/>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="J214" s="3" t="inlineStr"/>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+      <c r="A215" s="3" t="inlineStr">
         <is>
           <t>a2dd40f2973fbbf39189478657ab5df1220313893d7c2c2cbd173d8c6635085e</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B215" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>Vosyn Inc</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>AI Integration &amp; Data Engineer (Vibecoding) - Master-Level Internship</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G215" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782235740?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H215" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I215" s="3" t="inlineStr">
         <is>
           <t>About Us At Vosyn, we embrace the exciting, game-changing world of Artificial Intelligence, driving innovation and pioneering impactful projects across various industries. We are a trailblazing Language Synthesis AI firm reshaping global communication by dissolving language barriers and empowering u</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L215" s="2" t="inlineStr"/>
+      <c r="J215" s="3" t="inlineStr"/>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+      <c r="A216" s="3" t="inlineStr">
         <is>
           <t>90ddeac6d86ff32584308b144d4fd37db17cfa14343aad5c656632dee257b5db</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B216" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>Short Term 2026 Software Engineering Intern/Co-Op</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G216" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4412180457</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="2" t="inlineStr"/>
-      <c r="K216" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L216" s="2" t="inlineStr"/>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr"/>
+      <c r="J216" s="3" t="inlineStr"/>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+      <c r="A217" s="3" t="inlineStr">
         <is>
           <t>adbc40cf64d6efcc0c3aa7b2a2a5dfd7abeb6497b2a2db92bda30779a779562a</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B217" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>Intuit</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>Fall 2026: Software Developer Co-op (8 months)</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G217" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434706769</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" s="2" t="inlineStr"/>
-      <c r="K217" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L217" s="2" t="inlineStr"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr"/>
+      <c r="J217" s="3" t="inlineStr"/>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="A218" s="3" t="inlineStr">
         <is>
           <t>7afa59f9cd5ac306c33c648d9e3f3f8e1f8edf6258ae3390888b533f2a9b7d49</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B218" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>Canada Life</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>Software Developer (Student Position)</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr">
         <is>
           <t>Regina, Saskatchewan, Canada</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G218" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434152970</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L218" s="2" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr"/>
+      <c r="J218" s="3" t="inlineStr"/>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+      <c r="A219" s="3" t="inlineStr">
         <is>
           <t>f04b06531bc76e84ce96e6b72dcf326c3039759dd4d429f9ccba23dc57c6c185</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>Engineering Student</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr">
         <is>
           <t>Etobicoke, ON, CA</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G219" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=0ffe3ace782c40f3</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H219" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I219" s="3" t="inlineStr">
         <is>
           <t>**Job descriptions may display in multiple languages****based on your language selection.**
 **What we offer:**
@@ -11879,110 +11879,110 @@
 At Magna, you can expect an engaging and dynamic environment where you can help to develop industry\-leading automotive technologies. We invest in our employees, provi</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L219" s="2" t="inlineStr"/>
+      <c r="J219" s="3" t="inlineStr"/>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+      <c r="A220" s="3" t="inlineStr">
         <is>
           <t>2f4b3e0a0dc5c866a67d8af1fa0ff4661513c2b16228c6e8fde3439f141f83a6</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B220" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C220" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>Zafarro Restoration Inc.</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>Civil Engineering Intern (Co-op / Internship)</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F220" s="3" t="inlineStr">
         <is>
           <t>Greater Toronto Area, ON, CA</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G220" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=75881add41fb048d</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H220" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I220" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Zafarro Restoration Inc. is a Canadian restoration contractor specializing in building envelope restoration, concrete repair, waterproofing, masonry restoration, balcony rehabilitation, and underground parking garage restoration. We work on residential and commercial high\-rise buildings throughout </t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L220" s="2" t="inlineStr"/>
+      <c r="J220" s="3" t="inlineStr"/>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+      <c r="A221" s="3" t="inlineStr">
         <is>
           <t>8b4f77198576b05b80d327b424b3ede120a80cb8ba55dde72ae94a529f957c3a</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B221" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>Engineering Student</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
         <is>
           <t>Etobicoke, ON, CA</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G221" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=18a31d037350f459</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H221" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I221" s="3" t="inlineStr">
         <is>
           <t>**Job descriptions may display in multiple languages** **based on your language selection.**
 **What we offer:**
@@ -11990,369 +11990,627 @@
 At Magna, you can expect an engaging and dynamic environment where you can help to develop industry\-leading automotive technologies. We invest in our employees, provi</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L221" s="2" t="inlineStr"/>
+      <c r="J221" s="3" t="inlineStr"/>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+      <c r="A222" s="3" t="inlineStr">
         <is>
           <t>532439e9a807a17bec91748c9794df11c5ac1135b8216d75813a26fd1f0a21ef</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>Short Term 2026 Firmware Engineering Intern/Co-Op</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G222" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4412186374</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr"/>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L222" s="2" t="inlineStr"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr"/>
+      <c r="J222" s="3" t="inlineStr"/>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="A223" s="3" t="inlineStr">
         <is>
           <t>160d3bdada33b595ae75460098000bc20d8959b6969e71f64ca546fff941bb79</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B223" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer, Cloud Platform Services, Applications &amp; Products [Vancouver]</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F223" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G223" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434175218</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr"/>
-      <c r="J223" s="2" t="inlineStr"/>
-      <c r="K223" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L223" s="2" t="inlineStr"/>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr"/>
+      <c r="J223" s="3" t="inlineStr"/>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+      <c r="A224" s="3" t="inlineStr">
         <is>
           <t>55346cd368b70de0e3a373f3ac270b9c6234ac718d12849f5c71e5cf70e873d2</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B224" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C224" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>Ribbon Communications</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>Canada (Co-op)</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G224" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1cd35ee14cdba273</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H224" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I224" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ribbon Communications is looking for a hands\-on UI Engineer to assist in the design and development of features in our next\-generation application user interface. The ideal candidate will have experience in or interest and aptitude toward contemporary user interface design.
 The position will be </t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L224" s="2" t="inlineStr"/>
+      <c r="J224" s="3" t="inlineStr"/>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+      <c r="A225" s="3" t="inlineStr">
         <is>
           <t>c5a9982d1d7cb6991e8fa03c6d56c3e960cab025574c315500ef6505c33a8219</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B225" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C225" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t>Ricoh USA, Inc.</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>Intern, Developer Gen AI</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G225" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434903258</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr"/>
-      <c r="J225" s="2" t="inlineStr"/>
-      <c r="K225" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L225" s="2" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr"/>
+      <c r="J225" s="3" t="inlineStr"/>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+      <c r="A226" s="3" t="inlineStr">
         <is>
           <t>5c184e29ea823d714a2442a465f65c8750538574cb1e42ef50153bc4d3bf7b65</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B226" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C226" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t>Coveo</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>Backend Development Intern, Fall 2026</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G226" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427012174</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I226" s="2" t="inlineStr"/>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L226" s="2" t="inlineStr"/>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr"/>
+      <c r="J226" s="3" t="inlineStr"/>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+      <c r="A227" s="3" t="inlineStr">
         <is>
           <t>0d0033c5b45f0207f20cb99553596a741bdfe93ee2e0acaebc1665769b2e5020</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B227" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C227" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D227" s="3" t="inlineStr">
         <is>
           <t>NEXTIN LABS (formerly ForAll A Tech)</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>Full Stack Laravel Web Developer
 Full-Time Internship</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F227" s="3" t="inlineStr">
         <is>
           <t>Regional Municipality of York, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G227" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433227399</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I227" s="2" t="inlineStr"/>
-      <c r="J227" s="2" t="inlineStr"/>
-      <c r="K227" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L227" s="2" t="inlineStr"/>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr"/>
+      <c r="J227" s="3" t="inlineStr"/>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+      <c r="A228" s="3" t="inlineStr">
         <is>
           <t>a11e91d2944502e6ad7092c9938fc073083f2eb46e1c7a2e084c738f5b03637b</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Cloud Developer, Platform Engineering</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F228" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G228" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434732602</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr"/>
-      <c r="J228" s="2" t="inlineStr"/>
-      <c r="K228" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L228" s="2" t="inlineStr"/>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr"/>
+      <c r="J228" s="3" t="inlineStr"/>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>65cabe3a297f58aef5cf4d4fa1ecd48330d927bc8456399c4e5439418278c30f</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5782238865?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>What You’ll Build The SAP Internship Experience Program is SAP’s global, strategic, paid internship program that provides university students with opportunities to find purpose in their careers. This is more than an internship, it’s the foundation for a career built on connection, creativity, and im</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2c85dc14d93e268fda2941d248bf6828b0f0a90b7757e617685ece97714efb83</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5783779079?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>ab954e063432bce6857dd5d4d09bb5df76e1207343356fefb23f2cd277f20216</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Canada Life</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer (Student Position)</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434155992</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>e20b1ccd202880615cb463eb1e641d9188586d19771c57dfdcf166c06eff81ee</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4432508447</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>f1ec18577611dfc42ef04c478d4e75f69c2367365ab281dd774fd510db822ce8</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Coveo</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Backend Development Intern, Fall 2026</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Québec, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4426796367</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L233"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12355,262 +12355,662 @@
       <c r="L228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+      <c r="A229" s="3" t="inlineStr">
         <is>
           <t>65cabe3a297f58aef5cf4d4fa1ecd48330d927bc8456399c4e5439418278c30f</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B229" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C229" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D229" s="3" t="inlineStr">
         <is>
           <t>SAP SE</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F229" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G229" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5782238865?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H229" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I229" s="3" t="inlineStr">
         <is>
           <t>What You’ll Build The SAP Internship Experience Program is SAP’s global, strategic, paid internship program that provides university students with opportunities to find purpose in their careers. This is more than an internship, it’s the foundation for a career built on connection, creativity, and im</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L229" s="2" t="inlineStr"/>
+      <c r="J229" s="3" t="inlineStr"/>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+      <c r="A230" s="3" t="inlineStr">
         <is>
           <t>2c85dc14d93e268fda2941d248bf6828b0f0a90b7757e617685ece97714efb83</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G230" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5783779079?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H230" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I230" s="3" t="inlineStr">
         <is>
           <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr"/>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L230" s="2" t="inlineStr"/>
+      <c r="J230" s="3" t="inlineStr"/>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+      <c r="A231" s="3" t="inlineStr">
         <is>
           <t>ab954e063432bce6857dd5d4d09bb5df76e1207343356fefb23f2cd277f20216</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B231" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
         <is>
           <t>Canada Life</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>Software Developer (Student Position)</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F231" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G231" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434155992</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L231" s="2" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr"/>
+      <c r="J231" s="3" t="inlineStr"/>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+      <c r="A232" s="3" t="inlineStr">
         <is>
           <t>e20b1ccd202880615cb463eb1e641d9188586d19771c57dfdcf166c06eff81ee</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B232" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C232" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D232" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E232" s="3" t="inlineStr">
         <is>
           <t>AI Automation Engineer Co-op</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F232" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G232" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4432508447</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr"/>
-      <c r="J232" s="2" t="inlineStr"/>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L232" s="2" t="inlineStr"/>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr"/>
+      <c r="J232" s="3" t="inlineStr"/>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+      <c r="A233" s="3" t="inlineStr">
         <is>
           <t>f1ec18577611dfc42ef04c478d4e75f69c2367365ab281dd774fd510db822ce8</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B233" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>Coveo</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>Backend Development Intern, Fall 2026</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F233" s="3" t="inlineStr">
         <is>
           <t>Québec, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G233" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426796367</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L233" s="2" t="inlineStr"/>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr"/>
+      <c r="J233" s="3" t="inlineStr"/>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>cd060389436c737538ec851d40c62e1416449febd232414d29eef1fbc5c024cf</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Victoria, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434343303</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>48e207375a6580e7a4ca7ec4acc43ce3fe6379eb5c27a34df92ba7ff33e3c376</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Coop</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Strathcona, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417684034</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>5eca8f4f62990ea8ecb1249f855fcf0aecad20f98cca672bb0ffc8958ce3af9d</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>QuadReal Property Group</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Integration Developer, Fall 2026 - Toronto or Vancouver (Co-op/Internship) - 4 Months</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434769058</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>85146fd0aef13dcf273c36340065c4e8db6ed6bd3573b38a8ec6c018b5badf7c</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer Intern (12-16 months - September 2026)</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431437502</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>bdfae98ff731b5241c69f2ca93131bbc8ecef86f938ffcb168a576dcb7ccb301</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Software Test Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406430191</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2e3d1d6316e2899c8754b3eb8536651dd3fee05f7bcce64c8c6734967c063b0f</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Software Tester – Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406422799</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr"/>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>c028af51117f96ebf9257cc563c26d53a97fba8b6112cfd06a9bb603c95d2e5d</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Canada Life</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer (Student Position)</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>London, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434351901</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>f7feb75d414f40e21bf765239143aa299ae8a80eb215f7ca386b4bfebdbc8df0</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>ProCogia</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Statistical Programming Intern</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429572367</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr"/>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12613,404 +12613,560 @@
       <c r="L233" s="3" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+      <c r="A234" s="3" t="inlineStr">
         <is>
           <t>cd060389436c737538ec851d40c62e1416449febd232414d29eef1fbc5c024cf</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B234" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C234" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F234" s="3" t="inlineStr">
         <is>
           <t>Victoria, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G234" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434343303</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I234" s="2" t="inlineStr"/>
-      <c r="J234" s="2" t="inlineStr"/>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr"/>
+      <c r="J234" s="3" t="inlineStr"/>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+      <c r="A235" s="3" t="inlineStr">
         <is>
           <t>48e207375a6580e7a4ca7ec4acc43ce3fe6379eb5c27a34df92ba7ff33e3c376</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B235" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C235" s="3" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D235" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E235" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Coop</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F235" s="3" t="inlineStr">
         <is>
           <t>Strathcona, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G235" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417684034</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L235" s="2" t="inlineStr"/>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr"/>
+      <c r="J235" s="3" t="inlineStr"/>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+      <c r="A236" s="3" t="inlineStr">
         <is>
           <t>5eca8f4f62990ea8ecb1249f855fcf0aecad20f98cca672bb0ffc8958ce3af9d</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B236" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
         <is>
           <t>QuadReal Property Group</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>Integration Developer, Fall 2026 - Toronto or Vancouver (Co-op/Internship) - 4 Months</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G236" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434769058</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I236" s="2" t="inlineStr"/>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L236" s="2" t="inlineStr"/>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I236" s="3" t="inlineStr"/>
+      <c r="J236" s="3" t="inlineStr"/>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+      <c r="A237" s="3" t="inlineStr">
         <is>
           <t>85146fd0aef13dcf273c36340065c4e8db6ed6bd3573b38a8ec6c018b5badf7c</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B237" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C237" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D237" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>Embedded Software Engineer Intern (12-16 months - September 2026)</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F237" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G237" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431437502</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I237" s="2" t="inlineStr"/>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L237" s="2" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr"/>
+      <c r="J237" s="3" t="inlineStr"/>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+      <c r="A238" s="3" t="inlineStr">
         <is>
           <t>bdfae98ff731b5241c69f2ca93131bbc8ecef86f938ffcb168a576dcb7ccb301</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B238" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C238" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D238" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>Software Test Co-op/Intern</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F238" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G238" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406430191</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr"/>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L238" s="2" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr"/>
+      <c r="J238" s="3" t="inlineStr"/>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+      <c r="A239" s="3" t="inlineStr">
         <is>
           <t>2e3d1d6316e2899c8754b3eb8536651dd3fee05f7bcce64c8c6734967c063b0f</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B239" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C239" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D239" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>Software Tester – Co-op/Intern</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F239" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G239" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406422799</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr"/>
-      <c r="J239" s="2" t="inlineStr"/>
-      <c r="K239" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L239" s="2" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr"/>
+      <c r="J239" s="3" t="inlineStr"/>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>c028af51117f96ebf9257cc563c26d53a97fba8b6112cfd06a9bb603c95d2e5d</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B240" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C240" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D240" s="3" t="inlineStr">
         <is>
           <t>Canada Life</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>Software Developer (Student Position)</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F240" s="3" t="inlineStr">
         <is>
           <t>London, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G240" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434351901</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr"/>
-      <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="inlineStr"/>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr"/>
+      <c r="J240" s="3" t="inlineStr"/>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+      <c r="A241" s="3" t="inlineStr">
         <is>
           <t>f7feb75d414f40e21bf765239143aa299ae8a80eb215f7ca386b4bfebdbc8df0</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B241" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C241" s="3" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D241" s="3" t="inlineStr">
         <is>
           <t>ProCogia</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E241" s="3" t="inlineStr">
         <is>
           <t>Statistical Programming Intern</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F241" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G241" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429572367</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I241" s="2" t="inlineStr"/>
-      <c r="J241" s="2" t="inlineStr"/>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L241" s="2" t="inlineStr"/>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I241" s="3" t="inlineStr"/>
+      <c r="J241" s="3" t="inlineStr"/>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>86c1919632dfb4eaea67996c2463352736db46c9f1af3cef16f46dafa512625c</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Maple Leaf Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=c9cee38f95368546</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>**Powered by Passion. United by Purpose. Build for Impact.**
+At Maple Leaf Sports \&amp; Entertainment Partnership (MLSE), we exist to deliver the ultimate fan experience by lifting trophies, spirits, and communities – united as one.
+We're more than a workplace. We are a team of passionate peo</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>ac2ad65a0a7c3cd416830d93ac180f3de51b272cdc88666bddf64f8527e0f44a</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Interac Corp.</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Operations Intern</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430045246</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr"/>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>9fe5829647683f4a5a7338ae896c6bd085db23be32d7dcc1e7715f5a5f9e9b95</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Clio</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Business Operations Co-op</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431878961</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L244"/>
+  <dimension ref="A1:L249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13013,160 +13013,425 @@
       <c r="L241" s="3" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+      <c r="A242" s="3" t="inlineStr">
         <is>
           <t>86c1919632dfb4eaea67996c2463352736db46c9f1af3cef16f46dafa512625c</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B242" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C242" s="3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D242" s="3" t="inlineStr">
         <is>
           <t>Maple Leaf Sports &amp; Entertainment</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F242" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G242" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=c9cee38f95368546</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H242" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I242" s="3" t="inlineStr">
         <is>
           <t>**Powered by Passion. United by Purpose. Build for Impact.**
 At Maple Leaf Sports \&amp; Entertainment Partnership (MLSE), we exist to deliver the ultimate fan experience by lifting trophies, spirits, and communities – united as one.
 We're more than a workplace. We are a team of passionate peo</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L242" s="2" t="inlineStr"/>
+      <c r="J242" s="3" t="inlineStr"/>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+      <c r="A243" s="3" t="inlineStr">
         <is>
           <t>ac2ad65a0a7c3cd416830d93ac180f3de51b272cdc88666bddf64f8527e0f44a</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B243" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C243" s="3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D243" s="3" t="inlineStr">
         <is>
           <t>Interac Corp.</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>Cloud Operations Intern</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F243" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G243" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430045246</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I243" s="2" t="inlineStr"/>
-      <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L243" s="2" t="inlineStr"/>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I243" s="3" t="inlineStr"/>
+      <c r="J243" s="3" t="inlineStr"/>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+      <c r="A244" s="3" t="inlineStr">
         <is>
           <t>9fe5829647683f4a5a7338ae896c6bd085db23be32d7dcc1e7715f5a5f9e9b95</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B244" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C244" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D244" s="3" t="inlineStr">
         <is>
           <t>Clio</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>Business Operations Co-op</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F244" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G244" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431878961</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I244" s="2" t="inlineStr"/>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L244" s="2" t="inlineStr"/>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr"/>
+      <c r="J244" s="3" t="inlineStr"/>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>5e8f688019ede74f4d510778eca8790192278b610cca1f5fa7a269b42463ae97</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Dynamsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=38c60bf7430cb362</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>**Algorithm Engineer INtern**
+=============================
+Location: Vancouver, BCType: Full\-time Contract (6\-month)Reports to: Chief Product OfficerStart Date: ASAPBase Salary: $50,000 \- 60,000 CAD annually, depending on qualifications and experience.  
+**About Us**
+------------
+At Dyna</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>706dc989782cc1b9a54f8d7b09849c8f1b684e839dfb83fe4ebfec43bec297da</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Kinaxis</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Co-op/Intern Associate Software Developer</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1638d391b17b1f86</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>About Kinaxis:
+**About Kinaxis**
+Are you looking to join an innovative, market\-leading company where you can truly elevate your career? At Kinaxis we are serious about culture, we are serious about technology, we are serious about customers, and we are serious about not taking ourselves too serio</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>5b7615fa074913627d800fcdac51d6674a749d56c27d8c331206081baf1a4c0b</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern — Full-Stack / AI Product</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4389769700</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr"/>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>b888b6d54618d081dbf93e070116061fa6f5f899025e633ad90aabcc4a4f740e</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Architectural Intern</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=69eb1c9b0faaebfc</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Stantec’s Buildings team is on a mission to become the world’s leading integrated design practice. Our architects, engineers, interior designers, consultants, sustainability specialists, and technologists are passionate about the power of design. Our collaborative culture and our innovative, sustain</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>96cbca80843344f64c767429cac1e9439a55d59c5fb83c5a9ab2bd77d2202532</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Kinaxis</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Co-op/Intern Associate Software Developer</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4426583392</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr"/>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L249"/>
+  <dimension ref="A1:L253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13169,47 +13169,47 @@
       <c r="L244" s="3" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+      <c r="A245" s="3" t="inlineStr">
         <is>
           <t>5e8f688019ede74f4d510778eca8790192278b610cca1f5fa7a269b42463ae97</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B245" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C245" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D245" s="3" t="inlineStr">
         <is>
           <t>Dynamsoft Corporation</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E245" s="3" t="inlineStr">
         <is>
           <t>Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F245" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G245" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=38c60bf7430cb362</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H245" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I245" s="3" t="inlineStr">
         <is>
           <t>**Algorithm Engineer INtern**
 =============================
@@ -13219,219 +13219,423 @@
 At Dyna</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L245" s="2" t="inlineStr"/>
+      <c r="J245" s="3" t="inlineStr"/>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+      <c r="A246" s="3" t="inlineStr">
         <is>
           <t>706dc989782cc1b9a54f8d7b09849c8f1b684e839dfb83fe4ebfec43bec297da</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B246" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C246" s="3" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Associate Software Developer</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F246" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G246" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1638d391b17b1f86</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H246" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I246" s="3" t="inlineStr">
         <is>
           <t>About Kinaxis:
 **About Kinaxis**
 Are you looking to join an innovative, market\-leading company where you can truly elevate your career? At Kinaxis we are serious about culture, we are serious about technology, we are serious about customers, and we are serious about not taking ourselves too serio</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr"/>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L246" s="2" t="inlineStr"/>
+      <c r="J246" s="3" t="inlineStr"/>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+      <c r="A247" s="3" t="inlineStr">
         <is>
           <t>5b7615fa074913627d800fcdac51d6674a749d56c27d8c331206081baf1a4c0b</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B247" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C247" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D247" s="3" t="inlineStr">
         <is>
           <t>Olivia</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E247" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern — Full-Stack / AI Product</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="F247" s="3" t="inlineStr"/>
+      <c r="G247" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4389769700</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I247" s="2" t="inlineStr"/>
-      <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L247" s="2" t="inlineStr"/>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr"/>
+      <c r="J247" s="3" t="inlineStr"/>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+      <c r="A248" s="3" t="inlineStr">
         <is>
           <t>b888b6d54618d081dbf93e070116061fa6f5f899025e633ad90aabcc4a4f740e</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B248" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C248" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>Stantec</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>Architectural Intern</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F248" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G248" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=69eb1c9b0faaebfc</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H248" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I248" s="3" t="inlineStr">
         <is>
           <t>Stantec’s Buildings team is on a mission to become the world’s leading integrated design practice. Our architects, engineers, interior designers, consultants, sustainability specialists, and technologists are passionate about the power of design. Our collaborative culture and our innovative, sustain</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr"/>
-      <c r="K248" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L248" s="2" t="inlineStr"/>
+      <c r="J248" s="3" t="inlineStr"/>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+      <c r="A249" s="3" t="inlineStr">
         <is>
           <t>96cbca80843344f64c767429cac1e9439a55d59c5fb83c5a9ab2bd77d2202532</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B249" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C249" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D249" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Associate Software Developer</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F249" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="G249" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426583392</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I249" s="2" t="inlineStr"/>
-      <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L249" s="2" t="inlineStr"/>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="3" t="inlineStr"/>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>165eaec130f04d79b164b52451ef79ff2652ca068b107472abc02703abafc480</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>6th Man</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Developer Internship (SEO &amp; E-commerce)</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434728364</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>a375d24cb7bd26da6d87acda09334429b396236db2546b3870dd561ab1947d10</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Audiokinetic</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development, Wwise Acoustics (Autumn 2026)</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428166455</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>47f2e761883358844d4caf61c9065df1c75e9f188016b3dd79710df22a53b496</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>IP R&amp;D Lab Technologist Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4406420926</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>955d6daebfa5b4311ae5e0f448bf94df27772cc1cb2f3eebb639d6277290d933</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Developer - Intern</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=38c4f2b5d8a227fe</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>At Compass Digital, our core product engineering team builds innovative technology solutions for the hospitality industry. We develop a range of products, including food ordering apps, kitchen display systems, and operator management tools. Our back\-end services are shared along the guest's hospita</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L253"/>
+  <dimension ref="A1:L259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13434,208 +13434,545 @@
       <c r="L249" s="3" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+      <c r="A250" s="3" t="inlineStr">
         <is>
           <t>165eaec130f04d79b164b52451ef79ff2652ca068b107472abc02703abafc480</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>6th Man</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>Developer Internship (SEO &amp; E-commerce)</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F250" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G250" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434728364</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I250" s="2" t="inlineStr"/>
-      <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L250" s="2" t="inlineStr"/>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr"/>
+      <c r="J250" s="3" t="inlineStr"/>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+      <c r="A251" s="3" t="inlineStr">
         <is>
           <t>a375d24cb7bd26da6d87acda09334429b396236db2546b3870dd561ab1947d10</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B251" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C251" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D251" s="3" t="inlineStr">
         <is>
           <t>Audiokinetic</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E251" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development, Wwise Acoustics (Autumn 2026)</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F251" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
+      <c r="G251" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4428166455</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I251" s="2" t="inlineStr"/>
-      <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L251" s="2" t="inlineStr"/>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I251" s="3" t="inlineStr"/>
+      <c r="J251" s="3" t="inlineStr"/>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+      <c r="A252" s="3" t="inlineStr">
         <is>
           <t>47f2e761883358844d4caf61c9065df1c75e9f188016b3dd79710df22a53b496</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="B252" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C252" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D252" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>IP R&amp;D Lab Technologist Co-op/Intern</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F252" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G252" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4406420926</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L252" s="2" t="inlineStr"/>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I252" s="3" t="inlineStr"/>
+      <c r="J252" s="3" t="inlineStr"/>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+      <c r="A253" s="3" t="inlineStr">
         <is>
           <t>955d6daebfa5b4311ae5e0f448bf94df27772cc1cb2f3eebb639d6277290d933</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B253" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C253" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D253" s="3" t="inlineStr">
         <is>
           <t>Compass Group</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E253" s="3" t="inlineStr">
         <is>
           <t>Mobile Developer - Intern</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F253" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G253" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=38c4f2b5d8a227fe</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H253" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I253" s="3" t="inlineStr">
         <is>
           <t>At Compass Digital, our core product engineering team builds innovative technology solutions for the hospitality industry. We develop a range of products, including food ordering apps, kitchen display systems, and operator management tools. Our back\-end services are shared along the guest's hospita</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L253" s="2" t="inlineStr"/>
+      <c r="J253" s="3" t="inlineStr"/>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>866f9be14156be4135d29fbd475db49e9cf7feae6131c56e201a252ac0b9588b</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Software Dev Engineer, Measurement Ad Tech Data Science</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5787257021?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Are you excited about operating at Internet scale? Inventing how ads performance is measured in the online retail world? Growing and learning from the world class engineers? If so, we want to hear from you! Key job responsibilities You will be responsible for designing and developing software produc</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>e98948086d1951cb8c68fa5081898f18121477226d1e85facdea1b076769b6f2</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Full Stack Developer)</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=97b35699e34fa384</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>At Compass Digital, our core product engineering team builds innovative technology solutions for the hospitality industry. We develop a range of products, including food ordering apps, kitchen display systems, and operator management tools. Our back\-end services are shared along the guest's hospita</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>ba955e247417bb9f30f6b7af1863d41092a81eb43b4bffb3127bd020d026abca</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Sentra</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>North York, ON, CA</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=325cd5b22cc8863f</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>### **What You'll Do**
+* Build production software that real customers use.
+* Work alongside engineers developing AI\-native products.
+* Contribute to backend systems, APIs, product features, and internal tools.
+* Participate in technical design discussions and code reviews.
+* Learn how high\-perfo</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>01cfa8a096900e112af5365ee14f936d9269af2503282aabe54bbe251014f45d</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Synopsys</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Intern (Technical-IT)</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=0a285a08d9f95048</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>**We Are:**Drive technology innovations that shape the way we live and connect. Our technology drives the Era of Pervasive Intelligence, where smart tech and AI are seamlessly woven into daily life. From self\-driving cars and health\-monitoring smartwatches to renewable energy systems that efficien</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>53894ada4d4058e0e722d96276961790c7fe506911810c2f4d372b9f3ee9ee70</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op - Canada - Richmond, BC - Remote</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436435035</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>9edbf8155dac5941adf3a47677b824a389bbf8033fe326e7c8ce1a84d1ade48b</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>WorkSafeBC</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Student, Strategy and Planning (Student Intern)</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, BC, CA</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=db2249e1a359a79f</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">* Job requisition number
+040147
+* Job location
+Richmond
+* Full\-time / part\-time
+Full\-time
+* Salary
+$34\.04/hourly
+* Posting period
+From 07/03/2026 to 07/16/2026
+**Overview**
+------------
+We’re looking for a **Strategy and Planning Intern (MBA Co\-op Student)** to work in the Office of Strategy </t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13638,155 +13638,155 @@
       <c r="L253" s="3" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+      <c r="A254" s="3" t="inlineStr">
         <is>
           <t>866f9be14156be4135d29fbd475db49e9cf7feae6131c56e201a252ac0b9588b</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B254" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D254" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E254" s="3" t="inlineStr">
         <is>
           <t>Sr. Software Dev Engineer, Measurement Ad Tech Data Science</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F254" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G254" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5787257021?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H254" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I254" s="3" t="inlineStr">
         <is>
           <t>Are you excited about operating at Internet scale? Inventing how ads performance is measured in the online retail world? Growing and learning from the world class engineers? If so, we want to hear from you! Key job responsibilities You will be responsible for designing and developing software produc</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr"/>
-      <c r="K254" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L254" s="2" t="inlineStr"/>
+      <c r="J254" s="3" t="inlineStr"/>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+      <c r="A255" s="3" t="inlineStr">
         <is>
           <t>e98948086d1951cb8c68fa5081898f18121477226d1e85facdea1b076769b6f2</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B255" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C255" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D255" s="3" t="inlineStr">
         <is>
           <t>Compass Group</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E255" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern (Full Stack Developer)</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F255" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G255" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=97b35699e34fa384</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="H255" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="I255" s="3" t="inlineStr">
         <is>
           <t>At Compass Digital, our core product engineering team builds innovative technology solutions for the hospitality industry. We develop a range of products, including food ordering apps, kitchen display systems, and operator management tools. Our back\-end services are shared along the guest's hospita</t>
         </is>
       </c>
-      <c r="J255" s="2" t="inlineStr"/>
-      <c r="K255" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L255" s="2" t="inlineStr"/>
+      <c r="J255" s="3" t="inlineStr"/>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+      <c r="A256" s="3" t="inlineStr">
         <is>
           <t>ba955e247417bb9f30f6b7af1863d41092a81eb43b4bffb3127bd020d026abca</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B256" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C256" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D256" s="3" t="inlineStr">
         <is>
           <t>Sentra</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E256" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F256" s="3" t="inlineStr">
         <is>
           <t>North York, ON, CA</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G256" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=325cd5b22cc8863f</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="H256" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I256" s="3" t="inlineStr">
         <is>
           <t>### **What You'll Do**
 * Build production software that real customers use.
@@ -13796,160 +13796,160 @@
 * Learn how high\-perfo</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr"/>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L256" s="2" t="inlineStr"/>
+      <c r="J256" s="3" t="inlineStr"/>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+      <c r="A257" s="3" t="inlineStr">
         <is>
           <t>01cfa8a096900e112af5365ee14f936d9269af2503282aabe54bbe251014f45d</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B257" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C257" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D257" s="3" t="inlineStr">
         <is>
           <t>Synopsys</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E257" s="3" t="inlineStr">
         <is>
           <t>Intern (Technical-IT)</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F257" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G257" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=0a285a08d9f95048</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="H257" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="I257" s="3" t="inlineStr">
         <is>
           <t>**We Are:**Drive technology innovations that shape the way we live and connect. Our technology drives the Era of Pervasive Intelligence, where smart tech and AI are seamlessly woven into daily life. From self\-driving cars and health\-monitoring smartwatches to renewable energy systems that efficien</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr"/>
-      <c r="K257" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L257" s="2" t="inlineStr"/>
+      <c r="J257" s="3" t="inlineStr"/>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+      <c r="A258" s="3" t="inlineStr">
         <is>
           <t>53894ada4d4058e0e722d96276961790c7fe506911810c2f4d372b9f3ee9ee70</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C258" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D258" s="3" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E258" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op - Canada - Richmond, BC - Remote</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F258" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G258" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436435035</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I258" s="2" t="inlineStr"/>
-      <c r="J258" s="2" t="inlineStr"/>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L258" s="2" t="inlineStr"/>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr"/>
+      <c r="J258" s="3" t="inlineStr"/>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+      <c r="A259" s="3" t="inlineStr">
         <is>
           <t>9edbf8155dac5941adf3a47677b824a389bbf8033fe326e7c8ce1a84d1ade48b</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B259" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C259" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="D259" s="3" t="inlineStr">
         <is>
           <t>WorkSafeBC</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E259" s="3" t="inlineStr">
         <is>
           <t>Co-op Student, Strategy and Planning (Student Intern)</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F259" s="3" t="inlineStr">
         <is>
           <t>Richmond, BC, CA</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G259" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=db2249e1a359a79f</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="H259" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I259" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">* Job requisition number
 040147
@@ -13966,13 +13966,113 @@
 We’re looking for a **Strategy and Planning Intern (MBA Co\-op Student)** to work in the Office of Strategy </t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L259" s="2" t="inlineStr"/>
+      <c r="J259" s="3" t="inlineStr"/>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>23651e0c3dfb66fda398a99ed666f1f8daabf234eb9751df663ddb8f2538f25d</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>TMX Group</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4431869987</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>a07198cd772a02974320e3cff88c7c64363019a1113e41c2d4dac9fdf44145a0</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Dynamsoft</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436460565</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13975,104 +13975,154 @@
       <c r="L259" s="3" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+      <c r="A260" s="3" t="inlineStr">
         <is>
           <t>23651e0c3dfb66fda398a99ed666f1f8daabf234eb9751df663ddb8f2538f25d</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B260" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C260" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D260" s="3" t="inlineStr">
         <is>
           <t>TMX Group</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E260" s="3" t="inlineStr">
         <is>
           <t>AI Intern</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F260" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G260" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4431869987</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="2" t="inlineStr"/>
-      <c r="K260" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L260" s="2" t="inlineStr"/>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="3" t="inlineStr"/>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+      <c r="A261" s="3" t="inlineStr">
         <is>
           <t>a07198cd772a02974320e3cff88c7c64363019a1113e41c2d4dac9fdf44145a0</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="B261" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C261" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D261" s="3" t="inlineStr">
         <is>
           <t>Dynamsoft</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E261" s="3" t="inlineStr">
         <is>
           <t>Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F261" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G261" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436460565</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I261" s="2" t="inlineStr"/>
-      <c r="J261" s="2" t="inlineStr"/>
-      <c r="K261" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L261" s="2" t="inlineStr"/>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr"/>
+      <c r="J261" s="3" t="inlineStr"/>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>c02b1c9d54f0589212ae7b1ea1e4ad5c8967937fc1556127523b7ed26e3b60da</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern/Co-op (Fall 2026) Preferred Candidate</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436785285</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr"/>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L262"/>
+  <dimension ref="A1:L264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14075,54 +14075,158 @@
       <c r="L261" s="3" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+      <c r="A262" s="3" t="inlineStr">
         <is>
           <t>c02b1c9d54f0589212ae7b1ea1e4ad5c8967937fc1556127523b7ed26e3b60da</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B262" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C262" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D262" s="3" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E262" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern/Co-op (Fall 2026) Preferred Candidate</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F262" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G262" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436785285</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I262" s="2" t="inlineStr"/>
-      <c r="J262" s="2" t="inlineStr"/>
-      <c r="K262" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L262" s="2" t="inlineStr"/>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="3" t="inlineStr"/>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>f3b5f4054fa4ae55fb5c63fd422ff2d13f83987979fb37fbd02d7a04699c7822</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Coveo</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern (Professional Services team), Fall 2026</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Québec, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427001347</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr"/>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>645c75885bc1feb82db65694e90216ef076dbe92bb0da086c88f4f856621f45f</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>upzoids</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Power Platform Developer Intern</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=8c8b12a586a29691</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>As a Power Platform Developer Intern, you will gain hands\-on experience working on real\-world projects that involve designing, developing, and enhancing Power Pages applications. You will collaborate with our experienced developers and consultants to create visually appealing and user\-friendly in</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L264"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14125,108 +14125,458 @@
       <c r="L262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+      <c r="A263" s="3" t="inlineStr">
         <is>
           <t>f3b5f4054fa4ae55fb5c63fd422ff2d13f83987979fb37fbd02d7a04699c7822</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B263" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C263" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D263" s="3" t="inlineStr">
         <is>
           <t>Coveo</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E263" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern (Professional Services team), Fall 2026</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F263" s="3" t="inlineStr">
         <is>
           <t>Québec, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G263" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427001347</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I263" s="2" t="inlineStr"/>
-      <c r="J263" s="2" t="inlineStr"/>
-      <c r="K263" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L263" s="2" t="inlineStr"/>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="inlineStr"/>
+      <c r="J263" s="3" t="inlineStr"/>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+      <c r="A264" s="3" t="inlineStr">
         <is>
           <t>645c75885bc1feb82db65694e90216ef076dbe92bb0da086c88f4f856621f45f</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B264" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C264" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D264" s="3" t="inlineStr">
         <is>
           <t>upzoids</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E264" s="3" t="inlineStr">
         <is>
           <t>Power Platform Developer Intern</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F264" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G264" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=8c8b12a586a29691</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="H264" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="I264" s="3" t="inlineStr">
         <is>
           <t>As a Power Platform Developer Intern, you will gain hands\-on experience working on real\-world projects that involve designing, developing, and enhancing Power Pages applications. You will collaborate with our experienced developers and consultants to create visually appealing and user\-friendly in</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr"/>
-      <c r="K264" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L264" s="2" t="inlineStr"/>
+      <c r="J264" s="3" t="inlineStr"/>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>e7160756a89ec4c5a5b19f59b60bbbecdea5499421d10bc2a6ec709c5b6a90cd</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Hanzilla</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5789953531?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>09845be12633ef3f715174885726e5144b1b24efa638be5f11fb73627a47bcbd</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>CCRC SW Developer Intern</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417505652</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2b01c976d734c96511726369323c24f6b7781b2b90aa47fa77d1eeeb631bb858</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Aircraft Systems Research &amp; Technology - Software Engineering (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Dorval, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4422466628</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr"/>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>6deeb9491adedf1ef2aaa5fa2fddc486a45b81603df76aa726d77943a6725411</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer – RL Post-Training for LLMs</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4425916917</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>89eeeb6568f38c08158ae396129927f099274a11cecb96357c90da81a35fcf50</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Embedded C/C++ SW Developer Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417062448</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>41ec52d9415d28493540b57c12ac1c08aa80415e2d489238c69be8dbf7087ff4</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Kinaxis</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Co-op/Intern Software Development - C++</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Québec, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430152929</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>f569ebb8c939f3f8fcffb2a44beb9ae71d4ffc172d798d9c506930072280354b</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Stealth Startup</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434613829</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L271"/>
+  <dimension ref="A1:L273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14229,354 +14229,459 @@
       <c r="L264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+      <c r="A265" s="3" t="inlineStr">
         <is>
           <t>e7160756a89ec4c5a5b19f59b60bbbecdea5499421d10bc2a6ec709c5b6a90cd</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B265" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C265" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D265" s="3" t="inlineStr">
         <is>
           <t>Hanzilla</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E265" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern - Android Connectivity (Fall/Spring Co-op)</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F265" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G265" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5789953531?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="H265" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="I265" s="3" t="inlineStr">
         <is>
           <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
         </is>
       </c>
-      <c r="J265" s="2" t="inlineStr"/>
-      <c r="K265" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L265" s="2" t="inlineStr"/>
+      <c r="J265" s="3" t="inlineStr"/>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+      <c r="A266" s="3" t="inlineStr">
         <is>
           <t>09845be12633ef3f715174885726e5144b1b24efa638be5f11fb73627a47bcbd</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B266" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C266" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="D266" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E266" s="3" t="inlineStr">
         <is>
           <t>CCRC SW Developer Intern</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F266" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="G266" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417505652</t>
         </is>
       </c>
-      <c r="H266" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I266" s="2" t="inlineStr"/>
-      <c r="J266" s="2" t="inlineStr"/>
-      <c r="K266" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L266" s="2" t="inlineStr"/>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
+      <c r="J266" s="3" t="inlineStr"/>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+      <c r="A267" s="3" t="inlineStr">
         <is>
           <t>2b01c976d734c96511726369323c24f6b7781b2b90aa47fa77d1eeeb631bb858</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
+      <c r="C267" s="3" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="D267" s="3" t="inlineStr">
         <is>
           <t>Bombardier</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E267" s="3" t="inlineStr">
         <is>
           <t>Intern, Aircraft Systems Research &amp; Technology - Software Engineering (Fall 2026)</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F267" s="3" t="inlineStr">
         <is>
           <t>Dorval, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="G267" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4422466628</t>
         </is>
       </c>
-      <c r="H267" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I267" s="2" t="inlineStr"/>
-      <c r="J267" s="2" t="inlineStr"/>
-      <c r="K267" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L267" s="2" t="inlineStr"/>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="inlineStr"/>
+      <c r="J267" s="3" t="inlineStr"/>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+      <c r="A268" s="3" t="inlineStr">
         <is>
           <t>6deeb9491adedf1ef2aaa5fa2fddc486a45b81603df76aa726d77943a6725411</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C268" s="3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="D268" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E268" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer – RL Post-Training for LLMs</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F268" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="G268" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4425916917</t>
         </is>
       </c>
-      <c r="H268" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I268" s="2" t="inlineStr"/>
-      <c r="J268" s="2" t="inlineStr"/>
-      <c r="K268" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L268" s="2" t="inlineStr"/>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
+      <c r="J268" s="3" t="inlineStr"/>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t>89eeeb6568f38c08158ae396129927f099274a11cecb96357c90da81a35fcf50</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
+      <c r="C269" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="D269" s="3" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E269" s="3" t="inlineStr">
         <is>
           <t>Embedded C/C++ SW Developer Co-op/Intern</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F269" s="3" t="inlineStr">
         <is>
           <t>Kanata, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="G269" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417062448</t>
         </is>
       </c>
-      <c r="H269" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I269" s="2" t="inlineStr"/>
-      <c r="J269" s="2" t="inlineStr"/>
-      <c r="K269" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L269" s="2" t="inlineStr"/>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr"/>
+      <c r="J269" s="3" t="inlineStr"/>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>41ec52d9415d28493540b57c12ac1c08aa80415e2d489238c69be8dbf7087ff4</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C270" s="3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="D270" s="3" t="inlineStr">
         <is>
           <t>Kinaxis</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E270" s="3" t="inlineStr">
         <is>
           <t>Co-op/Intern Software Development - C++</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F270" s="3" t="inlineStr">
         <is>
           <t>Québec, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G270" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430152929</t>
         </is>
       </c>
-      <c r="H270" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I270" s="2" t="inlineStr"/>
-      <c r="J270" s="2" t="inlineStr"/>
-      <c r="K270" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L270" s="2" t="inlineStr"/>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr"/>
+      <c r="J270" s="3" t="inlineStr"/>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>f569ebb8c939f3f8fcffb2a44beb9ae71d4ffc172d798d9c506930072280354b</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="D271" s="3" t="inlineStr">
         <is>
           <t>Stealth Startup</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E271" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr"/>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="F271" s="3" t="inlineStr"/>
+      <c r="G271" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434613829</t>
         </is>
       </c>
-      <c r="H271" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I271" s="2" t="inlineStr"/>
-      <c r="J271" s="2" t="inlineStr"/>
-      <c r="K271" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L271" s="2" t="inlineStr"/>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
+      <c r="J271" s="3" t="inlineStr"/>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>0f76ff1c61cb371438045846d77dde5ba222debc1830e9046e2fc6d13e9c5000</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Synopsys</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Co-Op</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=78e7fd9e6193f1b9</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>### **We Are:**
+Drive technology innovations that shape the way we live and connect. Our technology drives the Era of Pervasive Intelligence, where smart tech and AI are seamlessly woven into daily life. From self\-driving cars and health\-monitoring smartwatches to renewable energy systems that e</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>e357ca7e8e0211504ea4f908f1a9892533e06db5f8a17440203c93236f6e8d82</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Buttcon</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Web Development Student</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Woodbridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436053151</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L273"/>
+  <dimension ref="A1:L282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14579,109 +14579,681 @@
       <c r="L271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>0f76ff1c61cb371438045846d77dde5ba222debc1830e9046e2fc6d13e9c5000</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="D272" s="3" t="inlineStr">
         <is>
           <t>Synopsys</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E272" s="3" t="inlineStr">
         <is>
           <t>Intern, Co-Op</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F272" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G272" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=78e7fd9e6193f1b9</t>
         </is>
       </c>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="H272" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I272" s="2" t="inlineStr">
+      <c r="I272" s="3" t="inlineStr">
         <is>
           <t>### **We Are:**
 Drive technology innovations that shape the way we live and connect. Our technology drives the Era of Pervasive Intelligence, where smart tech and AI are seamlessly woven into daily life. From self\-driving cars and health\-monitoring smartwatches to renewable energy systems that e</t>
         </is>
       </c>
-      <c r="J272" s="2" t="inlineStr"/>
-      <c r="K272" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L272" s="2" t="inlineStr"/>
+      <c r="J272" s="3" t="inlineStr"/>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t>e357ca7e8e0211504ea4f908f1a9892533e06db5f8a17440203c93236f6e8d82</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="B273" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>Buttcon</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E273" s="3" t="inlineStr">
         <is>
           <t>Web Development Student</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F273" s="3" t="inlineStr">
         <is>
           <t>Woodbridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G273" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436053151</t>
         </is>
       </c>
-      <c r="H273" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr"/>
-      <c r="J273" s="2" t="inlineStr"/>
-      <c r="K273" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L273" s="2" t="inlineStr"/>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+      <c r="J273" s="3" t="inlineStr"/>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>8286626aa5595989fbedc6042575152fba7ada2e9142cc33b552430034236da7</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Hanzilla</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5789954919?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>As a Software Developer Intern on the Concur Platform Engineering team, you will contribute to scaling the Concur App Center by building elastically scalable microservices. You will work across the full stack from UI clients and server applications to data stores and delivery pipelines. This 8‑month</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>3b9997ac9de4fdd0091d668165f7c29fca2868157a96e203dc47b0724f418b3b</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Vosyn</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>AI Integration &amp; Data Engineer (Vibecoding) - Master-Level Internship (Toronto)</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5791007698?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>About Us At Vosyn, we embrace the exciting, game‑changing world of Artificial Intelligence, driving innovation and pioneering impactful projects across various industries. We are a trailblazing Language Synthesis AI firm reshaping global communication by dissolving language barriers and empowering u</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>f4d250d20a79fa487cfab2218d54a23d41f7eaf5b64664ea9e2bd2519bbc9047</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 4/8/12 months)</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, BC, CA</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3452dbc841f9ee14</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Burnaby, British Columbia, Canada
+**Job ID:**
+R1012892
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+IT, Telecom \&amp; Internet
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help crea</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>31a33b3e99e192b7114e50330046d62be470f559ae80d41e83b78965c3c42f83</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=edd45c2a54d81045</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012739
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+IT, Telecom \&amp; Internet
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a lega</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>449e7774a71465e9c7a55c1f71140a504cbeb14af7fc337bc64ce80b5bd94b10</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7ba066afb65b8839</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012810
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+IT, Telecom \&amp; Internet
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a lega</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>9e081e1db6d2d0405164a5755c01aea21eca9c3b2c0b47c2f043bfe8e63a5f3f</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 12months)</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=c7b0cbc095bf6deb</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012380
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Administration \&amp; Facilities
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>71b3bcdcddfee7c6e63c2ae4000a87efc81b85d7752afec0969f5443817ffdfb</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Knowledge Management Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=92d33c240f240e87</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012818
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Administration \&amp; Facilities
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>9ac448af46b7e23740631c561654c44183302100ac0c2bdb43b0c7c5ed024037</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Signalling Design Intern (Fall 2026, 8 or 12 months)</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, BC, CA</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=0baa6f68ee2e7610</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Burnaby, British Columbia, Canada
+**Job ID:**
+R1012842
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Engineering \&amp; Science
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help creat</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>5a1b85139965e878417bfe02d79cd40c13cb16580f2c02c844108404e9f9fa93</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>CO-OP Radio SWIT</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435274464</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L282"/>
+  <dimension ref="A1:L283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14684,155 +14684,155 @@
       <c r="L273" s="3" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+      <c r="A274" s="3" t="inlineStr">
         <is>
           <t>8286626aa5595989fbedc6042575152fba7ada2e9142cc33b552430034236da7</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
+      <c r="C274" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="D274" s="3" t="inlineStr">
         <is>
           <t>Hanzilla</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E274" s="3" t="inlineStr">
         <is>
           <t>SAP Concur iXp Intern - Software Developer [Vancouver]</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F274" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="G274" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5789954919?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="H274" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I274" s="2" t="inlineStr">
+      <c r="I274" s="3" t="inlineStr">
         <is>
           <t>As a Software Developer Intern on the Concur Platform Engineering team, you will contribute to scaling the Concur App Center by building elastically scalable microservices. You will work across the full stack from UI clients and server applications to data stores and delivery pipelines. This 8‑month</t>
         </is>
       </c>
-      <c r="J274" s="2" t="inlineStr"/>
-      <c r="K274" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L274" s="2" t="inlineStr"/>
+      <c r="J274" s="3" t="inlineStr"/>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L274" s="3" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>3b9997ac9de4fdd0091d668165f7c29fca2868157a96e203dc47b0724f418b3b</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
+      <c r="B275" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
+      <c r="C275" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="D275" s="3" t="inlineStr">
         <is>
           <t>Vosyn</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E275" s="3" t="inlineStr">
         <is>
           <t>AI Integration &amp; Data Engineer (Vibecoding) - Master-Level Internship (Toronto)</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F275" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="G275" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5791007698?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="H275" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I275" s="2" t="inlineStr">
+      <c r="I275" s="3" t="inlineStr">
         <is>
           <t>About Us At Vosyn, we embrace the exciting, game‑changing world of Artificial Intelligence, driving innovation and pioneering impactful projects across various industries. We are a trailblazing Language Synthesis AI firm reshaping global communication by dissolving language barriers and empowering u</t>
         </is>
       </c>
-      <c r="J275" s="2" t="inlineStr"/>
-      <c r="K275" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L275" s="2" t="inlineStr"/>
+      <c r="J275" s="3" t="inlineStr"/>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+      <c r="A276" s="3" t="inlineStr">
         <is>
           <t>f4d250d20a79fa487cfab2218d54a23d41f7eaf5b64664ea9e2bd2519bbc9047</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
+      <c r="B276" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
+      <c r="C276" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="D276" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 4/8/12 months)</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F276" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr">
+      <c r="G276" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3452dbc841f9ee14</t>
         </is>
       </c>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="H276" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I276" s="2" t="inlineStr">
+      <c r="I276" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Burnaby, British Columbia, Canada
@@ -14852,56 +14852,56 @@
 A career at Hitachi Rail will help crea</t>
         </is>
       </c>
-      <c r="J276" s="2" t="inlineStr"/>
-      <c r="K276" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L276" s="2" t="inlineStr"/>
+      <c r="J276" s="3" t="inlineStr"/>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+      <c r="A277" s="3" t="inlineStr">
         <is>
           <t>31a33b3e99e192b7114e50330046d62be470f559ae80d41e83b78965c3c42f83</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
+      <c r="B277" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
+      <c r="C277" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="D277" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E277" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F277" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr">
+      <c r="G277" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=edd45c2a54d81045</t>
         </is>
       </c>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="H277" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I277" s="2" t="inlineStr">
+      <c r="I277" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -14921,56 +14921,56 @@
 A career at Hitachi Rail will help create a lega</t>
         </is>
       </c>
-      <c r="J277" s="2" t="inlineStr"/>
-      <c r="K277" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L277" s="2" t="inlineStr"/>
+      <c r="J277" s="3" t="inlineStr"/>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+      <c r="A278" s="3" t="inlineStr">
         <is>
           <t>449e7774a71465e9c7a55c1f71140a504cbeb14af7fc337bc64ce80b5bd94b10</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
+      <c r="B278" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
+      <c r="C278" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="D278" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E278" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F278" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
+      <c r="G278" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7ba066afb65b8839</t>
         </is>
       </c>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="H278" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I278" s="2" t="inlineStr">
+      <c r="I278" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -14990,56 +14990,56 @@
 A career at Hitachi Rail will help create a lega</t>
         </is>
       </c>
-      <c r="J278" s="2" t="inlineStr"/>
-      <c r="K278" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L278" s="2" t="inlineStr"/>
+      <c r="J278" s="3" t="inlineStr"/>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+      <c r="A279" s="3" t="inlineStr">
         <is>
           <t>9e081e1db6d2d0405164a5755c01aea21eca9c3b2c0b47c2f043bfe8e63a5f3f</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
+      <c r="B279" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
+      <c r="C279" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="D279" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E279" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 12months)</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F279" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
+      <c r="G279" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=c7b0cbc095bf6deb</t>
         </is>
       </c>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="H279" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I279" s="2" t="inlineStr">
+      <c r="I279" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -15059,56 +15059,56 @@
 A career at Hitachi Rail will help create a</t>
         </is>
       </c>
-      <c r="J279" s="2" t="inlineStr"/>
-      <c r="K279" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L279" s="2" t="inlineStr"/>
+      <c r="J279" s="3" t="inlineStr"/>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="inlineStr">
+      <c r="A280" s="3" t="inlineStr">
         <is>
           <t>71b3bcdcddfee7c6e63c2ae4000a87efc81b85d7752afec0969f5443817ffdfb</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
+      <c r="B280" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
+      <c r="C280" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="D280" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E280" s="3" t="inlineStr">
         <is>
           <t>Engineering Knowledge Management Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F280" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr">
+      <c r="G280" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=92d33c240f240e87</t>
         </is>
       </c>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="H280" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I280" s="2" t="inlineStr">
+      <c r="I280" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -15128,56 +15128,56 @@
 A career at Hitachi Rail will help create a</t>
         </is>
       </c>
-      <c r="J280" s="2" t="inlineStr"/>
-      <c r="K280" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L280" s="2" t="inlineStr"/>
+      <c r="J280" s="3" t="inlineStr"/>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="inlineStr">
+      <c r="A281" s="3" t="inlineStr">
         <is>
           <t>9ac448af46b7e23740631c561654c44183302100ac0c2bdb43b0c7c5ed024037</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
+      <c r="B281" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
+      <c r="C281" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="D281" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E281" s="3" t="inlineStr">
         <is>
           <t>Signalling Design Intern (Fall 2026, 8 or 12 months)</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F281" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr">
+      <c r="G281" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=0baa6f68ee2e7610</t>
         </is>
       </c>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="H281" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I281" s="2" t="inlineStr">
+      <c r="I281" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Burnaby, British Columbia, Canada
@@ -15197,63 +15197,113 @@
 A career at Hitachi Rail will help creat</t>
         </is>
       </c>
-      <c r="J281" s="2" t="inlineStr"/>
-      <c r="K281" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L281" s="2" t="inlineStr"/>
+      <c r="J281" s="3" t="inlineStr"/>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+      <c r="A282" s="3" t="inlineStr">
         <is>
           <t>5a1b85139965e878417bfe02d79cd40c13cb16580f2c02c844108404e9f9fa93</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
+      <c r="B282" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C282" s="3" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="D282" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E282" s="3" t="inlineStr">
         <is>
           <t>CO-OP Radio SWIT</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F282" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
+      <c r="G282" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435274464</t>
         </is>
       </c>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I282" s="2" t="inlineStr"/>
-      <c r="J282" s="2" t="inlineStr"/>
-      <c r="K282" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L282" s="2" t="inlineStr"/>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr"/>
+      <c r="J282" s="3" t="inlineStr"/>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>401c14a0f6b9806bb03653c630ee6b0f572ea66315733df0ef15572bb816ca5a</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>[FALL 2026] Software Developer Intern 8 Months</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433953965</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L283"/>
+  <dimension ref="A1:L285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15256,54 +15256,150 @@
       <c r="L282" s="3" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="inlineStr">
+      <c r="A283" s="3" t="inlineStr">
         <is>
           <t>401c14a0f6b9806bb03653c630ee6b0f572ea66315733df0ef15572bb816ca5a</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
+      <c r="B283" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
+      <c r="C283" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="D283" s="3" t="inlineStr">
         <is>
           <t>Dayforce</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E283" s="3" t="inlineStr">
         <is>
           <t>[FALL 2026] Software Developer Intern 8 Months</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F283" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
+      <c r="G283" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433953965</t>
         </is>
       </c>
-      <c r="H283" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I283" s="2" t="inlineStr"/>
-      <c r="J283" s="2" t="inlineStr"/>
-      <c r="K283" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L283" s="2" t="inlineStr"/>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr"/>
+      <c r="J283" s="3" t="inlineStr"/>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>02d2ef060e303b0431f93cf6989444388bc537fa2d5e2a9d52408db798247249</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>SecureRx Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer / Engineer Intern (Co-op) – Fall 2026, (Healthcare SaaS) - Remote</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436515105</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>44acf9f6aa2eefbc35cef713cdb15762f154404b08af8818f075345927697c98</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>American Bureau of Shipping (ABS)</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Intern - AI Software Engineering</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436271162</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:L294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15306,100 +15306,564 @@
       <c r="L283" s="3" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+      <c r="A284" s="3" t="inlineStr">
         <is>
           <t>02d2ef060e303b0431f93cf6989444388bc537fa2d5e2a9d52408db798247249</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
+      <c r="B284" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
+      <c r="C284" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="D284" s="3" t="inlineStr">
         <is>
           <t>SecureRx Technologies Inc.</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E284" s="3" t="inlineStr">
         <is>
           <t>Software Developer / Engineer Intern (Co-op) – Fall 2026, (Healthcare SaaS) - Remote</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F284" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
+      <c r="G284" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436515105</t>
         </is>
       </c>
-      <c r="H284" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I284" s="2" t="inlineStr"/>
-      <c r="J284" s="2" t="inlineStr"/>
-      <c r="K284" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L284" s="2" t="inlineStr"/>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
+      <c r="J284" s="3" t="inlineStr"/>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+      <c r="A285" s="3" t="inlineStr">
         <is>
           <t>44acf9f6aa2eefbc35cef713cdb15762f154404b08af8818f075345927697c98</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
+      <c r="B285" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
+      <c r="C285" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="D285" s="3" t="inlineStr">
         <is>
           <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E285" s="3" t="inlineStr">
         <is>
           <t>Intern - AI Software Engineering</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="F285" s="3" t="inlineStr"/>
+      <c r="G285" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436271162</t>
         </is>
       </c>
-      <c r="H285" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I285" s="2" t="inlineStr"/>
-      <c r="J285" s="2" t="inlineStr"/>
-      <c r="K285" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L285" s="2" t="inlineStr"/>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr"/>
+      <c r="J285" s="3" t="inlineStr"/>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>443e6dc56b1434b5d1a959a22552b13d28089b332e3aa5e45a97d7c966ba2b1b</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>[FALL 2026] Software Developer Intern 8 Months</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5793205035?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>About the opportunity: The Software Developer Intern will closely work with developers in the team and will directly report to the Development Manager. Intern will be primarily responsible for contributing to software development activities including development and testing of deliverables throughou</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>83dcc6ade1fc9918d3a3d9fdb5e2019e266c21809e8e5da5fad359ecd6444328</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>BMO</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist, Fall 2026 ( Co-op/Internship) - 12 months</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437808934</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>23f6f12fe1320f6440824bfa8562c15a51604db0a2786bd641e78f3f1f70d2d5</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern/Co-op (Fall 2026) Preferred Candidate</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429963681</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>af8dc4c7c7b27ba6736c8817bf83101d214c14cedbdf3c64229fef1ce90f36d5</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 12months)</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434560789</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>cfc21413e371d02b4fd3ed163003cfb9e65cc4f2c046476948de734d59df38f3</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 4/8/12 months)</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434579016</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>9110f57e8050482a4d0c9e741c87522f204da76c1362e1befd9c0534580b9cbb</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Thurber Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Geotechnical Engineering Intern (2026070892)</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>Oakville, ON, CA</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=4c79c3e285e1dbfa</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>### **Overview**
+Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Oakville, St. Catharines, or Pickering, Ontario**.
+Thurber provides geotechnical, environmental and construction materials engineering and testing services for a va</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr"/>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>778c120a9af022ca764b4cc6e4ab8f083f22697d4d80ab6e74f060ac1b03aaff</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434563710</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>69b454b356b58b35355954a0cd77e5b83c4c9c4f75b747f618dc1b9d8f13bc8f</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434575094</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr"/>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>8382c30dbe8d38d6487c59958337efe9bff2f7e27e26860fbf1377ae05061ab4</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=513f1e45241c21d6</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L294"/>
+  <dimension ref="A1:L302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15402,468 +15402,889 @@
       <c r="L285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+      <c r="A286" s="3" t="inlineStr">
         <is>
           <t>443e6dc56b1434b5d1a959a22552b13d28089b332e3aa5e45a97d7c966ba2b1b</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
+      <c r="B286" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C286" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="D286" s="3" t="inlineStr">
         <is>
           <t>Dayforce</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E286" s="3" t="inlineStr">
         <is>
           <t>[FALL 2026] Software Developer Intern 8 Months</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F286" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="G286" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5793205035?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="H286" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I286" s="2" t="inlineStr">
+      <c r="I286" s="3" t="inlineStr">
         <is>
           <t>About the opportunity: The Software Developer Intern will closely work with developers in the team and will directly report to the Development Manager. Intern will be primarily responsible for contributing to software development activities including development and testing of deliverables throughou</t>
         </is>
       </c>
-      <c r="J286" s="2" t="inlineStr"/>
-      <c r="K286" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L286" s="2" t="inlineStr"/>
+      <c r="J286" s="3" t="inlineStr"/>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+      <c r="A287" s="3" t="inlineStr">
         <is>
           <t>83dcc6ade1fc9918d3a3d9fdb5e2019e266c21809e8e5da5fad359ecd6444328</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
+      <c r="B287" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr">
+      <c r="C287" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="D287" s="3" t="inlineStr">
         <is>
           <t>BMO</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E287" s="3" t="inlineStr">
         <is>
           <t>Data Scientist, Fall 2026 ( Co-op/Internship) - 12 months</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F287" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="G287" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437808934</t>
         </is>
       </c>
-      <c r="H287" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I287" s="2" t="inlineStr"/>
-      <c r="J287" s="2" t="inlineStr"/>
-      <c r="K287" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L287" s="2" t="inlineStr"/>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr"/>
+      <c r="J287" s="3" t="inlineStr"/>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="inlineStr">
+      <c r="A288" s="3" t="inlineStr">
         <is>
           <t>23f6f12fe1320f6440824bfa8562c15a51604db0a2786bd641e78f3f1f70d2d5</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
+      <c r="B288" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C288" s="3" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="D288" s="3" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E288" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern/Co-op (Fall 2026) Preferred Candidate</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F288" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
+      <c r="G288" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429963681</t>
         </is>
       </c>
-      <c r="H288" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I288" s="2" t="inlineStr"/>
-      <c r="J288" s="2" t="inlineStr"/>
-      <c r="K288" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L288" s="2" t="inlineStr"/>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr"/>
+      <c r="J288" s="3" t="inlineStr"/>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="inlineStr">
+      <c r="A289" s="3" t="inlineStr">
         <is>
           <t>af8dc4c7c7b27ba6736c8817bf83101d214c14cedbdf3c64229fef1ce90f36d5</t>
         </is>
       </c>
-      <c r="B289" s="2" t="inlineStr">
+      <c r="B289" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr">
+      <c r="C289" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="D289" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="E289" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 12months)</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="F289" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr">
+      <c r="G289" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434560789</t>
         </is>
       </c>
-      <c r="H289" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I289" s="2" t="inlineStr"/>
-      <c r="J289" s="2" t="inlineStr"/>
-      <c r="K289" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L289" s="2" t="inlineStr"/>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr"/>
+      <c r="J289" s="3" t="inlineStr"/>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="inlineStr">
+      <c r="A290" s="3" t="inlineStr">
         <is>
           <t>cfc21413e371d02b4fd3ed163003cfb9e65cc4f2c046476948de734d59df38f3</t>
         </is>
       </c>
-      <c r="B290" s="2" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
+      <c r="C290" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="D290" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="E290" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 4/8/12 months)</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="F290" s="3" t="inlineStr">
         <is>
           <t>British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr">
+      <c r="G290" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434579016</t>
         </is>
       </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="inlineStr"/>
-      <c r="J290" s="2" t="inlineStr"/>
-      <c r="K290" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L290" s="2" t="inlineStr"/>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr"/>
+      <c r="J290" s="3" t="inlineStr"/>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="inlineStr">
+      <c r="A291" s="3" t="inlineStr">
         <is>
           <t>9110f57e8050482a4d0c9e741c87522f204da76c1362e1befd9c0534580b9cbb</t>
         </is>
       </c>
-      <c r="B291" s="2" t="inlineStr">
+      <c r="B291" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C291" s="2" t="inlineStr">
+      <c r="C291" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D291" s="2" t="inlineStr">
+      <c r="D291" s="3" t="inlineStr">
         <is>
           <t>Thurber Engineering Ltd.</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr">
+      <c r="E291" s="3" t="inlineStr">
         <is>
           <t>Geotechnical Engineering Intern (2026070892)</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr">
+      <c r="F291" s="3" t="inlineStr">
         <is>
           <t>Oakville, ON, CA</t>
         </is>
       </c>
-      <c r="G291" s="2" t="inlineStr">
+      <c r="G291" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=4c79c3e285e1dbfa</t>
         </is>
       </c>
-      <c r="H291" s="2" t="inlineStr">
+      <c r="H291" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I291" s="2" t="inlineStr">
+      <c r="I291" s="3" t="inlineStr">
         <is>
           <t>### **Overview**
 Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Oakville, St. Catharines, or Pickering, Ontario**.
 Thurber provides geotechnical, environmental and construction materials engineering and testing services for a va</t>
         </is>
       </c>
-      <c r="J291" s="2" t="inlineStr"/>
-      <c r="K291" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L291" s="2" t="inlineStr"/>
+      <c r="J291" s="3" t="inlineStr"/>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L291" s="3" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="inlineStr">
+      <c r="A292" s="3" t="inlineStr">
         <is>
           <t>778c120a9af022ca764b4cc6e4ab8f083f22697d4d80ab6e74f060ac1b03aaff</t>
         </is>
       </c>
-      <c r="B292" s="2" t="inlineStr">
+      <c r="B292" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
+      <c r="C292" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="D292" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E292" s="2" t="inlineStr">
+      <c r="E292" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F292" s="2" t="inlineStr">
+      <c r="F292" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G292" s="2" t="inlineStr">
+      <c r="G292" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434563710</t>
         </is>
       </c>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I292" s="2" t="inlineStr"/>
-      <c r="J292" s="2" t="inlineStr"/>
-      <c r="K292" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L292" s="2" t="inlineStr"/>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr"/>
+      <c r="J292" s="3" t="inlineStr"/>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="inlineStr">
+      <c r="A293" s="3" t="inlineStr">
         <is>
           <t>69b454b356b58b35355954a0cd77e5b83c4c9c4f75b747f618dc1b9d8f13bc8f</t>
         </is>
       </c>
-      <c r="B293" s="2" t="inlineStr">
+      <c r="B293" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr">
+      <c r="C293" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D293" s="2" t="inlineStr">
+      <c r="D293" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E293" s="2" t="inlineStr">
+      <c r="E293" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F293" s="2" t="inlineStr">
+      <c r="F293" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr">
+      <c r="G293" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434575094</t>
         </is>
       </c>
-      <c r="H293" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I293" s="2" t="inlineStr"/>
-      <c r="J293" s="2" t="inlineStr"/>
-      <c r="K293" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L293" s="2" t="inlineStr"/>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr"/>
+      <c r="J293" s="3" t="inlineStr"/>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="inlineStr">
+      <c r="A294" s="3" t="inlineStr">
         <is>
           <t>8382c30dbe8d38d6487c59958337efe9bff2f7e27e26860fbf1377ae05061ab4</t>
         </is>
       </c>
-      <c r="B294" s="2" t="inlineStr">
+      <c r="B294" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr">
+      <c r="C294" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D294" s="2" t="inlineStr">
+      <c r="D294" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E294" s="2" t="inlineStr">
+      <c r="E294" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F294" s="2" t="inlineStr">
+      <c r="F294" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr">
+      <c r="G294" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=513f1e45241c21d6</t>
         </is>
       </c>
-      <c r="H294" s="2" t="inlineStr">
+      <c r="H294" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I294" s="2" t="inlineStr">
+      <c r="I294" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J294" s="2" t="inlineStr"/>
-      <c r="K294" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L294" s="2" t="inlineStr"/>
+      <c r="J294" s="3" t="inlineStr"/>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>9ba3e29a7776f4fbdb684114e07145521f52b1785f807148a3b4ab6389c224d3</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>ABS Dubai</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Intern - AI Software Engineering</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437462667</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr"/>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>3706306fda77a32cbc274750aa3b9daa2ff5da0fa26734507f3d2851abf0672e</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Humber College</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Energy Engineer</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Etobicoke, ON, CA</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3dfe6d1ba91629d6</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>**Energy Engineer \- CDFM \- FT Admin**
+ \- (36365\) **Find Your Spot at Humber**
+At Humber, we are a vibrant, diverse community of professionals dedicated to providing an exceptional learning experience for our students. Through our strategic vision and exciting new brand Builders of Brilliance</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>e5929e6309cd61e54c8584e922e694f99a48f19779bcd9ed3474857686935e48</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 12months)</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=ca556c1712cc9d03</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012380
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Administration \&amp; Facilities
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr"/>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>a692e824b02d3ef799aeeee2636f682f3a63b19090964167b36d6a8b2fe37d0e</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Synopsys Inc</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Internship (Fall 2026 Co-op)</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438196426</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>fd99e3dde9364b4e5ab5fcd013bd9ba1e42250f593e5498bf21ca5e0f794c0d9</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Firmware Engineering</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437827854</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>f138a87681d701e38eea99ef87863df52f3bd546839121d2611e88b80ffe42d2</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>CARFAX Canada</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Developer, Co-op</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>London, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434317793</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr"/>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>8cf4f54423ff5db249aeae361a52bcf316998bfe13af78a04c7ac50106df26e6</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Planitar Inc.</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Internal Efficiency</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437838896</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr"/>
+      <c r="J301" s="2" t="inlineStr"/>
+      <c r="K301" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>204c16f383779ec16a38292481186fb6bd8a170eae35351f3e05f5aa39b7c4b3</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>FCC Construcción</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst (Co-op)</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437855651</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr"/>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L302" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L302"/>
+  <dimension ref="A1:L308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15866,149 +15866,149 @@
       <c r="L294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="inlineStr">
+      <c r="A295" s="3" t="inlineStr">
         <is>
           <t>9ba3e29a7776f4fbdb684114e07145521f52b1785f807148a3b4ab6389c224d3</t>
         </is>
       </c>
-      <c r="B295" s="2" t="inlineStr">
+      <c r="B295" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C295" s="2" t="inlineStr">
+      <c r="C295" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D295" s="2" t="inlineStr">
+      <c r="D295" s="3" t="inlineStr">
         <is>
           <t>ABS Dubai</t>
         </is>
       </c>
-      <c r="E295" s="2" t="inlineStr">
+      <c r="E295" s="3" t="inlineStr">
         <is>
           <t>Intern - AI Software Engineering</t>
         </is>
       </c>
-      <c r="F295" s="2" t="inlineStr"/>
-      <c r="G295" s="2" t="inlineStr">
+      <c r="F295" s="3" t="inlineStr"/>
+      <c r="G295" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437462667</t>
         </is>
       </c>
-      <c r="H295" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I295" s="2" t="inlineStr"/>
-      <c r="J295" s="2" t="inlineStr"/>
-      <c r="K295" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L295" s="2" t="inlineStr"/>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr"/>
+      <c r="J295" s="3" t="inlineStr"/>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="inlineStr">
+      <c r="A296" s="3" t="inlineStr">
         <is>
           <t>3706306fda77a32cbc274750aa3b9daa2ff5da0fa26734507f3d2851abf0672e</t>
         </is>
       </c>
-      <c r="B296" s="2" t="inlineStr">
+      <c r="B296" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
+      <c r="C296" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D296" s="2" t="inlineStr">
+      <c r="D296" s="3" t="inlineStr">
         <is>
           <t>Humber College</t>
         </is>
       </c>
-      <c r="E296" s="2" t="inlineStr">
+      <c r="E296" s="3" t="inlineStr">
         <is>
           <t>Energy Engineer</t>
         </is>
       </c>
-      <c r="F296" s="2" t="inlineStr">
+      <c r="F296" s="3" t="inlineStr">
         <is>
           <t>Etobicoke, ON, CA</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr">
+      <c r="G296" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3dfe6d1ba91629d6</t>
         </is>
       </c>
-      <c r="H296" s="2" t="inlineStr">
+      <c r="H296" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I296" s="2" t="inlineStr">
+      <c r="I296" s="3" t="inlineStr">
         <is>
           <t>**Energy Engineer \- CDFM \- FT Admin**
  \- (36365\) **Find Your Spot at Humber**
 At Humber, we are a vibrant, diverse community of professionals dedicated to providing an exceptional learning experience for our students. Through our strategic vision and exciting new brand Builders of Brilliance</t>
         </is>
       </c>
-      <c r="J296" s="2" t="inlineStr"/>
-      <c r="K296" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L296" s="2" t="inlineStr"/>
+      <c r="J296" s="3" t="inlineStr"/>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
+      <c r="A297" s="3" t="inlineStr">
         <is>
           <t>e5929e6309cd61e54c8584e922e694f99a48f19779bcd9ed3474857686935e48</t>
         </is>
       </c>
-      <c r="B297" s="2" t="inlineStr">
+      <c r="B297" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr">
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr">
+      <c r="D297" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E297" s="2" t="inlineStr">
+      <c r="E297" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 12months)</t>
         </is>
       </c>
-      <c r="F297" s="2" t="inlineStr">
+      <c r="F297" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr">
+      <c r="G297" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=ca556c1712cc9d03</t>
         </is>
       </c>
-      <c r="H297" s="2" t="inlineStr">
+      <c r="H297" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I297" s="2" t="inlineStr">
+      <c r="I297" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -16028,263 +16028,573 @@
 A career at Hitachi Rail will help create a</t>
         </is>
       </c>
-      <c r="J297" s="2" t="inlineStr"/>
-      <c r="K297" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L297" s="2" t="inlineStr"/>
+      <c r="J297" s="3" t="inlineStr"/>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="inlineStr">
+      <c r="A298" s="3" t="inlineStr">
         <is>
           <t>a692e824b02d3ef799aeeee2636f682f3a63b19090964167b36d6a8b2fe37d0e</t>
         </is>
       </c>
-      <c r="B298" s="2" t="inlineStr">
+      <c r="B298" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C298" s="2" t="inlineStr">
+      <c r="C298" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D298" s="2" t="inlineStr">
+      <c r="D298" s="3" t="inlineStr">
         <is>
           <t>Synopsys Inc</t>
         </is>
       </c>
-      <c r="E298" s="2" t="inlineStr">
+      <c r="E298" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Internship (Fall 2026 Co-op)</t>
         </is>
       </c>
-      <c r="F298" s="2" t="inlineStr">
+      <c r="F298" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr">
+      <c r="G298" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438196426</t>
         </is>
       </c>
-      <c r="H298" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I298" s="2" t="inlineStr"/>
-      <c r="J298" s="2" t="inlineStr"/>
-      <c r="K298" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L298" s="2" t="inlineStr"/>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr"/>
+      <c r="J298" s="3" t="inlineStr"/>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L298" s="3" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="inlineStr">
+      <c r="A299" s="3" t="inlineStr">
         <is>
           <t>fd99e3dde9364b4e5ab5fcd013bd9ba1e42250f593e5498bf21ca5e0f794c0d9</t>
         </is>
       </c>
-      <c r="B299" s="2" t="inlineStr">
+      <c r="B299" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
+      <c r="C299" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D299" s="2" t="inlineStr">
+      <c r="D299" s="3" t="inlineStr">
         <is>
           <t>Rockwell Automation</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="E299" s="3" t="inlineStr">
         <is>
           <t>Intern, Firmware Engineering</t>
         </is>
       </c>
-      <c r="F299" s="2" t="inlineStr">
+      <c r="F299" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G299" s="2" t="inlineStr">
+      <c r="G299" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437827854</t>
         </is>
       </c>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr"/>
-      <c r="J299" s="2" t="inlineStr"/>
-      <c r="K299" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L299" s="2" t="inlineStr"/>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr"/>
+      <c r="J299" s="3" t="inlineStr"/>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L299" s="3" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="inlineStr">
+      <c r="A300" s="3" t="inlineStr">
         <is>
           <t>f138a87681d701e38eea99ef87863df52f3bd546839121d2611e88b80ffe42d2</t>
         </is>
       </c>
-      <c r="B300" s="2" t="inlineStr">
+      <c r="B300" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C300" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="D300" s="3" t="inlineStr">
         <is>
           <t>CARFAX Canada</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E300" s="3" t="inlineStr">
         <is>
           <t>Developer, Co-op</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr">
+      <c r="F300" s="3" t="inlineStr">
         <is>
           <t>London, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr">
+      <c r="G300" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434317793</t>
         </is>
       </c>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr"/>
-      <c r="J300" s="2" t="inlineStr"/>
-      <c r="K300" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L300" s="2" t="inlineStr"/>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr"/>
+      <c r="J300" s="3" t="inlineStr"/>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="inlineStr">
+      <c r="A301" s="3" t="inlineStr">
         <is>
           <t>8cf4f54423ff5db249aeae361a52bcf316998bfe13af78a04c7ac50106df26e6</t>
         </is>
       </c>
-      <c r="B301" s="2" t="inlineStr">
+      <c r="B301" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
+      <c r="C301" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="D301" s="3" t="inlineStr">
         <is>
           <t>Planitar Inc.</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E301" s="3" t="inlineStr">
         <is>
           <t>Full Stack Engineer, Internal Efficiency</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr">
+      <c r="F301" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G301" s="2" t="inlineStr">
+      <c r="G301" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437838896</t>
         </is>
       </c>
-      <c r="H301" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I301" s="2" t="inlineStr"/>
-      <c r="J301" s="2" t="inlineStr"/>
-      <c r="K301" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L301" s="2" t="inlineStr"/>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr"/>
+      <c r="J301" s="3" t="inlineStr"/>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L301" s="3" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
+      <c r="A302" s="3" t="inlineStr">
         <is>
           <t>204c16f383779ec16a38292481186fb6bd8a170eae35351f3e05f5aa39b7c4b3</t>
         </is>
       </c>
-      <c r="B302" s="2" t="inlineStr">
+      <c r="B302" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
+      <c r="C302" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D302" s="2" t="inlineStr">
+      <c r="D302" s="3" t="inlineStr">
         <is>
           <t>FCC Construcción</t>
         </is>
       </c>
-      <c r="E302" s="2" t="inlineStr">
+      <c r="E302" s="3" t="inlineStr">
         <is>
           <t>Data Analyst (Co-op)</t>
         </is>
       </c>
-      <c r="F302" s="2" t="inlineStr">
+      <c r="F302" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr">
+      <c r="G302" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437855651</t>
         </is>
       </c>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr"/>
-      <c r="J302" s="2" t="inlineStr"/>
-      <c r="K302" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L302" s="2" t="inlineStr"/>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr"/>
+      <c r="J302" s="3" t="inlineStr"/>
+      <c r="K302" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L302" s="3" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>efc3f38b31c5f40e131566846aa8f2e63ea31a020add8d8fa090f52f2c04f9d5</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>OLG</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Front End Developer Student</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437315708</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr"/>
+      <c r="J303" s="2" t="inlineStr"/>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>9959f56813f52812497aebf64244bf11813c52b2c3124ae8422d7651574a47a0</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate  Co-op Student – Software Engineer – Large Molecule Discovery - Technology</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438247234</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr"/>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>0ba86004b4b2b36bce46d353fe82a441170d7060ec5ce25d81577609b55d2400</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437303852</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr"/>
+      <c r="J305" s="2" t="inlineStr"/>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>50cb97526e9c8598ce44b9e4e280e5362ed5640a8201669a0d882dfce7df050a</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>OLG</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Front End Developer Student</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Sault Ste. Marie, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437322492</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr"/>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>f73eb072d7292a64d5d7acff066204aed7809b8d82c8401fefc57877e0196ee4</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Systems Business Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1ccb0e4b13084ef8</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>bab502dae7821c9dc8f2a594a77c4e3430ad8a38c61afe90f0c6de7998e9c926</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Systems Business Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7fd95462624553a2</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L308" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L308"/>
+  <dimension ref="A1:L314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16287,314 +16287,622 @@
       <c r="L302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
+      <c r="A303" s="3" t="inlineStr">
         <is>
           <t>efc3f38b31c5f40e131566846aa8f2e63ea31a020add8d8fa090f52f2c04f9d5</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
+      <c r="B303" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C303" s="2" t="inlineStr">
+      <c r="C303" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D303" s="2" t="inlineStr">
+      <c r="D303" s="3" t="inlineStr">
         <is>
           <t>OLG</t>
         </is>
       </c>
-      <c r="E303" s="2" t="inlineStr">
+      <c r="E303" s="3" t="inlineStr">
         <is>
           <t>Front End Developer Student</t>
         </is>
       </c>
-      <c r="F303" s="2" t="inlineStr">
+      <c r="F303" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G303" s="2" t="inlineStr">
+      <c r="G303" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437315708</t>
         </is>
       </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I303" s="2" t="inlineStr"/>
-      <c r="J303" s="2" t="inlineStr"/>
-      <c r="K303" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L303" s="2" t="inlineStr"/>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr"/>
+      <c r="J303" s="3" t="inlineStr"/>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
+      <c r="A304" s="3" t="inlineStr">
         <is>
           <t>9959f56813f52812497aebf64244bf11813c52b2c3124ae8422d7651574a47a0</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
+      <c r="C304" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D304" s="2" t="inlineStr">
+      <c r="D304" s="3" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E304" s="3" t="inlineStr">
         <is>
           <t>Undergraduate  Co-op Student – Software Engineer – Large Molecule Discovery - Technology</t>
         </is>
       </c>
-      <c r="F304" s="2" t="inlineStr">
+      <c r="F304" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G304" s="2" t="inlineStr">
+      <c r="G304" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438247234</t>
         </is>
       </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr"/>
-      <c r="J304" s="2" t="inlineStr"/>
-      <c r="K304" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L304" s="2" t="inlineStr"/>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr"/>
+      <c r="J304" s="3" t="inlineStr"/>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
+      <c r="A305" s="3" t="inlineStr">
         <is>
           <t>0ba86004b4b2b36bce46d353fe82a441170d7060ec5ce25d81577609b55d2400</t>
         </is>
       </c>
-      <c r="B305" s="2" t="inlineStr">
+      <c r="B305" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
+      <c r="C305" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D305" s="2" t="inlineStr">
+      <c r="D305" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E305" s="2" t="inlineStr">
+      <c r="E305" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F305" s="2" t="inlineStr">
+      <c r="F305" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G305" s="2" t="inlineStr">
+      <c r="G305" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437303852</t>
         </is>
       </c>
-      <c r="H305" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr"/>
-      <c r="J305" s="2" t="inlineStr"/>
-      <c r="K305" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L305" s="2" t="inlineStr"/>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr"/>
+      <c r="J305" s="3" t="inlineStr"/>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
+      <c r="A306" s="3" t="inlineStr">
         <is>
           <t>50cb97526e9c8598ce44b9e4e280e5362ed5640a8201669a0d882dfce7df050a</t>
         </is>
       </c>
-      <c r="B306" s="2" t="inlineStr">
+      <c r="B306" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
+      <c r="C306" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D306" s="2" t="inlineStr">
+      <c r="D306" s="3" t="inlineStr">
         <is>
           <t>OLG</t>
         </is>
       </c>
-      <c r="E306" s="2" t="inlineStr">
+      <c r="E306" s="3" t="inlineStr">
         <is>
           <t>Front End Developer Student</t>
         </is>
       </c>
-      <c r="F306" s="2" t="inlineStr">
+      <c r="F306" s="3" t="inlineStr">
         <is>
           <t>Sault Ste. Marie, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G306" s="2" t="inlineStr">
+      <c r="G306" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437322492</t>
         </is>
       </c>
-      <c r="H306" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr"/>
-      <c r="J306" s="2" t="inlineStr"/>
-      <c r="K306" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L306" s="2" t="inlineStr"/>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr"/>
+      <c r="J306" s="3" t="inlineStr"/>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L306" s="3" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
+      <c r="A307" s="3" t="inlineStr">
         <is>
           <t>f73eb072d7292a64d5d7acff066204aed7809b8d82c8401fefc57877e0196ee4</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
+      <c r="B307" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
+      <c r="C307" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D307" s="2" t="inlineStr">
+      <c r="D307" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E307" s="2" t="inlineStr">
+      <c r="E307" s="3" t="inlineStr">
         <is>
           <t>Systems Business Analyst Intern</t>
         </is>
       </c>
-      <c r="F307" s="2" t="inlineStr">
+      <c r="F307" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G307" s="2" t="inlineStr">
+      <c r="G307" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1ccb0e4b13084ef8</t>
         </is>
       </c>
-      <c r="H307" s="2" t="inlineStr">
+      <c r="H307" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I307" s="2" t="inlineStr">
+      <c r="I307" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J307" s="2" t="inlineStr"/>
-      <c r="K307" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L307" s="2" t="inlineStr"/>
+      <c r="J307" s="3" t="inlineStr"/>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
+      <c r="A308" s="3" t="inlineStr">
         <is>
           <t>bab502dae7821c9dc8f2a594a77c4e3430ad8a38c61afe90f0c6de7998e9c926</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
+      <c r="B308" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C308" s="2" t="inlineStr">
+      <c r="C308" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D308" s="2" t="inlineStr">
+      <c r="D308" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E308" s="2" t="inlineStr">
+      <c r="E308" s="3" t="inlineStr">
         <is>
           <t>Systems Business Analyst Intern</t>
         </is>
       </c>
-      <c r="F308" s="2" t="inlineStr">
+      <c r="F308" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G308" s="2" t="inlineStr">
+      <c r="G308" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7fd95462624553a2</t>
         </is>
       </c>
-      <c r="H308" s="2" t="inlineStr">
+      <c r="H308" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I308" s="2" t="inlineStr">
+      <c r="I308" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J308" s="2" t="inlineStr"/>
-      <c r="K308" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L308" s="2" t="inlineStr"/>
+      <c r="J308" s="3" t="inlineStr"/>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L308" s="3" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2466ac71e0b4d483b31f2a408649ebe00d02dd815b27f16061a507b7dbc12683</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Eclipse Automation</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438558850</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr"/>
+      <c r="J309" s="2" t="inlineStr"/>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>d33e75d292ab9531dd2e69aa43726d65e27b20c398e7f572fedaa158c435539c</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>OLG</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist Student</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437084273</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr"/>
+      <c r="J310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>acd21634bb8af7c82fa87947636750f3c963f0c59e066b506925ff533c846f59</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Agile Tester, Co-op, September 2026 - September 2027</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435739747</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr"/>
+      <c r="J311" s="2" t="inlineStr"/>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>3b2c25bf43b4bb3f419e12bbdd2963b57fceacac9b3996501fe56a0a789354ef</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern - CD1</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=272908ff96fd8ca0</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>- **Intern** **Associate Engineer \- Cloud**
+Location: Kanata, ON
+**ABOUT WIND RIVER**
+Within the Wind River Cloud team, we work with large\-scale projects including Kubernetes, Docker, OpenStack and fast\-paced Open\-Source technologies that are in high demand from our customers.
+Wind River C</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>1830da221f02f06bc7d9550a8fa52907ef941326edf3e802bae95a9cfb42cef1</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437383499</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr"/>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>f9821550dd51b1b88b74ff903b8fdbef2f511e8ec253a712252a1d133c06b044</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>PMP SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMMING SOFTWARE INTERN</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Québec, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437772079</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr"/>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L314"/>
+  <dimension ref="A1:L319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16597,197 +16597,197 @@
       <c r="L308" s="3" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="inlineStr">
+      <c r="A309" s="3" t="inlineStr">
         <is>
           <t>2466ac71e0b4d483b31f2a408649ebe00d02dd815b27f16061a507b7dbc12683</t>
         </is>
       </c>
-      <c r="B309" s="2" t="inlineStr">
+      <c r="B309" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
+      <c r="C309" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D309" s="2" t="inlineStr">
+      <c r="D309" s="3" t="inlineStr">
         <is>
           <t>Eclipse Automation</t>
         </is>
       </c>
-      <c r="E309" s="2" t="inlineStr">
+      <c r="E309" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op</t>
         </is>
       </c>
-      <c r="F309" s="2" t="inlineStr">
+      <c r="F309" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G309" s="2" t="inlineStr">
+      <c r="G309" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438558850</t>
         </is>
       </c>
-      <c r="H309" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr"/>
-      <c r="J309" s="2" t="inlineStr"/>
-      <c r="K309" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L309" s="2" t="inlineStr"/>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr"/>
+      <c r="J309" s="3" t="inlineStr"/>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="inlineStr">
+      <c r="A310" s="3" t="inlineStr">
         <is>
           <t>d33e75d292ab9531dd2e69aa43726d65e27b20c398e7f572fedaa158c435539c</t>
         </is>
       </c>
-      <c r="B310" s="2" t="inlineStr">
+      <c r="B310" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C310" s="2" t="inlineStr">
+      <c r="C310" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D310" s="2" t="inlineStr">
+      <c r="D310" s="3" t="inlineStr">
         <is>
           <t>OLG</t>
         </is>
       </c>
-      <c r="E310" s="2" t="inlineStr">
+      <c r="E310" s="3" t="inlineStr">
         <is>
           <t>Data Scientist Student</t>
         </is>
       </c>
-      <c r="F310" s="2" t="inlineStr">
+      <c r="F310" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr">
+      <c r="G310" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437084273</t>
         </is>
       </c>
-      <c r="H310" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I310" s="2" t="inlineStr"/>
-      <c r="J310" s="2" t="inlineStr"/>
-      <c r="K310" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L310" s="2" t="inlineStr"/>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr"/>
+      <c r="J310" s="3" t="inlineStr"/>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L310" s="3" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="inlineStr">
+      <c r="A311" s="3" t="inlineStr">
         <is>
           <t>acd21634bb8af7c82fa87947636750f3c963f0c59e066b506925ff533c846f59</t>
         </is>
       </c>
-      <c r="B311" s="2" t="inlineStr">
+      <c r="B311" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C311" s="2" t="inlineStr">
+      <c r="C311" s="3" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="D311" s="2" t="inlineStr">
+      <c r="D311" s="3" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="E311" s="2" t="inlineStr">
+      <c r="E311" s="3" t="inlineStr">
         <is>
           <t>Agile Tester, Co-op, September 2026 - September 2027</t>
         </is>
       </c>
-      <c r="F311" s="2" t="inlineStr">
+      <c r="F311" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr">
+      <c r="G311" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435739747</t>
         </is>
       </c>
-      <c r="H311" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I311" s="2" t="inlineStr"/>
-      <c r="J311" s="2" t="inlineStr"/>
-      <c r="K311" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L311" s="2" t="inlineStr"/>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I311" s="3" t="inlineStr"/>
+      <c r="J311" s="3" t="inlineStr"/>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="inlineStr">
+      <c r="A312" s="3" t="inlineStr">
         <is>
           <t>3b2c25bf43b4bb3f419e12bbdd2963b57fceacac9b3996501fe56a0a789354ef</t>
         </is>
       </c>
-      <c r="B312" s="2" t="inlineStr">
+      <c r="B312" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C312" s="2" t="inlineStr">
+      <c r="C312" s="3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D312" s="2" t="inlineStr">
+      <c r="D312" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E312" s="2" t="inlineStr">
+      <c r="E312" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern - CD1</t>
         </is>
       </c>
-      <c r="F312" s="2" t="inlineStr">
+      <c r="F312" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G312" s="2" t="inlineStr">
+      <c r="G312" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=272908ff96fd8ca0</t>
         </is>
       </c>
-      <c r="H312" s="2" t="inlineStr">
+      <c r="H312" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I312" s="2" t="inlineStr">
+      <c r="I312" s="3" t="inlineStr">
         <is>
           <t>- **Intern** **Associate Engineer \- Cloud**
 Location: Kanata, ON
@@ -16796,113 +16796,369 @@
 Wind River C</t>
         </is>
       </c>
-      <c r="J312" s="2" t="inlineStr"/>
-      <c r="K312" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L312" s="2" t="inlineStr"/>
+      <c r="J312" s="3" t="inlineStr"/>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L312" s="3" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="inlineStr">
+      <c r="A313" s="3" t="inlineStr">
         <is>
           <t>1830da221f02f06bc7d9550a8fa52907ef941326edf3e802bae95a9cfb42cef1</t>
         </is>
       </c>
-      <c r="B313" s="2" t="inlineStr">
+      <c r="B313" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C313" s="2" t="inlineStr">
+      <c r="C313" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D313" s="2" t="inlineStr">
+      <c r="D313" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E313" s="2" t="inlineStr">
+      <c r="E313" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer</t>
         </is>
       </c>
-      <c r="F313" s="2" t="inlineStr">
+      <c r="F313" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr">
+      <c r="G313" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437383499</t>
         </is>
       </c>
-      <c r="H313" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I313" s="2" t="inlineStr"/>
-      <c r="J313" s="2" t="inlineStr"/>
-      <c r="K313" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L313" s="2" t="inlineStr"/>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I313" s="3" t="inlineStr"/>
+      <c r="J313" s="3" t="inlineStr"/>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L313" s="3" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="inlineStr">
+      <c r="A314" s="3" t="inlineStr">
         <is>
           <t>f9821550dd51b1b88b74ff903b8fdbef2f511e8ec253a712252a1d133c06b044</t>
         </is>
       </c>
-      <c r="B314" s="2" t="inlineStr">
+      <c r="B314" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
+      <c r="C314" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D314" s="2" t="inlineStr">
+      <c r="D314" s="3" t="inlineStr">
         <is>
           <t>PMP SOLUTIONS</t>
         </is>
       </c>
-      <c r="E314" s="2" t="inlineStr">
+      <c r="E314" s="3" t="inlineStr">
         <is>
           <t>PROGRAMMING SOFTWARE INTERN</t>
         </is>
       </c>
-      <c r="F314" s="2" t="inlineStr">
+      <c r="F314" s="3" t="inlineStr">
         <is>
           <t>Québec, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G314" s="2" t="inlineStr">
+      <c r="G314" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437772079</t>
         </is>
       </c>
-      <c r="H314" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I314" s="2" t="inlineStr"/>
-      <c r="J314" s="2" t="inlineStr"/>
-      <c r="K314" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L314" s="2" t="inlineStr"/>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr"/>
+      <c r="J314" s="3" t="inlineStr"/>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>ae6bf5d8c949b930c72e44f9e6d01a246c45de25e118530a0fcd87938b49e79d</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (React + Node/NestJS + Agentic Development)</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438816757</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr"/>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>d98c35cb679e5474254adc4733901b847e1187d51b9774fecbf327d47fdc565b</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>CGI</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Fall 2026: WiSE AI Developer Co-op (12 months)</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438568207</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr"/>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>5edbbff4ac4a459db81c333452c2e567587c7a5087f2bba975c00dcf19a39f82</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Stryker</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Graduate Intern, Systems R&amp;D</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, BC, CA</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=84812111726226da</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>### **Why join Stryker?**
+Looking for a place that values your unique talents? Discover Stryker's award\-winning culture.  
+We are proud to offer you our total rewards package which includes bonuses, healthcare, insurance benefits, retirement programs, wellness programs, as well as service and pe</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>8e35e3f25f8a6125a95e233776b028fd9a8468f896b61f47a2b7f87a480dbd2c</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern - CD1</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438883102</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr"/>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>36a9dae3ad43123e74a1a5f86718b80e43ce144a6021538be34e54ad65d54bd2</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Rodan Energy Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Data Science - Co-op Student</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436627074</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr"/>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L319"/>
+  <dimension ref="A1:L322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16905,260 +16905,415 @@
       <c r="L314" s="3" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="inlineStr">
+      <c r="A315" s="3" t="inlineStr">
         <is>
           <t>ae6bf5d8c949b930c72e44f9e6d01a246c45de25e118530a0fcd87938b49e79d</t>
         </is>
       </c>
-      <c r="B315" s="2" t="inlineStr">
+      <c r="B315" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C315" s="2" t="inlineStr">
+      <c r="C315" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D315" s="2" t="inlineStr">
+      <c r="D315" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E315" s="2" t="inlineStr">
+      <c r="E315" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (React + Node/NestJS + Agentic Development)</t>
         </is>
       </c>
-      <c r="F315" s="2" t="inlineStr">
+      <c r="F315" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G315" s="2" t="inlineStr">
+      <c r="G315" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438816757</t>
         </is>
       </c>
-      <c r="H315" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I315" s="2" t="inlineStr"/>
-      <c r="J315" s="2" t="inlineStr"/>
-      <c r="K315" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L315" s="2" t="inlineStr"/>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I315" s="3" t="inlineStr"/>
+      <c r="J315" s="3" t="inlineStr"/>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="inlineStr">
+      <c r="A316" s="3" t="inlineStr">
         <is>
           <t>d98c35cb679e5474254adc4733901b847e1187d51b9774fecbf327d47fdc565b</t>
         </is>
       </c>
-      <c r="B316" s="2" t="inlineStr">
+      <c r="B316" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
+      <c r="C316" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D316" s="2" t="inlineStr">
+      <c r="D316" s="3" t="inlineStr">
         <is>
           <t>CGI</t>
         </is>
       </c>
-      <c r="E316" s="2" t="inlineStr">
+      <c r="E316" s="3" t="inlineStr">
         <is>
           <t>Fall 2026: WiSE AI Developer Co-op (12 months)</t>
         </is>
       </c>
-      <c r="F316" s="2" t="inlineStr">
+      <c r="F316" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G316" s="2" t="inlineStr">
+      <c r="G316" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438568207</t>
         </is>
       </c>
-      <c r="H316" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I316" s="2" t="inlineStr"/>
-      <c r="J316" s="2" t="inlineStr"/>
-      <c r="K316" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L316" s="2" t="inlineStr"/>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr"/>
+      <c r="J316" s="3" t="inlineStr"/>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L316" s="3" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="inlineStr">
+      <c r="A317" s="3" t="inlineStr">
         <is>
           <t>5edbbff4ac4a459db81c333452c2e567587c7a5087f2bba975c00dcf19a39f82</t>
         </is>
       </c>
-      <c r="B317" s="2" t="inlineStr">
+      <c r="B317" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C317" s="2" t="inlineStr">
+      <c r="C317" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D317" s="2" t="inlineStr">
+      <c r="D317" s="3" t="inlineStr">
         <is>
           <t>Stryker</t>
         </is>
       </c>
-      <c r="E317" s="2" t="inlineStr">
+      <c r="E317" s="3" t="inlineStr">
         <is>
           <t>Graduate Intern, Systems R&amp;D</t>
         </is>
       </c>
-      <c r="F317" s="2" t="inlineStr">
+      <c r="F317" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G317" s="2" t="inlineStr">
+      <c r="G317" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=84812111726226da</t>
         </is>
       </c>
-      <c r="H317" s="2" t="inlineStr">
+      <c r="H317" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I317" s="2" t="inlineStr">
+      <c r="I317" s="3" t="inlineStr">
         <is>
           <t>### **Why join Stryker?**
 Looking for a place that values your unique talents? Discover Stryker's award\-winning culture.  
 We are proud to offer you our total rewards package which includes bonuses, healthcare, insurance benefits, retirement programs, wellness programs, as well as service and pe</t>
         </is>
       </c>
-      <c r="J317" s="2" t="inlineStr"/>
-      <c r="K317" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L317" s="2" t="inlineStr"/>
+      <c r="J317" s="3" t="inlineStr"/>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L317" s="3" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="inlineStr">
+      <c r="A318" s="3" t="inlineStr">
         <is>
           <t>8e35e3f25f8a6125a95e233776b028fd9a8468f896b61f47a2b7f87a480dbd2c</t>
         </is>
       </c>
-      <c r="B318" s="2" t="inlineStr">
+      <c r="B318" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C318" s="2" t="inlineStr">
+      <c r="C318" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D318" s="2" t="inlineStr">
+      <c r="D318" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E318" s="2" t="inlineStr">
+      <c r="E318" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern - CD1</t>
         </is>
       </c>
-      <c r="F318" s="2" t="inlineStr">
+      <c r="F318" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G318" s="2" t="inlineStr">
+      <c r="G318" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438883102</t>
         </is>
       </c>
-      <c r="H318" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I318" s="2" t="inlineStr"/>
-      <c r="J318" s="2" t="inlineStr"/>
-      <c r="K318" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L318" s="2" t="inlineStr"/>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr"/>
+      <c r="J318" s="3" t="inlineStr"/>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L318" s="3" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="inlineStr">
+      <c r="A319" s="3" t="inlineStr">
         <is>
           <t>36a9dae3ad43123e74a1a5f86718b80e43ce144a6021538be34e54ad65d54bd2</t>
         </is>
       </c>
-      <c r="B319" s="2" t="inlineStr">
+      <c r="B319" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C319" s="2" t="inlineStr">
+      <c r="C319" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D319" s="2" t="inlineStr">
+      <c r="D319" s="3" t="inlineStr">
         <is>
           <t>Rodan Energy Solutions Inc.</t>
         </is>
       </c>
-      <c r="E319" s="2" t="inlineStr">
+      <c r="E319" s="3" t="inlineStr">
         <is>
           <t>Data Science - Co-op Student</t>
         </is>
       </c>
-      <c r="F319" s="2" t="inlineStr">
+      <c r="F319" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G319" s="2" t="inlineStr">
+      <c r="G319" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436627074</t>
         </is>
       </c>
-      <c r="H319" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I319" s="2" t="inlineStr"/>
-      <c r="J319" s="2" t="inlineStr"/>
-      <c r="K319" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L319" s="2" t="inlineStr"/>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr"/>
+      <c r="J319" s="3" t="inlineStr"/>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>ddfd710515f2eaf9a3d67e04bbe686805145012fe3c858ec6a806530ec0953a6</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Parsons</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Digital Innovation Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=635a5e7a697b0a2c</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>In a world of possibilities, pursue one with endless opportunities. Imagine Next!  
+At Parsons, you can imagine a career where you thrive, work with exceptional people, and be yourself. Guided by our leadership vision of valuing people, embracing agility, and fostering growth, we cultivate an inno</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>6554459ceb52e8f8c35e3800ffd0eb55978de2d5cad4b3eb3f1013a0faedda7c</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Q-Block Computing</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Systems Developer Intern</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439029520</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr"/>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>a7cd271c3744215809ce5a941d863435421bc9b2aab321ef8d6c124d54214020</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Business Intelligence co-op</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436870305</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr"/>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L322"/>
+  <dimension ref="A1:L323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17161,159 +17161,209 @@
       <c r="L319" s="3" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="inlineStr">
+      <c r="A320" s="3" t="inlineStr">
         <is>
           <t>ddfd710515f2eaf9a3d67e04bbe686805145012fe3c858ec6a806530ec0953a6</t>
         </is>
       </c>
-      <c r="B320" s="2" t="inlineStr">
+      <c r="B320" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C320" s="2" t="inlineStr">
+      <c r="C320" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D320" s="2" t="inlineStr">
+      <c r="D320" s="3" t="inlineStr">
         <is>
           <t>Parsons</t>
         </is>
       </c>
-      <c r="E320" s="2" t="inlineStr">
+      <c r="E320" s="3" t="inlineStr">
         <is>
           <t>AI &amp; Digital Innovation Engineering Intern</t>
         </is>
       </c>
-      <c r="F320" s="2" t="inlineStr">
+      <c r="F320" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G320" s="2" t="inlineStr">
+      <c r="G320" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=635a5e7a697b0a2c</t>
         </is>
       </c>
-      <c r="H320" s="2" t="inlineStr">
+      <c r="H320" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I320" s="2" t="inlineStr">
+      <c r="I320" s="3" t="inlineStr">
         <is>
           <t>In a world of possibilities, pursue one with endless opportunities. Imagine Next!  
 At Parsons, you can imagine a career where you thrive, work with exceptional people, and be yourself. Guided by our leadership vision of valuing people, embracing agility, and fostering growth, we cultivate an inno</t>
         </is>
       </c>
-      <c r="J320" s="2" t="inlineStr"/>
-      <c r="K320" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L320" s="2" t="inlineStr"/>
+      <c r="J320" s="3" t="inlineStr"/>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="inlineStr">
+      <c r="A321" s="3" t="inlineStr">
         <is>
           <t>6554459ceb52e8f8c35e3800ffd0eb55978de2d5cad4b3eb3f1013a0faedda7c</t>
         </is>
       </c>
-      <c r="B321" s="2" t="inlineStr">
+      <c r="B321" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
+      <c r="C321" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D321" s="2" t="inlineStr">
+      <c r="D321" s="3" t="inlineStr">
         <is>
           <t>Q-Block Computing</t>
         </is>
       </c>
-      <c r="E321" s="2" t="inlineStr">
+      <c r="E321" s="3" t="inlineStr">
         <is>
           <t>Embedded Systems Developer Intern</t>
         </is>
       </c>
-      <c r="F321" s="2" t="inlineStr">
+      <c r="F321" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G321" s="2" t="inlineStr">
+      <c r="G321" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439029520</t>
         </is>
       </c>
-      <c r="H321" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I321" s="2" t="inlineStr"/>
-      <c r="J321" s="2" t="inlineStr"/>
-      <c r="K321" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L321" s="2" t="inlineStr"/>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr"/>
+      <c r="J321" s="3" t="inlineStr"/>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="inlineStr">
+      <c r="A322" s="3" t="inlineStr">
         <is>
           <t>a7cd271c3744215809ce5a941d863435421bc9b2aab321ef8d6c124d54214020</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
+      <c r="B322" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
+      <c r="C322" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D322" s="2" t="inlineStr">
+      <c r="D322" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E322" s="2" t="inlineStr">
+      <c r="E322" s="3" t="inlineStr">
         <is>
           <t>Business Intelligence co-op</t>
         </is>
       </c>
-      <c r="F322" s="2" t="inlineStr">
+      <c r="F322" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G322" s="2" t="inlineStr">
+      <c r="G322" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436870305</t>
         </is>
       </c>
-      <c r="H322" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I322" s="2" t="inlineStr"/>
-      <c r="J322" s="2" t="inlineStr"/>
-      <c r="K322" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L322" s="2" t="inlineStr"/>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I322" s="3" t="inlineStr"/>
+      <c r="J322" s="3" t="inlineStr"/>
+      <c r="K322" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L322" s="3" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>0402b35805c8f719d85ad26188991bc0348c374987e380e97c022c89381b0b49</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Calgary Airports</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Corporate Services &amp; IT Student (12 Months Term)</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439352103</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr"/>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L323"/>
+  <dimension ref="A1:L328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17316,54 +17316,305 @@
       <c r="L322" s="3" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="inlineStr">
+      <c r="A323" s="3" t="inlineStr">
         <is>
           <t>0402b35805c8f719d85ad26188991bc0348c374987e380e97c022c89381b0b49</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
+      <c r="B323" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
+      <c r="C323" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr">
+      <c r="D323" s="3" t="inlineStr">
         <is>
           <t>Calgary Airports</t>
         </is>
       </c>
-      <c r="E323" s="2" t="inlineStr">
+      <c r="E323" s="3" t="inlineStr">
         <is>
           <t>Co-op, Corporate Services &amp; IT Student (12 Months Term)</t>
         </is>
       </c>
-      <c r="F323" s="2" t="inlineStr">
+      <c r="F323" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G323" s="2" t="inlineStr">
+      <c r="G323" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439352103</t>
         </is>
       </c>
-      <c r="H323" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I323" s="2" t="inlineStr"/>
-      <c r="J323" s="2" t="inlineStr"/>
-      <c r="K323" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L323" s="2" t="inlineStr"/>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I323" s="3" t="inlineStr"/>
+      <c r="J323" s="3" t="inlineStr"/>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>b2417b6476264a4db7df56f7c35f6593f48dfccc8a337cf1171cb288e16e4a12</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Automation AI ML for Open RAN CoOp</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436549137</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr"/>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>891e3c7b50a8b83b66e1bf83173dd761d4431612ebdc6c76f271ffda76f41a6b</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer - AI Agent for Data</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433875740</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr"/>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>48b98020ab0bd9c0ac421dd49327e99cb67f5915a4f5d5ff86805337c9a79c99</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>NEXTIN LABS (formerly ForAll A Tech)</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Laravel Web Developer
+Full-Time Internship</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Regional Municipality of York, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439088147</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr"/>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>a1aa4a68e466cc3782cfe1b57e88d9d9e940d49ef5987a2e4cfc69010aff6ca8</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Data Governance Analyst Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439319081</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr"/>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>c6eadae06f07ae7f5c820e579100b92d007a672e7ef3f5c31f81afb2fef54d6f</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>PCL Construction</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Predictive Analytics &amp; Strategy Student</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Oakville, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438830197</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr"/>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L328"/>
+  <dimension ref="A1:L333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17366,255 +17366,501 @@
       <c r="L323" s="3" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="inlineStr">
+      <c r="A324" s="3" t="inlineStr">
         <is>
           <t>b2417b6476264a4db7df56f7c35f6593f48dfccc8a337cf1171cb288e16e4a12</t>
         </is>
       </c>
-      <c r="B324" s="2" t="inlineStr">
+      <c r="B324" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C324" s="2" t="inlineStr">
+      <c r="C324" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D324" s="2" t="inlineStr">
+      <c r="D324" s="3" t="inlineStr">
         <is>
           <t>Ericsson</t>
         </is>
       </c>
-      <c r="E324" s="2" t="inlineStr">
+      <c r="E324" s="3" t="inlineStr">
         <is>
           <t>Automation AI ML for Open RAN CoOp</t>
         </is>
       </c>
-      <c r="F324" s="2" t="inlineStr">
+      <c r="F324" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G324" s="2" t="inlineStr">
+      <c r="G324" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436549137</t>
         </is>
       </c>
-      <c r="H324" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I324" s="2" t="inlineStr"/>
-      <c r="J324" s="2" t="inlineStr"/>
-      <c r="K324" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L324" s="2" t="inlineStr"/>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="inlineStr"/>
+      <c r="J324" s="3" t="inlineStr"/>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="inlineStr">
+      <c r="A325" s="3" t="inlineStr">
         <is>
           <t>891e3c7b50a8b83b66e1bf83173dd761d4431612ebdc6c76f271ffda76f41a6b</t>
         </is>
       </c>
-      <c r="B325" s="2" t="inlineStr">
+      <c r="B325" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C325" s="2" t="inlineStr">
+      <c r="C325" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D325" s="2" t="inlineStr">
+      <c r="D325" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E325" s="2" t="inlineStr">
+      <c r="E325" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer - AI Agent for Data</t>
         </is>
       </c>
-      <c r="F325" s="2" t="inlineStr">
+      <c r="F325" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G325" s="2" t="inlineStr">
+      <c r="G325" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433875740</t>
         </is>
       </c>
-      <c r="H325" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I325" s="2" t="inlineStr"/>
-      <c r="J325" s="2" t="inlineStr"/>
-      <c r="K325" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L325" s="2" t="inlineStr"/>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I325" s="3" t="inlineStr"/>
+      <c r="J325" s="3" t="inlineStr"/>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="inlineStr">
+      <c r="A326" s="3" t="inlineStr">
         <is>
           <t>48b98020ab0bd9c0ac421dd49327e99cb67f5915a4f5d5ff86805337c9a79c99</t>
         </is>
       </c>
-      <c r="B326" s="2" t="inlineStr">
+      <c r="B326" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
+      <c r="C326" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr">
+      <c r="D326" s="3" t="inlineStr">
         <is>
           <t>NEXTIN LABS (formerly ForAll A Tech)</t>
         </is>
       </c>
-      <c r="E326" s="2" t="inlineStr">
+      <c r="E326" s="3" t="inlineStr">
         <is>
           <t>Full Stack Laravel Web Developer
 Full-Time Internship</t>
         </is>
       </c>
-      <c r="F326" s="2" t="inlineStr">
+      <c r="F326" s="3" t="inlineStr">
         <is>
           <t>Regional Municipality of York, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G326" s="2" t="inlineStr">
+      <c r="G326" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439088147</t>
         </is>
       </c>
-      <c r="H326" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I326" s="2" t="inlineStr"/>
-      <c r="J326" s="2" t="inlineStr"/>
-      <c r="K326" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L326" s="2" t="inlineStr"/>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="inlineStr"/>
+      <c r="J326" s="3" t="inlineStr"/>
+      <c r="K326" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="inlineStr">
+      <c r="A327" s="3" t="inlineStr">
         <is>
           <t>a1aa4a68e466cc3782cfe1b57e88d9d9e940d49ef5987a2e4cfc69010aff6ca8</t>
         </is>
       </c>
-      <c r="B327" s="2" t="inlineStr">
+      <c r="B327" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C327" s="2" t="inlineStr">
+      <c r="C327" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D327" s="2" t="inlineStr">
+      <c r="D327" s="3" t="inlineStr">
         <is>
           <t>McKesson</t>
         </is>
       </c>
-      <c r="E327" s="2" t="inlineStr">
+      <c r="E327" s="3" t="inlineStr">
         <is>
           <t>Data Governance Analyst Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F327" s="2" t="inlineStr">
+      <c r="F327" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G327" s="2" t="inlineStr">
+      <c r="G327" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439319081</t>
         </is>
       </c>
-      <c r="H327" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I327" s="2" t="inlineStr"/>
-      <c r="J327" s="2" t="inlineStr"/>
-      <c r="K327" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L327" s="2" t="inlineStr"/>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I327" s="3" t="inlineStr"/>
+      <c r="J327" s="3" t="inlineStr"/>
+      <c r="K327" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L327" s="3" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="inlineStr">
+      <c r="A328" s="3" t="inlineStr">
         <is>
           <t>c6eadae06f07ae7f5c820e579100b92d007a672e7ef3f5c31f81afb2fef54d6f</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
+      <c r="B328" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
+      <c r="C328" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D328" s="2" t="inlineStr">
+      <c r="D328" s="3" t="inlineStr">
         <is>
           <t>PCL Construction</t>
         </is>
       </c>
-      <c r="E328" s="2" t="inlineStr">
+      <c r="E328" s="3" t="inlineStr">
         <is>
           <t>Predictive Analytics &amp; Strategy Student</t>
         </is>
       </c>
-      <c r="F328" s="2" t="inlineStr">
+      <c r="F328" s="3" t="inlineStr">
         <is>
           <t>Oakville, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G328" s="2" t="inlineStr">
+      <c r="G328" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438830197</t>
         </is>
       </c>
-      <c r="H328" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I328" s="2" t="inlineStr"/>
-      <c r="J328" s="2" t="inlineStr"/>
-      <c r="K328" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L328" s="2" t="inlineStr"/>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I328" s="3" t="inlineStr"/>
+      <c r="J328" s="3" t="inlineStr"/>
+      <c r="K328" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L328" s="3" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>55b93e7e35729575fc0e5333e76f39e282a3b29dbb51c8dc7bb20c55614c4353</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>BNP Paribas</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>AI Data Scientist Intern – Fall 2026</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4409626072</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr"/>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>c43a03adf510cbff18fb12c3731beeaa5622b485b461f72b0b6c6a61524355be</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>ada CX</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437496054</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr"/>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>302f87a2b30b027e14f72e9a44b190e8003d458bc45558d3baa0c3fcbdf51935</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Aircraft Systems Research &amp; Technology - Software Engineering (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Dorval, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4422453738</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr"/>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>646f4a91401e60eb0c440c6eda7f60ac0b8eb686e77fe93907b04691a0d64b93</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Multimatic</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Application Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>East Gwillimbury, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439359158</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr"/>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>fb4f7a88fb2f88c03c4bfdfef3d02deb19169022703ad392b17693dc3ecd8931</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Engineer - AI4Research</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436902552</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr"/>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L333"/>
+  <dimension ref="A1:L335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17617,250 +17617,350 @@
       <c r="L328" s="3" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="inlineStr">
+      <c r="A329" s="3" t="inlineStr">
         <is>
           <t>55b93e7e35729575fc0e5333e76f39e282a3b29dbb51c8dc7bb20c55614c4353</t>
         </is>
       </c>
-      <c r="B329" s="2" t="inlineStr">
+      <c r="B329" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
+      <c r="C329" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D329" s="2" t="inlineStr">
+      <c r="D329" s="3" t="inlineStr">
         <is>
           <t>BNP Paribas</t>
         </is>
       </c>
-      <c r="E329" s="2" t="inlineStr">
+      <c r="E329" s="3" t="inlineStr">
         <is>
           <t>AI Data Scientist Intern – Fall 2026</t>
         </is>
       </c>
-      <c r="F329" s="2" t="inlineStr">
+      <c r="F329" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G329" s="2" t="inlineStr">
+      <c r="G329" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4409626072</t>
         </is>
       </c>
-      <c r="H329" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I329" s="2" t="inlineStr"/>
-      <c r="J329" s="2" t="inlineStr"/>
-      <c r="K329" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L329" s="2" t="inlineStr"/>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I329" s="3" t="inlineStr"/>
+      <c r="J329" s="3" t="inlineStr"/>
+      <c r="K329" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L329" s="3" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="inlineStr">
+      <c r="A330" s="3" t="inlineStr">
         <is>
           <t>c43a03adf510cbff18fb12c3731beeaa5622b485b461f72b0b6c6a61524355be</t>
         </is>
       </c>
-      <c r="B330" s="2" t="inlineStr">
+      <c r="B330" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
+      <c r="C330" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D330" s="2" t="inlineStr">
+      <c r="D330" s="3" t="inlineStr">
         <is>
           <t>ada CX</t>
         </is>
       </c>
-      <c r="E330" s="2" t="inlineStr">
+      <c r="E330" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern</t>
         </is>
       </c>
-      <c r="F330" s="2" t="inlineStr"/>
-      <c r="G330" s="2" t="inlineStr">
+      <c r="F330" s="3" t="inlineStr"/>
+      <c r="G330" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437496054</t>
         </is>
       </c>
-      <c r="H330" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I330" s="2" t="inlineStr"/>
-      <c r="J330" s="2" t="inlineStr"/>
-      <c r="K330" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L330" s="2" t="inlineStr"/>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I330" s="3" t="inlineStr"/>
+      <c r="J330" s="3" t="inlineStr"/>
+      <c r="K330" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L330" s="3" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="inlineStr">
+      <c r="A331" s="3" t="inlineStr">
         <is>
           <t>302f87a2b30b027e14f72e9a44b190e8003d458bc45558d3baa0c3fcbdf51935</t>
         </is>
       </c>
-      <c r="B331" s="2" t="inlineStr">
+      <c r="B331" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
+      <c r="C331" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D331" s="2" t="inlineStr">
+      <c r="D331" s="3" t="inlineStr">
         <is>
           <t>Bombardier</t>
         </is>
       </c>
-      <c r="E331" s="2" t="inlineStr">
+      <c r="E331" s="3" t="inlineStr">
         <is>
           <t>Intern, Aircraft Systems Research &amp; Technology - Software Engineering (Fall 2026)</t>
         </is>
       </c>
-      <c r="F331" s="2" t="inlineStr">
+      <c r="F331" s="3" t="inlineStr">
         <is>
           <t>Dorval, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G331" s="2" t="inlineStr">
+      <c r="G331" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4422453738</t>
         </is>
       </c>
-      <c r="H331" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I331" s="2" t="inlineStr"/>
-      <c r="J331" s="2" t="inlineStr"/>
-      <c r="K331" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L331" s="2" t="inlineStr"/>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I331" s="3" t="inlineStr"/>
+      <c r="J331" s="3" t="inlineStr"/>
+      <c r="K331" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L331" s="3" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
+      <c r="A332" s="3" t="inlineStr">
         <is>
           <t>646f4a91401e60eb0c440c6eda7f60ac0b8eb686e77fe93907b04691a0d64b93</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
+      <c r="B332" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
+      <c r="C332" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D332" s="2" t="inlineStr">
+      <c r="D332" s="3" t="inlineStr">
         <is>
           <t>Multimatic</t>
         </is>
       </c>
-      <c r="E332" s="2" t="inlineStr">
+      <c r="E332" s="3" t="inlineStr">
         <is>
           <t>Application Engineering Co-op</t>
         </is>
       </c>
-      <c r="F332" s="2" t="inlineStr">
+      <c r="F332" s="3" t="inlineStr">
         <is>
           <t>East Gwillimbury, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G332" s="2" t="inlineStr">
+      <c r="G332" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439359158</t>
         </is>
       </c>
-      <c r="H332" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I332" s="2" t="inlineStr"/>
-      <c r="J332" s="2" t="inlineStr"/>
-      <c r="K332" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L332" s="2" t="inlineStr"/>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I332" s="3" t="inlineStr"/>
+      <c r="J332" s="3" t="inlineStr"/>
+      <c r="K332" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L332" s="3" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="inlineStr">
+      <c r="A333" s="3" t="inlineStr">
         <is>
           <t>fb4f7a88fb2f88c03c4bfdfef3d02deb19169022703ad392b17693dc3ecd8931</t>
         </is>
       </c>
-      <c r="B333" s="2" t="inlineStr">
+      <c r="B333" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C333" s="2" t="inlineStr">
+      <c r="C333" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D333" s="2" t="inlineStr">
+      <c r="D333" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E333" s="2" t="inlineStr">
+      <c r="E333" s="3" t="inlineStr">
         <is>
           <t>Co-op Engineer - AI4Research</t>
         </is>
       </c>
-      <c r="F333" s="2" t="inlineStr">
+      <c r="F333" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G333" s="2" t="inlineStr">
+      <c r="G333" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436902552</t>
         </is>
       </c>
-      <c r="H333" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I333" s="2" t="inlineStr"/>
-      <c r="J333" s="2" t="inlineStr"/>
-      <c r="K333" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L333" s="2" t="inlineStr"/>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I333" s="3" t="inlineStr"/>
+      <c r="J333" s="3" t="inlineStr"/>
+      <c r="K333" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>62ca582e48b4cf202a7894759d4563dbf8829d4d81a989eb072034010d1042a0</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>CGI</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Fall 2026: WiSE Developer Co-op (8 month)</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438565317</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr"/>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>62d891a62eb82a43f48f9fe6eb66b377efd618f4d6f815a46cea2bdc9e6bb3e6</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Definity</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Reporting Specialist - Fall 2026 Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429186286</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr"/>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L335"/>
+  <dimension ref="A1:L339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17863,104 +17863,312 @@
       <c r="L333" s="3" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="inlineStr">
+      <c r="A334" s="3" t="inlineStr">
         <is>
           <t>62ca582e48b4cf202a7894759d4563dbf8829d4d81a989eb072034010d1042a0</t>
         </is>
       </c>
-      <c r="B334" s="2" t="inlineStr">
+      <c r="B334" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C334" s="2" t="inlineStr">
+      <c r="C334" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D334" s="2" t="inlineStr">
+      <c r="D334" s="3" t="inlineStr">
         <is>
           <t>CGI</t>
         </is>
       </c>
-      <c r="E334" s="2" t="inlineStr">
+      <c r="E334" s="3" t="inlineStr">
         <is>
           <t>Fall 2026: WiSE Developer Co-op (8 month)</t>
         </is>
       </c>
-      <c r="F334" s="2" t="inlineStr">
+      <c r="F334" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G334" s="2" t="inlineStr">
+      <c r="G334" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438565317</t>
         </is>
       </c>
-      <c r="H334" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I334" s="2" t="inlineStr"/>
-      <c r="J334" s="2" t="inlineStr"/>
-      <c r="K334" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L334" s="2" t="inlineStr"/>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I334" s="3" t="inlineStr"/>
+      <c r="J334" s="3" t="inlineStr"/>
+      <c r="K334" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L334" s="3" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="inlineStr">
+      <c r="A335" s="3" t="inlineStr">
         <is>
           <t>62d891a62eb82a43f48f9fe6eb66b377efd618f4d6f815a46cea2bdc9e6bb3e6</t>
         </is>
       </c>
-      <c r="B335" s="2" t="inlineStr">
+      <c r="B335" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C335" s="2" t="inlineStr">
+      <c r="C335" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D335" s="2" t="inlineStr">
+      <c r="D335" s="3" t="inlineStr">
         <is>
           <t>Definity</t>
         </is>
       </c>
-      <c r="E335" s="2" t="inlineStr">
+      <c r="E335" s="3" t="inlineStr">
         <is>
           <t>Reporting Specialist - Fall 2026 Co-op/Intern</t>
         </is>
       </c>
-      <c r="F335" s="2" t="inlineStr">
+      <c r="F335" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G335" s="2" t="inlineStr">
+      <c r="G335" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429186286</t>
         </is>
       </c>
-      <c r="H335" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I335" s="2" t="inlineStr"/>
-      <c r="J335" s="2" t="inlineStr"/>
-      <c r="K335" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L335" s="2" t="inlineStr"/>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I335" s="3" t="inlineStr"/>
+      <c r="J335" s="3" t="inlineStr"/>
+      <c r="K335" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L335" s="3" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>b818dc0f08121d35254f9a08bfa6b518fea30c5e60cd76be439f5f6a587f1582</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5799879390?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2498f4490e00a0e94dff6b346ab965e71cd5860fae6212a1939c46d11d07278b</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5799881034?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>59d5bec967c6bb693c5b727e9bb68de9583691d5fec4d098a8229bade366f07a</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Marvell Technology</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Design Verification Engineer Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427369140</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr"/>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>1678cc7662caba09b83824d5104ac6da806f2973ae7fc90d3a0b50d2edc663e4</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>House of Commons of Canada Chambre des communes du Canada</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Students - Various Positions</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4350836087</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr"/>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L339" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L339"/>
+  <dimension ref="A1:L349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17963,212 +17963,744 @@
       <c r="L335" s="3" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="inlineStr">
+      <c r="A336" s="3" t="inlineStr">
         <is>
           <t>b818dc0f08121d35254f9a08bfa6b518fea30c5e60cd76be439f5f6a587f1582</t>
         </is>
       </c>
-      <c r="B336" s="2" t="inlineStr">
+      <c r="B336" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C336" s="2" t="inlineStr">
+      <c r="C336" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D336" s="2" t="inlineStr">
+      <c r="D336" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E336" s="2" t="inlineStr">
+      <c r="E336" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F336" s="2" t="inlineStr">
+      <c r="F336" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G336" s="2" t="inlineStr">
+      <c r="G336" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5799879390?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H336" s="2" t="inlineStr">
+      <c r="H336" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I336" s="2" t="inlineStr">
+      <c r="I336" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
         </is>
       </c>
-      <c r="J336" s="2" t="inlineStr"/>
-      <c r="K336" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L336" s="2" t="inlineStr"/>
+      <c r="J336" s="3" t="inlineStr"/>
+      <c r="K336" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L336" s="3" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="inlineStr">
+      <c r="A337" s="3" t="inlineStr">
         <is>
           <t>2498f4490e00a0e94dff6b346ab965e71cd5860fae6212a1939c46d11d07278b</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
+      <c r="B337" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
+      <c r="C337" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr">
+      <c r="D337" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E337" s="2" t="inlineStr">
+      <c r="E337" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F337" s="2" t="inlineStr">
+      <c r="F337" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G337" s="2" t="inlineStr">
+      <c r="G337" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5799881034?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H337" s="2" t="inlineStr">
+      <c r="H337" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I337" s="2" t="inlineStr">
+      <c r="I337" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
         </is>
       </c>
-      <c r="J337" s="2" t="inlineStr"/>
-      <c r="K337" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L337" s="2" t="inlineStr"/>
+      <c r="J337" s="3" t="inlineStr"/>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L337" s="3" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="inlineStr">
+      <c r="A338" s="3" t="inlineStr">
         <is>
           <t>59d5bec967c6bb693c5b727e9bb68de9583691d5fec4d098a8229bade366f07a</t>
         </is>
       </c>
-      <c r="B338" s="2" t="inlineStr">
+      <c r="B338" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C338" s="2" t="inlineStr">
+      <c r="C338" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D338" s="2" t="inlineStr">
+      <c r="D338" s="3" t="inlineStr">
         <is>
           <t>Marvell Technology</t>
         </is>
       </c>
-      <c r="E338" s="2" t="inlineStr">
+      <c r="E338" s="3" t="inlineStr">
         <is>
           <t>Design Verification Engineer Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F338" s="2" t="inlineStr">
+      <c r="F338" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G338" s="2" t="inlineStr">
+      <c r="G338" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427369140</t>
         </is>
       </c>
-      <c r="H338" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I338" s="2" t="inlineStr"/>
-      <c r="J338" s="2" t="inlineStr"/>
-      <c r="K338" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L338" s="2" t="inlineStr"/>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr"/>
+      <c r="J338" s="3" t="inlineStr"/>
+      <c r="K338" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L338" s="3" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="inlineStr">
+      <c r="A339" s="3" t="inlineStr">
         <is>
           <t>1678cc7662caba09b83824d5104ac6da806f2973ae7fc90d3a0b50d2edc663e4</t>
         </is>
       </c>
-      <c r="B339" s="2" t="inlineStr">
+      <c r="B339" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C339" s="2" t="inlineStr">
+      <c r="C339" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D339" s="2" t="inlineStr">
+      <c r="D339" s="3" t="inlineStr">
         <is>
           <t>House of Commons of Canada Chambre des communes du Canada</t>
         </is>
       </c>
-      <c r="E339" s="2" t="inlineStr">
+      <c r="E339" s="3" t="inlineStr">
         <is>
           <t>Co-op Students - Various Positions</t>
         </is>
       </c>
-      <c r="F339" s="2" t="inlineStr">
+      <c r="F339" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G339" s="2" t="inlineStr">
+      <c r="G339" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4350836087</t>
         </is>
       </c>
-      <c r="H339" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I339" s="2" t="inlineStr"/>
-      <c r="J339" s="2" t="inlineStr"/>
-      <c r="K339" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L339" s="2" t="inlineStr"/>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I339" s="3" t="inlineStr"/>
+      <c r="J339" s="3" t="inlineStr"/>
+      <c r="K339" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L339" s="3" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2c148fba7ffd8f7876dc7ddc04851f39b2ae224390ae0427c93b9f669759b11f</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Business Web Solutions</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer Intern - Remote</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Park, Calgary</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5800148553?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>This is a remote position. Job Overview We are hiring Full Stack Web Developer Interns who are passionate about learning and applying modern web development skills. This remote internship, available for 1 to 6 months, provides hands-on experience through live projects and mentorship from industry pr</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>e58d13c1c30372b208727df9492464ba9538bb6a77c3eee7f5ee2cf215b63d47</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Business Web Solutions</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Web Development Intern / Trainee - Remote</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Dalhousie Ward, Ottawa</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5800148554?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>This is a remote position. Job Overview We are seeking motivated candidates for Web Development Intern / Trainee to provide hands-on exposure to real-world web projects. This internship program runs for 1 to 6 months, depending on your availability, and focuses on building practical skills in modern</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>98967e22b9ddaa516b5db5e1f4b2ddcab858048bb233b75f89e9f1d233c7e8fe</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Java)</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=fd06376834c767a8</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>c00de0812d18f46083567f0453a989eaa6b19eab5283e0a4d2a0421edfe49b9d</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Java)</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=4d10b14108506048</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L343" s="2" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>38383cd26118f760a6ed848abd772ac9421515b0effd63653b21bdcc6efca70f</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440069507</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr"/>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>182f973ee093ead211312b6070b8d98bcf2e76292704459255b6e062ad67cdaf</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>DRW</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437615263</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr"/>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>db50a8ec1fe13767b0e0f61de74fbe24ae9bec0bbfe232f8333baf9bb834e82d</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>De Havilland Aircraft of Canada Ltd</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Weights Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, ON, CA</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=19cf80242e70e60f</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>De Havilland Aircraft of Canada Limited (DHC) is a storied name in the aerospace industry, recognized worldwide for its pioneering contributions to aviation and its unwavering commitment to quality, innovation, and reliability. Headquartered in Calgary, AB, DHC currently has approximately 2,400 empl</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>1d7d38b38af64c6713217750ed54046a6d27b6b5e195daa27a134ea451d75672</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Maple Leaf Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7a912eb423bae936</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>**Powered by Passion. United by Purpose. Build for Impact.**
+At Maple Leaf Sports \&amp; Entertainment Partnership (MLSE), we exist to deliver the ultimate fan experience by lifting trophies, spirits, and communities – united as one.
+We're more than a workplace. We are a team of passionate peo</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>56fa9f87d4db309e9bea79bebe47a391f2a6f6d0682a48534875f812b42a4e51</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Engineer- Distributed Agent System</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440053849</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr"/>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>b336b018571dc3319874d6073f310c30cf5c008765941e38d52b549bc32b2378</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>De Havilland Aircraft of Canada Ltd</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Project Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, ON, CA</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7ecc63ab47134871</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>De Havilland Aircraft of Canada Limited (DHC) is a storied name in the aerospace industry, recognized worldwide for its pioneering contributions to aviation and its unwavering commitment to quality, innovation, and reliability. Headquartered in Calgary, AB, DHC currently has approximately 2,400 empl</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L349"/>
+  <dimension ref="A1:L352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18171,536 +18171,686 @@
       <c r="L339" s="3" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="inlineStr">
+      <c r="A340" s="3" t="inlineStr">
         <is>
           <t>2c148fba7ffd8f7876dc7ddc04851f39b2ae224390ae0427c93b9f669759b11f</t>
         </is>
       </c>
-      <c r="B340" s="2" t="inlineStr">
+      <c r="B340" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C340" s="2" t="inlineStr">
+      <c r="C340" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D340" s="2" t="inlineStr">
+      <c r="D340" s="3" t="inlineStr">
         <is>
           <t>Business Web Solutions</t>
         </is>
       </c>
-      <c r="E340" s="2" t="inlineStr">
+      <c r="E340" s="3" t="inlineStr">
         <is>
           <t>Full Stack Web Developer Intern - Remote</t>
         </is>
       </c>
-      <c r="F340" s="2" t="inlineStr">
+      <c r="F340" s="3" t="inlineStr">
         <is>
           <t>Victoria Park, Calgary</t>
         </is>
       </c>
-      <c r="G340" s="2" t="inlineStr">
+      <c r="G340" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5800148553?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H340" s="2" t="inlineStr">
+      <c r="H340" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I340" s="2" t="inlineStr">
+      <c r="I340" s="3" t="inlineStr">
         <is>
           <t>This is a remote position. Job Overview We are hiring Full Stack Web Developer Interns who are passionate about learning and applying modern web development skills. This remote internship, available for 1 to 6 months, provides hands-on experience through live projects and mentorship from industry pr</t>
         </is>
       </c>
-      <c r="J340" s="2" t="inlineStr"/>
-      <c r="K340" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L340" s="2" t="inlineStr"/>
+      <c r="J340" s="3" t="inlineStr"/>
+      <c r="K340" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L340" s="3" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="inlineStr">
+      <c r="A341" s="3" t="inlineStr">
         <is>
           <t>e58d13c1c30372b208727df9492464ba9538bb6a77c3eee7f5ee2cf215b63d47</t>
         </is>
       </c>
-      <c r="B341" s="2" t="inlineStr">
+      <c r="B341" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C341" s="2" t="inlineStr">
+      <c r="C341" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr">
+      <c r="D341" s="3" t="inlineStr">
         <is>
           <t>Business Web Solutions</t>
         </is>
       </c>
-      <c r="E341" s="2" t="inlineStr">
+      <c r="E341" s="3" t="inlineStr">
         <is>
           <t>Web Development Intern / Trainee - Remote</t>
         </is>
       </c>
-      <c r="F341" s="2" t="inlineStr">
+      <c r="F341" s="3" t="inlineStr">
         <is>
           <t>Dalhousie Ward, Ottawa</t>
         </is>
       </c>
-      <c r="G341" s="2" t="inlineStr">
+      <c r="G341" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5800148554?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H341" s="2" t="inlineStr">
+      <c r="H341" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I341" s="2" t="inlineStr">
+      <c r="I341" s="3" t="inlineStr">
         <is>
           <t>This is a remote position. Job Overview We are seeking motivated candidates for Web Development Intern / Trainee to provide hands-on exposure to real-world web projects. This internship program runs for 1 to 6 months, depending on your availability, and focuses on building practical skills in modern</t>
         </is>
       </c>
-      <c r="J341" s="2" t="inlineStr"/>
-      <c r="K341" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L341" s="2" t="inlineStr"/>
+      <c r="J341" s="3" t="inlineStr"/>
+      <c r="K341" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L341" s="3" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="inlineStr">
+      <c r="A342" s="3" t="inlineStr">
         <is>
           <t>98967e22b9ddaa516b5db5e1f4b2ddcab858048bb233b75f89e9f1d233c7e8fe</t>
         </is>
       </c>
-      <c r="B342" s="2" t="inlineStr">
+      <c r="B342" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C342" s="2" t="inlineStr">
+      <c r="C342" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D342" s="2" t="inlineStr">
+      <c r="D342" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E342" s="2" t="inlineStr">
+      <c r="E342" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern (Java)</t>
         </is>
       </c>
-      <c r="F342" s="2" t="inlineStr">
+      <c r="F342" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G342" s="2" t="inlineStr">
+      <c r="G342" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=fd06376834c767a8</t>
         </is>
       </c>
-      <c r="H342" s="2" t="inlineStr">
+      <c r="H342" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I342" s="2" t="inlineStr">
+      <c r="I342" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J342" s="2" t="inlineStr"/>
-      <c r="K342" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L342" s="2" t="inlineStr"/>
+      <c r="J342" s="3" t="inlineStr"/>
+      <c r="K342" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L342" s="3" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="inlineStr">
+      <c r="A343" s="3" t="inlineStr">
         <is>
           <t>c00de0812d18f46083567f0453a989eaa6b19eab5283e0a4d2a0421edfe49b9d</t>
         </is>
       </c>
-      <c r="B343" s="2" t="inlineStr">
+      <c r="B343" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C343" s="2" t="inlineStr">
+      <c r="C343" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D343" s="2" t="inlineStr">
+      <c r="D343" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E343" s="2" t="inlineStr">
+      <c r="E343" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern (Java)</t>
         </is>
       </c>
-      <c r="F343" s="2" t="inlineStr">
+      <c r="F343" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G343" s="2" t="inlineStr">
+      <c r="G343" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=4d10b14108506048</t>
         </is>
       </c>
-      <c r="H343" s="2" t="inlineStr">
+      <c r="H343" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I343" s="2" t="inlineStr">
+      <c r="I343" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J343" s="2" t="inlineStr"/>
-      <c r="K343" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L343" s="2" t="inlineStr"/>
+      <c r="J343" s="3" t="inlineStr"/>
+      <c r="K343" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L343" s="3" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="inlineStr">
+      <c r="A344" s="3" t="inlineStr">
         <is>
           <t>38383cd26118f760a6ed848abd772ac9421515b0effd63653b21bdcc6efca70f</t>
         </is>
       </c>
-      <c r="B344" s="2" t="inlineStr">
+      <c r="B344" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C344" s="2" t="inlineStr">
+      <c r="C344" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D344" s="2" t="inlineStr">
+      <c r="D344" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E344" s="2" t="inlineStr">
+      <c r="E344" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F344" s="2" t="inlineStr">
+      <c r="F344" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G344" s="2" t="inlineStr">
+      <c r="G344" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440069507</t>
         </is>
       </c>
-      <c r="H344" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I344" s="2" t="inlineStr"/>
-      <c r="J344" s="2" t="inlineStr"/>
-      <c r="K344" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L344" s="2" t="inlineStr"/>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I344" s="3" t="inlineStr"/>
+      <c r="J344" s="3" t="inlineStr"/>
+      <c r="K344" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L344" s="3" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="inlineStr">
+      <c r="A345" s="3" t="inlineStr">
         <is>
           <t>182f973ee093ead211312b6070b8d98bcf2e76292704459255b6e062ad67cdaf</t>
         </is>
       </c>
-      <c r="B345" s="2" t="inlineStr">
+      <c r="B345" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C345" s="2" t="inlineStr">
+      <c r="C345" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D345" s="2" t="inlineStr">
+      <c r="D345" s="3" t="inlineStr">
         <is>
           <t>DRW</t>
         </is>
       </c>
-      <c r="E345" s="2" t="inlineStr">
+      <c r="E345" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern</t>
         </is>
       </c>
-      <c r="F345" s="2" t="inlineStr">
+      <c r="F345" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G345" s="2" t="inlineStr">
+      <c r="G345" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437615263</t>
         </is>
       </c>
-      <c r="H345" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I345" s="2" t="inlineStr"/>
-      <c r="J345" s="2" t="inlineStr"/>
-      <c r="K345" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L345" s="2" t="inlineStr"/>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I345" s="3" t="inlineStr"/>
+      <c r="J345" s="3" t="inlineStr"/>
+      <c r="K345" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L345" s="3" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="inlineStr">
+      <c r="A346" s="3" t="inlineStr">
         <is>
           <t>db50a8ec1fe13767b0e0f61de74fbe24ae9bec0bbfe232f8333baf9bb834e82d</t>
         </is>
       </c>
-      <c r="B346" s="2" t="inlineStr">
+      <c r="B346" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C346" s="2" t="inlineStr">
+      <c r="C346" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D346" s="2" t="inlineStr">
+      <c r="D346" s="3" t="inlineStr">
         <is>
           <t>De Havilland Aircraft of Canada Ltd</t>
         </is>
       </c>
-      <c r="E346" s="2" t="inlineStr">
+      <c r="E346" s="3" t="inlineStr">
         <is>
           <t>Weights Engineering Intern</t>
         </is>
       </c>
-      <c r="F346" s="2" t="inlineStr">
+      <c r="F346" s="3" t="inlineStr">
         <is>
           <t>Mississauga, ON, CA</t>
         </is>
       </c>
-      <c r="G346" s="2" t="inlineStr">
+      <c r="G346" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=19cf80242e70e60f</t>
         </is>
       </c>
-      <c r="H346" s="2" t="inlineStr">
+      <c r="H346" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I346" s="2" t="inlineStr">
+      <c r="I346" s="3" t="inlineStr">
         <is>
           <t>De Havilland Aircraft of Canada Limited (DHC) is a storied name in the aerospace industry, recognized worldwide for its pioneering contributions to aviation and its unwavering commitment to quality, innovation, and reliability. Headquartered in Calgary, AB, DHC currently has approximately 2,400 empl</t>
         </is>
       </c>
-      <c r="J346" s="2" t="inlineStr"/>
-      <c r="K346" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L346" s="2" t="inlineStr"/>
+      <c r="J346" s="3" t="inlineStr"/>
+      <c r="K346" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="inlineStr">
+      <c r="A347" s="3" t="inlineStr">
         <is>
           <t>1d7d38b38af64c6713217750ed54046a6d27b6b5e195daa27a134ea451d75672</t>
         </is>
       </c>
-      <c r="B347" s="2" t="inlineStr">
+      <c r="B347" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C347" s="2" t="inlineStr">
+      <c r="C347" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D347" s="2" t="inlineStr">
+      <c r="D347" s="3" t="inlineStr">
         <is>
           <t>Maple Leaf Sports &amp; Entertainment</t>
         </is>
       </c>
-      <c r="E347" s="2" t="inlineStr">
+      <c r="E347" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="F347" s="2" t="inlineStr">
+      <c r="F347" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G347" s="2" t="inlineStr">
+      <c r="G347" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7a912eb423bae936</t>
         </is>
       </c>
-      <c r="H347" s="2" t="inlineStr">
+      <c r="H347" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I347" s="2" t="inlineStr">
+      <c r="I347" s="3" t="inlineStr">
         <is>
           <t>**Powered by Passion. United by Purpose. Build for Impact.**
 At Maple Leaf Sports \&amp; Entertainment Partnership (MLSE), we exist to deliver the ultimate fan experience by lifting trophies, spirits, and communities – united as one.
 We're more than a workplace. We are a team of passionate peo</t>
         </is>
       </c>
-      <c r="J347" s="2" t="inlineStr"/>
-      <c r="K347" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L347" s="2" t="inlineStr"/>
+      <c r="J347" s="3" t="inlineStr"/>
+      <c r="K347" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L347" s="3" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="inlineStr">
+      <c r="A348" s="3" t="inlineStr">
         <is>
           <t>56fa9f87d4db309e9bea79bebe47a391f2a6f6d0682a48534875f812b42a4e51</t>
         </is>
       </c>
-      <c r="B348" s="2" t="inlineStr">
+      <c r="B348" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C348" s="2" t="inlineStr">
+      <c r="C348" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D348" s="2" t="inlineStr">
+      <c r="D348" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E348" s="2" t="inlineStr">
+      <c r="E348" s="3" t="inlineStr">
         <is>
           <t>Co-op Engineer- Distributed Agent System</t>
         </is>
       </c>
-      <c r="F348" s="2" t="inlineStr">
+      <c r="F348" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G348" s="2" t="inlineStr">
+      <c r="G348" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440053849</t>
         </is>
       </c>
-      <c r="H348" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I348" s="2" t="inlineStr"/>
-      <c r="J348" s="2" t="inlineStr"/>
-      <c r="K348" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L348" s="2" t="inlineStr"/>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I348" s="3" t="inlineStr"/>
+      <c r="J348" s="3" t="inlineStr"/>
+      <c r="K348" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L348" s="3" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="inlineStr">
+      <c r="A349" s="3" t="inlineStr">
         <is>
           <t>b336b018571dc3319874d6073f310c30cf5c008765941e38d52b549bc32b2378</t>
         </is>
       </c>
-      <c r="B349" s="2" t="inlineStr">
+      <c r="B349" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C349" s="2" t="inlineStr">
+      <c r="C349" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D349" s="2" t="inlineStr">
+      <c r="D349" s="3" t="inlineStr">
         <is>
           <t>De Havilland Aircraft of Canada Ltd</t>
         </is>
       </c>
-      <c r="E349" s="2" t="inlineStr">
+      <c r="E349" s="3" t="inlineStr">
         <is>
           <t>Project Engineering Intern</t>
         </is>
       </c>
-      <c r="F349" s="2" t="inlineStr">
+      <c r="F349" s="3" t="inlineStr">
         <is>
           <t>Mississauga, ON, CA</t>
         </is>
       </c>
-      <c r="G349" s="2" t="inlineStr">
+      <c r="G349" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7ecc63ab47134871</t>
         </is>
       </c>
-      <c r="H349" s="2" t="inlineStr">
+      <c r="H349" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I349" s="2" t="inlineStr">
+      <c r="I349" s="3" t="inlineStr">
         <is>
           <t>De Havilland Aircraft of Canada Limited (DHC) is a storied name in the aerospace industry, recognized worldwide for its pioneering contributions to aviation and its unwavering commitment to quality, innovation, and reliability. Headquartered in Calgary, AB, DHC currently has approximately 2,400 empl</t>
         </is>
       </c>
-      <c r="J349" s="2" t="inlineStr"/>
-      <c r="K349" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L349" s="2" t="inlineStr"/>
+      <c r="J349" s="3" t="inlineStr"/>
+      <c r="K349" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L349" s="3" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>02ba05a62fe117de796137529aa84f645935a71890e2108a1ef10c15b92a640f</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>OLG</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Technology Operations Engineering Student</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437309844</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr"/>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>642dd7fb85eee0d8a05ca9d24d6debf76e132d84511c3f098736b02c31479ba6</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Verifast</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Technical Innovation Intern/ Co-Op</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436056614</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr"/>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>1c7ac3797d8f0f66b4efb41fc99178d5a5bed2f427eff0362baaefe6aa16db05</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>SecureRx Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer / Engineer Intern (Co-op) – Fall 2026, (Healthcare SaaS) - Remote</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439492823</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr"/>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L352" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L352"/>
+  <dimension ref="A1:L363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18703,154 +18703,733 @@
       <c r="L349" s="3" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="inlineStr">
+      <c r="A350" s="3" t="inlineStr">
         <is>
           <t>02ba05a62fe117de796137529aa84f645935a71890e2108a1ef10c15b92a640f</t>
         </is>
       </c>
-      <c r="B350" s="2" t="inlineStr">
+      <c r="B350" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C350" s="2" t="inlineStr">
+      <c r="C350" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D350" s="2" t="inlineStr">
+      <c r="D350" s="3" t="inlineStr">
         <is>
           <t>OLG</t>
         </is>
       </c>
-      <c r="E350" s="2" t="inlineStr">
+      <c r="E350" s="3" t="inlineStr">
         <is>
           <t>Technology Operations Engineering Student</t>
         </is>
       </c>
-      <c r="F350" s="2" t="inlineStr">
+      <c r="F350" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G350" s="2" t="inlineStr">
+      <c r="G350" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437309844</t>
         </is>
       </c>
-      <c r="H350" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I350" s="2" t="inlineStr"/>
-      <c r="J350" s="2" t="inlineStr"/>
-      <c r="K350" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L350" s="2" t="inlineStr"/>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I350" s="3" t="inlineStr"/>
+      <c r="J350" s="3" t="inlineStr"/>
+      <c r="K350" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L350" s="3" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="inlineStr">
+      <c r="A351" s="3" t="inlineStr">
         <is>
           <t>642dd7fb85eee0d8a05ca9d24d6debf76e132d84511c3f098736b02c31479ba6</t>
         </is>
       </c>
-      <c r="B351" s="2" t="inlineStr">
+      <c r="B351" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C351" s="2" t="inlineStr">
+      <c r="C351" s="3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D351" s="2" t="inlineStr">
+      <c r="D351" s="3" t="inlineStr">
         <is>
           <t>Verifast</t>
         </is>
       </c>
-      <c r="E351" s="2" t="inlineStr">
+      <c r="E351" s="3" t="inlineStr">
         <is>
           <t>Technical Innovation Intern/ Co-Op</t>
         </is>
       </c>
-      <c r="F351" s="2" t="inlineStr">
+      <c r="F351" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G351" s="2" t="inlineStr">
+      <c r="G351" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436056614</t>
         </is>
       </c>
-      <c r="H351" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I351" s="2" t="inlineStr"/>
-      <c r="J351" s="2" t="inlineStr"/>
-      <c r="K351" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L351" s="2" t="inlineStr"/>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I351" s="3" t="inlineStr"/>
+      <c r="J351" s="3" t="inlineStr"/>
+      <c r="K351" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L351" s="3" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="inlineStr">
+      <c r="A352" s="3" t="inlineStr">
         <is>
           <t>1c7ac3797d8f0f66b4efb41fc99178d5a5bed2f427eff0362baaefe6aa16db05</t>
         </is>
       </c>
-      <c r="B352" s="2" t="inlineStr">
+      <c r="B352" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C352" s="2" t="inlineStr">
+      <c r="C352" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D352" s="2" t="inlineStr">
+      <c r="D352" s="3" t="inlineStr">
         <is>
           <t>SecureRx Technologies Inc.</t>
         </is>
       </c>
-      <c r="E352" s="2" t="inlineStr">
+      <c r="E352" s="3" t="inlineStr">
         <is>
           <t>Software Developer / Engineer Intern (Co-op) – Fall 2026, (Healthcare SaaS) - Remote</t>
         </is>
       </c>
-      <c r="F352" s="2" t="inlineStr">
+      <c r="F352" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G352" s="2" t="inlineStr">
+      <c r="G352" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439492823</t>
         </is>
       </c>
-      <c r="H352" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I352" s="2" t="inlineStr"/>
-      <c r="J352" s="2" t="inlineStr"/>
-      <c r="K352" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L352" s="2" t="inlineStr"/>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I352" s="3" t="inlineStr"/>
+      <c r="J352" s="3" t="inlineStr"/>
+      <c r="K352" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>bd7e252fbebc0f624fd2a7782846d677f5a39089ab5d6ef349d44cb2d73b0fbf</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Harbord, City of Toronto</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5801803318?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>afe4a66b20aac50fdb8cf772183887181421ac364d0c2568d0becfdb43c82374</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Harbord, City of Toronto</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5801767985?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>abccf9f1241972aa69740ba24f6cbabd7ad4f24cec622eb275f49d6c5d28f653</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Global</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Software Quality Assurance Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=af76f88610e75eb7</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>**Job Description:**
+Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>9e1215b501e32338df5fc17b2c3fe0c92f07257006f084d669cb6a28cd555d90</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Kobo</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Software Quality Assurance Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=442d17285175b527</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>**Job Description:**
+Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L356" s="2" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>b1a7ec3d9abb3c537bd300a092e35b40acd90f20638e90851492409103462ce6</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>ecobee Technologies ULC</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineering</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3fbee06b2d26dc98</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>**Hi, we are ecobee.**
+======================
+ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>9d23bdbf713245aa579bc702b3b26dd59c6b398f484b7a5df4473f8616d8c360</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Global Relay</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Co-op C# Developer - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440587508</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr"/>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>412f0fb4e0d3e8b5306482f56c0c5b0732f7ee82fd656fa4f459b755f6571085</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>TMX Group</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Java)</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439894812</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr"/>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>05623857ee6fed636d2dc7c96b7431e7ea83db1d7537aa89a0cd119a72383f06</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Disaster and Climate Resilience Co-op</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=64b5c0aeffbc0b66</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>Arcadis is the world's leading company delivering sustainable design, engineering, and consultancy solutions for natural and built assets.
+We are more than 34,000 people, in over 30 countries, dedicated to improving quality of life. Everyone has an important role to play. With the power of many c</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>b696e2670abb52d927fd48439d762a12af15d132f2970402e37146d65d4dc318</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Global Relay</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Frontend Software Developer (Information Archiving) - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440584606</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr"/>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>d0f730b02050b761833b09c75feeb398c06edae5e2884537771856b140cd939b</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Leesee</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Développeur Web ou Mobile (Stage Cégep) / Web or Mobile Developer (Cegep Internship)</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439879269</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr"/>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L362" s="2" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>b34536cba7b21243769872d1ec711478ae71ba3153736acfe8d9447a5f79a6e4</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Intern, DevSecOps (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Dorval, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438688939</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr"/>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L363" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L363"/>
+  <dimension ref="A1:L368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18853,583 +18853,850 @@
       <c r="L352" s="3" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="inlineStr">
+      <c r="A353" s="3" t="inlineStr">
         <is>
           <t>bd7e252fbebc0f624fd2a7782846d677f5a39089ab5d6ef349d44cb2d73b0fbf</t>
         </is>
       </c>
-      <c r="B353" s="2" t="inlineStr">
+      <c r="B353" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C353" s="2" t="inlineStr">
+      <c r="C353" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D353" s="2" t="inlineStr">
+      <c r="D353" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E353" s="2" t="inlineStr">
+      <c r="E353" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F353" s="2" t="inlineStr">
+      <c r="F353" s="3" t="inlineStr">
         <is>
           <t>Harbord, City of Toronto</t>
         </is>
       </c>
-      <c r="G353" s="2" t="inlineStr">
+      <c r="G353" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5801803318?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H353" s="2" t="inlineStr">
+      <c r="H353" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I353" s="2" t="inlineStr">
+      <c r="I353" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
         </is>
       </c>
-      <c r="J353" s="2" t="inlineStr"/>
-      <c r="K353" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L353" s="2" t="inlineStr"/>
+      <c r="J353" s="3" t="inlineStr"/>
+      <c r="K353" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L353" s="3" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="inlineStr">
+      <c r="A354" s="3" t="inlineStr">
         <is>
           <t>afe4a66b20aac50fdb8cf772183887181421ac364d0c2568d0becfdb43c82374</t>
         </is>
       </c>
-      <c r="B354" s="2" t="inlineStr">
+      <c r="B354" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C354" s="2" t="inlineStr">
+      <c r="C354" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D354" s="2" t="inlineStr">
+      <c r="D354" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E354" s="2" t="inlineStr">
+      <c r="E354" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F354" s="2" t="inlineStr">
+      <c r="F354" s="3" t="inlineStr">
         <is>
           <t>Harbord, City of Toronto</t>
         </is>
       </c>
-      <c r="G354" s="2" t="inlineStr">
+      <c r="G354" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5801767985?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H354" s="2" t="inlineStr">
+      <c r="H354" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I354" s="2" t="inlineStr">
+      <c r="I354" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
         </is>
       </c>
-      <c r="J354" s="2" t="inlineStr"/>
-      <c r="K354" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L354" s="2" t="inlineStr"/>
+      <c r="J354" s="3" t="inlineStr"/>
+      <c r="K354" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L354" s="3" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="inlineStr">
+      <c r="A355" s="3" t="inlineStr">
         <is>
           <t>abccf9f1241972aa69740ba24f6cbabd7ad4f24cec622eb275f49d6c5d28f653</t>
         </is>
       </c>
-      <c r="B355" s="2" t="inlineStr">
+      <c r="B355" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C355" s="2" t="inlineStr">
+      <c r="C355" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D355" s="2" t="inlineStr">
+      <c r="D355" s="3" t="inlineStr">
         <is>
           <t>Rakuten Global</t>
         </is>
       </c>
-      <c r="E355" s="2" t="inlineStr">
+      <c r="E355" s="3" t="inlineStr">
         <is>
           <t>Software Quality Assurance Engineer Co-op</t>
         </is>
       </c>
-      <c r="F355" s="2" t="inlineStr">
+      <c r="F355" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G355" s="2" t="inlineStr">
+      <c r="G355" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=af76f88610e75eb7</t>
         </is>
       </c>
-      <c r="H355" s="2" t="inlineStr">
+      <c r="H355" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I355" s="2" t="inlineStr">
+      <c r="I355" s="3" t="inlineStr">
         <is>
           <t>**Job Description:**
 Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
         </is>
       </c>
-      <c r="J355" s="2" t="inlineStr"/>
-      <c r="K355" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L355" s="2" t="inlineStr"/>
+      <c r="J355" s="3" t="inlineStr"/>
+      <c r="K355" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="inlineStr">
+      <c r="A356" s="3" t="inlineStr">
         <is>
           <t>9e1215b501e32338df5fc17b2c3fe0c92f07257006f084d669cb6a28cd555d90</t>
         </is>
       </c>
-      <c r="B356" s="2" t="inlineStr">
+      <c r="B356" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C356" s="2" t="inlineStr">
+      <c r="C356" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D356" s="2" t="inlineStr">
+      <c r="D356" s="3" t="inlineStr">
         <is>
           <t>Rakuten Kobo</t>
         </is>
       </c>
-      <c r="E356" s="2" t="inlineStr">
+      <c r="E356" s="3" t="inlineStr">
         <is>
           <t>Software Quality Assurance Engineer Co-op</t>
         </is>
       </c>
-      <c r="F356" s="2" t="inlineStr">
+      <c r="F356" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G356" s="2" t="inlineStr">
+      <c r="G356" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=442d17285175b527</t>
         </is>
       </c>
-      <c r="H356" s="2" t="inlineStr">
+      <c r="H356" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I356" s="2" t="inlineStr">
+      <c r="I356" s="3" t="inlineStr">
         <is>
           <t>**Job Description:**
 Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
         </is>
       </c>
-      <c r="J356" s="2" t="inlineStr"/>
-      <c r="K356" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L356" s="2" t="inlineStr"/>
+      <c r="J356" s="3" t="inlineStr"/>
+      <c r="K356" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L356" s="3" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="inlineStr">
+      <c r="A357" s="3" t="inlineStr">
         <is>
           <t>b1a7ec3d9abb3c537bd300a092e35b40acd90f20638e90851492409103462ce6</t>
         </is>
       </c>
-      <c r="B357" s="2" t="inlineStr">
+      <c r="B357" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C357" s="2" t="inlineStr">
+      <c r="C357" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D357" s="2" t="inlineStr">
+      <c r="D357" s="3" t="inlineStr">
         <is>
           <t>ecobee Technologies ULC</t>
         </is>
       </c>
-      <c r="E357" s="2" t="inlineStr">
+      <c r="E357" s="3" t="inlineStr">
         <is>
           <t>Intern Engineering</t>
         </is>
       </c>
-      <c r="F357" s="2" t="inlineStr">
+      <c r="F357" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G357" s="2" t="inlineStr">
+      <c r="G357" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3fbee06b2d26dc98</t>
         </is>
       </c>
-      <c r="H357" s="2" t="inlineStr">
+      <c r="H357" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I357" s="2" t="inlineStr">
+      <c r="I357" s="3" t="inlineStr">
         <is>
           <t>**Hi, we are ecobee.**
 ======================
 ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
         </is>
       </c>
-      <c r="J357" s="2" t="inlineStr"/>
-      <c r="K357" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L357" s="2" t="inlineStr"/>
+      <c r="J357" s="3" t="inlineStr"/>
+      <c r="K357" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L357" s="3" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="inlineStr">
+      <c r="A358" s="3" t="inlineStr">
         <is>
           <t>9d23bdbf713245aa579bc702b3b26dd59c6b398f484b7a5df4473f8616d8c360</t>
         </is>
       </c>
-      <c r="B358" s="2" t="inlineStr">
+      <c r="B358" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C358" s="2" t="inlineStr">
+      <c r="C358" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D358" s="2" t="inlineStr">
+      <c r="D358" s="3" t="inlineStr">
         <is>
           <t>Global Relay</t>
         </is>
       </c>
-      <c r="E358" s="2" t="inlineStr">
+      <c r="E358" s="3" t="inlineStr">
         <is>
           <t>Co-op C# Developer - Fall 2026</t>
         </is>
       </c>
-      <c r="F358" s="2" t="inlineStr">
+      <c r="F358" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G358" s="2" t="inlineStr">
+      <c r="G358" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440587508</t>
         </is>
       </c>
-      <c r="H358" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I358" s="2" t="inlineStr"/>
-      <c r="J358" s="2" t="inlineStr"/>
-      <c r="K358" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L358" s="2" t="inlineStr"/>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I358" s="3" t="inlineStr"/>
+      <c r="J358" s="3" t="inlineStr"/>
+      <c r="K358" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L358" s="3" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="inlineStr">
+      <c r="A359" s="3" t="inlineStr">
         <is>
           <t>412f0fb4e0d3e8b5306482f56c0c5b0732f7ee82fd656fa4f459b755f6571085</t>
         </is>
       </c>
-      <c r="B359" s="2" t="inlineStr">
+      <c r="B359" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C359" s="2" t="inlineStr">
+      <c r="C359" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D359" s="2" t="inlineStr">
+      <c r="D359" s="3" t="inlineStr">
         <is>
           <t>TMX Group</t>
         </is>
       </c>
-      <c r="E359" s="2" t="inlineStr">
+      <c r="E359" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern (Java)</t>
         </is>
       </c>
-      <c r="F359" s="2" t="inlineStr">
+      <c r="F359" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G359" s="2" t="inlineStr">
+      <c r="G359" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439894812</t>
         </is>
       </c>
-      <c r="H359" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I359" s="2" t="inlineStr"/>
-      <c r="J359" s="2" t="inlineStr"/>
-      <c r="K359" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L359" s="2" t="inlineStr"/>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I359" s="3" t="inlineStr"/>
+      <c r="J359" s="3" t="inlineStr"/>
+      <c r="K359" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L359" s="3" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="inlineStr">
+      <c r="A360" s="3" t="inlineStr">
         <is>
           <t>05623857ee6fed636d2dc7c96b7431e7ea83db1d7537aa89a0cd119a72383f06</t>
         </is>
       </c>
-      <c r="B360" s="2" t="inlineStr">
+      <c r="B360" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C360" s="2" t="inlineStr">
+      <c r="C360" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D360" s="2" t="inlineStr">
+      <c r="D360" s="3" t="inlineStr">
         <is>
           <t>Arcadis</t>
         </is>
       </c>
-      <c r="E360" s="2" t="inlineStr">
+      <c r="E360" s="3" t="inlineStr">
         <is>
           <t>Disaster and Climate Resilience Co-op</t>
         </is>
       </c>
-      <c r="F360" s="2" t="inlineStr">
+      <c r="F360" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G360" s="2" t="inlineStr">
+      <c r="G360" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=64b5c0aeffbc0b66</t>
         </is>
       </c>
-      <c r="H360" s="2" t="inlineStr">
+      <c r="H360" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I360" s="2" t="inlineStr">
+      <c r="I360" s="3" t="inlineStr">
         <is>
           <t>Arcadis is the world's leading company delivering sustainable design, engineering, and consultancy solutions for natural and built assets.
 We are more than 34,000 people, in over 30 countries, dedicated to improving quality of life. Everyone has an important role to play. With the power of many c</t>
         </is>
       </c>
-      <c r="J360" s="2" t="inlineStr"/>
-      <c r="K360" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L360" s="2" t="inlineStr"/>
+      <c r="J360" s="3" t="inlineStr"/>
+      <c r="K360" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L360" s="3" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="inlineStr">
+      <c r="A361" s="3" t="inlineStr">
         <is>
           <t>b696e2670abb52d927fd48439d762a12af15d132f2970402e37146d65d4dc318</t>
         </is>
       </c>
-      <c r="B361" s="2" t="inlineStr">
+      <c r="B361" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C361" s="2" t="inlineStr">
+      <c r="C361" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr">
+      <c r="D361" s="3" t="inlineStr">
         <is>
           <t>Global Relay</t>
         </is>
       </c>
-      <c r="E361" s="2" t="inlineStr">
+      <c r="E361" s="3" t="inlineStr">
         <is>
           <t>Co-op Frontend Software Developer (Information Archiving) - Fall 2026</t>
         </is>
       </c>
-      <c r="F361" s="2" t="inlineStr">
+      <c r="F361" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G361" s="2" t="inlineStr">
+      <c r="G361" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440584606</t>
         </is>
       </c>
-      <c r="H361" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I361" s="2" t="inlineStr"/>
-      <c r="J361" s="2" t="inlineStr"/>
-      <c r="K361" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L361" s="2" t="inlineStr"/>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I361" s="3" t="inlineStr"/>
+      <c r="J361" s="3" t="inlineStr"/>
+      <c r="K361" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L361" s="3" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="inlineStr">
+      <c r="A362" s="3" t="inlineStr">
         <is>
           <t>d0f730b02050b761833b09c75feeb398c06edae5e2884537771856b140cd939b</t>
         </is>
       </c>
-      <c r="B362" s="2" t="inlineStr">
+      <c r="B362" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C362" s="2" t="inlineStr">
+      <c r="C362" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D362" s="2" t="inlineStr">
+      <c r="D362" s="3" t="inlineStr">
         <is>
           <t>Leesee</t>
         </is>
       </c>
-      <c r="E362" s="2" t="inlineStr">
+      <c r="E362" s="3" t="inlineStr">
         <is>
           <t>Développeur Web ou Mobile (Stage Cégep) / Web or Mobile Developer (Cegep Internship)</t>
         </is>
       </c>
-      <c r="F362" s="2" t="inlineStr">
+      <c r="F362" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G362" s="2" t="inlineStr">
+      <c r="G362" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439879269</t>
         </is>
       </c>
-      <c r="H362" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I362" s="2" t="inlineStr"/>
-      <c r="J362" s="2" t="inlineStr"/>
-      <c r="K362" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L362" s="2" t="inlineStr"/>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I362" s="3" t="inlineStr"/>
+      <c r="J362" s="3" t="inlineStr"/>
+      <c r="K362" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L362" s="3" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="inlineStr">
+      <c r="A363" s="3" t="inlineStr">
         <is>
           <t>b34536cba7b21243769872d1ec711478ae71ba3153736acfe8d9447a5f79a6e4</t>
         </is>
       </c>
-      <c r="B363" s="2" t="inlineStr">
+      <c r="B363" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C363" s="2" t="inlineStr">
+      <c r="C363" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D363" s="2" t="inlineStr">
+      <c r="D363" s="3" t="inlineStr">
         <is>
           <t>Bombardier</t>
         </is>
       </c>
-      <c r="E363" s="2" t="inlineStr">
+      <c r="E363" s="3" t="inlineStr">
         <is>
           <t>Intern, DevSecOps (Fall 2026)</t>
         </is>
       </c>
-      <c r="F363" s="2" t="inlineStr">
+      <c r="F363" s="3" t="inlineStr">
         <is>
           <t>Dorval, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G363" s="2" t="inlineStr">
+      <c r="G363" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438688939</t>
         </is>
       </c>
-      <c r="H363" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I363" s="2" t="inlineStr"/>
-      <c r="J363" s="2" t="inlineStr"/>
-      <c r="K363" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L363" s="2" t="inlineStr"/>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I363" s="3" t="inlineStr"/>
+      <c r="J363" s="3" t="inlineStr"/>
+      <c r="K363" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L363" s="3" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>686a976d1a6320778d5dca48e92aef9ba5f5238a12d5e75a52bcfb49bf5fb5f5</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5802728864?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>795afe1a9b1eccdab80eef1c63d3d6d94c7f990c3f7031c62acd41ffe02fd742</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5802729573?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration </t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>41b6406ae2439564d0509d653df4273b09a20251fcca849a1b7f74910b38fd7f</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5802726255?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description Salary: Forum Asset Management Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investment. </t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>349bc4cb53dbd1a24a93c6b82d08fdae0bed0bc9fb192c7672751c909d2851e9</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>The 401 Group of Companies</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, ON, CA</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=af3732d8e7f6a952</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands\-on and will involve working across backend, frontend, database, and basic system administration tasks.**
+ **The intern will </t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>c152cdc0bfe1811da84787e1153aa940d891ff47085196fed71ec61a1e5467db</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Global Relay</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Co-op AI Developer - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440841116</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr"/>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L368"/>
+  <dimension ref="A1:L377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19432,271 +19432,756 @@
       <c r="L363" s="3" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="inlineStr">
+      <c r="A364" s="3" t="inlineStr">
         <is>
           <t>686a976d1a6320778d5dca48e92aef9ba5f5238a12d5e75a52bcfb49bf5fb5f5</t>
         </is>
       </c>
-      <c r="B364" s="2" t="inlineStr">
+      <c r="B364" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C364" s="2" t="inlineStr">
+      <c r="C364" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D364" s="2" t="inlineStr">
+      <c r="D364" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E364" s="2" t="inlineStr">
+      <c r="E364" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F364" s="2" t="inlineStr">
+      <c r="F364" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G364" s="2" t="inlineStr">
+      <c r="G364" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5802728864?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H364" s="2" t="inlineStr">
+      <c r="H364" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I364" s="2" t="inlineStr">
+      <c r="I364" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
         </is>
       </c>
-      <c r="J364" s="2" t="inlineStr"/>
-      <c r="K364" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L364" s="2" t="inlineStr"/>
+      <c r="J364" s="3" t="inlineStr"/>
+      <c r="K364" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="inlineStr">
+      <c r="A365" s="3" t="inlineStr">
         <is>
           <t>795afe1a9b1eccdab80eef1c63d3d6d94c7f990c3f7031c62acd41ffe02fd742</t>
         </is>
       </c>
-      <c r="B365" s="2" t="inlineStr">
+      <c r="B365" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C365" s="2" t="inlineStr">
+      <c r="C365" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D365" s="2" t="inlineStr">
+      <c r="D365" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E365" s="2" t="inlineStr">
+      <c r="E365" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F365" s="2" t="inlineStr">
+      <c r="F365" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Waterloo region</t>
         </is>
       </c>
-      <c r="G365" s="2" t="inlineStr">
+      <c r="G365" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5802729573?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H365" s="2" t="inlineStr">
+      <c r="H365" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I365" s="2" t="inlineStr">
+      <c r="I365" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration </t>
         </is>
       </c>
-      <c r="J365" s="2" t="inlineStr"/>
-      <c r="K365" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L365" s="2" t="inlineStr"/>
+      <c r="J365" s="3" t="inlineStr"/>
+      <c r="K365" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L365" s="3" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="inlineStr">
+      <c r="A366" s="3" t="inlineStr">
         <is>
           <t>41b6406ae2439564d0509d653df4273b09a20251fcca849a1b7f74910b38fd7f</t>
         </is>
       </c>
-      <c r="B366" s="2" t="inlineStr">
+      <c r="B366" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C366" s="2" t="inlineStr">
+      <c r="C366" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr">
+      <c r="D366" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E366" s="2" t="inlineStr">
+      <c r="E366" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F366" s="2" t="inlineStr">
+      <c r="F366" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G366" s="2" t="inlineStr">
+      <c r="G366" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5802726255?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H366" s="2" t="inlineStr">
+      <c r="H366" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I366" s="2" t="inlineStr">
+      <c r="I366" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description Salary: Forum Asset Management Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investment. </t>
         </is>
       </c>
-      <c r="J366" s="2" t="inlineStr"/>
-      <c r="K366" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L366" s="2" t="inlineStr"/>
+      <c r="J366" s="3" t="inlineStr"/>
+      <c r="K366" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L366" s="3" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="inlineStr">
+      <c r="A367" s="3" t="inlineStr">
         <is>
           <t>349bc4cb53dbd1a24a93c6b82d08fdae0bed0bc9fb192c7672751c909d2851e9</t>
         </is>
       </c>
-      <c r="B367" s="2" t="inlineStr">
+      <c r="B367" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C367" s="2" t="inlineStr">
+      <c r="C367" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D367" s="2" t="inlineStr">
+      <c r="D367" s="3" t="inlineStr">
         <is>
           <t>The 401 Group of Companies</t>
         </is>
       </c>
-      <c r="E367" s="2" t="inlineStr">
+      <c r="E367" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F367" s="2" t="inlineStr">
+      <c r="F367" s="3" t="inlineStr">
         <is>
           <t>Cambridge, ON, CA</t>
         </is>
       </c>
-      <c r="G367" s="2" t="inlineStr">
+      <c r="G367" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=af3732d8e7f6a952</t>
         </is>
       </c>
-      <c r="H367" s="2" t="inlineStr">
+      <c r="H367" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I367" s="2" t="inlineStr">
+      <c r="I367" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands\-on and will involve working across backend, frontend, database, and basic system administration tasks.**
  **The intern will </t>
         </is>
       </c>
-      <c r="J367" s="2" t="inlineStr"/>
-      <c r="K367" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L367" s="2" t="inlineStr"/>
+      <c r="J367" s="3" t="inlineStr"/>
+      <c r="K367" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L367" s="3" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="inlineStr">
+      <c r="A368" s="3" t="inlineStr">
         <is>
           <t>c152cdc0bfe1811da84787e1153aa940d891ff47085196fed71ec61a1e5467db</t>
         </is>
       </c>
-      <c r="B368" s="2" t="inlineStr">
+      <c r="B368" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C368" s="2" t="inlineStr">
+      <c r="C368" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D368" s="2" t="inlineStr">
+      <c r="D368" s="3" t="inlineStr">
         <is>
           <t>Global Relay</t>
         </is>
       </c>
-      <c r="E368" s="2" t="inlineStr">
+      <c r="E368" s="3" t="inlineStr">
         <is>
           <t>Co-op AI Developer - Fall 2026</t>
         </is>
       </c>
-      <c r="F368" s="2" t="inlineStr">
+      <c r="F368" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G368" s="2" t="inlineStr">
+      <c r="G368" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440841116</t>
         </is>
       </c>
-      <c r="H368" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I368" s="2" t="inlineStr"/>
-      <c r="J368" s="2" t="inlineStr"/>
-      <c r="K368" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L368" s="2" t="inlineStr"/>
+      <c r="H368" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I368" s="3" t="inlineStr"/>
+      <c r="J368" s="3" t="inlineStr"/>
+      <c r="K368" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L368" s="3" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>97d1e22a891593f2ccaed6ddf18b5bed4d4411c54e42db447b75e80ada53c525</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Genesys</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer, Test Intern (12mos)</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=8de0acf25654e2fa</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>locations
+Toronto (Flexible)
+time type
+Full time
+posted on
+Posted Today
+job requisition id
+JR109267**Be the one building AI\-powered experiences where they matter most**
+At Genesys, we help organizations create better customer experiences through AI\-powered experience orchestration. Our platfo</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>261d5cfd69e4c8362bc63590df583dc79573de18cb7793495fa7eefc64ae27f8</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Aviva</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Quality Engineering Intern (8-Month Internship)</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6fe594c1af2b1c7d</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>The career you never expected could be waiting for you at Aviva.
+You are investing time and effort into your education and building the foundation for a rewarding career. Have you considered the insurance industry? More than 100,000 Canadians work in insurance, helping individuals, families, and b</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>43a2d4a302d0b655ff5ccf037dae86233de56dd8f43e1611ba4ee8cd5a071efe</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Browser Security Engineer Intern, (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f90127cf2cf9be71</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**About GeoComply**  
+We’re GeoComply! We are at the forefront of geolocation, cybersecurity, and anti\-fraud innovation, developing and delivering cutting\-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. </t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>9b9ec0b470d21bd3934d88ae8ba8d998d6090731ab4df74bd16e02f3af938032</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=8f930814c73b3131</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>**Location:** Vancouver, B.C. **Full\-time, 40 hrs/week ·** **Contract length:** \~4 months
+**Start date:** September 3rd, 2026
+**Application deadline:** July 23,2026
+**Salary range:** $54,000 and \~$62,000 (annualized, prorated to your \~4\-month placement).  
+We’re GeoComply, an identity verifi</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>d5400c304aeed66fe49ef1cc7f88604294ade183f147a494079a59ac9b2bfa3b</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Developer Intern</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441285844</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr"/>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>8d7cd346e13c32ded40b1e9e676472ff04f3973b2bd4d887e17b14e96ee93046</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Automation Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=03c907da78e15dc7</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>**Location:** Vancouver, B.C. Full\-time, 40 hrs/week · Contract length: (Sept–Dec 2026\)
+**Start date:** September 3rd, 2026
+**Application deadline:** July 23, 2026
+**Salary range:** $50,000 and $58,000 (annualized, prorated to your \~4\-month placement).
+### **The Role**
+GeoComply protects onli</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>42827b35132d6dfc6012aae21358a4d05f343531dbb52ffac197a4ba783d7c25</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Ededge Learning</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Training and Internship Program</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439872859</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr"/>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>bb0a9a939900060e55353dfba83bbabe4facc0ac5cb589dda4035bc12b7ff7bd</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>XPV Water Partners</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Analyst Intern- Fall 2026</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439462669</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr"/>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>1f1426dacc78ef08680830f7ebb0a8c1f34ed1fa5748e2c6db20d50c583f27b9</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437652060</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr"/>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L377"/>
+  <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19699,47 +19699,47 @@
       <c r="L368" s="3" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="inlineStr">
+      <c r="A369" s="3" t="inlineStr">
         <is>
           <t>97d1e22a891593f2ccaed6ddf18b5bed4d4411c54e42db447b75e80ada53c525</t>
         </is>
       </c>
-      <c r="B369" s="2" t="inlineStr">
+      <c r="B369" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C369" s="2" t="inlineStr">
+      <c r="C369" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D369" s="2" t="inlineStr">
+      <c r="D369" s="3" t="inlineStr">
         <is>
           <t>Genesys</t>
         </is>
       </c>
-      <c r="E369" s="2" t="inlineStr">
+      <c r="E369" s="3" t="inlineStr">
         <is>
           <t>Software Developer, Test Intern (12mos)</t>
         </is>
       </c>
-      <c r="F369" s="2" t="inlineStr">
+      <c r="F369" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G369" s="2" t="inlineStr">
+      <c r="G369" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=8de0acf25654e2fa</t>
         </is>
       </c>
-      <c r="H369" s="2" t="inlineStr">
+      <c r="H369" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I369" s="2" t="inlineStr">
+      <c r="I369" s="3" t="inlineStr">
         <is>
           <t>locations
 Toronto (Flexible)
@@ -19752,166 +19752,166 @@
 At Genesys, we help organizations create better customer experiences through AI\-powered experience orchestration. Our platfo</t>
         </is>
       </c>
-      <c r="J369" s="2" t="inlineStr"/>
-      <c r="K369" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L369" s="2" t="inlineStr"/>
+      <c r="J369" s="3" t="inlineStr"/>
+      <c r="K369" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L369" s="3" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="inlineStr">
+      <c r="A370" s="3" t="inlineStr">
         <is>
           <t>261d5cfd69e4c8362bc63590df583dc79573de18cb7793495fa7eefc64ae27f8</t>
         </is>
       </c>
-      <c r="B370" s="2" t="inlineStr">
+      <c r="B370" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C370" s="2" t="inlineStr">
+      <c r="C370" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D370" s="2" t="inlineStr">
+      <c r="D370" s="3" t="inlineStr">
         <is>
           <t>Aviva</t>
         </is>
       </c>
-      <c r="E370" s="2" t="inlineStr">
+      <c r="E370" s="3" t="inlineStr">
         <is>
           <t>Quality Engineering Intern (8-Month Internship)</t>
         </is>
       </c>
-      <c r="F370" s="2" t="inlineStr">
+      <c r="F370" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G370" s="2" t="inlineStr">
+      <c r="G370" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6fe594c1af2b1c7d</t>
         </is>
       </c>
-      <c r="H370" s="2" t="inlineStr">
+      <c r="H370" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I370" s="2" t="inlineStr">
+      <c r="I370" s="3" t="inlineStr">
         <is>
           <t>The career you never expected could be waiting for you at Aviva.
 You are investing time and effort into your education and building the foundation for a rewarding career. Have you considered the insurance industry? More than 100,000 Canadians work in insurance, helping individuals, families, and b</t>
         </is>
       </c>
-      <c r="J370" s="2" t="inlineStr"/>
-      <c r="K370" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L370" s="2" t="inlineStr"/>
+      <c r="J370" s="3" t="inlineStr"/>
+      <c r="K370" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L370" s="3" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="inlineStr">
+      <c r="A371" s="3" t="inlineStr">
         <is>
           <t>43a2d4a302d0b655ff5ccf037dae86233de56dd8f43e1611ba4ee8cd5a071efe</t>
         </is>
       </c>
-      <c r="B371" s="2" t="inlineStr">
+      <c r="B371" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C371" s="2" t="inlineStr">
+      <c r="C371" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D371" s="2" t="inlineStr">
+      <c r="D371" s="3" t="inlineStr">
         <is>
           <t>GeoComply</t>
         </is>
       </c>
-      <c r="E371" s="2" t="inlineStr">
+      <c r="E371" s="3" t="inlineStr">
         <is>
           <t>Browser Security Engineer Intern, (Fall 2026)</t>
         </is>
       </c>
-      <c r="F371" s="2" t="inlineStr">
+      <c r="F371" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G371" s="2" t="inlineStr">
+      <c r="G371" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f90127cf2cf9be71</t>
         </is>
       </c>
-      <c r="H371" s="2" t="inlineStr">
+      <c r="H371" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I371" s="2" t="inlineStr">
+      <c r="I371" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**About GeoComply**  
 We’re GeoComply! We are at the forefront of geolocation, cybersecurity, and anti\-fraud innovation, developing and delivering cutting\-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. </t>
         </is>
       </c>
-      <c r="J371" s="2" t="inlineStr"/>
-      <c r="K371" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L371" s="2" t="inlineStr"/>
+      <c r="J371" s="3" t="inlineStr"/>
+      <c r="K371" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L371" s="3" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="inlineStr">
+      <c r="A372" s="3" t="inlineStr">
         <is>
           <t>9b9ec0b470d21bd3934d88ae8ba8d998d6090731ab4df74bd16e02f3af938032</t>
         </is>
       </c>
-      <c r="B372" s="2" t="inlineStr">
+      <c r="B372" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C372" s="2" t="inlineStr">
+      <c r="C372" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D372" s="2" t="inlineStr">
+      <c r="D372" s="3" t="inlineStr">
         <is>
           <t>GeoComply</t>
         </is>
       </c>
-      <c r="E372" s="2" t="inlineStr">
+      <c r="E372" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F372" s="2" t="inlineStr">
+      <c r="F372" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G372" s="2" t="inlineStr">
+      <c r="G372" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=8f930814c73b3131</t>
         </is>
       </c>
-      <c r="H372" s="2" t="inlineStr">
+      <c r="H372" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I372" s="2" t="inlineStr">
+      <c r="I372" s="3" t="inlineStr">
         <is>
           <t>**Location:** Vancouver, B.C. **Full\-time, 40 hrs/week ·** **Contract length:** \~4 months
 **Start date:** September 3rd, 2026
@@ -19920,106 +19920,106 @@
 We’re GeoComply, an identity verifi</t>
         </is>
       </c>
-      <c r="J372" s="2" t="inlineStr"/>
-      <c r="K372" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L372" s="2" t="inlineStr"/>
+      <c r="J372" s="3" t="inlineStr"/>
+      <c r="K372" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L372" s="3" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="inlineStr">
+      <c r="A373" s="3" t="inlineStr">
         <is>
           <t>d5400c304aeed66fe49ef1cc7f88604294ade183f147a494079a59ac9b2bfa3b</t>
         </is>
       </c>
-      <c r="B373" s="2" t="inlineStr">
+      <c r="B373" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C373" s="2" t="inlineStr">
+      <c r="C373" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D373" s="2" t="inlineStr">
+      <c r="D373" s="3" t="inlineStr">
         <is>
           <t>Revvity</t>
         </is>
       </c>
-      <c r="E373" s="2" t="inlineStr">
+      <c r="E373" s="3" t="inlineStr">
         <is>
           <t>Full-Stack AI Developer Intern</t>
         </is>
       </c>
-      <c r="F373" s="2" t="inlineStr">
+      <c r="F373" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G373" s="2" t="inlineStr">
+      <c r="G373" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441285844</t>
         </is>
       </c>
-      <c r="H373" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I373" s="2" t="inlineStr"/>
-      <c r="J373" s="2" t="inlineStr"/>
-      <c r="K373" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L373" s="2" t="inlineStr"/>
+      <c r="H373" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I373" s="3" t="inlineStr"/>
+      <c r="J373" s="3" t="inlineStr"/>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L373" s="3" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="inlineStr">
+      <c r="A374" s="3" t="inlineStr">
         <is>
           <t>8d7cd346e13c32ded40b1e9e676472ff04f3973b2bd4d887e17b14e96ee93046</t>
         </is>
       </c>
-      <c r="B374" s="2" t="inlineStr">
+      <c r="B374" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C374" s="2" t="inlineStr">
+      <c r="C374" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D374" s="2" t="inlineStr">
+      <c r="D374" s="3" t="inlineStr">
         <is>
           <t>GeoComply</t>
         </is>
       </c>
-      <c r="E374" s="2" t="inlineStr">
+      <c r="E374" s="3" t="inlineStr">
         <is>
           <t>Marketing Automation Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F374" s="2" t="inlineStr">
+      <c r="F374" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G374" s="2" t="inlineStr">
+      <c r="G374" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=03c907da78e15dc7</t>
         </is>
       </c>
-      <c r="H374" s="2" t="inlineStr">
+      <c r="H374" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I374" s="2" t="inlineStr">
+      <c r="I374" s="3" t="inlineStr">
         <is>
           <t>**Location:** Vancouver, B.C. Full\-time, 40 hrs/week · Contract length: (Sept–Dec 2026\)
 **Start date:** September 3rd, 2026
@@ -20029,159 +20029,372 @@
 GeoComply protects onli</t>
         </is>
       </c>
-      <c r="J374" s="2" t="inlineStr"/>
-      <c r="K374" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L374" s="2" t="inlineStr"/>
+      <c r="J374" s="3" t="inlineStr"/>
+      <c r="K374" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L374" s="3" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="inlineStr">
+      <c r="A375" s="3" t="inlineStr">
         <is>
           <t>42827b35132d6dfc6012aae21358a4d05f343531dbb52ffac197a4ba783d7c25</t>
         </is>
       </c>
-      <c r="B375" s="2" t="inlineStr">
+      <c r="B375" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C375" s="2" t="inlineStr">
+      <c r="C375" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D375" s="2" t="inlineStr">
+      <c r="D375" s="3" t="inlineStr">
         <is>
           <t>Ededge Learning</t>
         </is>
       </c>
-      <c r="E375" s="2" t="inlineStr">
+      <c r="E375" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Training and Internship Program</t>
         </is>
       </c>
-      <c r="F375" s="2" t="inlineStr">
+      <c r="F375" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G375" s="2" t="inlineStr">
+      <c r="G375" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439872859</t>
         </is>
       </c>
-      <c r="H375" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr"/>
-      <c r="J375" s="2" t="inlineStr"/>
-      <c r="K375" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L375" s="2" t="inlineStr"/>
+      <c r="H375" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I375" s="3" t="inlineStr"/>
+      <c r="J375" s="3" t="inlineStr"/>
+      <c r="K375" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L375" s="3" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="inlineStr">
+      <c r="A376" s="3" t="inlineStr">
         <is>
           <t>bb0a9a939900060e55353dfba83bbabe4facc0ac5cb589dda4035bc12b7ff7bd</t>
         </is>
       </c>
-      <c r="B376" s="2" t="inlineStr">
+      <c r="B376" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C376" s="2" t="inlineStr">
+      <c r="C376" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D376" s="2" t="inlineStr">
+      <c r="D376" s="3" t="inlineStr">
         <is>
           <t>XPV Water Partners</t>
         </is>
       </c>
-      <c r="E376" s="2" t="inlineStr">
+      <c r="E376" s="3" t="inlineStr">
         <is>
           <t>AI &amp; Data Analyst Intern- Fall 2026</t>
         </is>
       </c>
-      <c r="F376" s="2" t="inlineStr">
+      <c r="F376" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G376" s="2" t="inlineStr">
+      <c r="G376" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439462669</t>
         </is>
       </c>
-      <c r="H376" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I376" s="2" t="inlineStr"/>
-      <c r="J376" s="2" t="inlineStr"/>
-      <c r="K376" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L376" s="2" t="inlineStr"/>
+      <c r="H376" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I376" s="3" t="inlineStr"/>
+      <c r="J376" s="3" t="inlineStr"/>
+      <c r="K376" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L376" s="3" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="inlineStr">
+      <c r="A377" s="3" t="inlineStr">
         <is>
           <t>1f1426dacc78ef08680830f7ebb0a8c1f34ed1fa5748e2c6db20d50c583f27b9</t>
         </is>
       </c>
-      <c r="B377" s="2" t="inlineStr">
+      <c r="B377" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C377" s="2" t="inlineStr">
+      <c r="C377" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D377" s="2" t="inlineStr">
+      <c r="D377" s="3" t="inlineStr">
         <is>
           <t>Stealth</t>
         </is>
       </c>
-      <c r="E377" s="2" t="inlineStr">
+      <c r="E377" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr">
+      <c r="F377" s="3" t="inlineStr"/>
+      <c r="G377" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437652060</t>
         </is>
       </c>
-      <c r="H377" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I377" s="2" t="inlineStr"/>
-      <c r="J377" s="2" t="inlineStr"/>
-      <c r="K377" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L377" s="2" t="inlineStr"/>
+      <c r="H377" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I377" s="3" t="inlineStr"/>
+      <c r="J377" s="3" t="inlineStr"/>
+      <c r="K377" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L377" s="3" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>d3da8112d8c887b9447f7615c813c8ab1d8e7596ae7334e528c36da8303b217f</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5804737441?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>9c47d7e501d0f12fdd191d9a451aa836a53819795a35490b2d820ba61cb9e4ac</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>C-MAD-100 Test Software Developer Intern-EN</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438099803</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr"/>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L379" s="2" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>fbf74cb741a69bd68413f74b2eac16cbbb7b281ebe1f32d1bbc1e171cd2213a5</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>CSMC</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering Intern (Advanced Energy &amp; Infrastructure)</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, ON, CA</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=eff5c2c01a049d89</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>**Civil Engineering Intern (Advanced Energy \&amp; Infrastructure)**
+**Location**: Waterloo, ON (On\-Site)  
+**Employment Type**: Internship / Co\-op / Student Position  
+**Term**: 4\-Month Initial Term (September\-December 2026\)
+ **About Canadian Strategic Missions Corp. (CSMC)**
+Canadian Stra</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>855cf0eb5267a16f8dcb6fb12aca8f01aa3b7194651f6a9a42d512b243c855fd</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Global Relay</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Software Development Engineer in Test (SDET) - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440592097</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr"/>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L381" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20184,151 +20184,151 @@
       <c r="L377" s="3" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="inlineStr">
+      <c r="A378" s="3" t="inlineStr">
         <is>
           <t>d3da8112d8c887b9447f7615c813c8ab1d8e7596ae7334e528c36da8303b217f</t>
         </is>
       </c>
-      <c r="B378" s="2" t="inlineStr">
+      <c r="B378" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C378" s="2" t="inlineStr">
+      <c r="C378" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D378" s="2" t="inlineStr">
+      <c r="D378" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E378" s="2" t="inlineStr">
+      <c r="E378" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F378" s="2" t="inlineStr">
+      <c r="F378" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Waterloo region</t>
         </is>
       </c>
-      <c r="G378" s="2" t="inlineStr">
+      <c r="G378" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5804737441?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H378" s="2" t="inlineStr">
+      <c r="H378" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I378" s="2" t="inlineStr">
+      <c r="I378" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
         </is>
       </c>
-      <c r="J378" s="2" t="inlineStr"/>
-      <c r="K378" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L378" s="2" t="inlineStr"/>
+      <c r="J378" s="3" t="inlineStr"/>
+      <c r="K378" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L378" s="3" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="inlineStr">
+      <c r="A379" s="3" t="inlineStr">
         <is>
           <t>9c47d7e501d0f12fdd191d9a451aa836a53819795a35490b2d820ba61cb9e4ac</t>
         </is>
       </c>
-      <c r="B379" s="2" t="inlineStr">
+      <c r="B379" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C379" s="2" t="inlineStr">
+      <c r="C379" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D379" s="2" t="inlineStr">
+      <c r="D379" s="3" t="inlineStr">
         <is>
           <t>CAE</t>
         </is>
       </c>
-      <c r="E379" s="2" t="inlineStr">
+      <c r="E379" s="3" t="inlineStr">
         <is>
           <t>C-MAD-100 Test Software Developer Intern-EN</t>
         </is>
       </c>
-      <c r="F379" s="2" t="inlineStr">
+      <c r="F379" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G379" s="2" t="inlineStr">
+      <c r="G379" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438099803</t>
         </is>
       </c>
-      <c r="H379" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I379" s="2" t="inlineStr"/>
-      <c r="J379" s="2" t="inlineStr"/>
-      <c r="K379" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L379" s="2" t="inlineStr"/>
+      <c r="H379" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I379" s="3" t="inlineStr"/>
+      <c r="J379" s="3" t="inlineStr"/>
+      <c r="K379" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L379" s="3" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="inlineStr">
+      <c r="A380" s="3" t="inlineStr">
         <is>
           <t>fbf74cb741a69bd68413f74b2eac16cbbb7b281ebe1f32d1bbc1e171cd2213a5</t>
         </is>
       </c>
-      <c r="B380" s="2" t="inlineStr">
+      <c r="B380" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C380" s="2" t="inlineStr">
+      <c r="C380" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D380" s="2" t="inlineStr">
+      <c r="D380" s="3" t="inlineStr">
         <is>
           <t>CSMC</t>
         </is>
       </c>
-      <c r="E380" s="2" t="inlineStr">
+      <c r="E380" s="3" t="inlineStr">
         <is>
           <t>Civil Engineering Intern (Advanced Energy &amp; Infrastructure)</t>
         </is>
       </c>
-      <c r="F380" s="2" t="inlineStr">
+      <c r="F380" s="3" t="inlineStr">
         <is>
           <t>Waterloo, ON, CA</t>
         </is>
       </c>
-      <c r="G380" s="2" t="inlineStr">
+      <c r="G380" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=eff5c2c01a049d89</t>
         </is>
       </c>
-      <c r="H380" s="2" t="inlineStr">
+      <c r="H380" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I380" s="2" t="inlineStr">
+      <c r="I380" s="3" t="inlineStr">
         <is>
           <t>**Civil Engineering Intern (Advanced Energy \&amp; Infrastructure)**
 **Location**: Waterloo, ON (On\-Site)  
@@ -20338,63 +20338,372 @@
 Canadian Stra</t>
         </is>
       </c>
-      <c r="J380" s="2" t="inlineStr"/>
-      <c r="K380" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L380" s="2" t="inlineStr"/>
+      <c r="J380" s="3" t="inlineStr"/>
+      <c r="K380" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L380" s="3" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="inlineStr">
+      <c r="A381" s="3" t="inlineStr">
         <is>
           <t>855cf0eb5267a16f8dcb6fb12aca8f01aa3b7194651f6a9a42d512b243c855fd</t>
         </is>
       </c>
-      <c r="B381" s="2" t="inlineStr">
+      <c r="B381" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C381" s="2" t="inlineStr">
+      <c r="C381" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D381" s="2" t="inlineStr">
+      <c r="D381" s="3" t="inlineStr">
         <is>
           <t>Global Relay</t>
         </is>
       </c>
-      <c r="E381" s="2" t="inlineStr">
+      <c r="E381" s="3" t="inlineStr">
         <is>
           <t>Co-op Software Development Engineer in Test (SDET) - Fall 2026</t>
         </is>
       </c>
-      <c r="F381" s="2" t="inlineStr">
+      <c r="F381" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G381" s="2" t="inlineStr">
+      <c r="G381" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440592097</t>
         </is>
       </c>
-      <c r="H381" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr"/>
-      <c r="J381" s="2" t="inlineStr"/>
-      <c r="K381" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L381" s="2" t="inlineStr"/>
+      <c r="H381" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I381" s="3" t="inlineStr"/>
+      <c r="J381" s="3" t="inlineStr"/>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L381" s="3" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>f706533b6dbadbc0843c06e6d5aea4d4081ba93b82686d3250b877a97b7ced9c</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Breslau, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5805405212?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration tasks. The intern will work clos</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L382" s="2" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>136f5ae1a9e2c135dd75548aa95018b832a0e855c7c2f499e16bb2d89cc5e9b5</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>ecobee</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineering</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438404389</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr"/>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>7e000d2fb68783da1a2beaf066b67c384246c2324e154b769388acebf7b6676f</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Egis Group</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Transportation Structures</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=38a78cdd66ed18df</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Company Description**  
+Join Egis, where your ambition meets unparalleled growth opportunities. As we continue to expand within Canada, we're looking for talented professionals like you to be a part of our innovative team. Imagine working alongside over 1,000 top\-tier engineers, architects, and </t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>e3c0c24a9a837428163e669717c4abb2754626003266ef3c50c6f2a651591c67</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Simon-Kucher</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Summer 2027 Intern - Elevate/Data Science [UG/Masters]</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437291302</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr"/>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>8009eec2d3a6578e4eca251725249545ee57c72f062cf7286f6897223bf023f0</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data analyst (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438810049</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr"/>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>34607c59bb46345a968b4ca04fbdcf49f1b358781635182678bc7187fd50a308</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Analysis</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433279476</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr"/>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L387" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L387"/>
+  <dimension ref="A1:L390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20397,313 +20397,463 @@
       <c r="L381" s="3" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="inlineStr">
+      <c r="A382" s="3" t="inlineStr">
         <is>
           <t>f706533b6dbadbc0843c06e6d5aea4d4081ba93b82686d3250b877a97b7ced9c</t>
         </is>
       </c>
-      <c r="B382" s="2" t="inlineStr">
+      <c r="B382" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C382" s="2" t="inlineStr">
+      <c r="C382" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D382" s="2" t="inlineStr">
+      <c r="D382" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E382" s="2" t="inlineStr">
+      <c r="E382" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F382" s="2" t="inlineStr">
+      <c r="F382" s="3" t="inlineStr">
         <is>
           <t>Breslau, Waterloo region</t>
         </is>
       </c>
-      <c r="G382" s="2" t="inlineStr">
+      <c r="G382" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5805405212?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H382" s="2" t="inlineStr">
+      <c r="H382" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I382" s="2" t="inlineStr">
+      <c r="I382" s="3" t="inlineStr">
         <is>
           <t>We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration tasks. The intern will work clos</t>
         </is>
       </c>
-      <c r="J382" s="2" t="inlineStr"/>
-      <c r="K382" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L382" s="2" t="inlineStr"/>
+      <c r="J382" s="3" t="inlineStr"/>
+      <c r="K382" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L382" s="3" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="inlineStr">
+      <c r="A383" s="3" t="inlineStr">
         <is>
           <t>136f5ae1a9e2c135dd75548aa95018b832a0e855c7c2f499e16bb2d89cc5e9b5</t>
         </is>
       </c>
-      <c r="B383" s="2" t="inlineStr">
+      <c r="B383" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C383" s="2" t="inlineStr">
+      <c r="C383" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D383" s="2" t="inlineStr">
+      <c r="D383" s="3" t="inlineStr">
         <is>
           <t>ecobee</t>
         </is>
       </c>
-      <c r="E383" s="2" t="inlineStr">
+      <c r="E383" s="3" t="inlineStr">
         <is>
           <t>Intern Engineering</t>
         </is>
       </c>
-      <c r="F383" s="2" t="inlineStr">
+      <c r="F383" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G383" s="2" t="inlineStr">
+      <c r="G383" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438404389</t>
         </is>
       </c>
-      <c r="H383" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr"/>
-      <c r="J383" s="2" t="inlineStr"/>
-      <c r="K383" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L383" s="2" t="inlineStr"/>
+      <c r="H383" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I383" s="3" t="inlineStr"/>
+      <c r="J383" s="3" t="inlineStr"/>
+      <c r="K383" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L383" s="3" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="inlineStr">
+      <c r="A384" s="3" t="inlineStr">
         <is>
           <t>7e000d2fb68783da1a2beaf066b67c384246c2324e154b769388acebf7b6676f</t>
         </is>
       </c>
-      <c r="B384" s="2" t="inlineStr">
+      <c r="B384" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C384" s="2" t="inlineStr">
+      <c r="C384" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D384" s="2" t="inlineStr">
+      <c r="D384" s="3" t="inlineStr">
         <is>
           <t>Egis Group</t>
         </is>
       </c>
-      <c r="E384" s="2" t="inlineStr">
+      <c r="E384" s="3" t="inlineStr">
         <is>
           <t>Intern, Transportation Structures</t>
         </is>
       </c>
-      <c r="F384" s="2" t="inlineStr">
+      <c r="F384" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G384" s="2" t="inlineStr">
+      <c r="G384" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=38a78cdd66ed18df</t>
         </is>
       </c>
-      <c r="H384" s="2" t="inlineStr">
+      <c r="H384" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I384" s="2" t="inlineStr">
+      <c r="I384" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Company Description**  
 Join Egis, where your ambition meets unparalleled growth opportunities. As we continue to expand within Canada, we're looking for talented professionals like you to be a part of our innovative team. Imagine working alongside over 1,000 top\-tier engineers, architects, and </t>
         </is>
       </c>
-      <c r="J384" s="2" t="inlineStr"/>
-      <c r="K384" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L384" s="2" t="inlineStr"/>
+      <c r="J384" s="3" t="inlineStr"/>
+      <c r="K384" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L384" s="3" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="inlineStr">
+      <c r="A385" s="3" t="inlineStr">
         <is>
           <t>e3c0c24a9a837428163e669717c4abb2754626003266ef3c50c6f2a651591c67</t>
         </is>
       </c>
-      <c r="B385" s="2" t="inlineStr">
+      <c r="B385" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C385" s="2" t="inlineStr">
+      <c r="C385" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D385" s="2" t="inlineStr">
+      <c r="D385" s="3" t="inlineStr">
         <is>
           <t>Simon-Kucher</t>
         </is>
       </c>
-      <c r="E385" s="2" t="inlineStr">
+      <c r="E385" s="3" t="inlineStr">
         <is>
           <t>Summer 2027 Intern - Elevate/Data Science [UG/Masters]</t>
         </is>
       </c>
-      <c r="F385" s="2" t="inlineStr">
+      <c r="F385" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G385" s="2" t="inlineStr">
+      <c r="G385" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437291302</t>
         </is>
       </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I385" s="2" t="inlineStr"/>
-      <c r="J385" s="2" t="inlineStr"/>
-      <c r="K385" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L385" s="2" t="inlineStr"/>
+      <c r="H385" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I385" s="3" t="inlineStr"/>
+      <c r="J385" s="3" t="inlineStr"/>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L385" s="3" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="inlineStr">
+      <c r="A386" s="3" t="inlineStr">
         <is>
           <t>8009eec2d3a6578e4eca251725249545ee57c72f062cf7286f6897223bf023f0</t>
         </is>
       </c>
-      <c r="B386" s="2" t="inlineStr">
+      <c r="B386" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C386" s="2" t="inlineStr">
+      <c r="C386" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D386" s="2" t="inlineStr">
+      <c r="D386" s="3" t="inlineStr">
         <is>
           <t>Bombardier</t>
         </is>
       </c>
-      <c r="E386" s="2" t="inlineStr">
+      <c r="E386" s="3" t="inlineStr">
         <is>
           <t>Intern, Data analyst (Fall 2026)</t>
         </is>
       </c>
-      <c r="F386" s="2" t="inlineStr">
+      <c r="F386" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G386" s="2" t="inlineStr">
+      <c r="G386" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438810049</t>
         </is>
       </c>
-      <c r="H386" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I386" s="2" t="inlineStr"/>
-      <c r="J386" s="2" t="inlineStr"/>
-      <c r="K386" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L386" s="2" t="inlineStr"/>
+      <c r="H386" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I386" s="3" t="inlineStr"/>
+      <c r="J386" s="3" t="inlineStr"/>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L386" s="3" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="inlineStr">
+      <c r="A387" s="3" t="inlineStr">
         <is>
           <t>34607c59bb46345a968b4ca04fbdcf49f1b358781635182678bc7187fd50a308</t>
         </is>
       </c>
-      <c r="B387" s="2" t="inlineStr">
+      <c r="B387" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C387" s="2" t="inlineStr">
+      <c r="C387" s="3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D387" s="2" t="inlineStr">
+      <c r="D387" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E387" s="2" t="inlineStr">
+      <c r="E387" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Analysis</t>
         </is>
       </c>
-      <c r="F387" s="2" t="inlineStr">
+      <c r="F387" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G387" s="2" t="inlineStr">
+      <c r="G387" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433279476</t>
         </is>
       </c>
-      <c r="H387" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I387" s="2" t="inlineStr"/>
-      <c r="J387" s="2" t="inlineStr"/>
-      <c r="K387" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L387" s="2" t="inlineStr"/>
+      <c r="H387" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I387" s="3" t="inlineStr"/>
+      <c r="J387" s="3" t="inlineStr"/>
+      <c r="K387" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L387" s="3" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>1b60232e579d92989ddaa992eab7ce41d6ab3b69d381e3e1dd7043bf977599d9</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>TommieTest</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (React + Node/NestJS + Agentic Development)</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441973247</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr"/>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>8d991d5d171dd3724f10e40d8e3434950672e95edc609caff8639fe1e5a484d0</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Afuva</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441164469</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr"/>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>7c133fef4a5bbb559c00a5e68d376b9ab0910dc5a34a9cc39dd694d04736106d</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Semtech</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce QA &amp; Data Analyst Co-Op</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Burlington, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441652546</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr"/>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L390" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L390"/>
+  <dimension ref="A1:L402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20706,154 +20706,774 @@
       <c r="L387" s="3" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="inlineStr">
+      <c r="A388" s="3" t="inlineStr">
         <is>
           <t>1b60232e579d92989ddaa992eab7ce41d6ab3b69d381e3e1dd7043bf977599d9</t>
         </is>
       </c>
-      <c r="B388" s="2" t="inlineStr">
+      <c r="B388" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C388" s="2" t="inlineStr">
+      <c r="C388" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D388" s="2" t="inlineStr">
+      <c r="D388" s="3" t="inlineStr">
         <is>
           <t>TommieTest</t>
         </is>
       </c>
-      <c r="E388" s="2" t="inlineStr">
+      <c r="E388" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (React + Node/NestJS + Agentic Development)</t>
         </is>
       </c>
-      <c r="F388" s="2" t="inlineStr">
+      <c r="F388" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G388" s="2" t="inlineStr">
+      <c r="G388" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441973247</t>
         </is>
       </c>
-      <c r="H388" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I388" s="2" t="inlineStr"/>
-      <c r="J388" s="2" t="inlineStr"/>
-      <c r="K388" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L388" s="2" t="inlineStr"/>
+      <c r="H388" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I388" s="3" t="inlineStr"/>
+      <c r="J388" s="3" t="inlineStr"/>
+      <c r="K388" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L388" s="3" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="inlineStr">
+      <c r="A389" s="3" t="inlineStr">
         <is>
           <t>8d991d5d171dd3724f10e40d8e3434950672e95edc609caff8639fe1e5a484d0</t>
         </is>
       </c>
-      <c r="B389" s="2" t="inlineStr">
+      <c r="B389" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C389" s="2" t="inlineStr">
+      <c r="C389" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D389" s="2" t="inlineStr">
+      <c r="D389" s="3" t="inlineStr">
         <is>
           <t>Afuva</t>
         </is>
       </c>
-      <c r="E389" s="2" t="inlineStr">
+      <c r="E389" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="F389" s="2" t="inlineStr">
+      <c r="F389" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G389" s="2" t="inlineStr">
+      <c r="G389" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441164469</t>
         </is>
       </c>
-      <c r="H389" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I389" s="2" t="inlineStr"/>
-      <c r="J389" s="2" t="inlineStr"/>
-      <c r="K389" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L389" s="2" t="inlineStr"/>
+      <c r="H389" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I389" s="3" t="inlineStr"/>
+      <c r="J389" s="3" t="inlineStr"/>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L389" s="3" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="inlineStr">
+      <c r="A390" s="3" t="inlineStr">
         <is>
           <t>7c133fef4a5bbb559c00a5e68d376b9ab0910dc5a34a9cc39dd694d04736106d</t>
         </is>
       </c>
-      <c r="B390" s="2" t="inlineStr">
+      <c r="B390" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="C390" s="2" t="inlineStr">
+      <c r="C390" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D390" s="2" t="inlineStr">
+      <c r="D390" s="3" t="inlineStr">
         <is>
           <t>Semtech</t>
         </is>
       </c>
-      <c r="E390" s="2" t="inlineStr">
+      <c r="E390" s="3" t="inlineStr">
         <is>
           <t>Salesforce QA &amp; Data Analyst Co-Op</t>
         </is>
       </c>
-      <c r="F390" s="2" t="inlineStr">
+      <c r="F390" s="3" t="inlineStr">
         <is>
           <t>Burlington, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G390" s="2" t="inlineStr">
+      <c r="G390" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441652546</t>
         </is>
       </c>
-      <c r="H390" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I390" s="2" t="inlineStr"/>
-      <c r="J390" s="2" t="inlineStr"/>
-      <c r="K390" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L390" s="2" t="inlineStr"/>
+      <c r="H390" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I390" s="3" t="inlineStr"/>
+      <c r="J390" s="3" t="inlineStr"/>
+      <c r="K390" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L390" s="3" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>f727c46e0f045c8b2cd40ddaedcf1e7bb18e07801278586ddfc30310dd44d166</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Software Dev Engineer, Cross Border Deals and Promotions tech</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806452924?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>Ever wondered how Amazon is using its Global presence to offer best of Amazon experience to its international customers? Amazon Cross border programs like Global store allows customers to buy imported products in their local current and experience. This is Amazon first cross marketplace initiative t</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L391" s="2" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>17c281a2fd7d212196970da5ef5e938f22d948a801775b6127e364db9b695cc3</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineering Assistant</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806191189?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>About Your Role As an ML software engineer intern, you will join a team full of talented experts in frontend, backend, and ML/NLP. We have an in-house product for call analysis, building, evaluating, and deploying conversational AI models and have labelers and analysts available. We work on a variet</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L392" s="2" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>70ceffa2aaf7878e42ab8daae098b2e190b8eeab916c5f068edc130277e33dc2</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Browser Security Engineer Intern, (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806557510?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>About GeoComply We’re GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L393" s="2" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>5028a4bfc213660ea1c505370b3326b827e41eec99bcc48008de95ce9cccc011</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply Job on T-Net</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806267822?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>Location: Vancouver, B.C. Full-time, 40 hrs/week Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We're GeoComply, an identity verification, anti-fraud and compliance co</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L394" s="2" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>a5e5a8a0c883899ea8651fe07409b245b462aba1841e6f2f52d16c1ecc9b05ea</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806557006?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location: Vancouver, B.C. Full-time, 40 hrs/week · Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We’re GeoComply, an identity verification, anti-fraud and compliance </t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L395" s="2" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>aa194547742294f91915209d725a0dc7eea02acef52da5136740f386d4de2fa3</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441388499</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr"/>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L396" s="2" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>3462695cd83572a2da0c8c66f8343924e5e4f63c1403b976b09318b6c6ad8257</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441393191</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr"/>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L397" s="2" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>5c9909f37e28da061007c213a1c3bc792adcec1ed14a5f928ff804fd73071603</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441398123</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr"/>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>43a775bcae51983ae1e7eb7db09fcaa61ca5d2f1a6b2afe4b8f13096ac7fd8fd</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>PCL Construction</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Student</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Edmonton, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442167452</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr"/>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>d9094ba5be7fd05ac9129b33c35e6e4e16f81518dbae386662c3f77739bb68c8</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Hach</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Aquatic Informatics - Software Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442193192</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr"/>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L400" s="2" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>4a8305774820be9c3b4ecd38ce22119020c044b5477030592686c9afe42f2efe</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440076146</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr"/>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>51e3b48fb136db24e7c11e9e27542014809d1a0bc435a3a24fc4648ff8d8828a</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Cost and Data Analyst Student - Fall</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441689929</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr"/>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L402" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L402"/>
+  <dimension ref="A1:L403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20856,624 +20856,674 @@
       <c r="L390" s="3" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="inlineStr">
+      <c r="A391" s="3" t="inlineStr">
         <is>
           <t>f727c46e0f045c8b2cd40ddaedcf1e7bb18e07801278586ddfc30310dd44d166</t>
         </is>
       </c>
-      <c r="B391" s="2" t="inlineStr">
+      <c r="B391" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C391" s="2" t="inlineStr">
+      <c r="C391" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D391" s="2" t="inlineStr">
+      <c r="D391" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E391" s="2" t="inlineStr">
+      <c r="E391" s="3" t="inlineStr">
         <is>
           <t>Software Dev Engineer, Cross Border Deals and Promotions tech</t>
         </is>
       </c>
-      <c r="F391" s="2" t="inlineStr">
+      <c r="F391" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G391" s="2" t="inlineStr">
+      <c r="G391" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806452924?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H391" s="2" t="inlineStr">
+      <c r="H391" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I391" s="2" t="inlineStr">
+      <c r="I391" s="3" t="inlineStr">
         <is>
           <t>Ever wondered how Amazon is using its Global presence to offer best of Amazon experience to its international customers? Amazon Cross border programs like Global store allows customers to buy imported products in their local current and experience. This is Amazon first cross marketplace initiative t</t>
         </is>
       </c>
-      <c r="J391" s="2" t="inlineStr"/>
-      <c r="K391" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L391" s="2" t="inlineStr"/>
+      <c r="J391" s="3" t="inlineStr"/>
+      <c r="K391" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L391" s="3" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="inlineStr">
+      <c r="A392" s="3" t="inlineStr">
         <is>
           <t>17c281a2fd7d212196970da5ef5e938f22d948a801775b6127e364db9b695cc3</t>
         </is>
       </c>
-      <c r="B392" s="2" t="inlineStr">
+      <c r="B392" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C392" s="2" t="inlineStr">
+      <c r="C392" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D392" s="2" t="inlineStr">
+      <c r="D392" s="3" t="inlineStr">
         <is>
           <t>Cresta</t>
         </is>
       </c>
-      <c r="E392" s="2" t="inlineStr">
+      <c r="E392" s="3" t="inlineStr">
         <is>
           <t>Machine Learning Engineering Assistant</t>
         </is>
       </c>
-      <c r="F392" s="2" t="inlineStr">
+      <c r="F392" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G392" s="2" t="inlineStr">
+      <c r="G392" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806191189?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H392" s="2" t="inlineStr">
+      <c r="H392" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I392" s="2" t="inlineStr">
+      <c r="I392" s="3" t="inlineStr">
         <is>
           <t>About Your Role As an ML software engineer intern, you will join a team full of talented experts in frontend, backend, and ML/NLP. We have an in-house product for call analysis, building, evaluating, and deploying conversational AI models and have labelers and analysts available. We work on a variet</t>
         </is>
       </c>
-      <c r="J392" s="2" t="inlineStr"/>
-      <c r="K392" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L392" s="2" t="inlineStr"/>
+      <c r="J392" s="3" t="inlineStr"/>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L392" s="3" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="inlineStr">
+      <c r="A393" s="3" t="inlineStr">
         <is>
           <t>70ceffa2aaf7878e42ab8daae098b2e190b8eeab916c5f068edc130277e33dc2</t>
         </is>
       </c>
-      <c r="B393" s="2" t="inlineStr">
+      <c r="B393" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C393" s="2" t="inlineStr">
+      <c r="C393" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D393" s="2" t="inlineStr">
+      <c r="D393" s="3" t="inlineStr">
         <is>
           <t>GeoComply</t>
         </is>
       </c>
-      <c r="E393" s="2" t="inlineStr">
+      <c r="E393" s="3" t="inlineStr">
         <is>
           <t>Browser Security Engineer Intern, (Fall 2026)</t>
         </is>
       </c>
-      <c r="F393" s="2" t="inlineStr">
+      <c r="F393" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G393" s="2" t="inlineStr">
+      <c r="G393" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806557510?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H393" s="2" t="inlineStr">
+      <c r="H393" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I393" s="2" t="inlineStr">
+      <c r="I393" s="3" t="inlineStr">
         <is>
           <t>About GeoComply We’re GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
         </is>
       </c>
-      <c r="J393" s="2" t="inlineStr"/>
-      <c r="K393" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L393" s="2" t="inlineStr"/>
+      <c r="J393" s="3" t="inlineStr"/>
+      <c r="K393" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L393" s="3" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="inlineStr">
+      <c r="A394" s="3" t="inlineStr">
         <is>
           <t>5028a4bfc213660ea1c505370b3326b827e41eec99bcc48008de95ce9cccc011</t>
         </is>
       </c>
-      <c r="B394" s="2" t="inlineStr">
+      <c r="B394" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C394" s="2" t="inlineStr">
+      <c r="C394" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D394" s="2" t="inlineStr">
+      <c r="D394" s="3" t="inlineStr">
         <is>
           <t>GeoComply Job on T-Net</t>
         </is>
       </c>
-      <c r="E394" s="2" t="inlineStr">
+      <c r="E394" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F394" s="2" t="inlineStr">
+      <c r="F394" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G394" s="2" t="inlineStr">
+      <c r="G394" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806267822?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H394" s="2" t="inlineStr">
+      <c r="H394" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I394" s="2" t="inlineStr">
+      <c r="I394" s="3" t="inlineStr">
         <is>
           <t>Location: Vancouver, B.C. Full-time, 40 hrs/week Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We're GeoComply, an identity verification, anti-fraud and compliance co</t>
         </is>
       </c>
-      <c r="J394" s="2" t="inlineStr"/>
-      <c r="K394" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L394" s="2" t="inlineStr"/>
+      <c r="J394" s="3" t="inlineStr"/>
+      <c r="K394" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L394" s="3" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="inlineStr">
+      <c r="A395" s="3" t="inlineStr">
         <is>
           <t>a5e5a8a0c883899ea8651fe07409b245b462aba1841e6f2f52d16c1ecc9b05ea</t>
         </is>
       </c>
-      <c r="B395" s="2" t="inlineStr">
+      <c r="B395" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C395" s="2" t="inlineStr">
+      <c r="C395" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D395" s="2" t="inlineStr">
+      <c r="D395" s="3" t="inlineStr">
         <is>
           <t>GeoComply</t>
         </is>
       </c>
-      <c r="E395" s="2" t="inlineStr">
+      <c r="E395" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F395" s="2" t="inlineStr">
+      <c r="F395" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G395" s="2" t="inlineStr">
+      <c r="G395" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806557006?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H395" s="2" t="inlineStr">
+      <c r="H395" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I395" s="2" t="inlineStr">
+      <c r="I395" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Location: Vancouver, B.C. Full-time, 40 hrs/week · Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We’re GeoComply, an identity verification, anti-fraud and compliance </t>
         </is>
       </c>
-      <c r="J395" s="2" t="inlineStr"/>
-      <c r="K395" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L395" s="2" t="inlineStr"/>
+      <c r="J395" s="3" t="inlineStr"/>
+      <c r="K395" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L395" s="3" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="inlineStr">
+      <c r="A396" s="3" t="inlineStr">
         <is>
           <t>aa194547742294f91915209d725a0dc7eea02acef52da5136740f386d4de2fa3</t>
         </is>
       </c>
-      <c r="B396" s="2" t="inlineStr">
+      <c r="B396" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
+      <c r="C396" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D396" s="2" t="inlineStr">
+      <c r="D396" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E396" s="2" t="inlineStr">
+      <c r="E396" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F396" s="2" t="inlineStr">
+      <c r="F396" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G396" s="2" t="inlineStr">
+      <c r="G396" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441388499</t>
         </is>
       </c>
-      <c r="H396" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I396" s="2" t="inlineStr"/>
-      <c r="J396" s="2" t="inlineStr"/>
-      <c r="K396" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L396" s="2" t="inlineStr"/>
+      <c r="H396" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I396" s="3" t="inlineStr"/>
+      <c r="J396" s="3" t="inlineStr"/>
+      <c r="K396" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L396" s="3" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="inlineStr">
+      <c r="A397" s="3" t="inlineStr">
         <is>
           <t>3462695cd83572a2da0c8c66f8343924e5e4f63c1403b976b09318b6c6ad8257</t>
         </is>
       </c>
-      <c r="B397" s="2" t="inlineStr">
+      <c r="B397" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C397" s="2" t="inlineStr">
+      <c r="C397" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D397" s="2" t="inlineStr">
+      <c r="D397" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E397" s="2" t="inlineStr">
+      <c r="E397" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F397" s="2" t="inlineStr">
+      <c r="F397" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G397" s="2" t="inlineStr">
+      <c r="G397" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441393191</t>
         </is>
       </c>
-      <c r="H397" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I397" s="2" t="inlineStr"/>
-      <c r="J397" s="2" t="inlineStr"/>
-      <c r="K397" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L397" s="2" t="inlineStr"/>
+      <c r="H397" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I397" s="3" t="inlineStr"/>
+      <c r="J397" s="3" t="inlineStr"/>
+      <c r="K397" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L397" s="3" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="inlineStr">
+      <c r="A398" s="3" t="inlineStr">
         <is>
           <t>5c9909f37e28da061007c213a1c3bc792adcec1ed14a5f928ff804fd73071603</t>
         </is>
       </c>
-      <c r="B398" s="2" t="inlineStr">
+      <c r="B398" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C398" s="2" t="inlineStr">
+      <c r="C398" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D398" s="2" t="inlineStr">
+      <c r="D398" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E398" s="2" t="inlineStr">
+      <c r="E398" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F398" s="2" t="inlineStr">
+      <c r="F398" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G398" s="2" t="inlineStr">
+      <c r="G398" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441398123</t>
         </is>
       </c>
-      <c r="H398" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I398" s="2" t="inlineStr"/>
-      <c r="J398" s="2" t="inlineStr"/>
-      <c r="K398" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L398" s="2" t="inlineStr"/>
+      <c r="H398" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I398" s="3" t="inlineStr"/>
+      <c r="J398" s="3" t="inlineStr"/>
+      <c r="K398" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L398" s="3" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="inlineStr">
+      <c r="A399" s="3" t="inlineStr">
         <is>
           <t>43a775bcae51983ae1e7eb7db09fcaa61ca5d2f1a6b2afe4b8f13096ac7fd8fd</t>
         </is>
       </c>
-      <c r="B399" s="2" t="inlineStr">
+      <c r="B399" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C399" s="2" t="inlineStr">
+      <c r="C399" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D399" s="2" t="inlineStr">
+      <c r="D399" s="3" t="inlineStr">
         <is>
           <t>PCL Construction</t>
         </is>
       </c>
-      <c r="E399" s="2" t="inlineStr">
+      <c r="E399" s="3" t="inlineStr">
         <is>
           <t>Software Developer Student</t>
         </is>
       </c>
-      <c r="F399" s="2" t="inlineStr">
+      <c r="F399" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G399" s="2" t="inlineStr">
+      <c r="G399" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442167452</t>
         </is>
       </c>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I399" s="2" t="inlineStr"/>
-      <c r="J399" s="2" t="inlineStr"/>
-      <c r="K399" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L399" s="2" t="inlineStr"/>
+      <c r="H399" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I399" s="3" t="inlineStr"/>
+      <c r="J399" s="3" t="inlineStr"/>
+      <c r="K399" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L399" s="3" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="inlineStr">
+      <c r="A400" s="3" t="inlineStr">
         <is>
           <t>d9094ba5be7fd05ac9129b33c35e6e4e16f81518dbae386662c3f77739bb68c8</t>
         </is>
       </c>
-      <c r="B400" s="2" t="inlineStr">
+      <c r="B400" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C400" s="2" t="inlineStr">
+      <c r="C400" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D400" s="2" t="inlineStr">
+      <c r="D400" s="3" t="inlineStr">
         <is>
           <t>Hach</t>
         </is>
       </c>
-      <c r="E400" s="2" t="inlineStr">
+      <c r="E400" s="3" t="inlineStr">
         <is>
           <t>Aquatic Informatics - Software Engineering Co-op</t>
         </is>
       </c>
-      <c r="F400" s="2" t="inlineStr">
+      <c r="F400" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G400" s="2" t="inlineStr">
+      <c r="G400" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442193192</t>
         </is>
       </c>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I400" s="2" t="inlineStr"/>
-      <c r="J400" s="2" t="inlineStr"/>
-      <c r="K400" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L400" s="2" t="inlineStr"/>
+      <c r="H400" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I400" s="3" t="inlineStr"/>
+      <c r="J400" s="3" t="inlineStr"/>
+      <c r="K400" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L400" s="3" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="inlineStr">
+      <c r="A401" s="3" t="inlineStr">
         <is>
           <t>4a8305774820be9c3b4ecd38ce22119020c044b5477030592686c9afe42f2efe</t>
         </is>
       </c>
-      <c r="B401" s="2" t="inlineStr">
+      <c r="B401" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C401" s="2" t="inlineStr">
+      <c r="C401" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D401" s="2" t="inlineStr">
+      <c r="D401" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E401" s="2" t="inlineStr">
+      <c r="E401" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F401" s="2" t="inlineStr">
+      <c r="F401" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G401" s="2" t="inlineStr">
+      <c r="G401" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440076146</t>
         </is>
       </c>
-      <c r="H401" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I401" s="2" t="inlineStr"/>
-      <c r="J401" s="2" t="inlineStr"/>
-      <c r="K401" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L401" s="2" t="inlineStr"/>
+      <c r="H401" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I401" s="3" t="inlineStr"/>
+      <c r="J401" s="3" t="inlineStr"/>
+      <c r="K401" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L401" s="3" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="inlineStr">
+      <c r="A402" s="3" t="inlineStr">
         <is>
           <t>51e3b48fb136db24e7c11e9e27542014809d1a0bc435a3a24fc4648ff8d8828a</t>
         </is>
       </c>
-      <c r="B402" s="2" t="inlineStr">
+      <c r="B402" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C402" s="2" t="inlineStr">
+      <c r="C402" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr">
+      <c r="D402" s="3" t="inlineStr">
         <is>
           <t>AtkinsRéalis</t>
         </is>
       </c>
-      <c r="E402" s="2" t="inlineStr">
+      <c r="E402" s="3" t="inlineStr">
         <is>
           <t>Cost and Data Analyst Student - Fall</t>
         </is>
       </c>
-      <c r="F402" s="2" t="inlineStr">
+      <c r="F402" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G402" s="2" t="inlineStr">
+      <c r="G402" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441689929</t>
         </is>
       </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I402" s="2" t="inlineStr"/>
-      <c r="J402" s="2" t="inlineStr"/>
-      <c r="K402" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L402" s="2" t="inlineStr"/>
+      <c r="H402" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I402" s="3" t="inlineStr"/>
+      <c r="J402" s="3" t="inlineStr"/>
+      <c r="K402" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L402" s="3" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>1208657d0063f6771285be56e46a3e5b37152ce399f8e8723352e48afe993fb1</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Nova Scotia Power</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Co-op (Master’s Student)</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442123334</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr"/>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L403" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L403"/>
+  <dimension ref="A1:L404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21476,54 +21476,108 @@
       <c r="L402" s="3" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="inlineStr">
+      <c r="A403" s="3" t="inlineStr">
         <is>
           <t>1208657d0063f6771285be56e46a3e5b37152ce399f8e8723352e48afe993fb1</t>
         </is>
       </c>
-      <c r="B403" s="2" t="inlineStr">
+      <c r="B403" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr">
+      <c r="C403" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D403" s="2" t="inlineStr">
+      <c r="D403" s="3" t="inlineStr">
         <is>
           <t>Nova Scotia Power</t>
         </is>
       </c>
-      <c r="E403" s="2" t="inlineStr">
+      <c r="E403" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Co-op (Master’s Student)</t>
         </is>
       </c>
-      <c r="F403" s="2" t="inlineStr">
+      <c r="F403" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G403" s="2" t="inlineStr">
+      <c r="G403" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442123334</t>
         </is>
       </c>
-      <c r="H403" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I403" s="2" t="inlineStr"/>
-      <c r="J403" s="2" t="inlineStr"/>
-      <c r="K403" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L403" s="2" t="inlineStr"/>
+      <c r="H403" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I403" s="3" t="inlineStr"/>
+      <c r="J403" s="3" t="inlineStr"/>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L403" s="3" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>1a28198788accdc77ee8dfb969f9ed2ff44d5a2b78daa68fa3d8c4b1208f47a5</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Hanzilla</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5807269903?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)at Rivian and Volkswagen Group Technologies LocationVancouver, British Columbia DetailsCo-op · 8mo · Fall 2026–Spring 2027 PostedJul 15, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the RoleD</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L404" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L404"/>
+  <dimension ref="A1:L411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21526,58 +21526,447 @@
       <c r="L403" s="3" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="inlineStr">
+      <c r="A404" s="3" t="inlineStr">
         <is>
           <t>1a28198788accdc77ee8dfb969f9ed2ff44d5a2b78daa68fa3d8c4b1208f47a5</t>
         </is>
       </c>
-      <c r="B404" s="2" t="inlineStr">
+      <c r="B404" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C404" s="2" t="inlineStr">
+      <c r="C404" s="3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="D404" s="2" t="inlineStr">
+      <c r="D404" s="3" t="inlineStr">
         <is>
           <t>Hanzilla</t>
         </is>
       </c>
-      <c r="E404" s="2" t="inlineStr">
+      <c r="E404" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F404" s="2" t="inlineStr">
+      <c r="F404" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G404" s="2" t="inlineStr">
+      <c r="G404" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5807269903?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H404" s="2" t="inlineStr">
+      <c r="H404" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I404" s="2" t="inlineStr">
+      <c r="I404" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)at Rivian and Volkswagen Group Technologies LocationVancouver, British Columbia DetailsCo-op · 8mo · Fall 2026–Spring 2027 PostedJul 15, 2026Apply on company site →Direct apply link, refreshed by the daily generator. About the RoleD</t>
         </is>
       </c>
-      <c r="J404" s="2" t="inlineStr"/>
-      <c r="K404" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L404" s="2" t="inlineStr"/>
+      <c r="J404" s="3" t="inlineStr"/>
+      <c r="K404" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L404" s="3" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>f9fed84277a9c5e6e587df2df605ef61cf80c686633b67f30a265d749c19abd9</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Zip</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5808538216?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>About Zip Zip is the AI platform for enterprise procurement — built for humans and agents working together. By orchestrating procurement across teams, tools, and suppliers with the help of AI agents, companies can secure the resources they need to innovate faster than ever before. The world’s most i</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L405" s="2" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>b8f1502e85535addf74197601780b76e8c3b8fe95bbce4e8e93d326f1c339171</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=2e20fcb7033eb1d2</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
+**Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>8b8dad51e82b7bdd9e03e7209eb84d1b9071cafe8fe48510b73d2f1a1aaf8cbc</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=5e8a89cab040cb0e</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
+**Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>8af9350e43e0675fab69d2a3e11e5622aab2fdd10652c7ed3cff7230c6be600d</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Kardium Inc.</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Hybrid) - September 2026</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, BC, CA</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1548cc5ab60c48c9</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>**Term:** September 2026
+**Duration:** 8 months
+**Openings:** 1 position
+**Salary Range:** $3,650 \- $4,525 CAD per month
+**Application Deadline:** July 22, 2026
+Your opportunity
+By joining the Kardium team, you can help make a difference in the lives of mil</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>d61871760ca4723bb7ff86e01666918edcd2e0548fe48f7d3b69e609ef0841ab</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, ON, CA</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=18b97fde7988972c</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
+**Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>b79cbba52be3544924bdafeb60ffdc82d93e530e496cf1489a18eb0bc941468d</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, ON, CA</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1ed0f153022a5461</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
+**Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>82b911b3132e96efa381959ffe29cca0d37d80b8624d6de28d363f4a9eefceab</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Wondershare</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, BC, CA</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6b1c99d999bd2202</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>**About Wondershare** 
+As a renowned global leader in creativity and productivity solutions, Wondershare is dedicated to making cutting\-edge technology accessible to everyone, fostering efficiency and innovation. With over 100 million users across 150 countries, we provide a wide range of creative</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L411" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L411"/>
+  <dimension ref="A1:L412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21580,211 +21580,211 @@
       <c r="L404" s="3" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="inlineStr">
+      <c r="A405" s="3" t="inlineStr">
         <is>
           <t>f9fed84277a9c5e6e587df2df605ef61cf80c686633b67f30a265d749c19abd9</t>
         </is>
       </c>
-      <c r="B405" s="2" t="inlineStr">
+      <c r="B405" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C405" s="2" t="inlineStr">
+      <c r="C405" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D405" s="2" t="inlineStr">
+      <c r="D405" s="3" t="inlineStr">
         <is>
           <t>Zip</t>
         </is>
       </c>
-      <c r="E405" s="2" t="inlineStr">
+      <c r="E405" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="F405" s="2" t="inlineStr">
+      <c r="F405" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G405" s="2" t="inlineStr">
+      <c r="G405" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5808538216?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H405" s="2" t="inlineStr">
+      <c r="H405" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I405" s="2" t="inlineStr">
+      <c r="I405" s="3" t="inlineStr">
         <is>
           <t>About Zip Zip is the AI platform for enterprise procurement — built for humans and agents working together. By orchestrating procurement across teams, tools, and suppliers with the help of AI agents, companies can secure the resources they need to innovate faster than ever before. The world’s most i</t>
         </is>
       </c>
-      <c r="J405" s="2" t="inlineStr"/>
-      <c r="K405" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L405" s="2" t="inlineStr"/>
+      <c r="J405" s="3" t="inlineStr"/>
+      <c r="K405" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L405" s="3" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="inlineStr">
+      <c r="A406" s="3" t="inlineStr">
         <is>
           <t>b8f1502e85535addf74197601780b76e8c3b8fe95bbce4e8e93d326f1c339171</t>
         </is>
       </c>
-      <c r="B406" s="2" t="inlineStr">
+      <c r="B406" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C406" s="2" t="inlineStr">
+      <c r="C406" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D406" s="2" t="inlineStr">
+      <c r="D406" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E406" s="2" t="inlineStr">
+      <c r="E406" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F406" s="2" t="inlineStr">
+      <c r="F406" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G406" s="2" t="inlineStr">
+      <c r="G406" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=2e20fcb7033eb1d2</t>
         </is>
       </c>
-      <c r="H406" s="2" t="inlineStr">
+      <c r="H406" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I406" s="2" t="inlineStr">
+      <c r="I406" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
 **Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
         </is>
       </c>
-      <c r="J406" s="2" t="inlineStr"/>
-      <c r="K406" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L406" s="2" t="inlineStr"/>
+      <c r="J406" s="3" t="inlineStr"/>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L406" s="3" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>8b8dad51e82b7bdd9e03e7209eb84d1b9071cafe8fe48510b73d2f1a1aaf8cbc</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
+      <c r="B407" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C407" s="2" t="inlineStr">
+      <c r="C407" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D407" s="2" t="inlineStr">
+      <c r="D407" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E407" s="2" t="inlineStr">
+      <c r="E407" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F407" s="2" t="inlineStr">
+      <c r="F407" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G407" s="2" t="inlineStr">
+      <c r="G407" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=5e8a89cab040cb0e</t>
         </is>
       </c>
-      <c r="H407" s="2" t="inlineStr">
+      <c r="H407" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I407" s="2" t="inlineStr">
+      <c r="I407" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
 **Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
         </is>
       </c>
-      <c r="J407" s="2" t="inlineStr"/>
-      <c r="K407" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L407" s="2" t="inlineStr"/>
+      <c r="J407" s="3" t="inlineStr"/>
+      <c r="K407" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L407" s="3" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>8af9350e43e0675fab69d2a3e11e5622aab2fdd10652c7ed3cff7230c6be600d</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
+      <c r="B408" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C408" s="2" t="inlineStr">
+      <c r="C408" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D408" s="2" t="inlineStr">
+      <c r="D408" s="3" t="inlineStr">
         <is>
           <t>Kardium Inc.</t>
         </is>
       </c>
-      <c r="E408" s="2" t="inlineStr">
+      <c r="E408" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Hybrid) - September 2026</t>
         </is>
       </c>
-      <c r="F408" s="2" t="inlineStr">
+      <c r="F408" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G408" s="2" t="inlineStr">
+      <c r="G408" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1548cc5ab60c48c9</t>
         </is>
       </c>
-      <c r="H408" s="2" t="inlineStr">
+      <c r="H408" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I408" s="2" t="inlineStr">
+      <c r="I408" s="3" t="inlineStr">
         <is>
           <t>**Term:** September 2026
 **Duration:** 8 months
@@ -21795,178 +21795,228 @@
 By joining the Kardium team, you can help make a difference in the lives of mil</t>
         </is>
       </c>
-      <c r="J408" s="2" t="inlineStr"/>
-      <c r="K408" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L408" s="2" t="inlineStr"/>
+      <c r="J408" s="3" t="inlineStr"/>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L408" s="3" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="inlineStr">
+      <c r="A409" s="3" t="inlineStr">
         <is>
           <t>d61871760ca4723bb7ff86e01666918edcd2e0548fe48f7d3b69e609ef0841ab</t>
         </is>
       </c>
-      <c r="B409" s="2" t="inlineStr">
+      <c r="B409" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C409" s="2" t="inlineStr">
+      <c r="C409" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D409" s="2" t="inlineStr">
+      <c r="D409" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E409" s="2" t="inlineStr">
+      <c r="E409" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F409" s="2" t="inlineStr">
+      <c r="F409" s="3" t="inlineStr">
         <is>
           <t>Waterloo, ON, CA</t>
         </is>
       </c>
-      <c r="G409" s="2" t="inlineStr">
+      <c r="G409" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=18b97fde7988972c</t>
         </is>
       </c>
-      <c r="H409" s="2" t="inlineStr">
+      <c r="H409" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I409" s="2" t="inlineStr">
+      <c r="I409" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
 **Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
         </is>
       </c>
-      <c r="J409" s="2" t="inlineStr"/>
-      <c r="K409" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L409" s="2" t="inlineStr"/>
+      <c r="J409" s="3" t="inlineStr"/>
+      <c r="K409" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L409" s="3" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="inlineStr">
+      <c r="A410" s="3" t="inlineStr">
         <is>
           <t>b79cbba52be3544924bdafeb60ffdc82d93e530e496cf1489a18eb0bc941468d</t>
         </is>
       </c>
-      <c r="B410" s="2" t="inlineStr">
+      <c r="B410" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C410" s="2" t="inlineStr">
+      <c r="C410" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D410" s="2" t="inlineStr">
+      <c r="D410" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E410" s="2" t="inlineStr">
+      <c r="E410" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F410" s="2" t="inlineStr">
+      <c r="F410" s="3" t="inlineStr">
         <is>
           <t>Waterloo, ON, CA</t>
         </is>
       </c>
-      <c r="G410" s="2" t="inlineStr">
+      <c r="G410" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1ed0f153022a5461</t>
         </is>
       </c>
-      <c r="H410" s="2" t="inlineStr">
+      <c r="H410" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I410" s="2" t="inlineStr">
+      <c r="I410" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle.**
 **Applications will be reviewed on a rolling basis and it’s in the candidate’s best interest to </t>
         </is>
       </c>
-      <c r="J410" s="2" t="inlineStr"/>
-      <c r="K410" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L410" s="2" t="inlineStr"/>
+      <c r="J410" s="3" t="inlineStr"/>
+      <c r="K410" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L410" s="3" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="inlineStr">
+      <c r="A411" s="3" t="inlineStr">
         <is>
           <t>82b911b3132e96efa381959ffe29cca0d37d80b8624d6de28d363f4a9eefceab</t>
         </is>
       </c>
-      <c r="B411" s="2" t="inlineStr">
+      <c r="B411" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C411" s="2" t="inlineStr">
+      <c r="C411" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D411" s="2" t="inlineStr">
+      <c r="D411" s="3" t="inlineStr">
         <is>
           <t>Wondershare</t>
         </is>
       </c>
-      <c r="E411" s="2" t="inlineStr">
+      <c r="E411" s="3" t="inlineStr">
         <is>
           <t>Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F411" s="2" t="inlineStr">
+      <c r="F411" s="3" t="inlineStr">
         <is>
           <t>Burnaby, BC, CA</t>
         </is>
       </c>
-      <c r="G411" s="2" t="inlineStr">
+      <c r="G411" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6b1c99d999bd2202</t>
         </is>
       </c>
-      <c r="H411" s="2" t="inlineStr">
+      <c r="H411" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I411" s="2" t="inlineStr">
+      <c r="I411" s="3" t="inlineStr">
         <is>
           <t>**About Wondershare** 
 As a renowned global leader in creativity and productivity solutions, Wondershare is dedicated to making cutting\-edge technology accessible to everyone, fostering efficiency and innovation. With over 100 million users across 150 countries, we provide a wide range of creative</t>
         </is>
       </c>
-      <c r="J411" s="2" t="inlineStr"/>
-      <c r="K411" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L411" s="2" t="inlineStr"/>
+      <c r="J411" s="3" t="inlineStr"/>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L411" s="3" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>fa9ad451edf671415f1f1de1eaa96c56d172a16f73f1050cc772af98d3a3a632</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Cost and Data Analyst Student - Fall</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441909116</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr"/>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L412"/>
+  <dimension ref="A1:L423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21969,54 +21969,625 @@
       <c r="L411" s="3" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="inlineStr">
+      <c r="A412" s="3" t="inlineStr">
         <is>
           <t>fa9ad451edf671415f1f1de1eaa96c56d172a16f73f1050cc772af98d3a3a632</t>
         </is>
       </c>
-      <c r="B412" s="2" t="inlineStr">
+      <c r="B412" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C412" s="2" t="inlineStr">
+      <c r="C412" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D412" s="2" t="inlineStr">
+      <c r="D412" s="3" t="inlineStr">
         <is>
           <t>AtkinsRéalis</t>
         </is>
       </c>
-      <c r="E412" s="2" t="inlineStr">
+      <c r="E412" s="3" t="inlineStr">
         <is>
           <t>Cost and Data Analyst Student - Fall</t>
         </is>
       </c>
-      <c r="F412" s="2" t="inlineStr">
+      <c r="F412" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G412" s="2" t="inlineStr">
+      <c r="G412" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441909116</t>
         </is>
       </c>
-      <c r="H412" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I412" s="2" t="inlineStr"/>
-      <c r="J412" s="2" t="inlineStr"/>
-      <c r="K412" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L412" s="2" t="inlineStr"/>
+      <c r="H412" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I412" s="3" t="inlineStr"/>
+      <c r="J412" s="3" t="inlineStr"/>
+      <c r="K412" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L412" s="3" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>4d8114ece6e6bb63a9eb3027fab2b1a590e2f0060a107b591c1c24ebc5d32fe3</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>ShyftLabs</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f7e7781c8bbe5238</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>**About ShyftLabs**
+At ShyftLabs, we live and breathe data. Since 2020, we’ve been helping Fortune 500 companies unlock growth through innovative digital solutions that drive real business impact. With teams across Canada, the U.S., and India, we’re growing quickly and looking for curious, motiva</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr"/>
+      <c r="K413" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>971df340591f968eeacd4c93fe84adc28c00b93ba5586642c6eacf728527802f</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>ecobee Technologies ULC</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>Sofware Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=90992815237050f4</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>**Hi, we are ecobee.**
+======================
+ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>6ca0bce23bf7ab6d2c3f06cd4f0f6e4b8817c56c08b6580124c4eb8af11bcdf0</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer – C++</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443004828</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr"/>
+      <c r="J415" s="2" t="inlineStr"/>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L415" s="2" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>bcd05327bf4a70c40cd4420cac34184a0d4a03a6fc315d25842c91b35281db9c</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Routing/IP Software Developer Intern (4-8 Months)</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=9aea6663e060072c</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>f66894d3816b486b8a410012906cfaf699daef50a0769fc2b419569eb7437c36</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442091621</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr"/>
+      <c r="J417" s="2" t="inlineStr"/>
+      <c r="K417" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L417" s="2" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>cab2e16cc06e37b72538b048c73fc189370b1ef3ec11ce9d7401793a5a539c7e</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442098361</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr"/>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L418" s="2" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>933f17573189b18ea21ea1131e2910fb0bd5e69ca0c099491afec64ffd8e4310</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Robotics - Software Development Engineer Intern - 2026 - Toronto</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443035914</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr"/>
+      <c r="J419" s="2" t="inlineStr"/>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L419" s="2" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>e98ce21945a141c1e6ee9886e914072c30fdea7edf62a316b854e76bb127aa8e</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Kardium Inc.</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Hybrid) - September 2026</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442225727</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr"/>
+      <c r="J420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>3c739bce2791b9d3187edb154b5b2ec2ec75654d224eb4c3abe04c54de8a4039</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442204058</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr"/>
+      <c r="J421" s="2" t="inlineStr"/>
+      <c r="K421" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L421" s="2" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>4c3ae2742302c61b92735be82d110171995a5a6a6d0250155f522c8bcaf49d74</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Ribbon Communications</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Canada (Co-op)</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434317680</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr"/>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L422" s="2" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>f2229fff4aa7a6c3da3eb14263c0565edf502c11c09661487d723acb2ae23aab</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>EQ Bank</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Intern, CloudOps</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f0baf0e899ea9845</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>**Join a Challenger**  
+At EQ, we're remaking banking so every Canadian gets ahead, every day. Serving nearly 4 million Canadians from coast to coast, we offer a wide variety of financial services from banking and lending, to trust and credit union solutions.  
+We've been at this since 197</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr"/>
+      <c r="K423" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L423" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L423"/>
+  <dimension ref="A1:L428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22019,575 +22019,833 @@
       <c r="L412" s="3" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="inlineStr">
+      <c r="A413" s="3" t="inlineStr">
         <is>
           <t>4d8114ece6e6bb63a9eb3027fab2b1a590e2f0060a107b591c1c24ebc5d32fe3</t>
         </is>
       </c>
-      <c r="B413" s="2" t="inlineStr">
+      <c r="B413" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C413" s="2" t="inlineStr">
+      <c r="C413" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D413" s="2" t="inlineStr">
+      <c r="D413" s="3" t="inlineStr">
         <is>
           <t>ShyftLabs</t>
         </is>
       </c>
-      <c r="E413" s="2" t="inlineStr">
+      <c r="E413" s="3" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="F413" s="2" t="inlineStr">
+      <c r="F413" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G413" s="2" t="inlineStr">
+      <c r="G413" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f7e7781c8bbe5238</t>
         </is>
       </c>
-      <c r="H413" s="2" t="inlineStr">
+      <c r="H413" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I413" s="2" t="inlineStr">
+      <c r="I413" s="3" t="inlineStr">
         <is>
           <t>**About ShyftLabs**
 At ShyftLabs, we live and breathe data. Since 2020, we’ve been helping Fortune 500 companies unlock growth through innovative digital solutions that drive real business impact. With teams across Canada, the U.S., and India, we’re growing quickly and looking for curious, motiva</t>
         </is>
       </c>
-      <c r="J413" s="2" t="inlineStr"/>
-      <c r="K413" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L413" s="2" t="inlineStr"/>
+      <c r="J413" s="3" t="inlineStr"/>
+      <c r="K413" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
+      <c r="A414" s="3" t="inlineStr">
         <is>
           <t>971df340591f968eeacd4c93fe84adc28c00b93ba5586642c6eacf728527802f</t>
         </is>
       </c>
-      <c r="B414" s="2" t="inlineStr">
+      <c r="B414" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C414" s="2" t="inlineStr">
+      <c r="C414" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D414" s="2" t="inlineStr">
+      <c r="D414" s="3" t="inlineStr">
         <is>
           <t>ecobee Technologies ULC</t>
         </is>
       </c>
-      <c r="E414" s="2" t="inlineStr">
+      <c r="E414" s="3" t="inlineStr">
         <is>
           <t>Sofware Engineer - Intern</t>
         </is>
       </c>
-      <c r="F414" s="2" t="inlineStr">
+      <c r="F414" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G414" s="2" t="inlineStr">
+      <c r="G414" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=90992815237050f4</t>
         </is>
       </c>
-      <c r="H414" s="2" t="inlineStr">
+      <c r="H414" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I414" s="2" t="inlineStr">
+      <c r="I414" s="3" t="inlineStr">
         <is>
           <t>**Hi, we are ecobee.**
 ======================
 ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
         </is>
       </c>
-      <c r="J414" s="2" t="inlineStr"/>
-      <c r="K414" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L414" s="2" t="inlineStr"/>
+      <c r="J414" s="3" t="inlineStr"/>
+      <c r="K414" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L414" s="3" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="inlineStr">
+      <c r="A415" s="3" t="inlineStr">
         <is>
           <t>6ca0bce23bf7ab6d2c3f06cd4f0f6e4b8817c56c08b6580124c4eb8af11bcdf0</t>
         </is>
       </c>
-      <c r="B415" s="2" t="inlineStr">
+      <c r="B415" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C415" s="2" t="inlineStr">
+      <c r="C415" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D415" s="2" t="inlineStr">
+      <c r="D415" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E415" s="2" t="inlineStr">
+      <c r="E415" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer – C++</t>
         </is>
       </c>
-      <c r="F415" s="2" t="inlineStr">
+      <c r="F415" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G415" s="2" t="inlineStr">
+      <c r="G415" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443004828</t>
         </is>
       </c>
-      <c r="H415" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr"/>
-      <c r="J415" s="2" t="inlineStr"/>
-      <c r="K415" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L415" s="2" t="inlineStr"/>
+      <c r="H415" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I415" s="3" t="inlineStr"/>
+      <c r="J415" s="3" t="inlineStr"/>
+      <c r="K415" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L415" s="3" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="inlineStr">
+      <c r="A416" s="3" t="inlineStr">
         <is>
           <t>bcd05327bf4a70c40cd4420cac34184a0d4a03a6fc315d25842c91b35281db9c</t>
         </is>
       </c>
-      <c r="B416" s="2" t="inlineStr">
+      <c r="B416" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C416" s="2" t="inlineStr">
+      <c r="C416" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D416" s="2" t="inlineStr">
+      <c r="D416" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E416" s="2" t="inlineStr">
+      <c r="E416" s="3" t="inlineStr">
         <is>
           <t>Routing/IP Software Developer Intern (4-8 Months)</t>
         </is>
       </c>
-      <c r="F416" s="2" t="inlineStr">
+      <c r="F416" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G416" s="2" t="inlineStr">
+      <c r="G416" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=9aea6663e060072c</t>
         </is>
       </c>
-      <c r="H416" s="2" t="inlineStr">
+      <c r="H416" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I416" s="2" t="inlineStr">
+      <c r="I416" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J416" s="2" t="inlineStr"/>
-      <c r="K416" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L416" s="2" t="inlineStr"/>
+      <c r="J416" s="3" t="inlineStr"/>
+      <c r="K416" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L416" s="3" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="inlineStr">
+      <c r="A417" s="3" t="inlineStr">
         <is>
           <t>f66894d3816b486b8a410012906cfaf699daef50a0769fc2b419569eb7437c36</t>
         </is>
       </c>
-      <c r="B417" s="2" t="inlineStr">
+      <c r="B417" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C417" s="2" t="inlineStr">
+      <c r="C417" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D417" s="2" t="inlineStr">
+      <c r="D417" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E417" s="2" t="inlineStr">
+      <c r="E417" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F417" s="2" t="inlineStr">
+      <c r="F417" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G417" s="2" t="inlineStr">
+      <c r="G417" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442091621</t>
         </is>
       </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr"/>
-      <c r="J417" s="2" t="inlineStr"/>
-      <c r="K417" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L417" s="2" t="inlineStr"/>
+      <c r="H417" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I417" s="3" t="inlineStr"/>
+      <c r="J417" s="3" t="inlineStr"/>
+      <c r="K417" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L417" s="3" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="inlineStr">
+      <c r="A418" s="3" t="inlineStr">
         <is>
           <t>cab2e16cc06e37b72538b048c73fc189370b1ef3ec11ce9d7401793a5a539c7e</t>
         </is>
       </c>
-      <c r="B418" s="2" t="inlineStr">
+      <c r="B418" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C418" s="2" t="inlineStr">
+      <c r="C418" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D418" s="2" t="inlineStr">
+      <c r="D418" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E418" s="2" t="inlineStr">
+      <c r="E418" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F418" s="2" t="inlineStr">
+      <c r="F418" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G418" s="2" t="inlineStr">
+      <c r="G418" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442098361</t>
         </is>
       </c>
-      <c r="H418" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I418" s="2" t="inlineStr"/>
-      <c r="J418" s="2" t="inlineStr"/>
-      <c r="K418" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L418" s="2" t="inlineStr"/>
+      <c r="H418" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I418" s="3" t="inlineStr"/>
+      <c r="J418" s="3" t="inlineStr"/>
+      <c r="K418" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L418" s="3" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="inlineStr">
+      <c r="A419" s="3" t="inlineStr">
         <is>
           <t>933f17573189b18ea21ea1131e2910fb0bd5e69ca0c099491afec64ffd8e4310</t>
         </is>
       </c>
-      <c r="B419" s="2" t="inlineStr">
+      <c r="B419" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C419" s="2" t="inlineStr">
+      <c r="C419" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D419" s="2" t="inlineStr">
+      <c r="D419" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E419" s="2" t="inlineStr">
+      <c r="E419" s="3" t="inlineStr">
         <is>
           <t>Robotics - Software Development Engineer Intern - 2026 - Toronto</t>
         </is>
       </c>
-      <c r="F419" s="2" t="inlineStr">
+      <c r="F419" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G419" s="2" t="inlineStr">
+      <c r="G419" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443035914</t>
         </is>
       </c>
-      <c r="H419" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr"/>
-      <c r="J419" s="2" t="inlineStr"/>
-      <c r="K419" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L419" s="2" t="inlineStr"/>
+      <c r="H419" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I419" s="3" t="inlineStr"/>
+      <c r="J419" s="3" t="inlineStr"/>
+      <c r="K419" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L419" s="3" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="inlineStr">
+      <c r="A420" s="3" t="inlineStr">
         <is>
           <t>e98ce21945a141c1e6ee9886e914072c30fdea7edf62a316b854e76bb127aa8e</t>
         </is>
       </c>
-      <c r="B420" s="2" t="inlineStr">
+      <c r="B420" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C420" s="2" t="inlineStr">
+      <c r="C420" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D420" s="2" t="inlineStr">
+      <c r="D420" s="3" t="inlineStr">
         <is>
           <t>Kardium Inc.</t>
         </is>
       </c>
-      <c r="E420" s="2" t="inlineStr">
+      <c r="E420" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Hybrid) - September 2026</t>
         </is>
       </c>
-      <c r="F420" s="2" t="inlineStr">
+      <c r="F420" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G420" s="2" t="inlineStr">
+      <c r="G420" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442225727</t>
         </is>
       </c>
-      <c r="H420" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr"/>
-      <c r="J420" s="2" t="inlineStr"/>
-      <c r="K420" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L420" s="2" t="inlineStr"/>
+      <c r="H420" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I420" s="3" t="inlineStr"/>
+      <c r="J420" s="3" t="inlineStr"/>
+      <c r="K420" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L420" s="3" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="inlineStr">
+      <c r="A421" s="3" t="inlineStr">
         <is>
           <t>3c739bce2791b9d3187edb154b5b2ec2ec75654d224eb4c3abe04c54de8a4039</t>
         </is>
       </c>
-      <c r="B421" s="2" t="inlineStr">
+      <c r="B421" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C421" s="2" t="inlineStr">
+      <c r="C421" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D421" s="2" t="inlineStr">
+      <c r="D421" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E421" s="2" t="inlineStr">
+      <c r="E421" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F421" s="2" t="inlineStr">
+      <c r="F421" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G421" s="2" t="inlineStr">
+      <c r="G421" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442204058</t>
         </is>
       </c>
-      <c r="H421" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I421" s="2" t="inlineStr"/>
-      <c r="J421" s="2" t="inlineStr"/>
-      <c r="K421" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L421" s="2" t="inlineStr"/>
+      <c r="H421" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I421" s="3" t="inlineStr"/>
+      <c r="J421" s="3" t="inlineStr"/>
+      <c r="K421" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L421" s="3" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="inlineStr">
+      <c r="A422" s="3" t="inlineStr">
         <is>
           <t>4c3ae2742302c61b92735be82d110171995a5a6a6d0250155f522c8bcaf49d74</t>
         </is>
       </c>
-      <c r="B422" s="2" t="inlineStr">
+      <c r="B422" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C422" s="2" t="inlineStr">
+      <c r="C422" s="3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D422" s="2" t="inlineStr">
+      <c r="D422" s="3" t="inlineStr">
         <is>
           <t>Ribbon Communications</t>
         </is>
       </c>
-      <c r="E422" s="2" t="inlineStr">
+      <c r="E422" s="3" t="inlineStr">
         <is>
           <t>Canada (Co-op)</t>
         </is>
       </c>
-      <c r="F422" s="2" t="inlineStr">
+      <c r="F422" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G422" s="2" t="inlineStr">
+      <c r="G422" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434317680</t>
         </is>
       </c>
-      <c r="H422" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I422" s="2" t="inlineStr"/>
-      <c r="J422" s="2" t="inlineStr"/>
-      <c r="K422" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L422" s="2" t="inlineStr"/>
+      <c r="H422" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I422" s="3" t="inlineStr"/>
+      <c r="J422" s="3" t="inlineStr"/>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L422" s="3" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="inlineStr">
+      <c r="A423" s="3" t="inlineStr">
         <is>
           <t>f2229fff4aa7a6c3da3eb14263c0565edf502c11c09661487d723acb2ae23aab</t>
         </is>
       </c>
-      <c r="B423" s="2" t="inlineStr">
+      <c r="B423" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C423" s="2" t="inlineStr">
+      <c r="C423" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D423" s="2" t="inlineStr">
+      <c r="D423" s="3" t="inlineStr">
         <is>
           <t>EQ Bank</t>
         </is>
       </c>
-      <c r="E423" s="2" t="inlineStr">
+      <c r="E423" s="3" t="inlineStr">
         <is>
           <t>Intern, CloudOps</t>
         </is>
       </c>
-      <c r="F423" s="2" t="inlineStr">
+      <c r="F423" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G423" s="2" t="inlineStr">
+      <c r="G423" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f0baf0e899ea9845</t>
         </is>
       </c>
-      <c r="H423" s="2" t="inlineStr">
+      <c r="H423" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I423" s="2" t="inlineStr">
+      <c r="I423" s="3" t="inlineStr">
         <is>
           <t>**Join a Challenger**  
 At EQ, we're remaking banking so every Canadian gets ahead, every day. Serving nearly 4 million Canadians from coast to coast, we offer a wide variety of financial services from banking and lending, to trust and credit union solutions.  
 We've been at this since 197</t>
         </is>
       </c>
-      <c r="J423" s="2" t="inlineStr"/>
-      <c r="K423" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L423" s="2" t="inlineStr"/>
+      <c r="J423" s="3" t="inlineStr"/>
+      <c r="K423" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L423" s="3" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>fd044b277b696006e75da11e5e5bea0f0f0c7ee975f1cffa461e4f83f7c50c51</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5810850140?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L424" s="2" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>a2c3bf226c20ff5499ef97ed3d7723dd9deaae8824bb5cf77079dc9b9217b741</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5810852625?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr"/>
+      <c r="K425" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L425" s="2" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>39a9c1262a5eabfb39061b7c55d40a0c53647d5015a3fc31729401bc002e1f12</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442201222</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr"/>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>ac7c45f073cedd3a745b885d3fae07c98aeb5eaa73bb9fdd022ab9c4e4cc2140</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442089661</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr"/>
+      <c r="J427" s="2" t="inlineStr"/>
+      <c r="K427" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L427" s="2" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>390a52833a6dd919b10721aecc65d9ddb8db6f24d26f39390b8e7cec76c85388</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Canfor</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Carbon Reporting</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443304364</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr"/>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L428" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L428"/>
+  <dimension ref="A1:L438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22590,262 +22590,786 @@
       <c r="L423" s="3" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="inlineStr">
+      <c r="A424" s="3" t="inlineStr">
         <is>
           <t>fd044b277b696006e75da11e5e5bea0f0f0c7ee975f1cffa461e4f83f7c50c51</t>
         </is>
       </c>
-      <c r="B424" s="2" t="inlineStr">
+      <c r="B424" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C424" s="2" t="inlineStr">
+      <c r="C424" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D424" s="2" t="inlineStr">
+      <c r="D424" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E424" s="2" t="inlineStr">
+      <c r="E424" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F424" s="2" t="inlineStr">
+      <c r="F424" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G424" s="2" t="inlineStr">
+      <c r="G424" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5810850140?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H424" s="2" t="inlineStr">
+      <c r="H424" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I424" s="2" t="inlineStr">
+      <c r="I424" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
         </is>
       </c>
-      <c r="J424" s="2" t="inlineStr"/>
-      <c r="K424" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L424" s="2" t="inlineStr"/>
+      <c r="J424" s="3" t="inlineStr"/>
+      <c r="K424" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L424" s="3" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="inlineStr">
+      <c r="A425" s="3" t="inlineStr">
         <is>
           <t>a2c3bf226c20ff5499ef97ed3d7723dd9deaae8824bb5cf77079dc9b9217b741</t>
         </is>
       </c>
-      <c r="B425" s="2" t="inlineStr">
+      <c r="B425" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C425" s="2" t="inlineStr">
+      <c r="C425" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D425" s="2" t="inlineStr">
+      <c r="D425" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E425" s="2" t="inlineStr">
+      <c r="E425" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F425" s="2" t="inlineStr">
+      <c r="F425" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Waterloo region</t>
         </is>
       </c>
-      <c r="G425" s="2" t="inlineStr">
+      <c r="G425" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5810852625?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H425" s="2" t="inlineStr">
+      <c r="H425" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I425" s="2" t="inlineStr">
+      <c r="I425" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
         </is>
       </c>
-      <c r="J425" s="2" t="inlineStr"/>
-      <c r="K425" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L425" s="2" t="inlineStr"/>
+      <c r="J425" s="3" t="inlineStr"/>
+      <c r="K425" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L425" s="3" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="inlineStr">
+      <c r="A426" s="3" t="inlineStr">
         <is>
           <t>39a9c1262a5eabfb39061b7c55d40a0c53647d5015a3fc31729401bc002e1f12</t>
         </is>
       </c>
-      <c r="B426" s="2" t="inlineStr">
+      <c r="B426" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C426" s="2" t="inlineStr">
+      <c r="C426" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D426" s="2" t="inlineStr">
+      <c r="D426" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E426" s="2" t="inlineStr">
+      <c r="E426" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F426" s="2" t="inlineStr">
+      <c r="F426" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G426" s="2" t="inlineStr">
+      <c r="G426" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442201222</t>
         </is>
       </c>
-      <c r="H426" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I426" s="2" t="inlineStr"/>
-      <c r="J426" s="2" t="inlineStr"/>
-      <c r="K426" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L426" s="2" t="inlineStr"/>
+      <c r="H426" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I426" s="3" t="inlineStr"/>
+      <c r="J426" s="3" t="inlineStr"/>
+      <c r="K426" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L426" s="3" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="inlineStr">
+      <c r="A427" s="3" t="inlineStr">
         <is>
           <t>ac7c45f073cedd3a745b885d3fae07c98aeb5eaa73bb9fdd022ab9c4e4cc2140</t>
         </is>
       </c>
-      <c r="B427" s="2" t="inlineStr">
+      <c r="B427" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C427" s="2" t="inlineStr">
+      <c r="C427" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D427" s="2" t="inlineStr">
+      <c r="D427" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E427" s="2" t="inlineStr">
+      <c r="E427" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F427" s="2" t="inlineStr">
+      <c r="F427" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G427" s="2" t="inlineStr">
+      <c r="G427" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442089661</t>
         </is>
       </c>
-      <c r="H427" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I427" s="2" t="inlineStr"/>
-      <c r="J427" s="2" t="inlineStr"/>
-      <c r="K427" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L427" s="2" t="inlineStr"/>
+      <c r="H427" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I427" s="3" t="inlineStr"/>
+      <c r="J427" s="3" t="inlineStr"/>
+      <c r="K427" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L427" s="3" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="inlineStr">
+      <c r="A428" s="3" t="inlineStr">
         <is>
           <t>390a52833a6dd919b10721aecc65d9ddb8db6f24d26f39390b8e7cec76c85388</t>
         </is>
       </c>
-      <c r="B428" s="2" t="inlineStr">
+      <c r="B428" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C428" s="2" t="inlineStr">
+      <c r="C428" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D428" s="2" t="inlineStr">
+      <c r="D428" s="3" t="inlineStr">
         <is>
           <t>Canfor</t>
         </is>
       </c>
-      <c r="E428" s="2" t="inlineStr">
+      <c r="E428" s="3" t="inlineStr">
         <is>
           <t>Co-op, Carbon Reporting</t>
         </is>
       </c>
-      <c r="F428" s="2" t="inlineStr">
+      <c r="F428" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G428" s="2" t="inlineStr">
+      <c r="G428" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443304364</t>
         </is>
       </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I428" s="2" t="inlineStr"/>
-      <c r="J428" s="2" t="inlineStr"/>
-      <c r="K428" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L428" s="2" t="inlineStr"/>
+      <c r="H428" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I428" s="3" t="inlineStr"/>
+      <c r="J428" s="3" t="inlineStr"/>
+      <c r="K428" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L428" s="3" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>15a189d75bb119fc6ee8cf8125230f89a817455c36e61abfc3ed4e0c43d784dd</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo region, Ontario</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5811353767?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>info_outline X This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle. Applications will be reviewed on a rolling basis and it’s in the candidate’s best inte</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr"/>
+      <c r="K429" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L429" s="2" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>f92db0e68329404634877365f09906883e3474b0b71adfd4bc31db0305339a29</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>ecobee</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Sofware Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441009317</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr"/>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L430" s="2" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>a2a605b129c4b981e04431cc656638b53ac7e82842919d9bed85cc0fe2195da2</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunications Corp.</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-Op</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Gatineau, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443530259</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr"/>
+      <c r="J431" s="2" t="inlineStr"/>
+      <c r="K431" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L431" s="2" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>af6f99abff4f861db4503312f35412970110e90083f38fd36d06b61e9b345ecb</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Routing/IP Software Developer Intern (4-8 Months)</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442672078</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr"/>
+      <c r="J432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L432" s="2" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>c2ea396b5ad5343981700ad754cb134a304bdd33cbb81d2d0983729fd79c5810</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Kepler Communications</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>FPGA Digital Design Engineering Intern (January 2027) (4-16 months)</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=05ee97fdaa7d3e43</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>**At** **Kepler Communications****, we're not just imagining the future of on\-demand space connectivity \-** ***we're*** ***leading it!***
+Our mission is to provide real\-time on\-orbit connectivity for critical missions, enabling a new era of data\-driven intelligence and innovation. With **33 sa</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr"/>
+      <c r="K433" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L433" s="2" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>c63f3894309d0926b605f6417b0e84077f9709ebb7e180a0a1983810ef9981b2</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro Inc.</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Malware Research Intern</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f853f7edc710034c</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>TrendAI™, the global AI security leader and enterprise business unit of Trend Micro, empowers organizations with full AI visibility and consolidated security that inspires confidence, drives innovation, and eliminates risk.
+At TrendAI™, we’re always seeking exceptional talent; people who wan</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L434" s="2" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>9a1d2e16834b3288e17c6792c175e9e18489b2c0c424e694b78499a4a2a40680</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Foresters Financial</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer Co-op Student (4-month contract)</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3a3999724aa932bc</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>**Career Opportunity**
+======================
+**Role Title**
+--------------
+Quality Assurance Engineer Co\-op Student (4\-month contract)**Purpose of role**
+-------------------
+The Quality Assurance Engineer Co\-op offers a fantastic opportunity for a student to validate changes to workflows, b</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr"/>
+      <c r="K435" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L435" s="2" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>46b8b8f02c7dcc04631b1b5ff5e9411a29851f3a7a5747a38e63a86a29186e68</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Leesee</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Développeur Web / Mobile (Stage Cégep) - Web / Mobile Developer (Cegep Internship)</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442667924</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr"/>
+      <c r="J436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L436" s="2" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>233138bd7d7ca3ad0ab2434bceab57bb8e8962217d8343dfb68d2ca911addfa6</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Sun Life</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>Student, DevOps Engineer (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443597422</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr"/>
+      <c r="J437" s="2" t="inlineStr"/>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L437" s="2" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>5d04a7ab326fec3ffefb0c0edeaaaf20c047a2ffa0c9b1b02dde84f913fd124a</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>Sun Life</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>Student, Associate Data Engineer (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442764705</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr"/>
+      <c r="J438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L438" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L438"/>
+  <dimension ref="A1:L439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22848,361 +22848,361 @@
       <c r="L428" s="3" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="inlineStr">
+      <c r="A429" s="3" t="inlineStr">
         <is>
           <t>15a189d75bb119fc6ee8cf8125230f89a817455c36e61abfc3ed4e0c43d784dd</t>
         </is>
       </c>
-      <c r="B429" s="2" t="inlineStr">
+      <c r="B429" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C429" s="2" t="inlineStr">
+      <c r="C429" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D429" s="2" t="inlineStr">
+      <c r="D429" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E429" s="2" t="inlineStr">
+      <c r="E429" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F429" s="2" t="inlineStr">
+      <c r="F429" s="3" t="inlineStr">
         <is>
           <t>Waterloo region, Ontario</t>
         </is>
       </c>
-      <c r="G429" s="2" t="inlineStr">
+      <c r="G429" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5811353767?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H429" s="2" t="inlineStr">
+      <c r="H429" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I429" s="2" t="inlineStr">
+      <c r="I429" s="3" t="inlineStr">
         <is>
           <t>info_outline X This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle. Applications will be reviewed on a rolling basis and it’s in the candidate’s best inte</t>
         </is>
       </c>
-      <c r="J429" s="2" t="inlineStr"/>
-      <c r="K429" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L429" s="2" t="inlineStr"/>
+      <c r="J429" s="3" t="inlineStr"/>
+      <c r="K429" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L429" s="3" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="inlineStr">
+      <c r="A430" s="3" t="inlineStr">
         <is>
           <t>f92db0e68329404634877365f09906883e3474b0b71adfd4bc31db0305339a29</t>
         </is>
       </c>
-      <c r="B430" s="2" t="inlineStr">
+      <c r="B430" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C430" s="2" t="inlineStr">
+      <c r="C430" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D430" s="2" t="inlineStr">
+      <c r="D430" s="3" t="inlineStr">
         <is>
           <t>ecobee</t>
         </is>
       </c>
-      <c r="E430" s="2" t="inlineStr">
+      <c r="E430" s="3" t="inlineStr">
         <is>
           <t>Sofware Engineer - Intern</t>
         </is>
       </c>
-      <c r="F430" s="2" t="inlineStr">
+      <c r="F430" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G430" s="2" t="inlineStr">
+      <c r="G430" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441009317</t>
         </is>
       </c>
-      <c r="H430" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I430" s="2" t="inlineStr"/>
-      <c r="J430" s="2" t="inlineStr"/>
-      <c r="K430" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L430" s="2" t="inlineStr"/>
+      <c r="H430" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I430" s="3" t="inlineStr"/>
+      <c r="J430" s="3" t="inlineStr"/>
+      <c r="K430" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L430" s="3" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="inlineStr">
+      <c r="A431" s="3" t="inlineStr">
         <is>
           <t>a2a605b129c4b981e04431cc656638b53ac7e82842919d9bed85cc0fe2195da2</t>
         </is>
       </c>
-      <c r="B431" s="2" t="inlineStr">
+      <c r="B431" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C431" s="2" t="inlineStr">
+      <c r="C431" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D431" s="2" t="inlineStr">
+      <c r="D431" s="3" t="inlineStr">
         <is>
           <t>Comtech Telecommunications Corp.</t>
         </is>
       </c>
-      <c r="E431" s="2" t="inlineStr">
+      <c r="E431" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-Op</t>
         </is>
       </c>
-      <c r="F431" s="2" t="inlineStr">
+      <c r="F431" s="3" t="inlineStr">
         <is>
           <t>Gatineau, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G431" s="2" t="inlineStr">
+      <c r="G431" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443530259</t>
         </is>
       </c>
-      <c r="H431" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I431" s="2" t="inlineStr"/>
-      <c r="J431" s="2" t="inlineStr"/>
-      <c r="K431" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L431" s="2" t="inlineStr"/>
+      <c r="H431" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I431" s="3" t="inlineStr"/>
+      <c r="J431" s="3" t="inlineStr"/>
+      <c r="K431" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L431" s="3" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="inlineStr">
+      <c r="A432" s="3" t="inlineStr">
         <is>
           <t>af6f99abff4f861db4503312f35412970110e90083f38fd36d06b61e9b345ecb</t>
         </is>
       </c>
-      <c r="B432" s="2" t="inlineStr">
+      <c r="B432" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C432" s="2" t="inlineStr">
+      <c r="C432" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D432" s="2" t="inlineStr">
+      <c r="D432" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E432" s="2" t="inlineStr">
+      <c r="E432" s="3" t="inlineStr">
         <is>
           <t>Routing/IP Software Developer Intern (4-8 Months)</t>
         </is>
       </c>
-      <c r="F432" s="2" t="inlineStr">
+      <c r="F432" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G432" s="2" t="inlineStr">
+      <c r="G432" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442672078</t>
         </is>
       </c>
-      <c r="H432" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I432" s="2" t="inlineStr"/>
-      <c r="J432" s="2" t="inlineStr"/>
-      <c r="K432" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L432" s="2" t="inlineStr"/>
+      <c r="H432" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I432" s="3" t="inlineStr"/>
+      <c r="J432" s="3" t="inlineStr"/>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L432" s="3" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="inlineStr">
+      <c r="A433" s="3" t="inlineStr">
         <is>
           <t>c2ea396b5ad5343981700ad754cb134a304bdd33cbb81d2d0983729fd79c5810</t>
         </is>
       </c>
-      <c r="B433" s="2" t="inlineStr">
+      <c r="B433" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C433" s="2" t="inlineStr">
+      <c r="C433" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D433" s="2" t="inlineStr">
+      <c r="D433" s="3" t="inlineStr">
         <is>
           <t>Kepler Communications</t>
         </is>
       </c>
-      <c r="E433" s="2" t="inlineStr">
+      <c r="E433" s="3" t="inlineStr">
         <is>
           <t>FPGA Digital Design Engineering Intern (January 2027) (4-16 months)</t>
         </is>
       </c>
-      <c r="F433" s="2" t="inlineStr">
+      <c r="F433" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G433" s="2" t="inlineStr">
+      <c r="G433" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=05ee97fdaa7d3e43</t>
         </is>
       </c>
-      <c r="H433" s="2" t="inlineStr">
+      <c r="H433" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I433" s="2" t="inlineStr">
+      <c r="I433" s="3" t="inlineStr">
         <is>
           <t>**At** **Kepler Communications****, we're not just imagining the future of on\-demand space connectivity \-** ***we're*** ***leading it!***
 Our mission is to provide real\-time on\-orbit connectivity for critical missions, enabling a new era of data\-driven intelligence and innovation. With **33 sa</t>
         </is>
       </c>
-      <c r="J433" s="2" t="inlineStr"/>
-      <c r="K433" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L433" s="2" t="inlineStr"/>
+      <c r="J433" s="3" t="inlineStr"/>
+      <c r="K433" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L433" s="3" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="inlineStr">
+      <c r="A434" s="3" t="inlineStr">
         <is>
           <t>c63f3894309d0926b605f6417b0e84077f9709ebb7e180a0a1983810ef9981b2</t>
         </is>
       </c>
-      <c r="B434" s="2" t="inlineStr">
+      <c r="B434" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C434" s="2" t="inlineStr">
+      <c r="C434" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D434" s="2" t="inlineStr">
+      <c r="D434" s="3" t="inlineStr">
         <is>
           <t>Trend Micro Inc.</t>
         </is>
       </c>
-      <c r="E434" s="2" t="inlineStr">
+      <c r="E434" s="3" t="inlineStr">
         <is>
           <t>Malware Research Intern</t>
         </is>
       </c>
-      <c r="F434" s="2" t="inlineStr">
+      <c r="F434" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G434" s="2" t="inlineStr">
+      <c r="G434" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f853f7edc710034c</t>
         </is>
       </c>
-      <c r="H434" s="2" t="inlineStr">
+      <c r="H434" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I434" s="2" t="inlineStr">
+      <c r="I434" s="3" t="inlineStr">
         <is>
           <t>TrendAI™, the global AI security leader and enterprise business unit of Trend Micro, empowers organizations with full AI visibility and consolidated security that inspires confidence, drives innovation, and eliminates risk.
 At TrendAI™, we’re always seeking exceptional talent; people who wan</t>
         </is>
       </c>
-      <c r="J434" s="2" t="inlineStr"/>
-      <c r="K434" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L434" s="2" t="inlineStr"/>
+      <c r="J434" s="3" t="inlineStr"/>
+      <c r="K434" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L434" s="3" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="inlineStr">
+      <c r="A435" s="3" t="inlineStr">
         <is>
           <t>9a1d2e16834b3288e17c6792c175e9e18489b2c0c424e694b78499a4a2a40680</t>
         </is>
       </c>
-      <c r="B435" s="2" t="inlineStr">
+      <c r="B435" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C435" s="2" t="inlineStr">
+      <c r="C435" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D435" s="2" t="inlineStr">
+      <c r="D435" s="3" t="inlineStr">
         <is>
           <t>Foresters Financial</t>
         </is>
       </c>
-      <c r="E435" s="2" t="inlineStr">
+      <c r="E435" s="3" t="inlineStr">
         <is>
           <t>Quality Assurance Engineer Co-op Student (4-month contract)</t>
         </is>
       </c>
-      <c r="F435" s="2" t="inlineStr">
+      <c r="F435" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G435" s="2" t="inlineStr">
+      <c r="G435" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3a3999724aa932bc</t>
         </is>
       </c>
-      <c r="H435" s="2" t="inlineStr">
+      <c r="H435" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I435" s="2" t="inlineStr">
+      <c r="I435" s="3" t="inlineStr">
         <is>
           <t>**Career Opportunity**
 ======================
@@ -23213,163 +23213,213 @@
 The Quality Assurance Engineer Co\-op offers a fantastic opportunity for a student to validate changes to workflows, b</t>
         </is>
       </c>
-      <c r="J435" s="2" t="inlineStr"/>
-      <c r="K435" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L435" s="2" t="inlineStr"/>
+      <c r="J435" s="3" t="inlineStr"/>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L435" s="3" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="inlineStr">
+      <c r="A436" s="3" t="inlineStr">
         <is>
           <t>46b8b8f02c7dcc04631b1b5ff5e9411a29851f3a7a5747a38e63a86a29186e68</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
+      <c r="B436" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
+      <c r="C436" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D436" s="2" t="inlineStr">
+      <c r="D436" s="3" t="inlineStr">
         <is>
           <t>Leesee</t>
         </is>
       </c>
-      <c r="E436" s="2" t="inlineStr">
+      <c r="E436" s="3" t="inlineStr">
         <is>
           <t>Développeur Web / Mobile (Stage Cégep) - Web / Mobile Developer (Cegep Internship)</t>
         </is>
       </c>
-      <c r="F436" s="2" t="inlineStr">
+      <c r="F436" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G436" s="2" t="inlineStr">
+      <c r="G436" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442667924</t>
         </is>
       </c>
-      <c r="H436" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I436" s="2" t="inlineStr"/>
-      <c r="J436" s="2" t="inlineStr"/>
-      <c r="K436" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L436" s="2" t="inlineStr"/>
+      <c r="H436" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I436" s="3" t="inlineStr"/>
+      <c r="J436" s="3" t="inlineStr"/>
+      <c r="K436" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L436" s="3" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="inlineStr">
+      <c r="A437" s="3" t="inlineStr">
         <is>
           <t>233138bd7d7ca3ad0ab2434bceab57bb8e8962217d8343dfb68d2ca911addfa6</t>
         </is>
       </c>
-      <c r="B437" s="2" t="inlineStr">
+      <c r="B437" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C437" s="2" t="inlineStr">
+      <c r="C437" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D437" s="2" t="inlineStr">
+      <c r="D437" s="3" t="inlineStr">
         <is>
           <t>Sun Life</t>
         </is>
       </c>
-      <c r="E437" s="2" t="inlineStr">
+      <c r="E437" s="3" t="inlineStr">
         <is>
           <t>Student, DevOps Engineer (Fall 2026)</t>
         </is>
       </c>
-      <c r="F437" s="2" t="inlineStr">
+      <c r="F437" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G437" s="2" t="inlineStr">
+      <c r="G437" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443597422</t>
         </is>
       </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I437" s="2" t="inlineStr"/>
-      <c r="J437" s="2" t="inlineStr"/>
-      <c r="K437" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L437" s="2" t="inlineStr"/>
+      <c r="H437" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I437" s="3" t="inlineStr"/>
+      <c r="J437" s="3" t="inlineStr"/>
+      <c r="K437" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L437" s="3" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="inlineStr">
+      <c r="A438" s="3" t="inlineStr">
         <is>
           <t>5d04a7ab326fec3ffefb0c0edeaaaf20c047a2ffa0c9b1b02dde84f913fd124a</t>
         </is>
       </c>
-      <c r="B438" s="2" t="inlineStr">
+      <c r="B438" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C438" s="2" t="inlineStr">
+      <c r="C438" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D438" s="2" t="inlineStr">
+      <c r="D438" s="3" t="inlineStr">
         <is>
           <t>Sun Life</t>
         </is>
       </c>
-      <c r="E438" s="2" t="inlineStr">
+      <c r="E438" s="3" t="inlineStr">
         <is>
           <t>Student, Associate Data Engineer (Fall 2026)</t>
         </is>
       </c>
-      <c r="F438" s="2" t="inlineStr">
+      <c r="F438" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G438" s="2" t="inlineStr">
+      <c r="G438" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442764705</t>
         </is>
       </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I438" s="2" t="inlineStr"/>
-      <c r="J438" s="2" t="inlineStr"/>
-      <c r="K438" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L438" s="2" t="inlineStr"/>
+      <c r="H438" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I438" s="3" t="inlineStr"/>
+      <c r="J438" s="3" t="inlineStr"/>
+      <c r="K438" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L438" s="3" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>9fc9a268be128c37b7944016d9b9f18d21b3445705690f6c18b78ec9e70b64d7</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, MS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442097406</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr"/>
+      <c r="J439" s="2" t="inlineStr"/>
+      <c r="K439" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L439" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L439"/>
+  <dimension ref="A1:L444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23372,54 +23372,318 @@
       <c r="L438" s="3" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="inlineStr">
+      <c r="A439" s="3" t="inlineStr">
         <is>
           <t>9fc9a268be128c37b7944016d9b9f18d21b3445705690f6c18b78ec9e70b64d7</t>
         </is>
       </c>
-      <c r="B439" s="2" t="inlineStr">
+      <c r="B439" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C439" s="2" t="inlineStr">
+      <c r="C439" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D439" s="2" t="inlineStr">
+      <c r="D439" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E439" s="2" t="inlineStr">
+      <c r="E439" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, MS, Summer 2027</t>
         </is>
       </c>
-      <c r="F439" s="2" t="inlineStr">
+      <c r="F439" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G439" s="2" t="inlineStr">
+      <c r="G439" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442097406</t>
         </is>
       </c>
-      <c r="H439" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I439" s="2" t="inlineStr"/>
-      <c r="J439" s="2" t="inlineStr"/>
-      <c r="K439" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L439" s="2" t="inlineStr"/>
+      <c r="H439" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I439" s="3" t="inlineStr"/>
+      <c r="J439" s="3" t="inlineStr"/>
+      <c r="K439" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L439" s="3" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>b11830d540bbb4391dfeae55bc93e22834f95aa251053a169f1714351d390817</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern, BS, Summer 2027</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo region, Ontario</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5812846022?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>info_outline X This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle. Applications will be reviewed on a rolling basis and it’s in the candidate’s best inte</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L440" s="2" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>9b85f6f6f66a36c631181d39d046e42f52d5b1e210121f13f41508af53c9e92c</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>CPKC</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>Intern Cloud Developer</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=c00383257b9e963d</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>Join CPKC, North America’s first transnational railroad connecting U.S., Canada, and Mexico, where your career drives progress and safety is paramount. We connect communities, fuel economic growth, and provide meaningful work in a culture that values diversity, accountability, and pride. With opport</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr"/>
+      <c r="K441" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L441" s="2" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>8bf58a08f2488c364a177b97a2e6ed0662eb8cd37a833fbc323cc49b3cf5d1ed</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Architectural Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=42d8e65dba8e6b4a</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description** **Work with Us. Change the World.**
+At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L442" s="2" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>864fa9120f59fab59852a4d7ddd3ad8d77844d50cf5b8117ff35252c9a096fd7</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Telecommunications and Electronic Security Systems Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=2a923d28f878ccfb</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description** **Work with Us. Change the World.**
+At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr"/>
+      <c r="K443" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L443" s="2" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>a9450425f7a6a50a7e05a08eae5a2a2ff19abed794b693fa5ca61a214b90df0c</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441004064</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr"/>
+      <c r="J444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L444" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L444"/>
+  <dimension ref="A1:L449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23422,268 +23422,526 @@
       <c r="L439" s="3" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="inlineStr">
+      <c r="A440" s="3" t="inlineStr">
         <is>
           <t>b11830d540bbb4391dfeae55bc93e22834f95aa251053a169f1714351d390817</t>
         </is>
       </c>
-      <c r="B440" s="2" t="inlineStr">
+      <c r="B440" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C440" s="2" t="inlineStr">
+      <c r="C440" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D440" s="2" t="inlineStr">
+      <c r="D440" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E440" s="2" t="inlineStr">
+      <c r="E440" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern, BS, Summer 2027</t>
         </is>
       </c>
-      <c r="F440" s="2" t="inlineStr">
+      <c r="F440" s="3" t="inlineStr">
         <is>
           <t>Waterloo region, Ontario</t>
         </is>
       </c>
-      <c r="G440" s="2" t="inlineStr">
+      <c r="G440" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5812846022?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H440" s="2" t="inlineStr">
+      <c r="H440" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I440" s="2" t="inlineStr">
+      <c r="I440" s="3" t="inlineStr">
         <is>
           <t>info_outline X This posting is for students who want early consideration for our Summer 2027 roles. If you aren't ready to apply yet, the same applications will open again during our regular fall recruiting cycle. Applications will be reviewed on a rolling basis and it’s in the candidate’s best inte</t>
         </is>
       </c>
-      <c r="J440" s="2" t="inlineStr"/>
-      <c r="K440" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L440" s="2" t="inlineStr"/>
+      <c r="J440" s="3" t="inlineStr"/>
+      <c r="K440" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L440" s="3" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="inlineStr">
+      <c r="A441" s="3" t="inlineStr">
         <is>
           <t>9b85f6f6f66a36c631181d39d046e42f52d5b1e210121f13f41508af53c9e92c</t>
         </is>
       </c>
-      <c r="B441" s="2" t="inlineStr">
+      <c r="B441" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C441" s="2" t="inlineStr">
+      <c r="C441" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D441" s="2" t="inlineStr">
+      <c r="D441" s="3" t="inlineStr">
         <is>
           <t>CPKC</t>
         </is>
       </c>
-      <c r="E441" s="2" t="inlineStr">
+      <c r="E441" s="3" t="inlineStr">
         <is>
           <t>Intern Cloud Developer</t>
         </is>
       </c>
-      <c r="F441" s="2" t="inlineStr">
+      <c r="F441" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G441" s="2" t="inlineStr">
+      <c r="G441" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=c00383257b9e963d</t>
         </is>
       </c>
-      <c r="H441" s="2" t="inlineStr">
+      <c r="H441" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I441" s="2" t="inlineStr">
+      <c r="I441" s="3" t="inlineStr">
         <is>
           <t>Join CPKC, North America’s first transnational railroad connecting U.S., Canada, and Mexico, where your career drives progress and safety is paramount. We connect communities, fuel economic growth, and provide meaningful work in a culture that values diversity, accountability, and pride. With opport</t>
         </is>
       </c>
-      <c r="J441" s="2" t="inlineStr"/>
-      <c r="K441" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L441" s="2" t="inlineStr"/>
+      <c r="J441" s="3" t="inlineStr"/>
+      <c r="K441" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L441" s="3" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="inlineStr">
+      <c r="A442" s="3" t="inlineStr">
         <is>
           <t>8bf58a08f2488c364a177b97a2e6ed0662eb8cd37a833fbc323cc49b3cf5d1ed</t>
         </is>
       </c>
-      <c r="B442" s="2" t="inlineStr">
+      <c r="B442" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C442" s="2" t="inlineStr">
+      <c r="C442" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D442" s="2" t="inlineStr">
+      <c r="D442" s="3" t="inlineStr">
         <is>
           <t>AECOM</t>
         </is>
       </c>
-      <c r="E442" s="2" t="inlineStr">
+      <c r="E442" s="3" t="inlineStr">
         <is>
           <t>Architectural Engineering Intern</t>
         </is>
       </c>
-      <c r="F442" s="2" t="inlineStr">
+      <c r="F442" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G442" s="2" t="inlineStr">
+      <c r="G442" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=42d8e65dba8e6b4a</t>
         </is>
       </c>
-      <c r="H442" s="2" t="inlineStr">
+      <c r="H442" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I442" s="2" t="inlineStr">
+      <c r="I442" s="3" t="inlineStr">
         <is>
           <t>**Company Description** **Work with Us. Change the World.**
 At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
         </is>
       </c>
-      <c r="J442" s="2" t="inlineStr"/>
-      <c r="K442" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L442" s="2" t="inlineStr"/>
+      <c r="J442" s="3" t="inlineStr"/>
+      <c r="K442" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L442" s="3" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="inlineStr">
+      <c r="A443" s="3" t="inlineStr">
         <is>
           <t>864fa9120f59fab59852a4d7ddd3ad8d77844d50cf5b8117ff35252c9a096fd7</t>
         </is>
       </c>
-      <c r="B443" s="2" t="inlineStr">
+      <c r="B443" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
+      <c r="C443" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D443" s="2" t="inlineStr">
+      <c r="D443" s="3" t="inlineStr">
         <is>
           <t>AECOM</t>
         </is>
       </c>
-      <c r="E443" s="2" t="inlineStr">
+      <c r="E443" s="3" t="inlineStr">
         <is>
           <t>Telecommunications and Electronic Security Systems Engineering Intern</t>
         </is>
       </c>
-      <c r="F443" s="2" t="inlineStr">
+      <c r="F443" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G443" s="2" t="inlineStr">
+      <c r="G443" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=2a923d28f878ccfb</t>
         </is>
       </c>
-      <c r="H443" s="2" t="inlineStr">
+      <c r="H443" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I443" s="2" t="inlineStr">
+      <c r="I443" s="3" t="inlineStr">
         <is>
           <t>**Company Description** **Work with Us. Change the World.**
 At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
         </is>
       </c>
-      <c r="J443" s="2" t="inlineStr"/>
-      <c r="K443" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L443" s="2" t="inlineStr"/>
+      <c r="J443" s="3" t="inlineStr"/>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L443" s="3" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="inlineStr">
+      <c r="A444" s="3" t="inlineStr">
         <is>
           <t>a9450425f7a6a50a7e05a08eae5a2a2ff19abed794b693fa5ca61a214b90df0c</t>
         </is>
       </c>
-      <c r="B444" s="2" t="inlineStr">
+      <c r="B444" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C444" s="2" t="inlineStr">
+      <c r="C444" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D444" s="2" t="inlineStr">
+      <c r="D444" s="3" t="inlineStr">
         <is>
           <t>Stealth</t>
         </is>
       </c>
-      <c r="E444" s="2" t="inlineStr">
+      <c r="E444" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F444" s="2" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr">
+      <c r="F444" s="3" t="inlineStr"/>
+      <c r="G444" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441004064</t>
         </is>
       </c>
-      <c r="H444" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr"/>
-      <c r="J444" s="2" t="inlineStr"/>
-      <c r="K444" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L444" s="2" t="inlineStr"/>
+      <c r="H444" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I444" s="3" t="inlineStr"/>
+      <c r="J444" s="3" t="inlineStr"/>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L444" s="3" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>20caf637685c3913072e7c80bad41d7fed4c0ab9cf93f930f27f26d0f19163a1</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (Later Influence)</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444249728</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr"/>
+      <c r="J445" s="2" t="inlineStr"/>
+      <c r="K445" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L445" s="2" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>3be7e34ba8d2875a76d57b4f3bd77961d067c8c88f048c017adab72c46703555</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>TommieTest</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (Later Influence)</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444224689</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr"/>
+      <c r="J446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L446" s="2" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>0562e736c59f9a98d44961e013b1c4bcfdc6ce9cfa39c407907e79a5eb40077a</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Hach Company</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Aquatic Informatics - Machine Learning Co-Op (Intern)</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>London, ON, CA</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6cb787a9ebefee48</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>Imagine yourself…
+* Doing meaningful work that makes an everyday impact on the world around you.
+* Growing your expertise and expanding your skillset with every project.
+It’s possible with a role at **Aquatic Informatics** (**https://aquaticinformatics.com/**).
+Aquatic Informatics (AQI), a **Ve</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr"/>
+      <c r="K447" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L447" s="2" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>5ca875938ef52ec114325c1166c1792fafda58be7affc125e4ddb4968a25d288</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Government of Nova Scotia</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst (Co-op Student)</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441984614</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr"/>
+      <c r="J448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L448" s="2" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>ff43dd8b7ee2e8340d8c3420e77f9aeb6826cfd3b254335b8806616bc65a76ef</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Valin Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Internship in Data Science with Python</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Valin, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435954657</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr"/>
+      <c r="J449" s="2" t="inlineStr"/>
+      <c r="K449" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L449" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L449"/>
+  <dimension ref="A1:L452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23686,147 +23686,147 @@
       <c r="L444" s="3" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="inlineStr">
+      <c r="A445" s="3" t="inlineStr">
         <is>
           <t>20caf637685c3913072e7c80bad41d7fed4c0ab9cf93f930f27f26d0f19163a1</t>
         </is>
       </c>
-      <c r="B445" s="2" t="inlineStr">
+      <c r="B445" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C445" s="2" t="inlineStr">
+      <c r="C445" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D445" s="2" t="inlineStr">
+      <c r="D445" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E445" s="2" t="inlineStr">
+      <c r="E445" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (Later Influence)</t>
         </is>
       </c>
-      <c r="F445" s="2" t="inlineStr">
+      <c r="F445" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G445" s="2" t="inlineStr">
+      <c r="G445" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444249728</t>
         </is>
       </c>
-      <c r="H445" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="inlineStr"/>
-      <c r="J445" s="2" t="inlineStr"/>
-      <c r="K445" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L445" s="2" t="inlineStr"/>
+      <c r="H445" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I445" s="3" t="inlineStr"/>
+      <c r="J445" s="3" t="inlineStr"/>
+      <c r="K445" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L445" s="3" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="inlineStr">
+      <c r="A446" s="3" t="inlineStr">
         <is>
           <t>3be7e34ba8d2875a76d57b4f3bd77961d067c8c88f048c017adab72c46703555</t>
         </is>
       </c>
-      <c r="B446" s="2" t="inlineStr">
+      <c r="B446" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C446" s="2" t="inlineStr">
+      <c r="C446" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D446" s="2" t="inlineStr">
+      <c r="D446" s="3" t="inlineStr">
         <is>
           <t>TommieTest</t>
         </is>
       </c>
-      <c r="E446" s="2" t="inlineStr">
+      <c r="E446" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (Later Influence)</t>
         </is>
       </c>
-      <c r="F446" s="2" t="inlineStr">
+      <c r="F446" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G446" s="2" t="inlineStr">
+      <c r="G446" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444224689</t>
         </is>
       </c>
-      <c r="H446" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr"/>
-      <c r="J446" s="2" t="inlineStr"/>
-      <c r="K446" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L446" s="2" t="inlineStr"/>
+      <c r="H446" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I446" s="3" t="inlineStr"/>
+      <c r="J446" s="3" t="inlineStr"/>
+      <c r="K446" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L446" s="3" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="inlineStr">
+      <c r="A447" s="3" t="inlineStr">
         <is>
           <t>0562e736c59f9a98d44961e013b1c4bcfdc6ce9cfa39c407907e79a5eb40077a</t>
         </is>
       </c>
-      <c r="B447" s="2" t="inlineStr">
+      <c r="B447" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C447" s="2" t="inlineStr">
+      <c r="C447" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D447" s="2" t="inlineStr">
+      <c r="D447" s="3" t="inlineStr">
         <is>
           <t>Hach Company</t>
         </is>
       </c>
-      <c r="E447" s="2" t="inlineStr">
+      <c r="E447" s="3" t="inlineStr">
         <is>
           <t>Aquatic Informatics - Machine Learning Co-Op (Intern)</t>
         </is>
       </c>
-      <c r="F447" s="2" t="inlineStr">
+      <c r="F447" s="3" t="inlineStr">
         <is>
           <t>London, ON, CA</t>
         </is>
       </c>
-      <c r="G447" s="2" t="inlineStr">
+      <c r="G447" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6cb787a9ebefee48</t>
         </is>
       </c>
-      <c r="H447" s="2" t="inlineStr">
+      <c r="H447" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I447" s="2" t="inlineStr">
+      <c r="I447" s="3" t="inlineStr">
         <is>
           <t>Imagine yourself…
 * Doing meaningful work that makes an everyday impact on the world around you.
@@ -23835,113 +23835,273 @@
 Aquatic Informatics (AQI), a **Ve</t>
         </is>
       </c>
-      <c r="J447" s="2" t="inlineStr"/>
-      <c r="K447" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L447" s="2" t="inlineStr"/>
+      <c r="J447" s="3" t="inlineStr"/>
+      <c r="K447" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L447" s="3" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="inlineStr">
+      <c r="A448" s="3" t="inlineStr">
         <is>
           <t>5ca875938ef52ec114325c1166c1792fafda58be7affc125e4ddb4968a25d288</t>
         </is>
       </c>
-      <c r="B448" s="2" t="inlineStr">
+      <c r="B448" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C448" s="2" t="inlineStr">
+      <c r="C448" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D448" s="2" t="inlineStr">
+      <c r="D448" s="3" t="inlineStr">
         <is>
           <t>Government of Nova Scotia</t>
         </is>
       </c>
-      <c r="E448" s="2" t="inlineStr">
+      <c r="E448" s="3" t="inlineStr">
         <is>
           <t>Data Analyst (Co-op Student)</t>
         </is>
       </c>
-      <c r="F448" s="2" t="inlineStr">
+      <c r="F448" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G448" s="2" t="inlineStr">
+      <c r="G448" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441984614</t>
         </is>
       </c>
-      <c r="H448" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I448" s="2" t="inlineStr"/>
-      <c r="J448" s="2" t="inlineStr"/>
-      <c r="K448" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L448" s="2" t="inlineStr"/>
+      <c r="H448" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I448" s="3" t="inlineStr"/>
+      <c r="J448" s="3" t="inlineStr"/>
+      <c r="K448" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L448" s="3" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="inlineStr">
+      <c r="A449" s="3" t="inlineStr">
         <is>
           <t>ff43dd8b7ee2e8340d8c3420e77f9aeb6826cfd3b254335b8806616bc65a76ef</t>
         </is>
       </c>
-      <c r="B449" s="2" t="inlineStr">
+      <c r="B449" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C449" s="2" t="inlineStr">
+      <c r="C449" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D449" s="2" t="inlineStr">
+      <c r="D449" s="3" t="inlineStr">
         <is>
           <t>Valin Solutions Limited</t>
         </is>
       </c>
-      <c r="E449" s="2" t="inlineStr">
+      <c r="E449" s="3" t="inlineStr">
         <is>
           <t>Internship in Data Science with Python</t>
         </is>
       </c>
-      <c r="F449" s="2" t="inlineStr">
+      <c r="F449" s="3" t="inlineStr">
         <is>
           <t>Mont-Valin, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G449" s="2" t="inlineStr">
+      <c r="G449" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435954657</t>
         </is>
       </c>
-      <c r="H449" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I449" s="2" t="inlineStr"/>
-      <c r="J449" s="2" t="inlineStr"/>
-      <c r="K449" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L449" s="2" t="inlineStr"/>
+      <c r="H449" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I449" s="3" t="inlineStr"/>
+      <c r="J449" s="3" t="inlineStr"/>
+      <c r="K449" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L449" s="3" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>92512ccbd89b79b6a8881b269cb6d6e2153d1a214c9b2691d956f0b3fd38ad97</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>CPKC</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Intern Cloud Developer</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444715702</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr"/>
+      <c r="J450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L450" s="2" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>1296ac58909932f85b2459e4482d44adfd8b9e086fb1c90580a70b41f4dc9727</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Introba</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=b5e758d897c2541f</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**WHERE PASSION \+ PURPOSE ALIGN**
+We are the curious. Problem solvers. Driven to unlock the potential in every system. Across five countries are 1,100 engineers, designers, and consultants collaborating to elevate the human experience, create more resilient communities, and protect the health of </t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr"/>
+      <c r="K451" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L451" s="2" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>02c1165808c08d4bf7dea212053c5e6e81a75a12280837e2e2f05e63e8d4eb0c</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer Intern - Fall</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=e7bcc5b6add0e088</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description**  
+CRB's nearly 1,400 expert professionals drive innovative, life\-changing and life\-saving solutions for manufacturers in the life sciences and food and beverage industries. Our mission, vision, and core values put client satisfaction and employee experience at the center o</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L452" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L452"/>
+  <dimension ref="A1:L454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23944,164 +23944,264 @@
       <c r="L449" s="3" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="inlineStr">
+      <c r="A450" s="3" t="inlineStr">
         <is>
           <t>92512ccbd89b79b6a8881b269cb6d6e2153d1a214c9b2691d956f0b3fd38ad97</t>
         </is>
       </c>
-      <c r="B450" s="2" t="inlineStr">
+      <c r="B450" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="C450" s="2" t="inlineStr">
+      <c r="C450" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D450" s="2" t="inlineStr">
+      <c r="D450" s="3" t="inlineStr">
         <is>
           <t>CPKC</t>
         </is>
       </c>
-      <c r="E450" s="2" t="inlineStr">
+      <c r="E450" s="3" t="inlineStr">
         <is>
           <t>Intern Cloud Developer</t>
         </is>
       </c>
-      <c r="F450" s="2" t="inlineStr">
+      <c r="F450" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G450" s="2" t="inlineStr">
+      <c r="G450" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444715702</t>
         </is>
       </c>
-      <c r="H450" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr"/>
-      <c r="J450" s="2" t="inlineStr"/>
-      <c r="K450" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L450" s="2" t="inlineStr"/>
+      <c r="H450" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I450" s="3" t="inlineStr"/>
+      <c r="J450" s="3" t="inlineStr"/>
+      <c r="K450" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L450" s="3" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="inlineStr">
+      <c r="A451" s="3" t="inlineStr">
         <is>
           <t>1296ac58909932f85b2459e4482d44adfd8b9e086fb1c90580a70b41f4dc9727</t>
         </is>
       </c>
-      <c r="B451" s="2" t="inlineStr">
+      <c r="B451" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="C451" s="2" t="inlineStr">
+      <c r="C451" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D451" s="2" t="inlineStr">
+      <c r="D451" s="3" t="inlineStr">
         <is>
           <t>Introba</t>
         </is>
       </c>
-      <c r="E451" s="2" t="inlineStr">
+      <c r="E451" s="3" t="inlineStr">
         <is>
           <t>Electrical Engineering Intern/Co-Op</t>
         </is>
       </c>
-      <c r="F451" s="2" t="inlineStr">
+      <c r="F451" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G451" s="2" t="inlineStr">
+      <c r="G451" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=b5e758d897c2541f</t>
         </is>
       </c>
-      <c r="H451" s="2" t="inlineStr">
+      <c r="H451" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I451" s="2" t="inlineStr">
+      <c r="I451" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**WHERE PASSION \+ PURPOSE ALIGN**
 We are the curious. Problem solvers. Driven to unlock the potential in every system. Across five countries are 1,100 engineers, designers, and consultants collaborating to elevate the human experience, create more resilient communities, and protect the health of </t>
         </is>
       </c>
-      <c r="J451" s="2" t="inlineStr"/>
-      <c r="K451" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L451" s="2" t="inlineStr"/>
+      <c r="J451" s="3" t="inlineStr"/>
+      <c r="K451" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L451" s="3" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="inlineStr">
+      <c r="A452" s="3" t="inlineStr">
         <is>
           <t>02c1165808c08d4bf7dea212053c5e6e81a75a12280837e2e2f05e63e8d4eb0c</t>
         </is>
       </c>
-      <c r="B452" s="2" t="inlineStr">
+      <c r="B452" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="C452" s="2" t="inlineStr">
+      <c r="C452" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D452" s="2" t="inlineStr">
+      <c r="D452" s="3" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="E452" s="2" t="inlineStr">
+      <c r="E452" s="3" t="inlineStr">
         <is>
           <t>Mechanical Engineer Intern - Fall</t>
         </is>
       </c>
-      <c r="F452" s="2" t="inlineStr">
+      <c r="F452" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G452" s="2" t="inlineStr">
+      <c r="G452" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=e7bcc5b6add0e088</t>
         </is>
       </c>
-      <c r="H452" s="2" t="inlineStr">
+      <c r="H452" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I452" s="2" t="inlineStr">
+      <c r="I452" s="3" t="inlineStr">
         <is>
           <t>**Company Description**  
 CRB's nearly 1,400 expert professionals drive innovative, life\-changing and life\-saving solutions for manufacturers in the life sciences and food and beverage industries. Our mission, vision, and core values put client satisfaction and employee experience at the center o</t>
         </is>
       </c>
-      <c r="J452" s="2" t="inlineStr"/>
-      <c r="K452" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L452" s="2" t="inlineStr"/>
+      <c r="J452" s="3" t="inlineStr"/>
+      <c r="K452" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L452" s="3" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>b17f6d72991990527d042e480b2ea66bf881fcd4d9417f5371c3df9c84df7ead</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Harris Computer</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en développement de logiciels / Software Development Intern</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444496734</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr"/>
+      <c r="J453" s="2" t="inlineStr"/>
+      <c r="K453" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L453" s="2" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>ab8e9541346d224c60f3ee3b0a0ca36e0a3e4da1f5ebeb62f1a26a81b0b069f6</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>BDO Canada</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Oakville, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444075364</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr"/>
+      <c r="J454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L454" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L454"/>
+  <dimension ref="A1:L460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24104,104 +24104,408 @@
       <c r="L452" s="3" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="inlineStr">
+      <c r="A453" s="3" t="inlineStr">
         <is>
           <t>b17f6d72991990527d042e480b2ea66bf881fcd4d9417f5371c3df9c84df7ead</t>
         </is>
       </c>
-      <c r="B453" s="2" t="inlineStr">
+      <c r="B453" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="C453" s="2" t="inlineStr">
+      <c r="C453" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D453" s="2" t="inlineStr">
+      <c r="D453" s="3" t="inlineStr">
         <is>
           <t>Harris Computer</t>
         </is>
       </c>
-      <c r="E453" s="2" t="inlineStr">
+      <c r="E453" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en développement de logiciels / Software Development Intern</t>
         </is>
       </c>
-      <c r="F453" s="2" t="inlineStr">
+      <c r="F453" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G453" s="2" t="inlineStr">
+      <c r="G453" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444496734</t>
         </is>
       </c>
-      <c r="H453" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I453" s="2" t="inlineStr"/>
-      <c r="J453" s="2" t="inlineStr"/>
-      <c r="K453" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L453" s="2" t="inlineStr"/>
+      <c r="H453" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I453" s="3" t="inlineStr"/>
+      <c r="J453" s="3" t="inlineStr"/>
+      <c r="K453" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="inlineStr">
+      <c r="A454" s="3" t="inlineStr">
         <is>
           <t>ab8e9541346d224c60f3ee3b0a0ca36e0a3e4da1f5ebeb62f1a26a81b0b069f6</t>
         </is>
       </c>
-      <c r="B454" s="2" t="inlineStr">
+      <c r="B454" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="C454" s="2" t="inlineStr">
+      <c r="C454" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D454" s="2" t="inlineStr">
+      <c r="D454" s="3" t="inlineStr">
         <is>
           <t>BDO Canada</t>
         </is>
       </c>
-      <c r="E454" s="2" t="inlineStr">
+      <c r="E454" s="3" t="inlineStr">
         <is>
           <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
         </is>
       </c>
-      <c r="F454" s="2" t="inlineStr">
+      <c r="F454" s="3" t="inlineStr">
         <is>
           <t>Oakville, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G454" s="2" t="inlineStr">
+      <c r="G454" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444075364</t>
         </is>
       </c>
-      <c r="H454" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr"/>
-      <c r="J454" s="2" t="inlineStr"/>
-      <c r="K454" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L454" s="2" t="inlineStr"/>
+      <c r="H454" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I454" s="3" t="inlineStr"/>
+      <c r="J454" s="3" t="inlineStr"/>
+      <c r="K454" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L454" s="3" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>dae9ac84128ef7748e30cfe88224db9d876f052604d41b0cfe59f39c1aaa8f64</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5815559040?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr"/>
+      <c r="K455" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L455" s="2" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>dcf01d11d159c4ceab0012ea1eee70d0bc3d8019984747af8c45320e849367e3</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444914683</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr"/>
+      <c r="J456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L456" s="2" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2c6f68b67267d004f5e973da3bce1f6a988b8d263f58858fec19f5b559e4c6cc</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>TechInsights</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445231398</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr"/>
+      <c r="J457" s="2" t="inlineStr"/>
+      <c r="K457" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L457" s="2" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>5c2781fec3478855036c976154ab9bab0c954a91e6387e86aa475f72d6fb65e5</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en automatisation de l'assurance qualité (AQ) - Automne 2026 / QA Automation Engineer Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445202195</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr"/>
+      <c r="J458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L458" s="2" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>c41623124b150eb12817fe736805b442ca5dd56e4eb92b008989f4ec2f615bb4</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>BDO Canada</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444088178</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr"/>
+      <c r="J459" s="2" t="inlineStr"/>
+      <c r="K459" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>c6e331e796edbc7c082fd6b07e9f710a8d6f68c20aab5f7f03b7fb48cb083224</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>BDO Canada</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444077354</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr"/>
+      <c r="J460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L460" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L460"/>
+  <dimension ref="A1:L461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24204,308 +24204,359 @@
       <c r="L454" s="3" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="inlineStr">
+      <c r="A455" s="3" t="inlineStr">
         <is>
           <t>dae9ac84128ef7748e30cfe88224db9d876f052604d41b0cfe59f39c1aaa8f64</t>
         </is>
       </c>
-      <c r="B455" s="2" t="inlineStr">
+      <c r="B455" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C455" s="2" t="inlineStr">
+      <c r="C455" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="D455" s="2" t="inlineStr">
+      <c r="D455" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E455" s="2" t="inlineStr">
+      <c r="E455" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern - Android Connectivity (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F455" s="2" t="inlineStr">
+      <c r="F455" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G455" s="2" t="inlineStr">
+      <c r="G455" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5815559040?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H455" s="2" t="inlineStr">
+      <c r="H455" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I455" s="2" t="inlineStr">
+      <c r="I455" s="3" t="inlineStr">
         <is>
           <t>About Us Rivian and Volkswagen Group Technologies is a joint venture between two industry leaders with a clear vision for automotive’s next chapter. From operating systems to zonal controllers to cloud and connectivity solutions, we’re addressing the challenges of electric vehicles through technolog</t>
         </is>
       </c>
-      <c r="J455" s="2" t="inlineStr"/>
-      <c r="K455" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L455" s="2" t="inlineStr"/>
+      <c r="J455" s="3" t="inlineStr"/>
+      <c r="K455" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L455" s="3" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="inlineStr">
+      <c r="A456" s="3" t="inlineStr">
         <is>
           <t>dcf01d11d159c4ceab0012ea1eee70d0bc3d8019984747af8c45320e849367e3</t>
         </is>
       </c>
-      <c r="B456" s="2" t="inlineStr">
+      <c r="B456" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C456" s="2" t="inlineStr">
+      <c r="C456" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D456" s="2" t="inlineStr">
+      <c r="D456" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="E456" s="2" t="inlineStr">
+      <c r="E456" s="3" t="inlineStr">
         <is>
           <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
         </is>
       </c>
-      <c r="F456" s="2" t="inlineStr">
+      <c r="F456" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G456" s="2" t="inlineStr">
+      <c r="G456" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444914683</t>
         </is>
       </c>
-      <c r="H456" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr"/>
-      <c r="J456" s="2" t="inlineStr"/>
-      <c r="K456" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L456" s="2" t="inlineStr"/>
+      <c r="H456" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I456" s="3" t="inlineStr"/>
+      <c r="J456" s="3" t="inlineStr"/>
+      <c r="K456" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L456" s="3" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="inlineStr">
+      <c r="A457" s="3" t="inlineStr">
         <is>
           <t>2c6f68b67267d004f5e973da3bce1f6a988b8d263f58858fec19f5b559e4c6cc</t>
         </is>
       </c>
-      <c r="B457" s="2" t="inlineStr">
+      <c r="B457" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C457" s="2" t="inlineStr">
+      <c r="C457" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D457" s="2" t="inlineStr">
+      <c r="D457" s="3" t="inlineStr">
         <is>
           <t>TechInsights</t>
         </is>
       </c>
-      <c r="E457" s="2" t="inlineStr">
+      <c r="E457" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F457" s="2" t="inlineStr">
+      <c r="F457" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G457" s="2" t="inlineStr">
+      <c r="G457" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445231398</t>
         </is>
       </c>
-      <c r="H457" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr"/>
-      <c r="J457" s="2" t="inlineStr"/>
-      <c r="K457" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L457" s="2" t="inlineStr"/>
+      <c r="H457" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I457" s="3" t="inlineStr"/>
+      <c r="J457" s="3" t="inlineStr"/>
+      <c r="K457" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L457" s="3" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="inlineStr">
+      <c r="A458" s="3" t="inlineStr">
         <is>
           <t>5c2781fec3478855036c976154ab9bab0c954a91e6387e86aa475f72d6fb65e5</t>
         </is>
       </c>
-      <c r="B458" s="2" t="inlineStr">
+      <c r="B458" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C458" s="2" t="inlineStr">
+      <c r="C458" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D458" s="2" t="inlineStr">
+      <c r="D458" s="3" t="inlineStr">
         <is>
           <t>McKesson</t>
         </is>
       </c>
-      <c r="E458" s="2" t="inlineStr">
+      <c r="E458" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en automatisation de l'assurance qualité (AQ) - Automne 2026 / QA Automation Engineer Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F458" s="2" t="inlineStr">
+      <c r="F458" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G458" s="2" t="inlineStr">
+      <c r="G458" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445202195</t>
         </is>
       </c>
-      <c r="H458" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I458" s="2" t="inlineStr"/>
-      <c r="J458" s="2" t="inlineStr"/>
-      <c r="K458" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L458" s="2" t="inlineStr"/>
+      <c r="H458" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I458" s="3" t="inlineStr"/>
+      <c r="J458" s="3" t="inlineStr"/>
+      <c r="K458" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L458" s="3" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="inlineStr">
+      <c r="A459" s="3" t="inlineStr">
         <is>
           <t>c41623124b150eb12817fe736805b442ca5dd56e4eb92b008989f4ec2f615bb4</t>
         </is>
       </c>
-      <c r="B459" s="2" t="inlineStr">
+      <c r="B459" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C459" s="2" t="inlineStr">
+      <c r="C459" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D459" s="2" t="inlineStr">
+      <c r="D459" s="3" t="inlineStr">
         <is>
           <t>BDO Canada</t>
         </is>
       </c>
-      <c r="E459" s="2" t="inlineStr">
+      <c r="E459" s="3" t="inlineStr">
         <is>
           <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
         </is>
       </c>
-      <c r="F459" s="2" t="inlineStr">
+      <c r="F459" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G459" s="2" t="inlineStr">
+      <c r="G459" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444088178</t>
         </is>
       </c>
-      <c r="H459" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I459" s="2" t="inlineStr"/>
-      <c r="J459" s="2" t="inlineStr"/>
-      <c r="K459" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L459" s="2" t="inlineStr"/>
+      <c r="H459" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I459" s="3" t="inlineStr"/>
+      <c r="J459" s="3" t="inlineStr"/>
+      <c r="K459" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L459" s="3" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="inlineStr">
+      <c r="A460" s="3" t="inlineStr">
         <is>
           <t>c6e331e796edbc7c082fd6b07e9f710a8d6f68c20aab5f7f03b7fb48cb083224</t>
         </is>
       </c>
-      <c r="B460" s="2" t="inlineStr">
+      <c r="B460" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C460" s="2" t="inlineStr">
+      <c r="C460" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D460" s="2" t="inlineStr">
+      <c r="D460" s="3" t="inlineStr">
         <is>
           <t>BDO Canada</t>
         </is>
       </c>
-      <c r="E460" s="2" t="inlineStr">
+      <c r="E460" s="3" t="inlineStr">
         <is>
           <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
         </is>
       </c>
-      <c r="F460" s="2" t="inlineStr">
+      <c r="F460" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G460" s="2" t="inlineStr">
+      <c r="G460" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444077354</t>
         </is>
       </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I460" s="2" t="inlineStr"/>
-      <c r="J460" s="2" t="inlineStr"/>
-      <c r="K460" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L460" s="2" t="inlineStr"/>
+      <c r="H460" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I460" s="3" t="inlineStr"/>
+      <c r="J460" s="3" t="inlineStr"/>
+      <c r="K460" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L460" s="3" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>559f2eae24ee195a8b835bc1351690ddd3efc24cd94e0b9f331dab440ebb321d</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr"/>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=a488bbbd82f1625d</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>**Job Overview**
+Inkaer is a Canadian talent platform that connects international students at top Canadian universities and colleges with Canadian startups and growing companies. We handle sourcing, matching, and support so our clients focus on building — and we stay involved throughout the placeme</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr"/>
+      <c r="K461" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L461" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L461"/>
+  <dimension ref="A1:L463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24508,55 +24508,159 @@
       <c r="L460" s="3" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="inlineStr">
+      <c r="A461" s="3" t="inlineStr">
         <is>
           <t>559f2eae24ee195a8b835bc1351690ddd3efc24cd94e0b9f331dab440ebb321d</t>
         </is>
       </c>
-      <c r="B461" s="2" t="inlineStr">
+      <c r="B461" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="C461" s="2" t="inlineStr">
+      <c r="C461" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D461" s="2" t="inlineStr"/>
-      <c r="E461" s="2" t="inlineStr">
+      <c r="D461" s="3" t="inlineStr"/>
+      <c r="E461" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern</t>
         </is>
       </c>
-      <c r="F461" s="2" t="inlineStr">
+      <c r="F461" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G461" s="2" t="inlineStr">
+      <c r="G461" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=a488bbbd82f1625d</t>
         </is>
       </c>
-      <c r="H461" s="2" t="inlineStr">
+      <c r="H461" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I461" s="2" t="inlineStr">
+      <c r="I461" s="3" t="inlineStr">
         <is>
           <t>**Job Overview**
 Inkaer is a Canadian talent platform that connects international students at top Canadian universities and colleges with Canadian startups and growing companies. We handle sourcing, matching, and support so our clients focus on building — and we stay involved throughout the placeme</t>
         </is>
       </c>
-      <c r="J461" s="2" t="inlineStr"/>
-      <c r="K461" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L461" s="2" t="inlineStr"/>
+      <c r="J461" s="3" t="inlineStr"/>
+      <c r="K461" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L461" s="3" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>93b2bddc2aa9509efd1eff9887e601386baddf16340d14adcb2435cacf03b533</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5814582048?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Type: Co-op/Intern Work Model: Hybrid Reference code: 134060 Primary Location: Toronto, ON All Available Locations: Toronto, ON Our Purpose At Deloitte, our Purpose is to make an impact that matters. We exist to inspire and help our people, organizations, communities, and countries to thrive by </t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L462" s="2" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>4f8882d69ad77da61b5e9340c179484e90d1f6e91a89dd25eaf0c74ebfffd9f7</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444605603</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr"/>
+      <c r="J463" s="2" t="inlineStr"/>
+      <c r="K463" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L463" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L463"/>
+  <dimension ref="A1:L465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24559,108 +24559,208 @@
       <c r="L461" s="3" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="inlineStr">
+      <c r="A462" s="3" t="inlineStr">
         <is>
           <t>93b2bddc2aa9509efd1eff9887e601386baddf16340d14adcb2435cacf03b533</t>
         </is>
       </c>
-      <c r="B462" s="2" t="inlineStr">
+      <c r="B462" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="C462" s="2" t="inlineStr">
+      <c r="C462" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D462" s="2" t="inlineStr">
+      <c r="D462" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="E462" s="2" t="inlineStr">
+      <c r="E462" s="3" t="inlineStr">
         <is>
           <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
         </is>
       </c>
-      <c r="F462" s="2" t="inlineStr">
+      <c r="F462" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G462" s="2" t="inlineStr">
+      <c r="G462" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5814582048?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H462" s="2" t="inlineStr">
+      <c r="H462" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I462" s="2" t="inlineStr">
+      <c r="I462" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Type: Co-op/Intern Work Model: Hybrid Reference code: 134060 Primary Location: Toronto, ON All Available Locations: Toronto, ON Our Purpose At Deloitte, our Purpose is to make an impact that matters. We exist to inspire and help our people, organizations, communities, and countries to thrive by </t>
         </is>
       </c>
-      <c r="J462" s="2" t="inlineStr"/>
-      <c r="K462" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L462" s="2" t="inlineStr"/>
+      <c r="J462" s="3" t="inlineStr"/>
+      <c r="K462" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L462" s="3" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="inlineStr">
+      <c r="A463" s="3" t="inlineStr">
         <is>
           <t>4f8882d69ad77da61b5e9340c179484e90d1f6e91a89dd25eaf0c74ebfffd9f7</t>
         </is>
       </c>
-      <c r="B463" s="2" t="inlineStr">
+      <c r="B463" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="C463" s="2" t="inlineStr">
+      <c r="C463" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D463" s="2" t="inlineStr">
+      <c r="D463" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E463" s="2" t="inlineStr">
+      <c r="E463" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F463" s="2" t="inlineStr">
+      <c r="F463" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G463" s="2" t="inlineStr">
+      <c r="G463" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444605603</t>
         </is>
       </c>
-      <c r="H463" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr"/>
-      <c r="J463" s="2" t="inlineStr"/>
-      <c r="K463" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L463" s="2" t="inlineStr"/>
+      <c r="H463" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I463" s="3" t="inlineStr"/>
+      <c r="J463" s="3" t="inlineStr"/>
+      <c r="K463" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L463" s="3" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>ffc25cf71ac87347d88c6bdb9dfa46f4baac7134698017c88401122586e0cea0</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>SpeedyApply</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op Student - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444831180</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr"/>
+      <c r="J464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L464" s="2" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>084f6d42807781aef485b5ff1a2c64edbad05814fe5f8b21d5eb0753245e3b85</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>BDO Canada</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444070422</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr"/>
+      <c r="J465" s="2" t="inlineStr"/>
+      <c r="K465" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L465" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L465"/>
+  <dimension ref="A1:L466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24663,104 +24663,154 @@
       <c r="L463" s="3" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="inlineStr">
+      <c r="A464" s="3" t="inlineStr">
         <is>
           <t>ffc25cf71ac87347d88c6bdb9dfa46f4baac7134698017c88401122586e0cea0</t>
         </is>
       </c>
-      <c r="B464" s="2" t="inlineStr">
+      <c r="B464" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="C464" s="2" t="inlineStr">
+      <c r="C464" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D464" s="2" t="inlineStr">
+      <c r="D464" s="3" t="inlineStr">
         <is>
           <t>SpeedyApply</t>
         </is>
       </c>
-      <c r="E464" s="2" t="inlineStr">
+      <c r="E464" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op Student - Fall 2026</t>
         </is>
       </c>
-      <c r="F464" s="2" t="inlineStr">
+      <c r="F464" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G464" s="2" t="inlineStr">
+      <c r="G464" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444831180</t>
         </is>
       </c>
-      <c r="H464" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I464" s="2" t="inlineStr"/>
-      <c r="J464" s="2" t="inlineStr"/>
-      <c r="K464" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L464" s="2" t="inlineStr"/>
+      <c r="H464" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I464" s="3" t="inlineStr"/>
+      <c r="J464" s="3" t="inlineStr"/>
+      <c r="K464" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L464" s="3" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="inlineStr">
+      <c r="A465" s="3" t="inlineStr">
         <is>
           <t>084f6d42807781aef485b5ff1a2c64edbad05814fe5f8b21d5eb0753245e3b85</t>
         </is>
       </c>
-      <c r="B465" s="2" t="inlineStr">
+      <c r="B465" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="C465" s="2" t="inlineStr">
+      <c r="C465" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D465" s="2" t="inlineStr">
+      <c r="D465" s="3" t="inlineStr">
         <is>
           <t>BDO Canada</t>
         </is>
       </c>
-      <c r="E465" s="2" t="inlineStr">
+      <c r="E465" s="3" t="inlineStr">
         <is>
           <t>Stagiaire ou stagiaire coop, Données et analyses (mai 2026)</t>
         </is>
       </c>
-      <c r="F465" s="2" t="inlineStr">
+      <c r="F465" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G465" s="2" t="inlineStr">
+      <c r="G465" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444070422</t>
         </is>
       </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="inlineStr"/>
-      <c r="J465" s="2" t="inlineStr"/>
-      <c r="K465" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L465" s="2" t="inlineStr"/>
+      <c r="H465" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I465" s="3" t="inlineStr"/>
+      <c r="J465" s="3" t="inlineStr"/>
+      <c r="K465" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L465" s="3" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>c0a0fa57c67a89fcb57d19efd3cfa3252f517a920fb4f85806840700b16c5aaa</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Motorola Solutions</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst Co-Op</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441254302</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr"/>
+      <c r="J466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L466" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L466"/>
+  <dimension ref="A1:L467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24763,54 +24763,111 @@
       <c r="L465" s="3" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="inlineStr">
+      <c r="A466" s="3" t="inlineStr">
         <is>
           <t>c0a0fa57c67a89fcb57d19efd3cfa3252f517a920fb4f85806840700b16c5aaa</t>
         </is>
       </c>
-      <c r="B466" s="2" t="inlineStr">
+      <c r="B466" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C466" s="2" t="inlineStr">
+      <c r="C466" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D466" s="2" t="inlineStr">
+      <c r="D466" s="3" t="inlineStr">
         <is>
           <t>Motorola Solutions</t>
         </is>
       </c>
-      <c r="E466" s="2" t="inlineStr">
+      <c r="E466" s="3" t="inlineStr">
         <is>
           <t>Data Analyst Co-Op</t>
         </is>
       </c>
-      <c r="F466" s="2" t="inlineStr">
+      <c r="F466" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G466" s="2" t="inlineStr">
+      <c r="G466" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441254302</t>
         </is>
       </c>
-      <c r="H466" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I466" s="2" t="inlineStr"/>
-      <c r="J466" s="2" t="inlineStr"/>
-      <c r="K466" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L466" s="2" t="inlineStr"/>
+      <c r="H466" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I466" s="3" t="inlineStr"/>
+      <c r="J466" s="3" t="inlineStr"/>
+      <c r="K466" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L466" s="3" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>6976f8db278232a6a41e1c8b2557a76d09ae53c55b0fc8248ea6549594feba51</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Enverus</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>GIS Intern - 26293</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7f1a3244570b28bd</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>**GIS Intern**
+**Why YOU want this position**
+At Enverus, we’re committed to empowering the global quality of life by helping our customers make energy affordable and accessible to the world.
+We are the most trusted energy\-dedicated SaaS company, with a platform built to maximize value from ge</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr"/>
+      <c r="K467" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L467" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L467"/>
+  <dimension ref="A1:L472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24813,47 +24813,47 @@
       <c r="L466" s="3" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="inlineStr">
+      <c r="A467" s="3" t="inlineStr">
         <is>
           <t>6976f8db278232a6a41e1c8b2557a76d09ae53c55b0fc8248ea6549594feba51</t>
         </is>
       </c>
-      <c r="B467" s="2" t="inlineStr">
+      <c r="B467" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C467" s="2" t="inlineStr">
+      <c r="C467" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D467" s="2" t="inlineStr">
+      <c r="D467" s="3" t="inlineStr">
         <is>
           <t>Enverus</t>
         </is>
       </c>
-      <c r="E467" s="2" t="inlineStr">
+      <c r="E467" s="3" t="inlineStr">
         <is>
           <t>GIS Intern - 26293</t>
         </is>
       </c>
-      <c r="F467" s="2" t="inlineStr">
+      <c r="F467" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G467" s="2" t="inlineStr">
+      <c r="G467" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7f1a3244570b28bd</t>
         </is>
       </c>
-      <c r="H467" s="2" t="inlineStr">
+      <c r="H467" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I467" s="2" t="inlineStr">
+      <c r="I467" s="3" t="inlineStr">
         <is>
           <t>**GIS Intern**
 **Why YOU want this position**
@@ -24861,13 +24861,278 @@
 We are the most trusted energy\-dedicated SaaS company, with a platform built to maximize value from ge</t>
         </is>
       </c>
-      <c r="J467" s="2" t="inlineStr"/>
-      <c r="K467" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L467" s="2" t="inlineStr"/>
+      <c r="J467" s="3" t="inlineStr"/>
+      <c r="K467" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L467" s="3" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>153f39c1e7647b77a2d27e3ed0444b6042b7f36170e0feb8c7e849663daddbff</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator Intern</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3f08fd72d7e4e021</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L468" s="2" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>74aca67a8279cc9dea6bb4fdde81338c7cfb287a8bf800d2c0a70813b2be75c2</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator Intern</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6c141689404fa785</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr"/>
+      <c r="K469" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>ad1229b95931f80f45c8765ce234f2809ff5025c1a24d899007ac08cd4c63c6b</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=922860bf52dff9f8</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L470" s="2" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>f43d8b9b623db585547e19352b9b29f8ad96aaded5ef219c4f6941d6053a885b</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (4 Months)</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445199222</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr"/>
+      <c r="J471" s="2" t="inlineStr"/>
+      <c r="K471" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L471" s="2" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>9dc61afa8ec512bd3599b1f2ab516e7f9e7be3f07febc71e50820b5893431002</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr"/>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Remote, CA</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=35e86411ab20e549</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>**Mechanical Engineering Intern \- Job Summary**
+The Mechanical Engineering Intern supports the engineering team in the design, development, testing, and documentation of mechanical products and systems. Working under the guidance of senior engineers, the intern applies engineering principles to as</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L472" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L472"/>
+  <dimension ref="A1:L473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24870,269 +24870,319 @@
       <c r="L467" s="3" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="inlineStr">
+      <c r="A468" s="3" t="inlineStr">
         <is>
           <t>153f39c1e7647b77a2d27e3ed0444b6042b7f36170e0feb8c7e849663daddbff</t>
         </is>
       </c>
-      <c r="B468" s="2" t="inlineStr">
+      <c r="B468" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C468" s="2" t="inlineStr">
+      <c r="C468" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D468" s="2" t="inlineStr">
+      <c r="D468" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E468" s="2" t="inlineStr">
+      <c r="E468" s="3" t="inlineStr">
         <is>
           <t>Technical Project Coordinator Intern</t>
         </is>
       </c>
-      <c r="F468" s="2" t="inlineStr">
+      <c r="F468" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G468" s="2" t="inlineStr">
+      <c r="G468" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3f08fd72d7e4e021</t>
         </is>
       </c>
-      <c r="H468" s="2" t="inlineStr">
+      <c r="H468" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I468" s="2" t="inlineStr">
+      <c r="I468" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J468" s="2" t="inlineStr"/>
-      <c r="K468" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L468" s="2" t="inlineStr"/>
+      <c r="J468" s="3" t="inlineStr"/>
+      <c r="K468" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L468" s="3" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="inlineStr">
+      <c r="A469" s="3" t="inlineStr">
         <is>
           <t>74aca67a8279cc9dea6bb4fdde81338c7cfb287a8bf800d2c0a70813b2be75c2</t>
         </is>
       </c>
-      <c r="B469" s="2" t="inlineStr">
+      <c r="B469" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C469" s="2" t="inlineStr">
+      <c r="C469" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D469" s="2" t="inlineStr">
+      <c r="D469" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E469" s="2" t="inlineStr">
+      <c r="E469" s="3" t="inlineStr">
         <is>
           <t>Technical Project Coordinator Intern</t>
         </is>
       </c>
-      <c r="F469" s="2" t="inlineStr">
+      <c r="F469" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G469" s="2" t="inlineStr">
+      <c r="G469" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6c141689404fa785</t>
         </is>
       </c>
-      <c r="H469" s="2" t="inlineStr">
+      <c r="H469" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I469" s="2" t="inlineStr">
+      <c r="I469" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J469" s="2" t="inlineStr"/>
-      <c r="K469" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L469" s="2" t="inlineStr"/>
+      <c r="J469" s="3" t="inlineStr"/>
+      <c r="K469" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="inlineStr">
+      <c r="A470" s="3" t="inlineStr">
         <is>
           <t>ad1229b95931f80f45c8765ce234f2809ff5025c1a24d899007ac08cd4c63c6b</t>
         </is>
       </c>
-      <c r="B470" s="2" t="inlineStr">
+      <c r="B470" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C470" s="2" t="inlineStr">
+      <c r="C470" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D470" s="2" t="inlineStr">
+      <c r="D470" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E470" s="2" t="inlineStr">
+      <c r="E470" s="3" t="inlineStr">
         <is>
           <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F470" s="2" t="inlineStr">
+      <c r="F470" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G470" s="2" t="inlineStr">
+      <c r="G470" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=922860bf52dff9f8</t>
         </is>
       </c>
-      <c r="H470" s="2" t="inlineStr">
+      <c r="H470" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I470" s="2" t="inlineStr">
+      <c r="I470" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J470" s="2" t="inlineStr"/>
-      <c r="K470" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L470" s="2" t="inlineStr"/>
+      <c r="J470" s="3" t="inlineStr"/>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L470" s="3" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="inlineStr">
+      <c r="A471" s="3" t="inlineStr">
         <is>
           <t>f43d8b9b623db585547e19352b9b29f8ad96aaded5ef219c4f6941d6053a885b</t>
         </is>
       </c>
-      <c r="B471" s="2" t="inlineStr">
+      <c r="B471" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C471" s="2" t="inlineStr">
+      <c r="C471" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D471" s="2" t="inlineStr">
+      <c r="D471" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E471" s="2" t="inlineStr">
+      <c r="E471" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern (4 Months)</t>
         </is>
       </c>
-      <c r="F471" s="2" t="inlineStr">
+      <c r="F471" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G471" s="2" t="inlineStr">
+      <c r="G471" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445199222</t>
         </is>
       </c>
-      <c r="H471" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I471" s="2" t="inlineStr"/>
-      <c r="J471" s="2" t="inlineStr"/>
-      <c r="K471" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L471" s="2" t="inlineStr"/>
+      <c r="H471" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I471" s="3" t="inlineStr"/>
+      <c r="J471" s="3" t="inlineStr"/>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L471" s="3" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="inlineStr">
+      <c r="A472" s="3" t="inlineStr">
         <is>
           <t>9dc61afa8ec512bd3599b1f2ab516e7f9e7be3f07febc71e50820b5893431002</t>
         </is>
       </c>
-      <c r="B472" s="2" t="inlineStr">
+      <c r="B472" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C472" s="2" t="inlineStr">
+      <c r="C472" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D472" s="2" t="inlineStr"/>
-      <c r="E472" s="2" t="inlineStr">
+      <c r="D472" s="3" t="inlineStr"/>
+      <c r="E472" s="3" t="inlineStr">
         <is>
           <t>Mechanical Engineering Intern</t>
         </is>
       </c>
-      <c r="F472" s="2" t="inlineStr">
+      <c r="F472" s="3" t="inlineStr">
         <is>
           <t>Remote, CA</t>
         </is>
       </c>
-      <c r="G472" s="2" t="inlineStr">
+      <c r="G472" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=35e86411ab20e549</t>
         </is>
       </c>
-      <c r="H472" s="2" t="inlineStr">
+      <c r="H472" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I472" s="2" t="inlineStr">
+      <c r="I472" s="3" t="inlineStr">
         <is>
           <t>**Mechanical Engineering Intern \- Job Summary**
 The Mechanical Engineering Intern supports the engineering team in the design, development, testing, and documentation of mechanical products and systems. Working under the guidance of senior engineers, the intern applies engineering principles to as</t>
         </is>
       </c>
-      <c r="J472" s="2" t="inlineStr"/>
-      <c r="K472" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L472" s="2" t="inlineStr"/>
+      <c r="J472" s="3" t="inlineStr"/>
+      <c r="K472" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L472" s="3" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>d9d7e379321790cb7d351645a6888d065951637521fae8f4ddf76ed71f3df21f</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Kobo Inc.</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (8 month Co-op)</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441288171</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr"/>
+      <c r="J473" s="2" t="inlineStr"/>
+      <c r="K473" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L473" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L473"/>
+  <dimension ref="A1:L476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25135,54 +25135,210 @@
       <c r="L472" s="3" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="inlineStr">
+      <c r="A473" s="3" t="inlineStr">
         <is>
           <t>d9d7e379321790cb7d351645a6888d065951637521fae8f4ddf76ed71f3df21f</t>
         </is>
       </c>
-      <c r="B473" s="2" t="inlineStr">
+      <c r="B473" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C473" s="2" t="inlineStr">
+      <c r="C473" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D473" s="2" t="inlineStr">
+      <c r="D473" s="3" t="inlineStr">
         <is>
           <t>Rakuten Kobo Inc.</t>
         </is>
       </c>
-      <c r="E473" s="2" t="inlineStr">
+      <c r="E473" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (8 month Co-op)</t>
         </is>
       </c>
-      <c r="F473" s="2" t="inlineStr">
+      <c r="F473" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G473" s="2" t="inlineStr">
+      <c r="G473" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441288171</t>
         </is>
       </c>
-      <c r="H473" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I473" s="2" t="inlineStr"/>
-      <c r="J473" s="2" t="inlineStr"/>
-      <c r="K473" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L473" s="2" t="inlineStr"/>
+      <c r="H473" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I473" s="3" t="inlineStr"/>
+      <c r="J473" s="3" t="inlineStr"/>
+      <c r="K473" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L473" s="3" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>89b0d3ed0261d9150e7aed8f3e4ad63b18150959b190a294b28a05702ac89a2d</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>ecobee Technologies ULC</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineering</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=11315b5edd218929</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>**Hi, we are ecobee.**
+======================
+ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L474" s="2" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>5015edfb77f8f390ec1cfa3e40f4084344e4267ff9f1bed8f26c453c79320b6f</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445778485</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr"/>
+      <c r="J475" s="2" t="inlineStr"/>
+      <c r="K475" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L475" s="2" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>fc7cb6dd8762e21435c6803ccec44fe47d7f41f60d8c4fecd787ecac6d225923</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>iGaming Ontario</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Student, Market Insights and Analytics</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443289028</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr"/>
+      <c r="J476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L476" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L476"/>
+  <dimension ref="A1:L478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25185,160 +25185,264 @@
       <c r="L473" s="3" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="inlineStr">
+      <c r="A474" s="3" t="inlineStr">
         <is>
           <t>89b0d3ed0261d9150e7aed8f3e4ad63b18150959b190a294b28a05702ac89a2d</t>
         </is>
       </c>
-      <c r="B474" s="2" t="inlineStr">
+      <c r="B474" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C474" s="2" t="inlineStr">
+      <c r="C474" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D474" s="2" t="inlineStr">
+      <c r="D474" s="3" t="inlineStr">
         <is>
           <t>ecobee Technologies ULC</t>
         </is>
       </c>
-      <c r="E474" s="2" t="inlineStr">
+      <c r="E474" s="3" t="inlineStr">
         <is>
           <t>Intern Engineering</t>
         </is>
       </c>
-      <c r="F474" s="2" t="inlineStr">
+      <c r="F474" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G474" s="2" t="inlineStr">
+      <c r="G474" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=11315b5edd218929</t>
         </is>
       </c>
-      <c r="H474" s="2" t="inlineStr">
+      <c r="H474" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I474" s="2" t="inlineStr">
+      <c r="I474" s="3" t="inlineStr">
         <is>
           <t>**Hi, we are ecobee.**
 ======================
 ecobee introduced the world’s first smart Wi\-Fi thermostat to help millions of consumers save money, conserve energy, and bring home automation into their lives. That was just the beginning. We continue our pursuit to create technology that brings pea</t>
         </is>
       </c>
-      <c r="J474" s="2" t="inlineStr"/>
-      <c r="K474" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L474" s="2" t="inlineStr"/>
+      <c r="J474" s="3" t="inlineStr"/>
+      <c r="K474" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L474" s="3" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="inlineStr">
+      <c r="A475" s="3" t="inlineStr">
         <is>
           <t>5015edfb77f8f390ec1cfa3e40f4084344e4267ff9f1bed8f26c453c79320b6f</t>
         </is>
       </c>
-      <c r="B475" s="2" t="inlineStr">
+      <c r="B475" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C475" s="2" t="inlineStr">
+      <c r="C475" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D475" s="2" t="inlineStr">
+      <c r="D475" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E475" s="2" t="inlineStr">
+      <c r="E475" s="3" t="inlineStr">
         <is>
           <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F475" s="2" t="inlineStr">
+      <c r="F475" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G475" s="2" t="inlineStr">
+      <c r="G475" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445778485</t>
         </is>
       </c>
-      <c r="H475" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I475" s="2" t="inlineStr"/>
-      <c r="J475" s="2" t="inlineStr"/>
-      <c r="K475" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L475" s="2" t="inlineStr"/>
+      <c r="H475" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I475" s="3" t="inlineStr"/>
+      <c r="J475" s="3" t="inlineStr"/>
+      <c r="K475" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="inlineStr">
+      <c r="A476" s="3" t="inlineStr">
         <is>
           <t>fc7cb6dd8762e21435c6803ccec44fe47d7f41f60d8c4fecd787ecac6d225923</t>
         </is>
       </c>
-      <c r="B476" s="2" t="inlineStr">
+      <c r="B476" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C476" s="2" t="inlineStr">
+      <c r="C476" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D476" s="2" t="inlineStr">
+      <c r="D476" s="3" t="inlineStr">
         <is>
           <t>iGaming Ontario</t>
         </is>
       </c>
-      <c r="E476" s="2" t="inlineStr">
+      <c r="E476" s="3" t="inlineStr">
         <is>
           <t>Co-op Student, Market Insights and Analytics</t>
         </is>
       </c>
-      <c r="F476" s="2" t="inlineStr">
+      <c r="F476" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G476" s="2" t="inlineStr">
+      <c r="G476" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443289028</t>
         </is>
       </c>
-      <c r="H476" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I476" s="2" t="inlineStr"/>
-      <c r="J476" s="2" t="inlineStr"/>
-      <c r="K476" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L476" s="2" t="inlineStr"/>
+      <c r="H476" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I476" s="3" t="inlineStr"/>
+      <c r="J476" s="3" t="inlineStr"/>
+      <c r="K476" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L476" s="3" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>0db5d8505294bdd9f09b9859c4d8f8d4aaaff09fd0ec8f499d12fd4a07ac28cd</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>ResponsiveAds, Inc.</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>ResponsiveAds Full-Stack Developer (2026 Summer and Fall Internship)</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5818288827?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description ResponsiveAds is the leader in advanced HTML5 premium ad creatives that are dynamic to any screen, user and context. The existing ad tech is stuck inside a box that can't adapt quickly enough. ResponsiveAds takes the "responsive" paradigm from web CMS, ad serving, and</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr"/>
+      <c r="K477" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L477" s="2" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>22437e057d6b3dd61be5ec1078e780abfcd21087c232d4b90bc75ef23ee4c844</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>QuadReal Property Group</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>AI Software Engineering, Fall 2026 - Toronto (Co-op/Internship) - 4 Months</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446540117</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr"/>
+      <c r="J478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L478" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L478"/>
+  <dimension ref="A1:L483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25341,108 +25341,358 @@
       <c r="L476" s="3" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="inlineStr">
+      <c r="A477" s="3" t="inlineStr">
         <is>
           <t>0db5d8505294bdd9f09b9859c4d8f8d4aaaff09fd0ec8f499d12fd4a07ac28cd</t>
         </is>
       </c>
-      <c r="B477" s="2" t="inlineStr">
+      <c r="B477" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C477" s="2" t="inlineStr">
+      <c r="C477" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D477" s="2" t="inlineStr">
+      <c r="D477" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds, Inc.</t>
         </is>
       </c>
-      <c r="E477" s="2" t="inlineStr">
+      <c r="E477" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds Full-Stack Developer (2026 Summer and Fall Internship)</t>
         </is>
       </c>
-      <c r="F477" s="2" t="inlineStr">
+      <c r="F477" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G477" s="2" t="inlineStr">
+      <c r="G477" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5818288827?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H477" s="2" t="inlineStr">
+      <c r="H477" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I477" s="2" t="inlineStr">
+      <c r="I477" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description ResponsiveAds is the leader in advanced HTML5 premium ad creatives that are dynamic to any screen, user and context. The existing ad tech is stuck inside a box that can't adapt quickly enough. ResponsiveAds takes the "responsive" paradigm from web CMS, ad serving, and</t>
         </is>
       </c>
-      <c r="J477" s="2" t="inlineStr"/>
-      <c r="K477" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L477" s="2" t="inlineStr"/>
+      <c r="J477" s="3" t="inlineStr"/>
+      <c r="K477" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L477" s="3" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="inlineStr">
+      <c r="A478" s="3" t="inlineStr">
         <is>
           <t>22437e057d6b3dd61be5ec1078e780abfcd21087c232d4b90bc75ef23ee4c844</t>
         </is>
       </c>
-      <c r="B478" s="2" t="inlineStr">
+      <c r="B478" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C478" s="2" t="inlineStr">
+      <c r="C478" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D478" s="2" t="inlineStr">
+      <c r="D478" s="3" t="inlineStr">
         <is>
           <t>QuadReal Property Group</t>
         </is>
       </c>
-      <c r="E478" s="2" t="inlineStr">
+      <c r="E478" s="3" t="inlineStr">
         <is>
           <t>AI Software Engineering, Fall 2026 - Toronto (Co-op/Internship) - 4 Months</t>
         </is>
       </c>
-      <c r="F478" s="2" t="inlineStr">
+      <c r="F478" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G478" s="2" t="inlineStr">
+      <c r="G478" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446540117</t>
         </is>
       </c>
-      <c r="H478" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I478" s="2" t="inlineStr"/>
-      <c r="J478" s="2" t="inlineStr"/>
-      <c r="K478" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L478" s="2" t="inlineStr"/>
+      <c r="H478" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I478" s="3" t="inlineStr"/>
+      <c r="J478" s="3" t="inlineStr"/>
+      <c r="K478" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L478" s="3" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>4ff25ffa49a77d3a32d1f5da26395ffe98c879e80033b1f49fdef9b12d56816d</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Loop Financial</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist intern</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446852333</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr"/>
+      <c r="J479" s="2" t="inlineStr"/>
+      <c r="K479" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L479" s="2" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>6139dc9c8a060fb1a5848b7907c4fdd7554958961390b52d4c5a6ea7e5c37b7e</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Key West Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444162886</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr"/>
+      <c r="J480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L480" s="2" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>d3a16bd708e137afee4ba032b94bdf7ad340e1ff8533f204ed4e224553bb76c2</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>2026 Fall Co-op Digital Vehicle Experience Software Developer</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446808823</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr"/>
+      <c r="J481" s="2" t="inlineStr"/>
+      <c r="K481" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L481" s="2" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>9fb8cfada4f03528321a8c9173e0b45a4f338819cca27088d6582a2ea3fb1bb2</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Telesat</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>Lightspeed Network Engineering Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443580281</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr"/>
+      <c r="J482" s="2" t="inlineStr"/>
+      <c r="K482" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L482" s="2" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>c20b347d9ea77c46f41aee9caba8addaec424d88d631ba8f03b93767b2fa162b</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>Data/Analytics Co-op</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446127161</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr"/>
+      <c r="J483" s="2" t="inlineStr"/>
+      <c r="K483" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L483" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L483"/>
+  <dimension ref="A1:L487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25445,254 +25445,454 @@
       <c r="L478" s="3" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="inlineStr">
+      <c r="A479" s="3" t="inlineStr">
         <is>
           <t>4ff25ffa49a77d3a32d1f5da26395ffe98c879e80033b1f49fdef9b12d56816d</t>
         </is>
       </c>
-      <c r="B479" s="2" t="inlineStr">
+      <c r="B479" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C479" s="2" t="inlineStr">
+      <c r="C479" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D479" s="2" t="inlineStr">
+      <c r="D479" s="3" t="inlineStr">
         <is>
           <t>Loop Financial</t>
         </is>
       </c>
-      <c r="E479" s="2" t="inlineStr">
+      <c r="E479" s="3" t="inlineStr">
         <is>
           <t>Data Scientist intern</t>
         </is>
       </c>
-      <c r="F479" s="2" t="inlineStr">
+      <c r="F479" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G479" s="2" t="inlineStr">
+      <c r="G479" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446852333</t>
         </is>
       </c>
-      <c r="H479" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I479" s="2" t="inlineStr"/>
-      <c r="J479" s="2" t="inlineStr"/>
-      <c r="K479" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L479" s="2" t="inlineStr"/>
+      <c r="H479" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I479" s="3" t="inlineStr"/>
+      <c r="J479" s="3" t="inlineStr"/>
+      <c r="K479" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L479" s="3" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="inlineStr">
+      <c r="A480" s="3" t="inlineStr">
         <is>
           <t>6139dc9c8a060fb1a5848b7907c4fdd7554958961390b52d4c5a6ea7e5c37b7e</t>
         </is>
       </c>
-      <c r="B480" s="2" t="inlineStr">
+      <c r="B480" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C480" s="2" t="inlineStr">
+      <c r="C480" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D480" s="2" t="inlineStr">
+      <c r="D480" s="3" t="inlineStr">
         <is>
           <t>Key West Travel &amp; Tours</t>
         </is>
       </c>
-      <c r="E480" s="2" t="inlineStr">
+      <c r="E480" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern</t>
         </is>
       </c>
-      <c r="F480" s="2" t="inlineStr">
+      <c r="F480" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G480" s="2" t="inlineStr">
+      <c r="G480" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444162886</t>
         </is>
       </c>
-      <c r="H480" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I480" s="2" t="inlineStr"/>
-      <c r="J480" s="2" t="inlineStr"/>
-      <c r="K480" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L480" s="2" t="inlineStr"/>
+      <c r="H480" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I480" s="3" t="inlineStr"/>
+      <c r="J480" s="3" t="inlineStr"/>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L480" s="3" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="inlineStr">
+      <c r="A481" s="3" t="inlineStr">
         <is>
           <t>d3a16bd708e137afee4ba032b94bdf7ad340e1ff8533f204ed4e224553bb76c2</t>
         </is>
       </c>
-      <c r="B481" s="2" t="inlineStr">
+      <c r="B481" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr">
+      <c r="C481" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D481" s="2" t="inlineStr">
+      <c r="D481" s="3" t="inlineStr">
         <is>
           <t>General Motors</t>
         </is>
       </c>
-      <c r="E481" s="2" t="inlineStr">
+      <c r="E481" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Co-op Digital Vehicle Experience Software Developer</t>
         </is>
       </c>
-      <c r="F481" s="2" t="inlineStr">
+      <c r="F481" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G481" s="2" t="inlineStr">
+      <c r="G481" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446808823</t>
         </is>
       </c>
-      <c r="H481" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I481" s="2" t="inlineStr"/>
-      <c r="J481" s="2" t="inlineStr"/>
-      <c r="K481" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L481" s="2" t="inlineStr"/>
+      <c r="H481" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I481" s="3" t="inlineStr"/>
+      <c r="J481" s="3" t="inlineStr"/>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L481" s="3" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="inlineStr">
+      <c r="A482" s="3" t="inlineStr">
         <is>
           <t>9fb8cfada4f03528321a8c9173e0b45a4f338819cca27088d6582a2ea3fb1bb2</t>
         </is>
       </c>
-      <c r="B482" s="2" t="inlineStr">
+      <c r="B482" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C482" s="2" t="inlineStr">
+      <c r="C482" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D482" s="2" t="inlineStr">
+      <c r="D482" s="3" t="inlineStr">
         <is>
           <t>Telesat</t>
         </is>
       </c>
-      <c r="E482" s="2" t="inlineStr">
+      <c r="E482" s="3" t="inlineStr">
         <is>
           <t>Lightspeed Network Engineering Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F482" s="2" t="inlineStr">
+      <c r="F482" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr">
+      <c r="G482" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443580281</t>
         </is>
       </c>
-      <c r="H482" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I482" s="2" t="inlineStr"/>
-      <c r="J482" s="2" t="inlineStr"/>
-      <c r="K482" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L482" s="2" t="inlineStr"/>
+      <c r="H482" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I482" s="3" t="inlineStr"/>
+      <c r="J482" s="3" t="inlineStr"/>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L482" s="3" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="inlineStr">
+      <c r="A483" s="3" t="inlineStr">
         <is>
           <t>c20b347d9ea77c46f41aee9caba8addaec424d88d631ba8f03b93767b2fa162b</t>
         </is>
       </c>
-      <c r="B483" s="2" t="inlineStr">
+      <c r="B483" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C483" s="2" t="inlineStr">
+      <c r="C483" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D483" s="2" t="inlineStr">
+      <c r="D483" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E483" s="2" t="inlineStr">
+      <c r="E483" s="3" t="inlineStr">
         <is>
           <t>Data/Analytics Co-op</t>
         </is>
       </c>
-      <c r="F483" s="2" t="inlineStr">
+      <c r="F483" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G483" s="2" t="inlineStr">
+      <c r="G483" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446127161</t>
         </is>
       </c>
-      <c r="H483" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="inlineStr"/>
-      <c r="J483" s="2" t="inlineStr"/>
-      <c r="K483" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L483" s="2" t="inlineStr"/>
+      <c r="H483" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I483" s="3" t="inlineStr"/>
+      <c r="J483" s="3" t="inlineStr"/>
+      <c r="K483" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L483" s="3" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>c0784525515734efc02aa27ed8780e2a65e89d10c15d609b7fb8bb117c2ec72e</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>AI Developer Intern 8 Months Fall 2026</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444187287</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr"/>
+      <c r="J484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L484" s="2" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>a07383d5826733e6ec1a025076483c9cbe35237c3a4e20f50323ebe6e42d8b8a</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>Backend Development Intern</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446101920</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr"/>
+      <c r="J485" s="2" t="inlineStr"/>
+      <c r="K485" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L485" s="2" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>30780e29136aef3428c06690f14bc955dc6fd9a5496a7cf313395fe84b7b4073</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Mitchell &amp; Associates</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>Software Design Engineering (Artificial Intelligence) Co-op Student</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Vaughan, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446536816</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr"/>
+      <c r="J486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L486" s="2" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>da5fc6ef15045b3e8875067e8ce505fe5a14c72b4f1b415d95d7453a2ff7b8a1</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>Critical Environment Technologies</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>Product Development Engineer Co-op (AI-Driven)</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>Delta, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444607645</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr"/>
+      <c r="J487" s="2" t="inlineStr"/>
+      <c r="K487" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L487" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L487"/>
+  <dimension ref="A1:L489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25695,204 +25695,304 @@
       <c r="L483" s="3" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="inlineStr">
+      <c r="A484" s="3" t="inlineStr">
         <is>
           <t>c0784525515734efc02aa27ed8780e2a65e89d10c15d609b7fb8bb117c2ec72e</t>
         </is>
       </c>
-      <c r="B484" s="2" t="inlineStr">
+      <c r="B484" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C484" s="2" t="inlineStr">
+      <c r="C484" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D484" s="2" t="inlineStr">
+      <c r="D484" s="3" t="inlineStr">
         <is>
           <t>Dayforce</t>
         </is>
       </c>
-      <c r="E484" s="2" t="inlineStr">
+      <c r="E484" s="3" t="inlineStr">
         <is>
           <t>AI Developer Intern 8 Months Fall 2026</t>
         </is>
       </c>
-      <c r="F484" s="2" t="inlineStr">
+      <c r="F484" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G484" s="2" t="inlineStr">
+      <c r="G484" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444187287</t>
         </is>
       </c>
-      <c r="H484" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I484" s="2" t="inlineStr"/>
-      <c r="J484" s="2" t="inlineStr"/>
-      <c r="K484" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L484" s="2" t="inlineStr"/>
+      <c r="H484" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I484" s="3" t="inlineStr"/>
+      <c r="J484" s="3" t="inlineStr"/>
+      <c r="K484" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L484" s="3" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="inlineStr">
+      <c r="A485" s="3" t="inlineStr">
         <is>
           <t>a07383d5826733e6ec1a025076483c9cbe35237c3a4e20f50323ebe6e42d8b8a</t>
         </is>
       </c>
-      <c r="B485" s="2" t="inlineStr">
+      <c r="B485" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C485" s="2" t="inlineStr">
+      <c r="C485" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D485" s="2" t="inlineStr">
+      <c r="D485" s="3" t="inlineStr">
         <is>
           <t>Zenith</t>
         </is>
       </c>
-      <c r="E485" s="2" t="inlineStr">
+      <c r="E485" s="3" t="inlineStr">
         <is>
           <t>Backend Development Intern</t>
         </is>
       </c>
-      <c r="F485" s="2" t="inlineStr">
+      <c r="F485" s="3" t="inlineStr">
         <is>
           <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G485" s="2" t="inlineStr">
+      <c r="G485" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446101920</t>
         </is>
       </c>
-      <c r="H485" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I485" s="2" t="inlineStr"/>
-      <c r="J485" s="2" t="inlineStr"/>
-      <c r="K485" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L485" s="2" t="inlineStr"/>
+      <c r="H485" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I485" s="3" t="inlineStr"/>
+      <c r="J485" s="3" t="inlineStr"/>
+      <c r="K485" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L485" s="3" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="inlineStr">
+      <c r="A486" s="3" t="inlineStr">
         <is>
           <t>30780e29136aef3428c06690f14bc955dc6fd9a5496a7cf313395fe84b7b4073</t>
         </is>
       </c>
-      <c r="B486" s="2" t="inlineStr">
+      <c r="B486" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C486" s="2" t="inlineStr">
+      <c r="C486" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D486" s="2" t="inlineStr">
+      <c r="D486" s="3" t="inlineStr">
         <is>
           <t>Mitchell &amp; Associates</t>
         </is>
       </c>
-      <c r="E486" s="2" t="inlineStr">
+      <c r="E486" s="3" t="inlineStr">
         <is>
           <t>Software Design Engineering (Artificial Intelligence) Co-op Student</t>
         </is>
       </c>
-      <c r="F486" s="2" t="inlineStr">
+      <c r="F486" s="3" t="inlineStr">
         <is>
           <t>Vaughan, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G486" s="2" t="inlineStr">
+      <c r="G486" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446536816</t>
         </is>
       </c>
-      <c r="H486" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I486" s="2" t="inlineStr"/>
-      <c r="J486" s="2" t="inlineStr"/>
-      <c r="K486" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L486" s="2" t="inlineStr"/>
+      <c r="H486" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I486" s="3" t="inlineStr"/>
+      <c r="J486" s="3" t="inlineStr"/>
+      <c r="K486" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L486" s="3" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="inlineStr">
+      <c r="A487" s="3" t="inlineStr">
         <is>
           <t>da5fc6ef15045b3e8875067e8ce505fe5a14c72b4f1b415d95d7453a2ff7b8a1</t>
         </is>
       </c>
-      <c r="B487" s="2" t="inlineStr">
+      <c r="B487" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C487" s="2" t="inlineStr">
+      <c r="C487" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D487" s="2" t="inlineStr">
+      <c r="D487" s="3" t="inlineStr">
         <is>
           <t>Critical Environment Technologies</t>
         </is>
       </c>
-      <c r="E487" s="2" t="inlineStr">
+      <c r="E487" s="3" t="inlineStr">
         <is>
           <t>Product Development Engineer Co-op (AI-Driven)</t>
         </is>
       </c>
-      <c r="F487" s="2" t="inlineStr">
+      <c r="F487" s="3" t="inlineStr">
         <is>
           <t>Delta, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G487" s="2" t="inlineStr">
+      <c r="G487" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444607645</t>
         </is>
       </c>
-      <c r="H487" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I487" s="2" t="inlineStr"/>
-      <c r="J487" s="2" t="inlineStr"/>
-      <c r="K487" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L487" s="2" t="inlineStr"/>
+      <c r="H487" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I487" s="3" t="inlineStr"/>
+      <c r="J487" s="3" t="inlineStr"/>
+      <c r="K487" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L487" s="3" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>4a731036db981edd431d9bc2790d7fd2053f3d9fa28081f91238c87834862b22</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>ShyftLabs</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443706179</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr"/>
+      <c r="J488" s="2" t="inlineStr"/>
+      <c r="K488" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L488" s="2" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>683c8ffa188bbc30e9c33cb08e5b95409e089b134110a95aa5e3847f68a58c14</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>GEI Consultants, Inc.</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447593311</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr"/>
+      <c r="J489" s="2" t="inlineStr"/>
+      <c r="K489" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L489" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L489"/>
+  <dimension ref="A1:L495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25895,104 +25895,410 @@
       <c r="L487" s="3" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="inlineStr">
+      <c r="A488" s="3" t="inlineStr">
         <is>
           <t>4a731036db981edd431d9bc2790d7fd2053f3d9fa28081f91238c87834862b22</t>
         </is>
       </c>
-      <c r="B488" s="2" t="inlineStr">
+      <c r="B488" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C488" s="2" t="inlineStr">
+      <c r="C488" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D488" s="2" t="inlineStr">
+      <c r="D488" s="3" t="inlineStr">
         <is>
           <t>ShyftLabs</t>
         </is>
       </c>
-      <c r="E488" s="2" t="inlineStr">
+      <c r="E488" s="3" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="F488" s="2" t="inlineStr">
+      <c r="F488" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G488" s="2" t="inlineStr">
+      <c r="G488" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443706179</t>
         </is>
       </c>
-      <c r="H488" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I488" s="2" t="inlineStr"/>
-      <c r="J488" s="2" t="inlineStr"/>
-      <c r="K488" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L488" s="2" t="inlineStr"/>
+      <c r="H488" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I488" s="3" t="inlineStr"/>
+      <c r="J488" s="3" t="inlineStr"/>
+      <c r="K488" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L488" s="3" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="inlineStr">
+      <c r="A489" s="3" t="inlineStr">
         <is>
           <t>683c8ffa188bbc30e9c33cb08e5b95409e089b134110a95aa5e3847f68a58c14</t>
         </is>
       </c>
-      <c r="B489" s="2" t="inlineStr">
+      <c r="B489" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C489" s="2" t="inlineStr">
+      <c r="C489" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D489" s="2" t="inlineStr">
+      <c r="D489" s="3" t="inlineStr">
         <is>
           <t>GEI Consultants, Inc.</t>
         </is>
       </c>
-      <c r="E489" s="2" t="inlineStr">
+      <c r="E489" s="3" t="inlineStr">
         <is>
           <t>AI Engineer Intern/Co-op</t>
         </is>
       </c>
-      <c r="F489" s="2" t="inlineStr">
+      <c r="F489" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G489" s="2" t="inlineStr">
+      <c r="G489" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447593311</t>
         </is>
       </c>
-      <c r="H489" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I489" s="2" t="inlineStr"/>
-      <c r="J489" s="2" t="inlineStr"/>
-      <c r="K489" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L489" s="2" t="inlineStr"/>
+      <c r="H489" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I489" s="3" t="inlineStr"/>
+      <c r="J489" s="3" t="inlineStr"/>
+      <c r="K489" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L489" s="3" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>bed935d70c792aa4521933fbd549824a810a240b682ec2d0051c1b12b5fb18d7</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>IKO North America</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Reliability Engineering Co-Op</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Brampton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411500649</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr"/>
+      <c r="J490" s="2" t="inlineStr"/>
+      <c r="K490" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L490" s="2" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>8ebc38658224ddd7449baf793e21105bffab023ad48354ec355380fa1e8b11b5</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>Thurber Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>Geotechnical Engineering Intern (2026073191)</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=253d2c312b718655</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>### **Overview**
+Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Ottawa, Ontario**.
+Thurber provides geotechnical, environmental and construction materials engineering and testing services for a variety of industries across Canad</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr"/>
+      <c r="K491" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L491" s="2" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>de3c58ddf54c6a364eb038b5cde2693bf42c44f4575d3410822b7597da5a78f3</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern - CD1</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447247459</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr"/>
+      <c r="J492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L492" s="2" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>f41a7a4bf3a1c1f99e5655b232f2e5dff1379390bb96f6c09e6bae326b8461be</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer - openJiuwen AI Agent Platform</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447061013</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr"/>
+      <c r="J493" s="2" t="inlineStr"/>
+      <c r="K493" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L493" s="2" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>404d5c870398d7a83cc5caebdb39699419b3e94737a46517f65959946e511f32</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Algo Communication Products Ltd</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Developer, Internal Applications</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444911874</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr"/>
+      <c r="J494" s="2" t="inlineStr"/>
+      <c r="K494" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L494" s="2" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>ca4313d94a7653a700de6107cf403bbc4d4dd3134a6836019c4403e78fa0885f</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>Building Ontario Fund</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>Indigenous Opportunities Financing Program (IOFP) Intern</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442086310</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr"/>
+      <c r="J495" s="2" t="inlineStr"/>
+      <c r="K495" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L495" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L495"/>
+  <dimension ref="A1:L500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25995,310 +25995,573 @@
       <c r="L489" s="3" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="inlineStr">
+      <c r="A490" s="3" t="inlineStr">
         <is>
           <t>bed935d70c792aa4521933fbd549824a810a240b682ec2d0051c1b12b5fb18d7</t>
         </is>
       </c>
-      <c r="B490" s="2" t="inlineStr">
+      <c r="B490" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C490" s="2" t="inlineStr">
+      <c r="C490" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D490" s="2" t="inlineStr">
+      <c r="D490" s="3" t="inlineStr">
         <is>
           <t>IKO North America</t>
         </is>
       </c>
-      <c r="E490" s="2" t="inlineStr">
+      <c r="E490" s="3" t="inlineStr">
         <is>
           <t>Corporate Reliability Engineering Co-Op</t>
         </is>
       </c>
-      <c r="F490" s="2" t="inlineStr">
+      <c r="F490" s="3" t="inlineStr">
         <is>
           <t>Brampton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G490" s="2" t="inlineStr">
+      <c r="G490" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411500649</t>
         </is>
       </c>
-      <c r="H490" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I490" s="2" t="inlineStr"/>
-      <c r="J490" s="2" t="inlineStr"/>
-      <c r="K490" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L490" s="2" t="inlineStr"/>
+      <c r="H490" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I490" s="3" t="inlineStr"/>
+      <c r="J490" s="3" t="inlineStr"/>
+      <c r="K490" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L490" s="3" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="inlineStr">
+      <c r="A491" s="3" t="inlineStr">
         <is>
           <t>8ebc38658224ddd7449baf793e21105bffab023ad48354ec355380fa1e8b11b5</t>
         </is>
       </c>
-      <c r="B491" s="2" t="inlineStr">
+      <c r="B491" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C491" s="2" t="inlineStr">
+      <c r="C491" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D491" s="2" t="inlineStr">
+      <c r="D491" s="3" t="inlineStr">
         <is>
           <t>Thurber Engineering Ltd.</t>
         </is>
       </c>
-      <c r="E491" s="2" t="inlineStr">
+      <c r="E491" s="3" t="inlineStr">
         <is>
           <t>Geotechnical Engineering Intern (2026073191)</t>
         </is>
       </c>
-      <c r="F491" s="2" t="inlineStr">
+      <c r="F491" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G491" s="2" t="inlineStr">
+      <c r="G491" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=253d2c312b718655</t>
         </is>
       </c>
-      <c r="H491" s="2" t="inlineStr">
+      <c r="H491" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I491" s="2" t="inlineStr">
+      <c r="I491" s="3" t="inlineStr">
         <is>
           <t>### **Overview**
 Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Ottawa, Ontario**.
 Thurber provides geotechnical, environmental and construction materials engineering and testing services for a variety of industries across Canad</t>
         </is>
       </c>
-      <c r="J491" s="2" t="inlineStr"/>
-      <c r="K491" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L491" s="2" t="inlineStr"/>
+      <c r="J491" s="3" t="inlineStr"/>
+      <c r="K491" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L491" s="3" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="inlineStr">
+      <c r="A492" s="3" t="inlineStr">
         <is>
           <t>de3c58ddf54c6a364eb038b5cde2693bf42c44f4575d3410822b7597da5a78f3</t>
         </is>
       </c>
-      <c r="B492" s="2" t="inlineStr">
+      <c r="B492" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C492" s="2" t="inlineStr">
+      <c r="C492" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
+      <c r="D492" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E492" s="2" t="inlineStr">
+      <c r="E492" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern - CD1</t>
         </is>
       </c>
-      <c r="F492" s="2" t="inlineStr">
+      <c r="F492" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G492" s="2" t="inlineStr">
+      <c r="G492" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447247459</t>
         </is>
       </c>
-      <c r="H492" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I492" s="2" t="inlineStr"/>
-      <c r="J492" s="2" t="inlineStr"/>
-      <c r="K492" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L492" s="2" t="inlineStr"/>
+      <c r="H492" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I492" s="3" t="inlineStr"/>
+      <c r="J492" s="3" t="inlineStr"/>
+      <c r="K492" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L492" s="3" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="inlineStr">
+      <c r="A493" s="3" t="inlineStr">
         <is>
           <t>f41a7a4bf3a1c1f99e5655b232f2e5dff1379390bb96f6c09e6bae326b8461be</t>
         </is>
       </c>
-      <c r="B493" s="2" t="inlineStr">
+      <c r="B493" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr">
+      <c r="C493" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D493" s="2" t="inlineStr">
+      <c r="D493" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E493" s="2" t="inlineStr">
+      <c r="E493" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer - openJiuwen AI Agent Platform</t>
         </is>
       </c>
-      <c r="F493" s="2" t="inlineStr">
+      <c r="F493" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G493" s="2" t="inlineStr">
+      <c r="G493" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447061013</t>
         </is>
       </c>
-      <c r="H493" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I493" s="2" t="inlineStr"/>
-      <c r="J493" s="2" t="inlineStr"/>
-      <c r="K493" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L493" s="2" t="inlineStr"/>
+      <c r="H493" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I493" s="3" t="inlineStr"/>
+      <c r="J493" s="3" t="inlineStr"/>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L493" s="3" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="inlineStr">
+      <c r="A494" s="3" t="inlineStr">
         <is>
           <t>404d5c870398d7a83cc5caebdb39699419b3e94737a46517f65959946e511f32</t>
         </is>
       </c>
-      <c r="B494" s="2" t="inlineStr">
+      <c r="B494" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C494" s="2" t="inlineStr">
+      <c r="C494" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D494" s="2" t="inlineStr">
+      <c r="D494" s="3" t="inlineStr">
         <is>
           <t>Algo Communication Products Ltd</t>
         </is>
       </c>
-      <c r="E494" s="2" t="inlineStr">
+      <c r="E494" s="3" t="inlineStr">
         <is>
           <t>Cloud Developer, Internal Applications</t>
         </is>
       </c>
-      <c r="F494" s="2" t="inlineStr">
+      <c r="F494" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G494" s="2" t="inlineStr">
+      <c r="G494" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444911874</t>
         </is>
       </c>
-      <c r="H494" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I494" s="2" t="inlineStr"/>
-      <c r="J494" s="2" t="inlineStr"/>
-      <c r="K494" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L494" s="2" t="inlineStr"/>
+      <c r="H494" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I494" s="3" t="inlineStr"/>
+      <c r="J494" s="3" t="inlineStr"/>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L494" s="3" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="inlineStr">
+      <c r="A495" s="3" t="inlineStr">
         <is>
           <t>ca4313d94a7653a700de6107cf403bbc4d4dd3134a6836019c4403e78fa0885f</t>
         </is>
       </c>
-      <c r="B495" s="2" t="inlineStr">
+      <c r="B495" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C495" s="2" t="inlineStr">
+      <c r="C495" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D495" s="2" t="inlineStr">
+      <c r="D495" s="3" t="inlineStr">
         <is>
           <t>Building Ontario Fund</t>
         </is>
       </c>
-      <c r="E495" s="2" t="inlineStr">
+      <c r="E495" s="3" t="inlineStr">
         <is>
           <t>Indigenous Opportunities Financing Program (IOFP) Intern</t>
         </is>
       </c>
-      <c r="F495" s="2" t="inlineStr">
+      <c r="F495" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G495" s="2" t="inlineStr">
+      <c r="G495" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442086310</t>
         </is>
       </c>
-      <c r="H495" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I495" s="2" t="inlineStr"/>
-      <c r="J495" s="2" t="inlineStr"/>
-      <c r="K495" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L495" s="2" t="inlineStr"/>
+      <c r="H495" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I495" s="3" t="inlineStr"/>
+      <c r="J495" s="3" t="inlineStr"/>
+      <c r="K495" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L495" s="3" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>7f6eb06835e098201dcd37869cd53a2f9ed08dd685e7859e677223b5071c96dc</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ottawa region</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5824814488?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high-speed connectivity, Ciena is committed to a people-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well-being, and belonging. We’re a technology company that leads with our humanity—driving ou</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L496" s="2" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>1fbd05245f3262616954cf63ccc480ccb8bca87a1becc028eb5edffb97ba3a1f</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply Job on T-Net</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>Browser Security Engineer Intern, (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5805023760?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>About GeoComply We're GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
+        </is>
+      </c>
+      <c r="J497" s="2" t="inlineStr"/>
+      <c r="K497" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L497" s="2" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>f4ed026cd75c4af3fadbce5ee9588ec734736e731d00157a0e12e0c0b72bbb45</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (Later Influence)</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447533782</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr"/>
+      <c r="J498" s="2" t="inlineStr"/>
+      <c r="K498" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L498" s="2" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>ab17c56e42d818f101b0e8e7667353754fbb970ef638cb4a7b65054c814f73af</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>Analyst, Market Insights, Student Intern</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=ec29b61ebe712f85</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J499" s="2" t="inlineStr"/>
+      <c r="K499" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L499" s="2" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>042d53443957cbe6a1d3f2b1ec8b36bb75407daeb633a1b312d8d1042cfdcf1c</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>Concert Properties</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>Climate Reporting Analyst Intern, Environment, Social &amp; Governance</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446388394</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr"/>
+      <c r="J500" s="2" t="inlineStr"/>
+      <c r="K500" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L500" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L500"/>
+  <dimension ref="A1:L509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26301,267 +26301,717 @@
       <c r="L495" s="3" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="inlineStr">
+      <c r="A496" s="3" t="inlineStr">
         <is>
           <t>7f6eb06835e098201dcd37869cd53a2f9ed08dd685e7859e677223b5071c96dc</t>
         </is>
       </c>
-      <c r="B496" s="2" t="inlineStr">
+      <c r="B496" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C496" s="2" t="inlineStr">
+      <c r="C496" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D496" s="2" t="inlineStr">
+      <c r="D496" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E496" s="2" t="inlineStr">
+      <c r="E496" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F496" s="2" t="inlineStr">
+      <c r="F496" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ottawa region</t>
         </is>
       </c>
-      <c r="G496" s="2" t="inlineStr">
+      <c r="G496" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5824814488?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H496" s="2" t="inlineStr">
+      <c r="H496" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I496" s="2" t="inlineStr">
+      <c r="I496" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high-speed connectivity, Ciena is committed to a people-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well-being, and belonging. We’re a technology company that leads with our humanity—driving ou</t>
         </is>
       </c>
-      <c r="J496" s="2" t="inlineStr"/>
-      <c r="K496" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L496" s="2" t="inlineStr"/>
+      <c r="J496" s="3" t="inlineStr"/>
+      <c r="K496" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L496" s="3" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="inlineStr">
+      <c r="A497" s="3" t="inlineStr">
         <is>
           <t>1fbd05245f3262616954cf63ccc480ccb8bca87a1becc028eb5edffb97ba3a1f</t>
         </is>
       </c>
-      <c r="B497" s="2" t="inlineStr">
+      <c r="B497" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C497" s="2" t="inlineStr">
+      <c r="C497" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D497" s="2" t="inlineStr">
+      <c r="D497" s="3" t="inlineStr">
         <is>
           <t>GeoComply Job on T-Net</t>
         </is>
       </c>
-      <c r="E497" s="2" t="inlineStr">
+      <c r="E497" s="3" t="inlineStr">
         <is>
           <t>Browser Security Engineer Intern, (Fall 2026)</t>
         </is>
       </c>
-      <c r="F497" s="2" t="inlineStr">
+      <c r="F497" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G497" s="2" t="inlineStr">
+      <c r="G497" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5805023760?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H497" s="2" t="inlineStr">
+      <c r="H497" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I497" s="2" t="inlineStr">
+      <c r="I497" s="3" t="inlineStr">
         <is>
           <t>About GeoComply We're GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
         </is>
       </c>
-      <c r="J497" s="2" t="inlineStr"/>
-      <c r="K497" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L497" s="2" t="inlineStr"/>
+      <c r="J497" s="3" t="inlineStr"/>
+      <c r="K497" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L497" s="3" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="inlineStr">
+      <c r="A498" s="3" t="inlineStr">
         <is>
           <t>f4ed026cd75c4af3fadbce5ee9588ec734736e731d00157a0e12e0c0b72bbb45</t>
         </is>
       </c>
-      <c r="B498" s="2" t="inlineStr">
+      <c r="B498" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C498" s="2" t="inlineStr">
+      <c r="C498" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D498" s="2" t="inlineStr">
+      <c r="D498" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E498" s="2" t="inlineStr">
+      <c r="E498" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (Later Influence)</t>
         </is>
       </c>
-      <c r="F498" s="2" t="inlineStr">
+      <c r="F498" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G498" s="2" t="inlineStr">
+      <c r="G498" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447533782</t>
         </is>
       </c>
-      <c r="H498" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I498" s="2" t="inlineStr"/>
-      <c r="J498" s="2" t="inlineStr"/>
-      <c r="K498" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L498" s="2" t="inlineStr"/>
+      <c r="H498" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I498" s="3" t="inlineStr"/>
+      <c r="J498" s="3" t="inlineStr"/>
+      <c r="K498" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L498" s="3" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="inlineStr">
+      <c r="A499" s="3" t="inlineStr">
         <is>
           <t>ab17c56e42d818f101b0e8e7667353754fbb970ef638cb4a7b65054c814f73af</t>
         </is>
       </c>
-      <c r="B499" s="2" t="inlineStr">
+      <c r="B499" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C499" s="2" t="inlineStr">
+      <c r="C499" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D499" s="2" t="inlineStr">
+      <c r="D499" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E499" s="2" t="inlineStr">
+      <c r="E499" s="3" t="inlineStr">
         <is>
           <t>Analyst, Market Insights, Student Intern</t>
         </is>
       </c>
-      <c r="F499" s="2" t="inlineStr">
+      <c r="F499" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G499" s="2" t="inlineStr">
+      <c r="G499" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=ec29b61ebe712f85</t>
         </is>
       </c>
-      <c r="H499" s="2" t="inlineStr">
+      <c r="H499" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I499" s="2" t="inlineStr">
+      <c r="I499" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J499" s="2" t="inlineStr"/>
-      <c r="K499" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L499" s="2" t="inlineStr"/>
+      <c r="J499" s="3" t="inlineStr"/>
+      <c r="K499" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L499" s="3" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="inlineStr">
+      <c r="A500" s="3" t="inlineStr">
         <is>
           <t>042d53443957cbe6a1d3f2b1ec8b36bb75407daeb633a1b312d8d1042cfdcf1c</t>
         </is>
       </c>
-      <c r="B500" s="2" t="inlineStr">
+      <c r="B500" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C500" s="2" t="inlineStr">
+      <c r="C500" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D500" s="2" t="inlineStr">
+      <c r="D500" s="3" t="inlineStr">
         <is>
           <t>Concert Properties</t>
         </is>
       </c>
-      <c r="E500" s="2" t="inlineStr">
+      <c r="E500" s="3" t="inlineStr">
         <is>
           <t>Climate Reporting Analyst Intern, Environment, Social &amp; Governance</t>
         </is>
       </c>
-      <c r="F500" s="2" t="inlineStr">
+      <c r="F500" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G500" s="2" t="inlineStr">
+      <c r="G500" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446388394</t>
         </is>
       </c>
-      <c r="H500" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I500" s="2" t="inlineStr"/>
-      <c r="J500" s="2" t="inlineStr"/>
-      <c r="K500" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L500" s="2" t="inlineStr"/>
+      <c r="H500" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I500" s="3" t="inlineStr"/>
+      <c r="J500" s="3" t="inlineStr"/>
+      <c r="K500" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L500" s="3" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>4534518d39648d532f1d8b0d4a33c6f975a2bdcf32f6bb9d8d4eaacf80fc6ae9</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>WaveLogic Software - Intern</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447435477</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr"/>
+      <c r="J501" s="2" t="inlineStr"/>
+      <c r="K501" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L501" s="2" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>88ae297fc007835fe3d3556c2e85de9bf19c0a6a45a3de450171e193a453cd91</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Agile Developer, Business Data Cloud</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447425537</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr"/>
+      <c r="J502" s="2" t="inlineStr"/>
+      <c r="K502" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L502" s="2" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>206ac00bde37511d1d7753b1c848dfe02f284cad8ad0add2b8a58060d52a52c3</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>OPAL-RT TECHNOLOGIES India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire – Développement logiciel bas niveau (Drivers / Linux embarqué) / Intern - Low-Level Software Development (Drivers / Embedded Linux)</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445547653</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr"/>
+      <c r="J503" s="2" t="inlineStr"/>
+      <c r="K503" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L503" s="2" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>3805955d4eebccc6738dc86aeb728bd07523f6f4195d88a133c4ff53113bc816</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>OPAL-RT TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire – Développement logiciel bas niveau (Drivers / Linux embarqué) / Intern - Low-Level Software Development (Drivers / Embedded Linux)</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447575186</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr"/>
+      <c r="J504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L504" s="2" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>d4ca5ce30649344985bb17a3d9676656cd3a78ae1d2cbc3e02a0bff50e07f082</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>OPAL-RT TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire – Développement logiciel bas niveau (Drivers / Linux embarqué) / Intern - Low-Level Software Development (Drivers / Embedded Linux)</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447563313</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr"/>
+      <c r="J505" s="2" t="inlineStr"/>
+      <c r="K505" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L505" s="2" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>7e921e8bfeb495c0f2f692fc4b662927578598510c707bc08a6e3e84f05349f5</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Martinrea International</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>Software Design Engineering (Artificial Intelligence) Co-op Student</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Woodbridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446740239</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr"/>
+      <c r="J506" s="2" t="inlineStr"/>
+      <c r="K506" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L506" s="2" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>aabdb47908a8652a0946701a15b6e63e0877e2730c1d7afdebc01b9b36f5ae7c</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>OPAL-RT TECHNOLOGIES India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire – Développement logiciel bas niveau (Drivers / Linux embarqué) / Intern - Low-Level Software Development (Drivers / Embedded Linux)</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445559521</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr"/>
+      <c r="J507" s="2" t="inlineStr"/>
+      <c r="K507" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L507" s="2" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>c1fb5967556b3f54d8a05947a02b352bc796ee5114533b3830c58e847e858d59</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>Field Engineering Co-Op</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4412453377</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr"/>
+      <c r="J508" s="2" t="inlineStr"/>
+      <c r="K508" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L508" s="2" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>d39bd54cac70dd1e7be5840333dc6d227af4fd0a1dbf4ab36be47a3cda61425d</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>Garland Commercial Ranges</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>Data and Power BI Intern</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446922818</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr"/>
+      <c r="J509" s="2" t="inlineStr"/>
+      <c r="K509" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L509" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -967,258 +967,4521 @@
       <c r="L10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>8dc264495e9d6c8b653f81f8c4cdb7f71abf7ffcd365e5414be1ed2e6681d9f8</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>QuadReal Property Group</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>AI Software Engineering, Fall 2026 - Toronto (Co-op/Internship) - 4 Months</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5825755561?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>About QuadReal Property Group QuadReal Property Group is a global real estate investment, development and operating company headquartered in Vancouver, British Columbia. Its assets under management are $98.5 billion. From its foundation in Canada as a full-service real estate operating company, Quad</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2974111084f5d194ed76f7f5a9a35f40a576015fa438fe214ad13825ad3e520a</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>ICUC</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Social Media Insight Analyst- International Remote</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4359131071</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>c94e90b42ffcd40817fdbb6aee0b39a4ad61e07b8a978975be91f2d245f7c694</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>M31 AI</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Research Technical Intern</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444036998</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>24ecb2a133ff296a9f5f38461d8fd6686c4adb4202c14a10e1ebf098872524c2</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>IWI Consulting Group</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Intern/Full time - Business Development Representative</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443192317</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>c6492da2760e5223b74a47c4e845d0a6de5d1106ac51d0dfb598bf618c53e6f8</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Data/Analytics Co-op</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447546525</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>bd7e252fbebc0f624fd2a7782846d677f5a39089ab5d6ef349d44cb2d73b0fbf</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Harbord, City of Toronto</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5801803318?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>fd044b277b696006e75da11e5e5bea0f0f0c7ee975f1cffa461e4f83f7c50c51</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5810850140?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>b818dc0f08121d35254f9a08bfa6b518fea30c5e60cd76be439f5f6a587f1582</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5799879390?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>7f6eb06835e098201dcd37869cd53a2f9ed08dd685e7859e677223b5071c96dc</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ottawa region</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5824814488?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high-speed connectivity, Ciena is committed to a people-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well-being, and belonging. We’re a technology company that leads with our humanity—driving ou</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>f706533b6dbadbc0843c06e6d5aea4d4081ba93b82686d3250b877a97b7ced9c</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Breslau, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5805405212?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration tasks. The intern will work clos</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>a2c3bf226c20ff5499ef97ed3d7723dd9deaae8824bb5cf77079dc9b9217b741</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5810852625?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>795afe1a9b1eccdab80eef1c63d3d6d94c7f990c3f7031c62acd41ffe02fd742</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>401 Auto</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Waterloo region</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5802729573?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration </t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>93b2bddc2aa9509efd1eff9887e601386baddf16340d14adcb2435cacf03b533</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5814582048?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Type: Co-op/Intern Work Model: Hybrid Reference code: 134060 Primary Location: Toronto, ON All Available Locations: Toronto, ON Our Purpose At Deloitte, our Purpose is to make an impact that matters. We exist to inspire and help our people, organizations, communities, and countries to thrive by </t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1fbd05245f3262616954cf63ccc480ccb8bca87a1becc028eb5edffb97ba3a1f</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply Job on T-Net</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Browser Security Engineer Intern, (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5805023760?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>About GeoComply We're GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2c148fba7ffd8f7876dc7ddc04851f39b2ae224390ae0427c93b9f669759b11f</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Business Web Solutions</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Web Developer Intern - Remote</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Park, Calgary</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5800148553?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>This is a remote position. Job Overview We are hiring Full Stack Web Developer Interns who are passionate about learning and applying modern web development skills. This remote internship, available for 1 to 6 months, provides hands-on experience through live projects and mentorship from industry pr</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>e58d13c1c30372b208727df9492464ba9538bb6a77c3eee7f5ee2cf215b63d47</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Business Web Solutions</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Web Development Intern / Trainee - Remote</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Dalhousie Ward, Ottawa</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5800148554?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>This is a remote position. Job Overview We are seeking motivated candidates for Web Development Intern / Trainee to provide hands-on exposure to real-world web projects. This internship program runs for 1 to 6 months, depending on your availability, and focuses on building practical skills in modern</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>5028a4bfc213660ea1c505370b3326b827e41eec99bcc48008de95ce9cccc011</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>GeoComply Job on T-Net</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806267822?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Location: Vancouver, B.C. Full-time, 40 hrs/week Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We're GeoComply, an identity verification, anti-fraud and compliance co</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>0db5d8505294bdd9f09b9859c4d8f8d4aaaff09fd0ec8f499d12fd4a07ac28cd</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ResponsiveAds, Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ResponsiveAds Full-Stack Developer (2026 Summer and Fall Internship)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, Greater Vancouver</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5818288827?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description ResponsiveAds is the leader in advanced HTML5 premium ad creatives that are dynamic to any screen, user and context. The existing ad tech is stuck inside a box that can't adapt quickly enough. ResponsiveAds takes the "responsive" paradigm from web CMS, ad serving, and</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>afe4a66b20aac50fdb8cf772183887181421ac364d0c2568d0becfdb43c82374</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Harbord, City of Toronto</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5801767985?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management – Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a North Am</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2498f4490e00a0e94dff6b346ab965e71cd5860fae6212a1939c46d11d07278b</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5799881034?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Job Description Job Description Forum Asset Management – Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Foru</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>41b6406ae2439564d0509d653df4273b09a20251fcca849a1b7f74910b38fd7f</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5802726255?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Job Description Salary: Forum Asset Management Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investment. </t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>9b85f6f6f66a36c631181d39d046e42f52d5b1e210121f13f41508af53c9e92c</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CPKC</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Intern Cloud Developer</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=c00383257b9e963d</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Join CPKC, North America’s first transnational railroad connecting U.S., Canada, and Mexico, where your career drives progress and safety is paramount. We connect communities, fuel economic growth, and provide meaningful work in a culture that values diversity, accountability, and pride. With opport</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>153f39c1e7647b77a2d27e3ed0444b6042b7f36170e0feb8c7e849663daddbff</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator Intern</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3f08fd72d7e4e021</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>74aca67a8279cc9dea6bb4fdde81338c7cfb287a8bf800d2c0a70813b2be75c2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator Intern</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6c141689404fa785</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>4d8114ece6e6bb63a9eb3027fab2b1a590e2f0060a107b591c1c24ebc5d32fe3</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ShyftLabs</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f7e7781c8bbe5238</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>**About ShyftLabs**
+At ShyftLabs, we live and breathe data. Since 2020, we’ve been helping Fortune 500 companies unlock growth through innovative digital solutions that drive real business impact. With teams across Canada, the U.S., and India, we’re growing quickly and looking for curious, motiva</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>abccf9f1241972aa69740ba24f6cbabd7ad4f24cec622eb275f49d6c5d28f653</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Global</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (8 month Co-op)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=af76f88610e75eb7</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>**Job Description:**
+Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>9e1215b501e32338df5fc17b2c3fe0c92f07257006f084d669cb6a28cd555d90</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Kobo</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (8 month Co-op)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=442d17285175b527</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>**Job Description:**
+Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>f4ed026cd75c4af3fadbce5ee9588ec734736e731d00157a0e12e0c0b72bbb45</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (Later Influence)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447533782</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>e9827589effa8a04a676233753a45a3e4e9c4cd399ff7cb633e9217dbdbfb6d9</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Systems Engineering (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417506534</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>3be7e34ba8d2875a76d57b4f3bd77961d067c8c88f048c017adab72c46703555</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TommieTest</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op (Later Influence)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444224689</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>7fe164d5e797067556ee9405fb6599442a00c7e2073ce62fae98ed1dbf78f5dc</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Applications (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424263570</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>c3e294f183878b78a9882ebea6a240b8595af9d86dbff8d30c9b550174f62c62</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Vehicle Controls (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4423978788</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>a59b987cbc91ef21b10ca138e4f3b98cf2ffaa43ce96816856e3ba04bc7f4432</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Corpay</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer (Co-op)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4192183195</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9959f56813f52812497aebf64244bf11813c52b2c3124ae8422d7651574a47a0</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate  Co-op Student – Software Engineer – Large Molecule Discovery - Technology</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438247234</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>349bc4cb53dbd1a24a93c6b82d08fdae0bed0bc9fb192c7672751c909d2851e9</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>The 401 Group of Companies</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Intern (Full-Stack / DevOps Support)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, ON, CA</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=af3732d8e7f6a952</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands\-on and will involve working across backend, frontend, database, and basic system administration tasks.**
+ **The intern will </t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>a17706332ed7f6485ce908257319c6d5ff3ce26a3001d4f7ebec3d5e866843f6</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411289794</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>af441cbca3987e0b5fb5c85ef8dcd62d069d591dfcfaddb8d977f42a5a043d74</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Fall / Winter 2026)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4407957965</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>f43d8b9b623db585547e19352b9b29f8ad96aaded5ef219c4f6941d6053a885b</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (4 Months)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445199222</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2c6f68b67267d004f5e973da3bce1f6a988b8d263f58858fec19f5b559e4c6cc</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>TechInsights</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445231398</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5c9909f37e28da061007c213a1c3bc792adcec1ed14a5f928ff804fd73071603</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441398123</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3462695cd83572a2da0c8c66f8343924e5e4f63c1403b976b09318b6c6ad8257</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441393191</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>aa194547742294f91915209d725a0dc7eea02acef52da5136740f386d4de2fa3</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441388499</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>00846fc045f2caf0ceecede53f8e0b63f2c1362374f4c3389ae40ba12be3c73a</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Applications (Fall-Spring Co-op)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424269238</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>38383cd26118f760a6ed848abd772ac9421515b0effd63653b21bdcc6efca70f</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Forum Asset Management</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440069507</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>8bf58a08f2488c364a177b97a2e6ed0662eb8cd37a833fbc323cc49b3cf5d1ed</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Architectural Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=42d8e65dba8e6b4a</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description** **Work with Us. Change the World.**
+At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>1296ac58909932f85b2459e4482d44adfd8b9e086fb1c90580a70b41f4dc9727</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Introba</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=b5e758d897c2541f</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**WHERE PASSION \+ PURPOSE ALIGN**
+We are the curious. Problem solvers. Driven to unlock the potential in every system. Across five countries are 1,100 engineers, designers, and consultants collaborating to elevate the human experience, create more resilient communities, and protect the health of </t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>02c1165808c08d4bf7dea212053c5e6e81a75a12280837e2e2f05e63e8d4eb0c</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer Intern - Fall</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=e7bcc5b6add0e088</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description**  
+CRB's nearly 1,400 expert professionals drive innovative, life\-changing and life\-saving solutions for manufacturers in the life sciences and food and beverage industries. Our mission, vision, and core values put client satisfaction and employee experience at the center o</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>864fa9120f59fab59852a4d7ddd3ad8d77844d50cf5b8117ff35252c9a096fd7</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Telecommunications and Electronic Security Systems Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=2a923d28f878ccfb</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>**Company Description** **Work with Us. Change the World.**
+At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>c2ea396b5ad5343981700ad754cb134a304bdd33cbb81d2d0983729fd79c5810</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Kepler Communications</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>FPGA Digital Design Engineering Intern (January 2027) (4-16 months)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=05ee97fdaa7d3e43</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>**At** **Kepler Communications****, we're not just imagining the future of on\-demand space connectivity \-** ***we're*** ***leading it!***
+Our mission is to provide real\-time on\-orbit connectivity for critical missions, enabling a new era of data\-driven intelligence and innovation. With **33 sa</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>c63f3894309d0926b605f6417b0e84077f9709ebb7e180a0a1983810ef9981b2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Malware Research Intern</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f853f7edc710034c</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>TrendAI™, the global AI security leader and enterprise business unit of Trend Micro, empowers organizations with full AI visibility and consolidated security that inspires confidence, drives innovation, and eliminates risk.
+At TrendAI™, we’re always seeking exceptional talent; people who wan</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>9a1d2e16834b3288e17c6792c175e9e18489b2c0c424e694b78499a4a2a40680</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Foresters Financial</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer Co-op Student (4-month contract)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3a3999724aa932bc</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>**Career Opportunity**
+======================
+**Role Title**
+--------------
+Quality Assurance Engineer Co\-op Student (4\-month contract)**Purpose of role**
+-------------------
+The Quality Assurance Engineer Co\-op offers a fantastic opportunity for a student to validate changes to workflows, b</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>449e7774a71465e9c7a55c1f71140a504cbeb14af7fc337bc64ce80b5bd94b10</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7ba066afb65b8839</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R1012810
+**Date Posted:**
+2026\-07\-07
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+IT, Telecom \&amp; Internet
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a lega</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>22437e057d6b3dd61be5ec1078e780abfcd21087c232d4b90bc75ef23ee4c844</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>QuadReal Property Group</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>AI Software Engineering, Fall 2026 - Toronto (Co-op/Internship) - 4 Months</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446540117</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>6ca0bce23bf7ab6d2c3f06cd4f0f6e4b8817c56c08b6580124c4eb8af11bcdf0</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer – C++</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443004828</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>933f17573189b18ea21ea1131e2910fb0bd5e69ca0c099491afec64ffd8e4310</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Robotics - Software Development Engineer Intern - 2026 - Toronto</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443035914</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2466ac71e0b4d483b31f2a408649ebe00d02dd815b27f16061a507b7dbc12683</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Eclipse Automation</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438558850</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>05623857ee6fed636d2dc7c96b7431e7ea83db1d7537aa89a0cd119a72383f06</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Disaster and Climate Resilience Co-op</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=64b5c0aeffbc0b66</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Arcadis is the world's leading company delivering sustainable design, engineering, and consultancy solutions for natural and built assets.
+We are more than 34,000 people, in over 30 countries, dedicated to improving quality of life. Everyone has an important role to play. With the power of many c</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>8ebc38658224ddd7449baf793e21105bffab023ad48354ec355380fa1e8b11b5</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Thurber Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Geotechnical Engineering Intern (2026073191)</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=253d2c312b718655</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>### **Overview**
+Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Ottawa, Ontario**.
+Thurber provides geotechnical, environmental and construction materials engineering and testing services for a variety of industries across Canad</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ad1229b95931f80f45c8765ce234f2809ff5025c1a24d899007ac08cd4c63c6b</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=922860bf52dff9f8</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>94ed7724371a2181bff162dbd1a95ed3b21a83c3947166533cfad6d68e82b965</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411409044</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>0ba86004b4b2b36bce46d353fe82a441170d7060ec5ce25d81577609b55d2400</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437303852</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>eec667a61dfae420add313e65c602214d3ff034f818eb9e59d4602668c940e7f</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer – Intern</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4424262762</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>5015edfb77f8f390ec1cfa3e40f4084344e4267ff9f1bed8f26c453c79320b6f</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445778485</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>0562e736c59f9a98d44961e013b1c4bcfdc6ce9cfa39c407907e79a5eb40077a</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Hach Company</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Aquatic Informatics - Machine Learning Co-Op (Intern)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>London, ON, CA</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6cb787a9ebefee48</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Imagine yourself…
+* Doing meaningful work that makes an everyday impact on the world around you.
+* Growing your expertise and expanding your skillset with every project.
+It’s possible with a role at **Aquatic Informatics** (**https://aquaticinformatics.com/**).
+Aquatic Informatics (AQI), a **Ve</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>fbf74cb741a69bd68413f74b2eac16cbbb7b281ebe1f32d1bbc1e171cd2213a5</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>CSMC</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Civil Engineering Intern (Advanced Energy &amp; Infrastructure)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, ON, CA</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=eff5c2c01a049d89</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>**Civil Engineering Intern (Advanced Energy \&amp; Infrastructure)**
+**Location**: Waterloo, ON (On\-Site)  
+**Employment Type**: Internship / Co\-op / Student Position  
+**Term**: 4\-Month Initial Term (September\-December 2026\)
+ **About Canadian Strategic Missions Corp. (CSMC)**
+Canadian Stra</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>845dafc4ba3b6f93aafaaf33dde5531220d6392e6b074eb6b6f1968307bf0d22</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4412449379</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>9dc61afa8ec512bd3599b1f2ab516e7f9e7be3f07febc71e50820b5893431002</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Remote, CA</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=35e86411ab20e549</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>**Mechanical Engineering Intern \- Job Summary**
+The Mechanical Engineering Intern supports the engineering team in the design, development, testing, and documentation of mechanical products and systems. Working under the guidance of senior engineers, the intern applies engineering principles to as</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>6284632573188b520c76cd7aa45fba122be70cc07b2de8cd99a2828c64c87cc6</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Co-op (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Halifax, Nova Scotia, Canada</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4411296638</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>de3c58ddf54c6a364eb038b5cde2693bf42c44f4575d3410822b7597da5a78f3</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern - CD1</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447247459</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>c0784525515734efc02aa27ed8780e2a65e89d10c15d609b7fb8bb117c2ec72e</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>AI Developer Intern 8 Months Fall 2026</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444187287</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>a07383d5826733e6ec1a025076483c9cbe35237c3a4e20f50323ebe6e42d8b8a</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Backend Development Intern</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446101920</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>30780e29136aef3428c06690f14bc955dc6fd9a5496a7cf313395fe84b7b4073</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Mitchell &amp; Associates</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Software Design Engineering (Artificial Intelligence) Co-op Student</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Vaughan, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446536816</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>182f973ee093ead211312b6070b8d98bcf2e76292704459255b6e062ad67cdaf</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>DRW</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437615263</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>645c75885bc1feb82db65694e90216ef076dbe92bb0da086c88f4f856621f45f</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>upzoids</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Power Platform Developer Intern</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=8c8b12a586a29691</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>As a Power Platform Developer Intern, you will gain hands\-on experience working on real\-world projects that involve designing, developing, and enhancing Power Pages applications. You will collaborate with our experienced developers and consultants to create visually appealing and user\-friendly in</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ab17c56e42d818f101b0e8e7667353754fbb970ef638cb4a7b65054c814f73af</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>TMX GROUP</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Analyst, Market Insights, Student Intern</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=ec29b61ebe712f85</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>**Venture outside the ordinary \- TMX Careers**
+The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>404d5c870398d7a83cc5caebdb39699419b3e94737a46517f65959946e511f32</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Algo Communication Products Ltd</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Developer, Internal Applications</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444911874</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>d5400c304aeed66fe49ef1cc7f88604294ade183f147a494079a59ac9b2bfa3b</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Developer Intern</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441285844</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>1fe63fed60547910f0db79c893c799e98442b574572cdde4583b5a50c25538bc</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Helcim</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (Internal Tools &amp; Systems)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4418686539</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ec85e55ad54c17d669ab730c75bee287cfa3ee8c20c3834dc7b10d0d2b79d4d2</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Junior Full Stack Developer Coop</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Milton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4420631844</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>f2229fff4aa7a6c3da3eb14263c0565edf502c11c09661487d723acb2ae23aab</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Intern, CloudOps</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f0baf0e899ea9845</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>**Join a Challenger**  
+At EQ, we're remaking banking so every Canadian gets ahead, every day. Serving nearly 4 million Canadians from coast to coast, we offer a wide variety of financial services from banking and lending, to trust and credit union solutions.  
+We've been at this since 197</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>8382c30dbe8d38d6487c59958337efe9bff2f7e27e26860fbf1377ae05061ab4</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=513f1e45241c21d6</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>91450c8aa27e99a20ce3ce5390742b2841128560dcf15cd4e65b0903317b0aa9</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>e-STORAGE</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>DevOps / DevSecOps Intern</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4421988308</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>5c2781fec3478855036c976154ab9bab0c954a91e6387e86aa475f72d6fb65e5</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en automatisation de l'assurance qualité (AQ) - Automne 2026 / QA Automation Engineer Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445202195</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>6976f8db278232a6a41e1c8b2557a76d09ae53c55b0fc8248ea6549594feba51</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Enverus</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>GIS Intern - 26293</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7f1a3244570b28bd</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>**GIS Intern**
+**Why YOU want this position**
+At Enverus, we’re committed to empowering the global quality of life by helping our customers make energy affordable and accessible to the world.
+We are the most trusted energy\-dedicated SaaS company, with a platform built to maximize value from ge</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>7e000d2fb68783da1a2beaf066b67c384246c2324e154b769388acebf7b6676f</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Egis Group</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Transportation Structures</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON, CA</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=38a78cdd66ed18df</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Company Description**  
+Join Egis, where your ambition meets unparalleled growth opportunities. As we continue to expand within Canada, we're looking for talented professionals like you to be a part of our innovative team. Imagine working alongside over 1,000 top\-tier engineers, architects, and </t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>f7feb75d414f40e21bf765239143aa299ae8a80eb215f7ca386b4bfebdbc8df0</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ProCogia</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Statistical Programming Intern</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4429572367</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1221,2421 +1221,2421 @@
       <c r="L15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>bd7e252fbebc0f624fd2a7782846d677f5a39089ab5d6ef349d44cb2d73b0fbf</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Harbord, City of Toronto</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5801803318?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a Nort</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>fd044b277b696006e75da11e5e5bea0f0f0c7ee975f1cffa461e4f83f7c50c51</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5810850140?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: Forum Asset Management Intern, Software Development (Fall 2026) 8 month OR 4 month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investme</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>b818dc0f08121d35254f9a08bfa6b518fea30c5e60cd76be439f5f6a587f1582</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5799879390?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description Forum Asset Management – Intern, Software Development (Fall 2026) 8 month OR 4 month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. </t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>7f6eb06835e098201dcd37869cd53a2f9ed08dd685e7859e677223b5071c96dc</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ottawa region</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5824814488?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high-speed connectivity, Ciena is committed to a people-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well-being, and belonging. We’re a technology company that leads with our humanity—driving ou</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>f706533b6dbadbc0843c06e6d5aea4d4081ba93b82686d3250b877a97b7ced9c</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Breslau, Waterloo region</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5805405212?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration tasks. The intern will work clos</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>a2c3bf226c20ff5499ef97ed3d7723dd9deaae8824bb5cf77079dc9b9217b741</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Waterloo region</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5810852625?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Salary: $24.00 - $28.00 Per Hour We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database,</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>795afe1a9b1eccdab80eef1c63d3d6d94c7f990c3f7031c62acd41ffe02fd742</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>401 Auto</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Waterloo region</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5802729573?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands-on and will involve working across backend, frontend, database, and basic system administration </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>93b2bddc2aa9509efd1eff9887e601386baddf16340d14adcb2435cacf03b533</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Analyst Intern, Software Engineering, Innovation CoE - Fall 2026 - Toronto</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5814582048?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Type: Co-op/Intern Work Model: Hybrid Reference code: 134060 Primary Location: Toronto, ON All Available Locations: Toronto, ON Our Purpose At Deloitte, our Purpose is to make an impact that matters. We exist to inspire and help our people, organizations, communities, and countries to thrive by </t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>1fbd05245f3262616954cf63ccc480ccb8bca87a1becc028eb5edffb97ba3a1f</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>GeoComply Job on T-Net</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Browser Security Engineer Intern, (Fall 2026)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5805023760?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>About GeoComply We're GeoComply! We are at the forefront of geolocation, cybersecurity, and anti-fraud innovation, developing and delivering cutting-edge technologies to help ensure regulatory compliance, combat bad online actors, alleviate user friction, and protect businesses from fraud. Achieving</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>2c148fba7ffd8f7876dc7ddc04851f39b2ae224390ae0427c93b9f669759b11f</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Business Web Solutions</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Full Stack Web Developer Intern - Remote</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Victoria Park, Calgary</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5800148553?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>This is a remote position. Job Overview We are hiring Full Stack Web Developer Interns who are passionate about learning and applying modern web development skills. This remote internship, available for 1 to 6 months, provides hands-on experience through live projects and mentorship from industry pr</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>e58d13c1c30372b208727df9492464ba9538bb6a77c3eee7f5ee2cf215b63d47</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Business Web Solutions</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Web Development Intern / Trainee - Remote</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Dalhousie Ward, Ottawa</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5800148554?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>This is a remote position. Job Overview We are seeking motivated candidates for Web Development Intern / Trainee to provide hands-on exposure to real-world web projects. This internship program runs for 1 to 6 months, depending on your availability, and focuses on building practical skills in modern</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>5028a4bfc213660ea1c505370b3326b827e41eec99bcc48008de95ce9cccc011</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>GeoComply Job on T-Net</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Full Stack Developer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5806267822?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Location: Vancouver, B.C. Full-time, 40 hrs/week Contract length: ~4 months Start date: September 3rd, 2026 Application deadline: July 23,2026 Salary range: $54,000 and ~$62,000 (annualized, prorated to your ~4-month placement). We're GeoComply, an identity verification, anti-fraud and compliance co</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>0db5d8505294bdd9f09b9859c4d8f8d4aaaff09fd0ec8f499d12fd4a07ac28cd</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds, Inc.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>ResponsiveAds Full-Stack Developer (2026 Summer and Fall Internship)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Vancouver, Greater Vancouver</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5818288827?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description ResponsiveAds is the leader in advanced HTML5 premium ad creatives that are dynamic to any screen, user and context. The existing ad tech is stuck inside a box that can't adapt quickly enough. ResponsiveAds takes the "responsive" paradigm from web CMS, ad serving, and</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>afe4a66b20aac50fdb8cf772183887181421ac364d0c2568d0becfdb43c82374</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Harbord, City of Toronto</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5801767985?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management – Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Forum Asset Management is a North Am</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>2498f4490e00a0e94dff6b346ab965e71cd5860fae6212a1939c46d11d07278b</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5799881034?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Job Description Job Description Forum Asset Management – Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location: In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes™ through Investment. Foru</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>41b6406ae2439564d0509d653df4273b09a20251fcca849a1b7f74910b38fd7f</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Intern, Data Engineering (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5802726255?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Description Job Description Salary: Forum Asset Management Intern, Data Engineering (Fall 2026) 8-month OR 4-month Location:In-Office, 181 Bay Street, Toronto Work Schedule: Full-time, in-office (5 days/week) from September 2026 About Forum: Delivering Extraordinary Outcomes through Investment. </t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>9b85f6f6f66a36c631181d39d046e42f52d5b1e210121f13f41508af53c9e92c</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>CPKC</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Intern Cloud Developer</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=c00383257b9e963d</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Join CPKC, North America’s first transnational railroad connecting U.S., Canada, and Mexico, where your career drives progress and safety is paramount. We connect communities, fuel economic growth, and provide meaningful work in a culture that values diversity, accountability, and pride. With opport</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>153f39c1e7647b77a2d27e3ed0444b6042b7f36170e0feb8c7e849663daddbff</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Technical Project Coordinator Intern</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3f08fd72d7e4e021</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>74aca67a8279cc9dea6bb4fdde81338c7cfb287a8bf800d2c0a70813b2be75c2</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Technical Project Coordinator Intern</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6c141689404fa785</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>4d8114ece6e6bb63a9eb3027fab2b1a590e2f0060a107b591c1c24ebc5d32fe3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>ShyftLabs</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f7e7781c8bbe5238</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>**About ShyftLabs**
 At ShyftLabs, we live and breathe data. Since 2020, we’ve been helping Fortune 500 companies unlock growth through innovative digital solutions that drive real business impact. With teams across Canada, the U.S., and India, we’re growing quickly and looking for curious, motiva</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>abccf9f1241972aa69740ba24f6cbabd7ad4f24cec622eb275f49d6c5d28f653</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Rakuten Global</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (8 month Co-op)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=af76f88610e75eb7</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>**Job Description:**
 Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>9e1215b501e32338df5fc17b2c3fe0c92f07257006f084d669cb6a28cd555d90</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Rakuten Kobo</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (8 month Co-op)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=442d17285175b527</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>**Job Description:**
 Here at Rakuten Kobo Inc., our mission is to make reading lives better. We stand for readers. We also stand for our employees – from interns and co\-ops to permanent staff – and support their growth and development. Whether you are a student at the start of your career or a pr</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>f4ed026cd75c4af3fadbce5ee9588ec734736e731d00157a0e12e0c0b72bbb45</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (Later Influence)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447533782</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>e9827589effa8a04a676233753a45a3e4e9c4cd399ff7cb633e9217dbdbfb6d9</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern - Systems Engineering (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417506534</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>3be7e34ba8d2875a76d57b4f3bd77961d067c8c88f048c017adab72c46703555</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>TommieTest</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op (Later Influence)</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444224689</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>7fe164d5e797067556ee9405fb6599442a00c7e2073ce62fae98ed1dbf78f5dc</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern - Applications (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424263570</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>c3e294f183878b78a9882ebea6a240b8595af9d86dbff8d30c9b550174f62c62</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern - Vehicle Controls (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4423978788</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>a59b987cbc91ef21b10ca138e4f3b98cf2ffaa43ce96816856e3ba04bc7f4432</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Corpay</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Software Developer (Co-op)</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4192183195</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>9959f56813f52812497aebf64244bf11813c52b2c3124ae8422d7651574a47a0</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Undergraduate  Co-op Student – Software Engineer – Large Molecule Discovery - Technology</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438247234</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>349bc4cb53dbd1a24a93c6b82d08fdae0bed0bc9fb192c7672751c909d2851e9</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>The 401 Group of Companies</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Software Development Intern (Full-Stack / DevOps Support)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Cambridge, ON, CA</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=af3732d8e7f6a952</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**We are looking for a Software Development Intern to support ongoing development, maintenance, and operational tasks across a production software system. This role is hands\-on and will involve working across backend, frontend, database, and basic system administration tasks.**
  **The intern will </t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>a17706332ed7f6485ce908257319c6d5ff3ce26a3001d4f7ebec3d5e866843f6</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Magnet Forensics</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Fall 2026)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411289794</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>af441cbca3987e0b5fb5c85ef8dcd62d069d591dfcfaddb8d977f42a5a043d74</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Cohere</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern (Fall / Winter 2026)</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4407957965</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>f43d8b9b623db585547e19352b9b29f8ad96aaded5ef219c4f6941d6053a885b</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern (4 Months)</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445199222</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>2c6f68b67267d004f5e973da3bce1f6a988b8d263f58858fec19f5b559e4c6cc</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>TechInsights</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445231398</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>5c9909f37e28da061007c213a1c3bc792adcec1ed14a5f928ff804fd73071603</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441398123</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>3462695cd83572a2da0c8c66f8343924e5e4f63c1403b976b09318b6c6ad8257</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441393191</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>aa194547742294f91915209d725a0dc7eea02acef52da5136740f386d4de2fa3</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Clearline</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern/Co-op - 2026 Fall</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Waterloo, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441388499</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>00846fc045f2caf0ceecede53f8e0b63f2c1362374f4c3389ae40ba12be3c73a</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern - Applications (Fall-Spring Co-op)</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424269238</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>38383cd26118f760a6ed848abd772ac9421515b0effd63653b21bdcc6efca70f</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Forum Asset Management</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Intern, Software Development (Fall 2026) 8 month OR 4 month</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440069507</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>8bf58a08f2488c364a177b97a2e6ed0662eb8cd37a833fbc323cc49b3cf5d1ed</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>AECOM</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Architectural Engineering Intern</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=42d8e65dba8e6b4a</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>**Company Description** **Work with Us. Change the World.**
 At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>1296ac58909932f85b2459e4482d44adfd8b9e086fb1c90580a70b41f4dc9727</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Introba</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Electrical Engineering Intern/Co-Op</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=b5e758d897c2541f</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**WHERE PASSION \+ PURPOSE ALIGN**
 We are the curious. Problem solvers. Driven to unlock the potential in every system. Across five countries are 1,100 engineers, designers, and consultants collaborating to elevate the human experience, create more resilient communities, and protect the health of </t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>02c1165808c08d4bf7dea212053c5e6e81a75a12280837e2e2f05e63e8d4eb0c</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Mechanical Engineer Intern - Fall</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=e7bcc5b6add0e088</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>**Company Description**  
 CRB's nearly 1,400 expert professionals drive innovative, life\-changing and life\-saving solutions for manufacturers in the life sciences and food and beverage industries. Our mission, vision, and core values put client satisfaction and employee experience at the center o</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>864fa9120f59fab59852a4d7ddd3ad8d77844d50cf5b8117ff35252c9a096fd7</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>AECOM</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Telecommunications and Electronic Security Systems Engineering Intern</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=2a923d28f878ccfb</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>**Company Description** **Work with Us. Change the World.**
 At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastr</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>c2ea396b5ad5343981700ad754cb134a304bdd33cbb81d2d0983729fd79c5810</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Kepler Communications</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>FPGA Digital Design Engineering Intern (January 2027) (4-16 months)</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=05ee97fdaa7d3e43</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>**At** **Kepler Communications****, we're not just imagining the future of on\-demand space connectivity \-** ***we're*** ***leading it!***
 Our mission is to provide real\-time on\-orbit connectivity for critical missions, enabling a new era of data\-driven intelligence and innovation. With **33 sa</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>c63f3894309d0926b605f6417b0e84077f9709ebb7e180a0a1983810ef9981b2</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Trend Micro Inc.</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Malware Research Intern</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f853f7edc710034c</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>TrendAI™, the global AI security leader and enterprise business unit of Trend Micro, empowers organizations with full AI visibility and consolidated security that inspires confidence, drives innovation, and eliminates risk.
 At TrendAI™, we’re always seeking exceptional talent; people who wan</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>9a1d2e16834b3288e17c6792c175e9e18489b2c0c424e694b78499a4a2a40680</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Foresters Financial</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Quality Assurance Engineer Co-op Student (4-month contract)</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3a3999724aa932bc</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>**Career Opportunity**
 ======================
@@ -3646,56 +3646,56 @@
 The Quality Assurance Engineer Co\-op offers a fantastic opportunity for a student to validate changes to workflows, b</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>449e7774a71465e9c7a55c1f71140a504cbeb14af7fc337bc64ce80b5bd94b10</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Hitachi Energy</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7ba066afb65b8839</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -3715,621 +3715,621 @@
 A career at Hitachi Rail will help create a lega</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>22437e057d6b3dd61be5ec1078e780abfcd21087c232d4b90bc75ef23ee4c844</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>QuadReal Property Group</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>AI Software Engineering, Fall 2026 - Toronto (Co-op/Internship) - 4 Months</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446540117</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>6ca0bce23bf7ab6d2c3f06cd4f0f6e4b8817c56c08b6580124c4eb8af11bcdf0</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer – C++</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443004828</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>933f17573189b18ea21ea1131e2910fb0bd5e69ca0c099491afec64ffd8e4310</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Robotics - Software Development Engineer Intern - 2026 - Toronto</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443035914</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>2466ac71e0b4d483b31f2a408649ebe00d02dd815b27f16061a507b7dbc12683</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Eclipse Automation</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438558850</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>05623857ee6fed636d2dc7c96b7431e7ea83db1d7537aa89a0cd119a72383f06</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Arcadis</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Disaster and Climate Resilience Co-op</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=64b5c0aeffbc0b66</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Arcadis is the world's leading company delivering sustainable design, engineering, and consultancy solutions for natural and built assets.
 We are more than 34,000 people, in over 30 countries, dedicated to improving quality of life. Everyone has an important role to play. With the power of many c</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>8ebc38658224ddd7449baf793e21105bffab023ad48354ec355380fa1e8b11b5</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Thurber Engineering Ltd.</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Geotechnical Engineering Intern (2026073191)</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=253d2c312b718655</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>### **Overview**
 Thurber has an exciting opportunity for an early career **Geotechnical Engineering Intern** to join our team in **Ottawa, Ontario**.
 Thurber provides geotechnical, environmental and construction materials engineering and testing services for a variety of industries across Canad</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>ad1229b95931f80f45c8765ce234f2809ff5025c1a24d899007ac08cd4c63c6b</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=922860bf52dff9f8</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>94ed7724371a2181bff162dbd1a95ed3b21a83c3947166533cfad6d68e82b965</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Magnet Forensics</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Fall 2026)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411409044</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>0ba86004b4b2b36bce46d353fe82a441170d7060ec5ce25d81577609b55d2400</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437303852</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>eec667a61dfae420add313e65c602214d3ff034f818eb9e59d4602668c940e7f</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Embedded Software Engineer – Intern</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4424262762</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>5015edfb77f8f390ec1cfa3e40f4084344e4267ff9f1bed8f26c453c79320b6f</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Software Liquid Spectrum Applications Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445778485</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>0562e736c59f9a98d44961e013b1c4bcfdc6ce9cfa39c407907e79a5eb40077a</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Hach Company</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Aquatic Informatics - Machine Learning Co-Op (Intern)</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>London, ON, CA</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6cb787a9ebefee48</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>Imagine yourself…
 * Doing meaningful work that makes an everyday impact on the world around you.
@@ -4338,56 +4338,56 @@
 Aquatic Informatics (AQI), a **Ve</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>fbf74cb741a69bd68413f74b2eac16cbbb7b281ebe1f32d1bbc1e171cd2213a5</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>CSMC</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Civil Engineering Intern (Advanced Energy &amp; Infrastructure)</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Waterloo, ON, CA</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=eff5c2c01a049d89</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>**Civil Engineering Intern (Advanced Energy \&amp; Infrastructure)**
 **Location**: Waterloo, ON (On\-Site)  
@@ -4397,972 +4397,972 @@
 Canadian Stra</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>845dafc4ba3b6f93aafaaf33dde5531220d6392e6b074eb6b6f1968307bf0d22</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Acceldata</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Co-op</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4412449379</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>9dc61afa8ec512bd3599b1f2ab516e7f9e7be3f07febc71e50820b5893431002</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Mechanical Engineering Intern</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Remote, CA</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=35e86411ab20e549</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>**Mechanical Engineering Intern \- Job Summary**
 The Mechanical Engineering Intern supports the engineering team in the design, development, testing, and documentation of mechanical products and systems. Working under the guidance of senior engineers, the intern applies engineering principles to as</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>6284632573188b520c76cd7aa45fba122be70cc07b2de8cd99a2828c64c87cc6</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Magnet Forensics</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Software Developer Co-op (Fall 2026)</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Halifax, Nova Scotia, Canada</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4411296638</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>de3c58ddf54c6a364eb038b5cde2693bf42c44f4575d3410822b7597da5a78f3</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern - CD1</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447247459</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>c0784525515734efc02aa27ed8780e2a65e89d10c15d609b7fb8bb117c2ec72e</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Dayforce</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>AI Developer Intern 8 Months Fall 2026</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444187287</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>a07383d5826733e6ec1a025076483c9cbe35237c3a4e20f50323ebe6e42d8b8a</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Zenith</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Backend Development Intern</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446101920</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>30780e29136aef3428c06690f14bc955dc6fd9a5496a7cf313395fe84b7b4073</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Mitchell &amp; Associates</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Software Design Engineering (Artificial Intelligence) Co-op Student</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>Vaughan, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446536816</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>182f973ee093ead211312b6070b8d98bcf2e76292704459255b6e062ad67cdaf</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>DRW</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437615263</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>645c75885bc1feb82db65694e90216ef076dbe92bb0da086c88f4f856621f45f</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>upzoids</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Power Platform Developer Intern</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=8c8b12a586a29691</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>As a Power Platform Developer Intern, you will gain hands\-on experience working on real\-world projects that involve designing, developing, and enhancing Power Pages applications. You will collaborate with our experienced developers and consultants to create visually appealing and user\-friendly in</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>ab17c56e42d818f101b0e8e7667353754fbb970ef638cb4a7b65054c814f73af</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>TMX GROUP</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Analyst, Market Insights, Student Intern</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=ec29b61ebe712f85</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>**Venture outside the ordinary \- TMX Careers**
 The TMX group of companies includes leading global exchanges such as the Toronto Stock Exchange, Montreal Exchange, and numerous innovative organizations enhancing capital markets. United as a global team, we’re connecting cross\-functionally, travers</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>404d5c870398d7a83cc5caebdb39699419b3e94737a46517f65959946e511f32</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Algo Communication Products Ltd</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Cloud Developer, Internal Applications</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444911874</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>d5400c304aeed66fe49ef1cc7f88604294ade183f147a494079a59ac9b2bfa3b</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Revvity</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Full-Stack AI Developer Intern</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441285844</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>1fe63fed60547910f0db79c893c799e98442b574572cdde4583b5a50c25538bc</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Helcim</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (Internal Tools &amp; Systems)</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4418686539</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>ec85e55ad54c17d669ab730c75bee287cfa3ee8c20c3834dc7b10d0d2b79d4d2</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Junior Full Stack Developer Coop</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>Milton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4420631844</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>f2229fff4aa7a6c3da3eb14263c0565edf502c11c09661487d723acb2ae23aab</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Intern, CloudOps</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f0baf0e899ea9845</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>**Join a Challenger**  
 At EQ, we're remaking banking so every Canadian gets ahead, every day. Serving nearly 4 million Canadians from coast to coast, we offer a wide variety of financial services from banking and lending, to trust and credit union solutions.  
 We've been at this since 197</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>8382c30dbe8d38d6487c59958337efe9bff2f7e27e26860fbf1377ae05061ab4</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Software Development– Kubernetes Platform Migration and Workflow Orchestration Intern</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=513f1e45241c21d6</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>91450c8aa27e99a20ce3ce5390742b2841128560dcf15cd4e65b0903317b0aa9</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>e-STORAGE</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>DevOps / DevSecOps Intern</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4421988308</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>5c2781fec3478855036c976154ab9bab0c954a91e6387e86aa475f72d6fb65e5</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>McKesson</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en automatisation de l'assurance qualité (AQ) - Automne 2026 / QA Automation Engineer Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445202195</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>6976f8db278232a6a41e1c8b2557a76d09ae53c55b0fc8248ea6549594feba51</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Enverus</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>GIS Intern - 26293</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7f1a3244570b28bd</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="I94" s="3" t="inlineStr">
         <is>
           <t>**GIS Intern**
 **Why YOU want this position**
@@ -5370,118 +5370,688 @@
 We are the most trusted energy\-dedicated SaaS company, with a platform built to maximize value from ge</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>7e000d2fb68783da1a2beaf066b67c384246c2324e154b769388acebf7b6676f</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Egis Group</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Intern, Transportation Structures</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>Markham, ON, CA</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=38a78cdd66ed18df</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="I95" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Company Description**  
 Join Egis, where your ambition meets unparalleled growth opportunities. As we continue to expand within Canada, we're looking for talented professionals like you to be a part of our innovative team. Imagine working alongside over 1,000 top\-tier engineers, architects, and </t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>f7feb75d414f40e21bf765239143aa299ae8a80eb215f7ca386b4bfebdbc8df0</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>ProCogia</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Statistical Programming Intern</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4429572367</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>92512ccbd89b79b6a8881b269cb6d6e2153d1a214c9b2691d956f0b3fd38ad97</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>CPKC</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Intern Cloud Developer</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444715702</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>dd6c003c751690b177e03749195629fddb7b7c462584a8fd5f200a64bd8b308a</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Internship - San Fransisco</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=47cae58d78b035fe</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Who we are**
+Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping </t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>de7106a3861189299a435445df2ab7f15216b94cc3bfd6e70321c65dfa89c24d</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>ALSTOM</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>CAD Designer intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=9aebaf621f97c756</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Req ID:526612
+At Alstom, we understand transport networks and what moves people. From high\-speed trains, metros, monorails, and trams, to turnkey systems, services, infrastructure, signalling and digital mobility, we offer our diverse customers the broadest portfolio in the industry. Every da</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>d3a16bd708e137afee4ba032b94bdf7ad340e1ff8533f204ed4e224553bb76c2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2026 Fall Co-op Digital Vehicle Experience Software Developer</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446808823</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>d9d7e379321790cb7d351645a6888d065951637521fae8f4ddf76ed71f3df21f</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Kobo Inc.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer (8 month Co-op)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441288171</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>56fa9f87d4db309e9bea79bebe47a391f2a6f6d0682a48534875f812b42a4e51</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Engineer- Distributed Agent System</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440053849</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>83dcc6ade1fc9918d3a3d9fdb5e2019e266c21809e8e5da5fad359ecd6444328</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>BMO</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist, Fall 2026 ( Co-op/Internship) - 12 months</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437808934</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>552a162035a1ecbedca2ee3d2f040ad0ed4c696c8528118723bfeb0e7b807956</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Internship - San Fransisco</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=38308847b4f53837</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Who we are**
+Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping </t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>301e664af8c5810489e23b26e42759a134e9fb23176f15e05c7fbb47bbb959d1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=f788545678b41dc1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Overview**  
+The Coalition is a flagship first\-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of **XBOX**'s </t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ad53c5727c4a45dbb4c5ebaa91e8ee899d9ba021ab731c7836424906cb8def8f</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434085436</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>a1aa4a68e466cc3782cfe1b57e88d9d9e940d49ef5987a2e4cfc69010aff6ca8</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Data Governance Analyst Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439319081</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5484,574 +5484,624 @@
       <c r="L96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>92512ccbd89b79b6a8881b269cb6d6e2153d1a214c9b2691d956f0b3fd38ad97</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>CPKC</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Intern Cloud Developer</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444715702</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>dd6c003c751690b177e03749195629fddb7b7c462584a8fd5f200a64bd8b308a</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Samsara</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Internship - San Fransisco</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=47cae58d78b035fe</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Who we are**
 Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping </t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>de7106a3861189299a435445df2ab7f15216b94cc3bfd6e70321c65dfa89c24d</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>ALSTOM</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>CAD Designer intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=9aebaf621f97c756</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>Req ID:526612
 At Alstom, we understand transport networks and what moves people. From high\-speed trains, metros, monorails, and trams, to turnkey systems, services, infrastructure, signalling and digital mobility, we offer our diverse customers the broadest portfolio in the industry. Every da</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>d3a16bd708e137afee4ba032b94bdf7ad340e1ff8533f204ed4e224553bb76c2</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>General Motors</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>2026 Fall Co-op Digital Vehicle Experience Software Developer</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446808823</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>d9d7e379321790cb7d351645a6888d065951637521fae8f4ddf76ed71f3df21f</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Rakuten Kobo Inc.</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Software Engineer (8 month Co-op)</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441288171</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>56fa9f87d4db309e9bea79bebe47a391f2a6f6d0682a48534875f812b42a4e51</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Co-op Engineer- Distributed Agent System</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440053849</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>83dcc6ade1fc9918d3a3d9fdb5e2019e266c21809e8e5da5fad359ecd6444328</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>BMO</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Data Scientist, Fall 2026 ( Co-op/Internship) - 12 months</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437808934</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>552a162035a1ecbedca2ee3d2f040ad0ed4c696c8528118723bfeb0e7b807956</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Samsara</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Internship - San Fransisco</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=38308847b4f53837</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Who we are**
 Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping </t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>301e664af8c5810489e23b26e42759a134e9fb23176f15e05c7fbb47bbb959d1</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=f788545678b41dc1</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Overview**  
 The Coalition is a flagship first\-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of **XBOX**'s </t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>ad53c5727c4a45dbb4c5ebaa91e8ee899d9ba021ab731c7836424906cb8def8f</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Engineering Intern</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434085436</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>a1aa4a68e466cc3782cfe1b57e88d9d9e940d49ef5987a2e4cfc69010aff6ca8</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>McKesson</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>Data Governance Analyst Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439319081</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>36a9dae3ad43123e74a1a5f86718b80e43ce144a6021538be34e54ad65d54bd2</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Rodan Energy Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Data Science - Co-op Student</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436627074</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6054,54 +6054,386 @@
       <c r="L107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>36a9dae3ad43123e74a1a5f86718b80e43ce144a6021538be34e54ad65d54bd2</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Rodan Energy Solutions Inc.</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Data Science - Co-op Student</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436627074</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>jobspy:linkedin</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>b849bab5c06a730fcc57fcbd8843cc93ec20f123815fc5c5c0a28d4c35095a6a</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5827923255?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Overview The Coalition is a flagship first-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of XBOX 's entertainmen</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>acd21634bb8af7c82fa87947636750f3c963f0c59e066b506925ff533c846f59</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Agile Tester, Co-op, September 2026 - September 2027</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435739747</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>417c3f928c3150f2ea565761c2f39df7ba2de6c183d268b39741f809023904be</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Lumentum Operations</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Optical VerificationTechnician Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=3bad200e228191d0</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>locations
+Canada \- Ottawa (Bill Leathem)
+time type
+Full time
+posted on
+Posted Today
+job requisition id
+20261049
+It's fun to work in a company where people truly BELIEVE in what they're doing!  
+*We're committed to bringing passion and customer focus to the business.*
+ *If you like wild growth and</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>b3d8599ea04e54956fb8ce5dab821e1ac882fdbe60a63f452ed10a3cd1620771</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Lumentum Operations</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Optical Verification Technician Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=8b6c3ee007f78535</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>locations
+Canada \- Ottawa (Bill Leathem)
+time type
+Full time
+posted on
+Posted Today
+job requisition id
+20261048
+It's fun to work in a company where people truly BELIEVE in what they're doing!  
+*We're committed to bringing passion and customer focus to the business.*
+ *If you like wild growth and</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>646f4a91401e60eb0c440c6eda7f60ac0b8eb686e77fe93907b04691a0d64b93</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Multimatic</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Application Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>East Gwillimbury, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439359158</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>16b2acc4d4e03732734156a85ac49ddea751336179b3a06677d4aeba06bc61f9</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>TMX Group</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Student Intern, DevOps (Fall Term)</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440251660</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6104,151 +6104,151 @@
       <c r="L108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>b849bab5c06a730fcc57fcbd8843cc93ec20f123815fc5c5c0a28d4c35095a6a</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5827923255?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>Overview The Coalition is a flagship first-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of XBOX 's entertainmen</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>acd21634bb8af7c82fa87947636750f3c963f0c59e066b506925ff533c846f59</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>Agile Tester, Co-op, September 2026 - September 2027</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435739747</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>417c3f928c3150f2ea565761c2f39df7ba2de6c183d268b39741f809023904be</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Lumentum Operations</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>Optical VerificationTechnician Intern/Co-op</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=3bad200e228191d0</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>locations
 Canada \- Ottawa (Bill Leathem)
@@ -6263,56 +6263,56 @@
  *If you like wild growth and</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>b3d8599ea04e54956fb8ce5dab821e1ac882fdbe60a63f452ed10a3cd1620771</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Lumentum Operations</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>Optical Verification Technician Intern/Co-op</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=8b6c3ee007f78535</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>locations
 Canada \- Ottawa (Bill Leathem)
@@ -6327,113 +6327,513 @@
  *If you like wild growth and</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>646f4a91401e60eb0c440c6eda7f60ac0b8eb686e77fe93907b04691a0d64b93</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Multimatic</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>Application Engineering Co-op</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>East Gwillimbury, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439359158</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>16b2acc4d4e03732734156a85ac49ddea751336179b3a06677d4aeba06bc61f9</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>TMX Group</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>Student Intern, DevOps (Fall Term)</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440251660</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>00b6c9cfa706a71230f2442f1b900788466746739ad34c5b91b873e701d8ee86</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>SS&amp;C Technologies</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Intern - Technical</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4378635211</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>f41a7a4bf3a1c1f99e5655b232f2e5dff1379390bb96f6c09e6bae326b8461be</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer - openJiuwen AI Agent Platform</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447061013</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>9fb8cfada4f03528321a8c9173e0b45a4f338819cca27088d6582a2ea3fb1bb2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Telesat</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Lightspeed Network Engineering Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443580281</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>6554459ceb52e8f8c35e3800ffd0eb55978de2d5cad4b3eb3f1013a0faedda7c</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Q-Block Computing</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Embedded Systems Developer Intern</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439029520</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>45034d6a95ea61e7ff5bdfaa2edbd4547e411d962933caf073c798acd48b0dae</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Survalent</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Quality and Infrastructure Co-op Developer</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444017350</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>c148548572d888c3372cc8901a29efd398fd2208025a5459739925d8c171e840</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>EQ Bank</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Intern, CloudOps</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443372544</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>042d53443957cbe6a1d3f2b1ec8b36bb75407daeb633a1b312d8d1042cfdcf1c</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Concert Properties</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Climate Reporting Analyst Intern, Environment, Social &amp; Governance</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446388394</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>390a52833a6dd919b10721aecc65d9ddb8db6f24d26f39390b8e7cec76c85388</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Canfor</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Carbon Reporting</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443304364</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6436,404 +6436,863 @@
       <c r="L114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>00b6c9cfa706a71230f2442f1b900788466746739ad34c5b91b873e701d8ee86</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>SS&amp;C Technologies</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>Intern - Technical</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4378635211</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>f41a7a4bf3a1c1f99e5655b232f2e5dff1379390bb96f6c09e6bae326b8461be</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Huawei Canada</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>Intern Engineer - openJiuwen AI Agent Platform</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447061013</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>9fb8cfada4f03528321a8c9173e0b45a4f338819cca27088d6582a2ea3fb1bb2</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Telesat</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>Lightspeed Network Engineering Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443580281</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>6554459ceb52e8f8c35e3800ffd0eb55978de2d5cad4b3eb3f1013a0faedda7c</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Q-Block Computing</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Embedded Systems Developer Intern</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439029520</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>45034d6a95ea61e7ff5bdfaa2edbd4547e411d962933caf073c798acd48b0dae</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Survalent</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>Quality and Infrastructure Co-op Developer</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444017350</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>c148548572d888c3372cc8901a29efd398fd2208025a5459739925d8c171e840</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>EQ Bank</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Intern, CloudOps</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443372544</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>042d53443957cbe6a1d3f2b1ec8b36bb75407daeb633a1b312d8d1042cfdcf1c</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Concert Properties</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>Climate Reporting Analyst Intern, Environment, Social &amp; Governance</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446388394</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>390a52833a6dd919b10721aecc65d9ddb8db6f24d26f39390b8e7cec76c85388</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Canfor</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Co-op, Carbon Reporting</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443304364</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>b336bfa111698bc3c29fcdfd30e19e3a6aa00777fbee113690ac0722e934700d</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Alida</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5829659807?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Our product team works at a fast pace, loves to collaborate, and thrives on solving complex problems with modern technologies to deliver meaningful experiences. We’re looking for a Software Engineer Intern who is curious about the latest tech, passionate about puzzle-solving, and looking to grow wit</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>f482422a0c67b5662e5ae4fa925b91201b3d9c302e892dc7867c9e65d7e00b42</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Apera AI</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer - C++ (Co-op)</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448568753</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>da5fc6ef15045b3e8875067e8ce505fe5a14c72b4f1b415d95d7453a2ff7b8a1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Critical Environment Technologies</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Product Development Engineer Co-op (AI-Driven)</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Delta, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444607645</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>4ee449834608ea9f0af96b93115f0962a6f3a9330d3946a5cb1b66b63a990c50</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Aptiv</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Intern - RTOS development</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434257753</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>eecb3034ddf1511c8323682a4dc86bf6fa2688964ed10165b3bff38b9367b160</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Intern Architect</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=173e38ad22db0b35</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Stantec’s Buildings team is on a mission to become the world’s leading integrated design practice. Our architects, engineers, interior designers, consultants, sustainability specialists, and technologists are passionate about the power of design. Our collaborative culture and our innovative, sustain</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>a6062239116f0a721b7f4d56f45812a18cf9c7ab5c9e4e217ee69ca9badb6624</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>HUB International</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Student Programmer Analyst</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Red Deer, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446684655</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>dbddcb16554ddb6bb6bdfb6228d4f909e99349634299a16f8ea8d8c193e09f57</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Buttcon</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Web Development Student</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Woodbridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448562031</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>48b98020ab0bd9c0ac421dd49327e99cb67f5915a4f5d5ff86805337c9a79c99</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>NEXTIN LABS (formerly ForAll A Tech)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Laravel Web Developer
+Full-Time Internship</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Regional Municipality of York, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439088147</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>c6eadae06f07ae7f5c820e579100b92d007a672e7ef3f5c31f81afb2fef54d6f</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>PCL Construction</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Predictive Analytics &amp; Strategy Student</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Oakville, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438830197</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6836,463 +6836,763 @@
       <c r="L122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>b336bfa111698bc3c29fcdfd30e19e3a6aa00777fbee113690ac0722e934700d</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Alida</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5829659807?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>Our product team works at a fast pace, loves to collaborate, and thrives on solving complex problems with modern technologies to deliver meaningful experiences. We’re looking for a Software Engineer Intern who is curious about the latest tech, passionate about puzzle-solving, and looking to grow wit</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>f482422a0c67b5662e5ae4fa925b91201b3d9c302e892dc7867c9e65d7e00b42</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Apera AI</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>Software Developer - C++ (Co-op)</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448568753</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>da5fc6ef15045b3e8875067e8ce505fe5a14c72b4f1b415d95d7453a2ff7b8a1</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Critical Environment Technologies</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>Product Development Engineer Co-op (AI-Driven)</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>Delta, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4444607645</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>4ee449834608ea9f0af96b93115f0962a6f3a9330d3946a5cb1b66b63a990c50</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Aptiv</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>Intern - RTOS development</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434257753</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>eecb3034ddf1511c8323682a4dc86bf6fa2688964ed10165b3bff38b9367b160</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Stantec</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>Intern Architect</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=173e38ad22db0b35</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>Stantec’s Buildings team is on a mission to become the world’s leading integrated design practice. Our architects, engineers, interior designers, consultants, sustainability specialists, and technologists are passionate about the power of design. Our collaborative culture and our innovative, sustain</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>a6062239116f0a721b7f4d56f45812a18cf9c7ab5c9e4e217ee69ca9badb6624</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>HUB International</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>Student Programmer Analyst</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>Red Deer, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446684655</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>dbddcb16554ddb6bb6bdfb6228d4f909e99349634299a16f8ea8d8c193e09f57</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Buttcon</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>Web Development Student</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>Woodbridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448562031</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>48b98020ab0bd9c0ac421dd49327e99cb67f5915a4f5d5ff86805337c9a79c99</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>NEXTIN LABS (formerly ForAll A Tech)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Full Stack Laravel Web Developer
 Full-Time Internship</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>Regional Municipality of York, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439088147</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>c6eadae06f07ae7f5c820e579100b92d007a672e7ef3f5c31f81afb2fef54d6f</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>PCL Construction</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>Predictive Analytics &amp; Strategy Student</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>Oakville, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438830197</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr"/>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>51e3401352fa34a708c5d053cfed7c6a2310b8175c77c2ec36d39dcdeac82106</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Co-op - Canada - Richmond, BC - Remote</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448928815</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>4d55ee60122e7deb40ae2c3659e3f73349d56c84d6edc24e4a4f35a33d235c1a</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Arlo Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Firmware Developer Co-op</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447300598</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>e4bf46849301576084fde0beb50d714c36d0d0d021e031b4084fb8620ad148ab</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Arlo Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4417991193</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>766874ebe1a4d5ceac20ec2802a465d2d85267eb2c74f59f51745e35cc481e02</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Themis Intelligence</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer - Post-training (Co-op / Intern)</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440245546</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>420c59bba49587dc5162cc7e3659fe2f67faf1ca739f96594305c400a5dad4af</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Eclipse Automation</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Controls Software Design Co-op</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439709078</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>dcb8b80cc601a0f55fe0fa0e0c93e2d217c28b5286eca71bc9d81705a2a793a8</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Front-End Development Intern</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446112881</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7295,304 +7295,514 @@
       <c r="L131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>51e3401352fa34a708c5d053cfed7c6a2310b8175c77c2ec36d39dcdeac82106</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>Software Development Co-op - Canada - Richmond, BC - Remote</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448928815</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>4d55ee60122e7deb40ae2c3659e3f73349d56c84d6edc24e4a4f35a33d235c1a</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>Firmware Developer Co-op</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447300598</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>e4bf46849301576084fde0beb50d714c36d0d0d021e031b4084fb8620ad148ab</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>Test Engineer Co-op</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>Richmond, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4417991193</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>766874ebe1a4d5ceac20ec2802a465d2d85267eb2c74f59f51745e35cc481e02</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Themis Intelligence</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Research Engineer - Post-training (Co-op / Intern)</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440245546</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>420c59bba49587dc5162cc7e3659fe2f67faf1ca739f96594305c400a5dad4af</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Eclipse Automation</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>Controls Software Design Co-op</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439709078</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr"/>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>dcb8b80cc601a0f55fe0fa0e0c93e2d217c28b5286eca71bc9d81705a2a793a8</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Zenith</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>Front-End Development Intern</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446112881</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>17372a308b757f4d97b1651cb8b16b3c5a70e6460c468d5558a1964591339bfa</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>HV Logic</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Internship/Co-op</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, AB, CA</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=9a01a0547d8796ec</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Summary:
+HV Logic Ltd. is an Alberta\-based High Voltage Electrical Engineering company that specializes in digital equipment in the power industry. Professional services include project consulting and management, substation electrical and relay settings design, automation logic, SCADA programming,</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>03cb21c7aca1e70baac904f2e7e50e270523937cacdccc1eb9737ca8b0ba495b</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Salas O'Brien Canada Inc.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=7ded57e5e1cb9b0a</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>**Mechanical/Electrical Internship**
+At Salas O’Brien we tell our clients that we’re engineered for impact. This passion for making a difference applies just as much to our team as it does to our projects. That’s why we’re committed to living our values every day: inspiring, achieving, and connec</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>11eb536946691e40421b8aa1cf4cf65e485a8ea77dfda5a233cb60d801d22c4a</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Ricoh USA, Inc.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Software Developer (Fall Work Term)</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449007974</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>60461e1cd1e90e8dbadd0a72567248499693aa30fdbce5e29d0683704939adea</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>HUB International</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Student Programmer Analyst</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Edmonton, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448063206</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7595,214 +7595,269 @@
       <c r="L137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>17372a308b757f4d97b1651cb8b16b3c5a70e6460c468d5558a1964591339bfa</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>HV Logic</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>Software Developer Internship/Co-op</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>Calgary, AB, CA</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=9a01a0547d8796ec</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>Summary:
 HV Logic Ltd. is an Alberta\-based High Voltage Electrical Engineering company that specializes in digital equipment in the power industry. Professional services include project consulting and management, substation electrical and relay settings design, automation logic, SCADA programming,</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>03cb21c7aca1e70baac904f2e7e50e270523937cacdccc1eb9737ca8b0ba495b</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Salas O'Brien Canada Inc.</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>Mechanical Engineer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=7ded57e5e1cb9b0a</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>**Mechanical/Electrical Internship**
 At Salas O’Brien we tell our clients that we’re engineered for impact. This passion for making a difference applies just as much to our team as it does to our projects. That’s why we’re committed to living our values every day: inspiring, achieving, and connec</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>11eb536946691e40421b8aa1cf4cf65e485a8ea77dfda5a233cb60d801d22c4a</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Ricoh USA, Inc.</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>Co-op, Software Developer (Fall Work Term)</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449007974</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>60461e1cd1e90e8dbadd0a72567248499693aa30fdbce5e29d0683704939adea</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>HUB International</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>Student Programmer Analyst</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448063206</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ce400b063dc8b9cfbfa30ed79a68c1a904a7e603eba830b5c8b78c6bc8c3c491</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Full Stack Software Engineer - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1584f0899d1849ca</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>161 Bay Street (93021\), Canada, Toronto,Toronto, Ontario,Intern, Full Stack Software Engineer \- Fall 2026### **About Capital One Canada**
+For 30 years, we’ve been on a mission to change banking for good. We challenge the traditional bank stereotype, fostering a culture where innovation thrives a</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7805,59 +7805,526 @@
       <c r="L141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>ce400b063dc8b9cfbfa30ed79a68c1a904a7e603eba830b5c8b78c6bc8c3c491</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Capital One</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>Intern, Full Stack Software Engineer - Fall 2026</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1584f0899d1849ca</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>161 Bay Street (93021\), Canada, Toronto,Toronto, Ontario,Intern, Full Stack Software Engineer \- Fall 2026### **About Capital One Canada**
 For 30 years, we’ve been on a mission to change banking for good. We challenge the traditional bank stereotype, fostering a culture where innovation thrives a</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>7f4384f530842404f1b2c7b25657bee04c84a6bc3506a99e8e536f525358950b</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Mawer Investment Management</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI &amp; Automation Fall Student</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449766435</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>762bc88215f7bc83fc792c437ec502a335ba6b127f3d8f15954dd9c084ffbe64</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Backend</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450632614</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2b238c99ce4fbd75f55b2aa02354919f9dd1b59ba933a468fd669bc0ca386a6e</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer in Test Automation Intern</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=89f734cd02a97e0f</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>a46ce76c634738eb8a6f85799fc24556946b7165968f4a9c23501276d42452e2</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=6ac971c2b2689d78</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>90ab7a7091751d6d2e957689d6434cccff64d935e573b4db5c4d9d10255a30a7</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>HV Logic Ltd.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Engineer Internship</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450601197</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>422b778ea1b0599582958da08189e5798004af4deb6de8f8ff0648465acdfd29</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Data Platform</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450624778</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>4a731036db981edd431d9bc2790d7fd2053f3d9fa28081f91238c87834862b22</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>ShyftLabs</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443706179</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>1b658795d00810f4afe3d474f27eb80c7fc03754ab23f6347fdd40e99110d5f3</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, CA</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=1250edd4d4b90fda</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Overview**  
+The Coalition is a flagship first\-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of **XBOX**'s </t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>64cf0d0814d53e5783d82773a27de02c412f6243c3cb415f06a3834ae03842fb</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ON DevOps Intern- Fall 2026</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, ON, CA</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=54e5e2c61d315898</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7860,471 +7860,521 @@
       <c r="L142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>7f4384f530842404f1b2c7b25657bee04c84a6bc3506a99e8e536f525358950b</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Mawer Investment Management</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>Applied AI &amp; Automation Fall Student</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449766435</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>762bc88215f7bc83fc792c437ec502a335ba6b127f3d8f15954dd9c084ffbe64</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern, Backend</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450632614</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>2b238c99ce4fbd75f55b2aa02354919f9dd1b59ba933a468fd669bc0ca386a6e</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>Software Developer in Test Automation Intern</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=89f734cd02a97e0f</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>a46ce76c634738eb8a6f85799fc24556946b7165968f4a9c23501276d42452e2</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=6ac971c2b2689d78</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr"/>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr"/>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>90ab7a7091751d6d2e957689d6434cccff64d935e573b4db5c4d9d10255a30a7</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>HV Logic Ltd.</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>Electrical Engineer Internship</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450601197</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>422b778ea1b0599582958da08189e5798004af4deb6de8f8ff0648465acdfd29</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern, Data Platform</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450624778</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>4a731036db981edd431d9bc2790d7fd2053f3d9fa28081f91238c87834862b22</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>ShyftLabs</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443706179</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr"/>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr"/>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>1b658795d00810f4afe3d474f27eb80c7fc03754ab23f6347fdd40e99110d5f3</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>Vancouver, BC, CA</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=1250edd4d4b90fda</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">**Overview**  
 The Coalition is a flagship first\-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of **XBOX**'s </t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>64cf0d0814d53e5783d82773a27de02c412f6243c3cb415f06a3834ae03842fb</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>ON DevOps Intern- Fall 2026</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>Ottawa, ON, CA</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=54e5e2c61d315898</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H151" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>As the global leader in high\-speed connectivity, Ciena is committed to a people\-first approach. Our teams enjoy a culture focused on prioritizing a flexible work environment that empowers individual growth, well\-being, and belonging. We’re a technology company that leads with our humanity—driving</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>a629913f7bf3a47d3c88c840a403b217d4f0e0aa6af2d979e17f38aebfbffeff</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448726485</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8327,54 +8327,512 @@
       <c r="L151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>a629913f7bf3a47d3c88c840a403b217d4f0e0aa6af2d979e17f38aebfbffeff</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448726485</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>72411d5af934790887925e50f4ce3ec4fa559ffef09b531a8b7906ad7e4be2be</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Data Platform</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5833566027?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>About Terminal Terminal builds telematics data infrastructure for the commercial fleet industry. Commercial auto insurers and fleet software companies, including industry leaders like Intact Insurance, depend on our platform to access GPS, speeding, and vehicle data from 330 telematics providers. We</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>3f5e7b31376081a658097a55fce6beb885dced5cf4d95381f26e85b6567ee8bb</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Greater Vancouver, British Columbia</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5833589506?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Overview The Coalition is a flagship first-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of XBOX 's entertainmen</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2e0867f697fcc8d81618f849738cd32ce2f5fb2b5a8fb246c56950ec5f117af5</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer in Test Automation Intern</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450794384</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>c2f77a2841f67bd7fa2e883ec63526857cb950000e0952a4d1b50fb16d25104c</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Canada | C#-Java-Scala Developer CO-OP| Fall 2026</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450378032</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>54b668844ce07febd691537ca3cd1d149c30b1faf310e2c389c0e75840aa12bf</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Bristol Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Richmond Hill, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450714436</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>dab146e2778c21d4f11da76fbafd1c4c41553771d5485a4fdbe44fdd59ab82fb</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450328431</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>5fbdc7dddde4ce94fecf16f2d1a5c27d37e7ded836db6631634eadc42c13ea22</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer Intern - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450344837</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>07c9dc8979ffc29b35373895d2e22be2ec53a494e798029315b23398a6e8e2e0</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Engineers and Geoscientists BC</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Information Systems Co-op</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Burnaby, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450784014</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>5d03a80184383c8eacbec1b2fa64aa5338a2243b1630c1a892499fc25dc33a04</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>ON DevOps Intern- Fall 2026</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450796341</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8377,462 +8377,512 @@
       <c r="L152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>72411d5af934790887925e50f4ce3ec4fa559ffef09b531a8b7906ad7e4be2be</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern, Data Platform</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5833566027?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>About Terminal Terminal builds telematics data infrastructure for the commercial fleet industry. Commercial auto insurers and fleet software companies, including industry leaders like Intact Insurance, depend on our platform to access GPS, speeding, and vehicle data from 330 telematics providers. We</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr"/>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr"/>
+      <c r="J153" s="3" t="inlineStr"/>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>3f5e7b31376081a658097a55fce6beb885dced5cf4d95381f26e85b6567ee8bb</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>Greater Vancouver, British Columbia</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G154" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5833589506?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H154" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>Overview The Coalition is a flagship first-party studio within Xbox Game Studios and the home to one of gaming’s most critically and commercially acclaimed series, Gears of War. We are a group of diverse and talented individuals working for a common purpose to push the limits of XBOX 's entertainmen</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr"/>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>2e0867f697fcc8d81618f849738cd32ce2f5fb2b5a8fb246c56950ec5f117af5</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>Software Developer in Test Automation Intern</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450794384</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr"/>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>c2f77a2841f67bd7fa2e883ec63526857cb950000e0952a4d1b50fb16d25104c</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Bank of America</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>Canada | C#-Java-Scala Developer CO-OP| Fall 2026</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450378032</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr"/>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>54b668844ce07febd691537ca3cd1d149c30b1faf310e2c389c0e75840aa12bf</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Bristol Capital Ltd.</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>Richmond Hill, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450714436</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr"/>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>dab146e2778c21d4f11da76fbafd1c4c41553771d5485a4fdbe44fdd59ab82fb</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>Software Engineer - Gears of War - The Coalition: Internship Opportunities</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450328431</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>5fbdc7dddde4ce94fecf16f2d1a5c27d37e7ded836db6631634eadc42c13ea22</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Software Developer Intern - Fall 2026</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450344837</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>07c9dc8979ffc29b35373895d2e22be2ec53a494e798029315b23398a6e8e2e0</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Engineers and Geoscientists BC</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>Information Systems Co-op</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>Burnaby, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450784014</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>5d03a80184383c8eacbec1b2fa64aa5338a2243b1630c1a892499fc25dc33a04</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>ON DevOps Intern- Fall 2026</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450796341</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr"/>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>e97045f94e9cbf6dfea1a48c05f748c24cd32d8326b1e9762d8fa91743a0e607</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Stichting Mission on Wheels</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>AI &amp; Internal Tools Developer</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451052654</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8835,54 +8835,154 @@
       <c r="L161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>e97045f94e9cbf6dfea1a48c05f748c24cd32d8326b1e9762d8fa91743a0e607</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Stichting Mission on Wheels</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>AI &amp; Internal Tools Developer</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G162" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451052654</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>c84fdd705f795883a15fddb4da04471928d02d76df0b3d6e011b5c3ea38b49e4</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>DataRobot</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Agentic AI Intern</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Greater Toronto Area, Canada</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438096979</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>a4344ad633bcd7fa560ea6f3e1463b1b732494d4d31cfd069bc59c22791b8f37</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>AI Developer, Intern/Co-op - REMOTE (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440869554</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8885,104 +8885,2317 @@
       <c r="L162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
         <is>
           <t>c84fdd705f795883a15fddb4da04471928d02d76df0b3d6e011b5c3ea38b49e4</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>DataRobot</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>Agentic AI Intern</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438096979</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr"/>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="inlineStr"/>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>a4344ad633bcd7fa560ea6f3e1463b1b732494d4d31cfd069bc59c22791b8f37</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Revvity</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>AI Developer, Intern/Co-op - REMOTE (Fall 2026)</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>Ontario, Canada</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G164" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440869554</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr"/>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>71c32a0cb7132cc5650357baac240546bacbca9574b2bb7794a21733a521b4e6</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>GHD</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Indigenous Engineer Intern/co-op</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4410331679</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>3a0ec8ae637db0bbd8a8786ad1f174f53d30b69f8296609ca69cd32f13d4d078</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2027 Returning Intern - Canada</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445554747</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>0712cf0800434f5cc32afc52fd7a56ce17716b605bd711316800561bdb28935d</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Mark's</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>AI Automation Student (4 months) - Fall 2026</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447215625</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>6fe0e371761eb78a574527b6bbf47ba58a9ea3b5a1fa14130667d2769089cc96</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Software Analyst Intern (Fall 2026, 8 months)</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448722603</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>6884f48fbd36d578f30a8451cd1af74f7a4037871243c30962f90561e54c48e5</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Warranty Co-op</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Newmarket, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449025276</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>8f57ccb842c38b42e5f736847d248f45331e4bc6362e46166f44e0ec86c361c8</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>TMX Group</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator Intern</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446302458</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>b046aa1bd5b4a7c1445ab9a14c259e652c5721e341c8996b6565447814a44e0c</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Eclipse Automation</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Software Design Co-op (Nuclear)</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440378753</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>1b927b6689f98339d406d872f89561a638cc0be189f6d6d600f228e1579e5b71</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Development Engine Infrastructure DevOps Co-op (Fall 2026 - 4-12 months)</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451459342</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>e71d3470f4ca71e4fbae5075319c61e0c23a5cea5865733a6508c0ad9a195c81</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>IoT Systems Engineer - Co-op (4 months) - Starting September</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Milton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442190530</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>e8787a96d041372ecfa959fe68c4c8115ead028a2eccc0bf0306372ea7e64634</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Execution Systems (MES) Co-Op - Starting in September</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Milton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4441685804</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>5ba114ee539dc8e5248045f0ffbf7f97bfc5fc2afcb7abefe135ec539e9f6338</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Sales Engineering Co-Op</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Kitchener, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4412445712</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>9c9fe4cf0d567fdddce0765728b720ba8830378c50827939ef1d019b62859363</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Electro-Mechanical Engineering Intern (Fall 2026, 16 months)</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=dd5c59f1ca63c542</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R0139829
+**Date Posted:**
+2026\-08\-11
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Administration \&amp; Facilities
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>7d3c1a48b6de1d2e7032203df1bb33b9c3f03bd5d1d2ad14f6db7a3160074b2f</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>CMiC</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Co-op</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=44c56c143a99aad3</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Computer Methods International Corp. (CMiC) is a Software Development firm specializing in enterprise financial and cost management systems designed for the Construction and Engineering industries.
+**About CMiC**
+**CMiC** is the leading provider of complete, integrated and advanced enterprise leve</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>54b809fbe2fd1bbb442501d97877f2e9607a3382fb8b2b2a964cc3892bacafa0</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>LevelOps</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447558047</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>a72f28955263be6d2ffc3c1f7b51a6c3bc764187778884c1246510bda8000861</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>AlayaCare</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Developer Fullstack (Intern - Python)</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450647656</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>5b55e7d0c9920c28741bd9485194a12e28d1543765c04e1bb53a7244a5f749c0</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Data and Platform, Technical Support [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451461077</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>9089e77dd8024d1cbc22d3320328b9063feae027769d6f92110bf1428af93eb4</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Peoples Group</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Jr Application Support / Network Intern</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446780250</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>62c9a2379b595fbfbe60a5d8ff7d9cb7f31aaee32899238d662b3f621b421518</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Canfor</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Co-op, Document Management</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4427158604</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>9f87902079d40cfc8911d6d43f793efb9be1f31eb45c76d3ef831f106e1a1a3c</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>telMAX Inc.</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Systems Operations &amp; Analytics Co-op - Fall Term (4 Months)</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Markham, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4438300632</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>e71f93edaac482f31424f3b3b1a6600db35904050f6a7e19714409a67a9f9093</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>API (Integration Engineer) Intern</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446106866</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>c88b71bd8e9c1952d9d4081864f9543dca73c96251d462ee762ee0fbf900b7c0</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Bombardier</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Intern, Developer Analyst (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Dorval, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4435308009</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>8581a716b5c9823c5a90120fd39d508eb27e04216b4bee4db8c5b17e14f69e89</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en Développement Cloud, Intern Cloud Developer</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450342585</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ea6e9177a2a2eb4d088e79a3a4fbfef46d5dfc107fbbda8948864ba8f1bc62a6</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Flare</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en développement logiciel / Intern Software Developer</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Montréal-Ouest, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447254461</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>e4a2dab57fc068d391ade5442fb297a2c51cd54676f5cb9fd8d91e8fad80eb67</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>AI Solutions Developer Co-op (4 months) - Starting September</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Milton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4442192398</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>9f31e707e1c0dcabf4e8e5e3c9327cb2b2c5895fd5b4963171f09415f3378e60</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en Développement Cloud, Intern Cloud Developer – FCAP</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450350390</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>432372745bdc56f9627fe4c4c7d8ceaeff1e85d3d91e18fcc0de9a1d264aea57</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Liminal Discovery</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Foresight tool developer internship (AI, automation, LLMs)</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Urban agglomeration of Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450079089</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>6b79ed8e63a037ec41bd26db3b308190e74e71607235be404be592ec492856d4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>CodeDeskStudio</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Mobile App Development Internship</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Division No. 11, Saskatchewan, Canada</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447364549</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>fbeb70d52e55ae4766ba7efb07ebc5d96cd8300e5d9b0a5715d631ada7340226</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Xsolla</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>AI-First Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4436624836</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>07bdea2f6b653ec1916ad33527e41d5bbbef72f333e54f0019340567dad929db</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Tecsys Inc.</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Intern - DevOps (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4437077370</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>be0b2805c1278a17017dcd3dbfd40501fd89542e81de5c273df5bf9783b58936</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Osler, Hoskin &amp; Harcourt LLP</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Applications Analyst Co-op (8 months)</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4433725216</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>1f8cff2e78bfdd4f3a5afe1680e915dab4f506a1d167c21ac05e150128255951</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>ITV - Intern (Fall 2026, 12-16 Month)</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439246905</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>58ccedb12cb9abada367fa8ec5cb972e0b30f01d774bdce29fa4eb03bf649e09</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Rakuten Kobo Inc.</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Software Quality Assurance Co-op</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450720999</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>9b096f6f8b09b3782faaf831d82d0fd0535f4300c94fe472f4c5ab1950435106</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>TechInsights</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>QA Test Automation Co-op Student (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4445230477</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>dcd116d772032c49a0f4de5f53b462fcb6e967d34c7cca840430cf093f5bdd0c</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Munich Re</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Women in Tech Program - Global IT Co-op (Fall 2026 - Toronto, 4 months)</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443916232</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>1678cc7662caba09b83824d5104ac6da806f2973ae7fc90d3a0b50d2edc663e4</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>House of Commons of Canada Chambre des communes du Canada</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Co-op Students - Various Positions</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4350836087</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2cfc1792f4a9d201f07693710a0b8f8cf95fa8a2307931ef7da90303c2e6e01c</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>InterPro Pipe + Steel</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Process Technology Co-op Student</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446840631</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>3165a2832a048afa37cf8450070685fc3fdcfb833961771ca407db9859f185a8</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>InterPro Pipe + Steel</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Operational Excellence Co-op</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Calgary, Alberta, Canada</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446351936</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>f6c4921a5d262fdfc2dbf872824bf1464bdb80f892814dcf91876aa76634bfa0</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>IKO North America</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Data Engineer Co-Op</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Mississauga, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449825324</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>98c8c212aef471fe634c9a231b94196cee28274b57e31bcfcef367faea836809</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>GBM - Client Insights and Analytics Internship/Co-op - Fall 2026 (12 months)</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448485888</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>86ebb0aa627c6330c78a91731184bbc36ead57857b22976ba55596e2747fedfd</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>TMX Group</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Analyst, Market Insights, Student Intern</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447497198</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>5161892207b4a9a650c26a18feee51fbd4b20e1d5d30af8533c610a9df36be61</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>ALM Scripting &amp; Reporting Intern</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4434564743</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>a149784ac2ee8495bf38777475d601ae4667483489f7cd259dbb85d8beec0330</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Teck Resources Limited</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Business Insights Co-op</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448070011</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>153758b2f5eb32e528e453bfe7ad4c943e6353c6d2c782eef527f23d2e1a7a82</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Teck Resources Limited</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Improvement Specialist Co-op</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448069020</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>352491cb0c9317071b1e43d2f444073185a16621c4d425a099dfca2a97458d3e</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Project Management and Reporting [Vancouver]</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4430420697</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8985,597 +8985,597 @@
       <c r="L164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>71c32a0cb7132cc5650357baac240546bacbca9574b2bb7794a21733a521b4e6</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>GHD</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>Indigenous Engineer Intern/co-op</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G165" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4410331679</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr"/>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr"/>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>3a0ec8ae637db0bbd8a8786ad1f174f53d30b69f8296609ca69cd32f13d4d078</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>2027 Returning Intern - Canada</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445554747</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>0712cf0800434f5cc32afc52fd7a56ce17716b605bd711316800561bdb28935d</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Mark's</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>AI Automation Student (4 months) - Fall 2026</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447215625</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>6fe0e371761eb78a574527b6bbf47ba58a9ea3b5a1fa14130667d2769089cc96</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>Software Analyst Intern (Fall 2026, 8 months)</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G168" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448722603</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>6884f48fbd36d578f30a8451cd1af74f7a4037871243c30962f90561e54c48e5</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>Warranty Co-op</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>Newmarket, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G169" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449025276</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr"/>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>8f57ccb842c38b42e5f736847d248f45331e4bc6362e46166f44e0ec86c361c8</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>TMX Group</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>Technical Project Coordinator Intern</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G170" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446302458</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="inlineStr"/>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>b046aa1bd5b4a7c1445ab9a14c259e652c5721e341c8996b6565447814a44e0c</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Eclipse Automation</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>Software Design Co-op (Nuclear)</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>Cambridge, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4440378753</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr"/>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>1b927b6689f98339d406d872f89561a638cc0be189f6d6d600f228e1579e5b71</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Ciena</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>Development Engine Infrastructure DevOps Co-op (Fall 2026 - 4-12 months)</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451459342</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>e71d3470f4ca71e4fbae5075319c61e0c23a5cea5865733a6508c0ad9a195c81</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>IoT Systems Engineer - Co-op (4 months) - Starting September</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>Milton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442190530</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr"/>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>e8787a96d041372ecfa959fe68c4c8115ead028a2eccc0bf0306372ea7e64634</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>Manufacturing Execution Systems (MES) Co-Op - Starting in September</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>Milton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4441685804</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>5ba114ee539dc8e5248045f0ffbf7f97bfc5fc2afcb7abefe135ec539e9f6338</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Acceldata</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>Sales Engineering Co-Op</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>Kitchener, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4412445712</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>9c9fe4cf0d567fdddce0765728b720ba8830378c50827939ef1d019b62859363</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Electro-Mechanical Engineering Intern (Fall 2026, 16 months)</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=dd5c59f1ca63c542</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H176" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="I176" s="3" t="inlineStr">
         <is>
           <t>**Location:**
 Toronto, Ontario, Canada
@@ -9595,1607 +9595,2488 @@
 A career at Hitachi Rail will help create a</t>
         </is>
       </c>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>7d3c1a48b6de1d2e7032203df1bb33b9c3f03bd5d1d2ad14f6db7a3160074b2f</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>CMiC</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Co-op</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>Toronto, ON, CA</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>https://ca.indeed.com/viewjob?jk=44c56c143a99aad3</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H177" s="3" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I177" s="3" t="inlineStr">
         <is>
           <t>Computer Methods International Corp. (CMiC) is a Software Development firm specializing in enterprise financial and cost management systems designed for the Construction and Engineering industries.
 **About CMiC**
 **CMiC** is the leading provider of complete, integrated and advanced enterprise leve</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L177" s="2" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr"/>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>54b809fbe2fd1bbb442501d97877f2e9607a3382fb8b2b2a964cc3892bacafa0</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>LevelOps</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447558047</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>a72f28955263be6d2ffc3c1f7b51a6c3bc764187778884c1246510bda8000861</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>AlayaCare</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Developer Fullstack (Intern - Python)</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr"/>
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450647656</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L179" s="2" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>5b55e7d0c9920c28741bd9485194a12e28d1543765c04e1bb53a7244a5f749c0</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Data and Platform, Technical Support [Vancouver]</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4451461077</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>9089e77dd8024d1cbc22d3320328b9063feae027769d6f92110bf1428af93eb4</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Peoples Group</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Jr Application Support / Network Intern</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446780250</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L181" s="2" t="inlineStr"/>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>62c9a2379b595fbfbe60a5d8ff7d9cb7f31aaee32899238d662b3f621b421518</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Canfor</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>Co-op, Document Management</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4427158604</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>9f87902079d40cfc8911d6d43f793efb9be1f31eb45c76d3ef831f106e1a1a3c</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>telMAX Inc.</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>Systems Operations &amp; Analytics Co-op - Fall Term (4 Months)</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>Markham, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4438300632</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L183" s="2" t="inlineStr"/>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>e71f93edaac482f31424f3b3b1a6600db35904050f6a7e19714409a67a9f9093</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Zenith</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>API (Integration Engineer) Intern</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>Timiskaming Unorganized West Part, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446106866</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>c88b71bd8e9c1952d9d4081864f9543dca73c96251d462ee762ee0fbf900b7c0</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Bombardier</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Intern, Developer Analyst (Fall 2026)</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>Dorval, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4435308009</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr"/>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>8581a716b5c9823c5a90120fd39d508eb27e04216b4bee4db8c5b17e14f69e89</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>Autodesk</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en Développement Cloud, Intern Cloud Developer</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450342585</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>ea6e9177a2a2eb4d088e79a3a4fbfef46d5dfc107fbbda8948864ba8f1bc62a6</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Flare</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en développement logiciel / Intern Software Developer</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>Montréal-Ouest, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447254461</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr"/>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>e4a2dab57fc068d391ade5442fb297a2c51cd54676f5cb9fd8d91e8fad80eb67</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Magna International</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>AI Solutions Developer Co-op (4 months) - Starting September</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>Milton, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4442192398</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>9f31e707e1c0dcabf4e8e5e3c9327cb2b2c5895fd5b4963171f09415f3378e60</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>Autodesk</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Stagiaire en Développement Cloud, Intern Cloud Developer – FCAP</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450350390</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="inlineStr"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>432372745bdc56f9627fe4c4c7d8ceaeff1e85d3d91e18fcc0de9a1d264aea57</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Liminal Discovery</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>Foresight tool developer internship (AI, automation, LLMs)</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>Urban agglomeration of Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450079089</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>6b79ed8e63a037ec41bd26db3b308190e74e71607235be404be592ec492856d4</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>CodeDeskStudio</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Mobile App Development Internship</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>Division No. 11, Saskatchewan, Canada</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447364549</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L191" s="2" t="inlineStr"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>fbeb70d52e55ae4766ba7efb07ebc5d96cd8300e5d9b0a5715d631ada7340226</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Xsolla</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>AI-First Engineering Intern</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4436624836</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>07bdea2f6b653ec1916ad33527e41d5bbbef72f333e54f0019340567dad929db</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Tecsys Inc.</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Intern - DevOps (Fall 2026)</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4437077370</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>be0b2805c1278a17017dcd3dbfd40501fd89542e81de5c273df5bf9783b58936</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Osler, Hoskin &amp; Harcourt LLP</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>Applications Analyst Co-op (8 months)</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4433725216</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>1f8cff2e78bfdd4f3a5afe1680e915dab4f506a1d167c21ac05e150128255951</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>ITV - Intern (Fall 2026, 12-16 Month)</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4439246905</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="inlineStr"/>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>58ccedb12cb9abada367fa8ec5cb972e0b30f01d774bdce29fa4eb03bf649e09</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>Rakuten Kobo Inc.</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>Software Quality Assurance Co-op</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4450720999</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>9b096f6f8b09b3782faaf831d82d0fd0535f4300c94fe472f4c5ab1950435106</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>TechInsights</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>QA Test Automation Co-op Student (Fall 2026)</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4445230477</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="inlineStr"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>dcd116d772032c49a0f4de5f53b462fcb6e967d34c7cca840430cf093f5bdd0c</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>Munich Re</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>Women in Tech Program - Global IT Co-op (Fall 2026 - Toronto, 4 months)</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4443916232</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>1678cc7662caba09b83824d5104ac6da806f2973ae7fc90d3a0b50d2edc663e4</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>House of Commons of Canada Chambre des communes du Canada</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Co-op Students - Various Positions</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>Ottawa, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4350836087</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="inlineStr"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>2cfc1792f4a9d201f07693710a0b8f8cf95fa8a2307931ef7da90303c2e6e01c</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>InterPro Pipe + Steel</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>Process Technology Co-op Student</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G200" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446840631</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>3165a2832a048afa37cf8450070685fc3fdcfb833961771ca407db9859f185a8</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>InterPro Pipe + Steel</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>Operational Excellence Co-op</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta, Canada</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4446351936</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="inlineStr"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="A202" s="3" t="inlineStr">
         <is>
           <t>f6c4921a5d262fdfc2dbf872824bf1464bdb80f892814dcf91876aa76634bfa0</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>IKO North America</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>Data Engineer Co-Op</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
         <is>
           <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4449825324</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>98c8c212aef471fe634c9a231b94196cee28274b57e31bcfcef367faea836809</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>Scotiabank</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>GBM - Client Insights and Analytics Internship/Co-op - Fall 2026 (12 months)</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448485888</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="inlineStr"/>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>86ebb0aa627c6330c78a91731184bbc36ead57857b22976ba55596e2747fedfd</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>TMX Group</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Analyst, Market Insights, Student Intern</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447497198</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>5161892207b4a9a650c26a18feee51fbd4b20e1d5d30af8533c610a9df36be61</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Hitachi Rail</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>ALM Scripting &amp; Reporting Intern</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario, Canada</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4434564743</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L205" s="2" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t>a149784ac2ee8495bf38777475d601ae4667483489f7cd259dbb85d8beec0330</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>Teck Resources Limited</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>Business Insights Co-op</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr"/>
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448070011</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>153758b2f5eb32e528e453bfe7ad4c943e6353c6d2c782eef527f23d2e1a7a82</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>Teck Resources Limited</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>Improvement Specialist Co-op</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr"/>
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4448069020</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L207" s="2" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr"/>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
         <is>
           <t>352491cb0c9317071b1e43d2f444073185a16621c4d425a099dfca2a97458d3e</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Project Management and Reporting [Vancouver]</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4430420697</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>jobspy:linkedin</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>d2043287507417658754a1f3826bcbfeabb577d8506a2464aacc2957acd8706f</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Backend</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5833569330?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>About Terminal Terminal builds telematics data infrastructure for the commercial fleet industry. Commercial auto insurers and fleet software companies, including industry leaders like Intact Insurance, depend on our platform to access GPS, speeding, and vehicle data from 330 telematics providers. We</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>0faeae98c5826a806041b7f5d85903b1badc209bcadf9ca78b1a5efb6f629e81</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>NationGraph</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Winter 2027 Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5837929086?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">About NationGraph NationGraph is making public sector data accessible and actionable for businesses selling to cities, counties, state agencies, schools, and special districts. NationGraph’s data and intelligence engine provides buying signals derived from millions of public sector sources. Founded </t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>79963be864ab164076e6376b1cbe72e25f77e706b845d7c77a937e8b9a4a8b1a</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Clearline</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern/Co-op - 2026 Fall</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo region, Ontario</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.ca/details/5806578811?utm_medium=api&amp;utm_source=99ff7338</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>IN-PERSON IN OUR KITCHENER OFFICE STARTING SEPT 2026. ONLY APPLY IF YOU CAN WORK LEGALLY IN CANADA. The Role Clearline's software engineering team is looking for intern/co-op who wants to ship real product inside a fast-moving startup. You'll join a small, senior engineering team building Clearline'</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>610426129b3ccb133d385b7fc6f4761b73014543558c123a4cf27156ef476a24</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en Développement Cloud, Intern Cloud Developer – FCAP</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4450335766</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>4c1c6ac601bf24f7842c17470dc6b22cd7bf3f6d9e6bcfcd4368a8975a721ca7</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Electro-Mechanical Engineering Intern (Fall 2026, 16 months)</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>https://ca.indeed.com/viewjob?jk=721fb3822ad38366</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>**Location:**
+Toronto, Ontario, Canada
+**Job ID:**
+R0139829
+**Date Posted:**
+2026\-08\-11
+**Company Name:**
+Hitachi Rail Canada Inc.
+**Profession (Job Category):**
+Administration \&amp; Facilities
+**Job Schedule:**
+Full time
+**Remote:**
+No
+**About Us**
+A career at Hitachi Rail will help create a</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>90c34fc2873697cb48183b896fd1dde799ef7877aa383a9592abc8702a2ef95f</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Canadian Strategic Missions Corporation (CSMC)</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Computer Science Intern</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451491794</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>22a21c2db3422794ed7bb397a423e2062ca9f2942ff7f64da18180849394a0e4</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Canada</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Intern Engineer - AI4RnD Engineer</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Waterloo, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446931297</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>43c5568b13e42424228788c449b326ca40a70d5f38fc1e9b2ba2e4efc4ba0220</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>House of Commons of Canada Chambre des communes du Canada</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Étudiant∙e∙s coop – Divers postes</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4350716201</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>39eff972d140794e976ffddf353631f4b3d8ed2e3dc909583cb1ec42d9587da0</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Research Internship (Fall, Winter 2026)</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4407973038</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>904eca29129c244378b7092e40526eeec7686f781911347cf9d8eae69afa4051</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>System Integration Specialist Intern</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4423955285</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>070ad5e0fe46a124208364424c730858ea4817d37c0a69e09c725d0a560080e4</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Price Industries</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Software QA Analyst (Coop Term)</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Winnipeg, Manitoba, Canada</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4448532970</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>b17f6d72991990527d042e480b2ea66bf881fcd4d9417f5371c3df9c84df7ead</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Harris Computer</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Stagiaire en développement de logiciels / Software Development Intern</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4444496734</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>c1c38472f74c7c6b30b39c493720367512414a54c55d3fd57b99811a60515d40</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Forest Group</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Intern</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Vaughan, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443997225</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>58b9f838de6f40e2b32d6c8d34d0f181c94c4acc1b58ba4d21c25f0418eeb6a6</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>KPMG Canada</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>GTA Office - Opportunities in Asset Management Digital Solutions - Product Specialist - Co-op &amp; Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4452137675</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>e5faecf4f903941c146a50c3781d8b49c9a3cb64cd0348a8fc9bf3cd3902c889</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>KPMG Canada</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Risk Services (Non-CPA) - Forensic Financial Crimes Intern/Co-op - Toronto - Winter, Summer or Fall 2027</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451021388</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>33811b35e7e5a9ebb35e073d75b383dbb224c5d62fac25bf4dc137f2a87c5e2f</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo Supply Chain Co-Op Fall 2026</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Brampton, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4409214488</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>aa26601fbc23c3843d39eeb0376010761cc7311a15d839e4d53d218ee071801d</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>EDF power solutions North America</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Intern - Canada and North East Development [Hybrid]</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4446546562</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>jobspy:linkedin</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L225"/>
+  <dimension ref="A1:L251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11198,259 +11198,259 @@
       <c r="L208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="A209" s="3" t="inlineStr">
         <is>
           <t>d2043287507417658754a1f3826bcbfeabb577d8506a2464aacc2957acd8706f</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>Software Engineering Intern, Backend</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
         <is>
           <t>Toronto, Ontario</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" s="3" t="inlineStr">
         <is>
           <t>https://www.adzuna.ca/details/5833569330?utm_medium=api&amp;utm_source=99ff7338</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H209" s="3" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I209" s="3" t="inlineStr">
         <is>
           <t>About Terminal Terminal builds telematics data infrastructure for the commercial fleet industry. Commercial auto insurers and fleet software companies, including industry leaders like Intact Insurance, depend on our platform to access GPS, speeding, and vehicle data from 330 telematics providers. We</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L209" s="2" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t>0faeae98c5826a806041b7f5d85903b1badc209bcadf9ca78b1a5efb6f629e81</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>NationGraph</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>Winter 2027 Software Engineering Intern</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F210" s